--- a/forms/app/infant_child.xlsx
+++ b/forms/app/infant_child.xlsx
@@ -19,7 +19,7 @@
   <definedNames>
     <definedName name="Z_781EBA2C_D8B1_4B7C_8F0C_A942CACA9398_.wvu.FilterData" localSheetId="0" hidden="1">survey!$A$389:$Z$420</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="162913"/>
   <customWorkbookViews>
     <customWorkbookView name="Filter 1" guid="{781EBA2C-D8B1-4B7C-8F0C-A942CACA9398}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
   </customWorkbookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2617" uniqueCount="1652">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2617" uniqueCount="1653">
   <si>
     <t>type</t>
   </si>
@@ -5425,6 +5425,10 @@
   </si>
   <si>
     <t>data</t>
+  </si>
+  <si>
+    <t>&lt;span style="color:#f58a1f;font-weight: bold"&gt;If possible, ask the mother to breastfeed and observe. If not possible, ask questions below rather than observing.WASH your hands. OBSERVE the mother breastfeeding. Try to UNDERSTAND the situation.Do you notice any problems with breastfeeding? Provide guidance based on what you observe. Try to solve any problems you identify or the mother describes.&lt;/span&gt;
+&lt;span style="color:#f58a1f;display:block;padding-left:1em"&gt;Je umegundua kuna tatizo lolote kwenye kunyonyesha? Toa muongozo kwa kile ulichokiona. Jaribu kutatua tatizo lolote uliloliona au alilolisema mama.&lt;/span&gt;</t>
   </si>
 </sst>
 </file>
@@ -5514,7 +5518,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -5567,6 +5571,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -11243,8 +11250,8 @@
       <c r="B195" s="1" t="s">
         <v>502</v>
       </c>
-      <c r="C195" s="18" t="s">
-        <v>503</v>
+      <c r="C195" s="48" t="s">
+        <v>1652</v>
       </c>
       <c r="D195" s="18" t="s">
         <v>503</v>
@@ -12314,7 +12321,7 @@
         <v>169</v>
       </c>
       <c r="F232" s="4" t="s">
-        <v>599</v>
+        <v>606</v>
       </c>
       <c r="G232" s="6"/>
       <c r="H232" s="6"/>
@@ -20037,6 +20044,19 @@
     </customSheetView>
   </customSheetViews>
   <mergeCells count="21">
+    <mergeCell ref="K275:L275"/>
+    <mergeCell ref="F276:G276"/>
+    <mergeCell ref="K279:L279"/>
+    <mergeCell ref="K282:L282"/>
+    <mergeCell ref="K285:L285"/>
+    <mergeCell ref="K288:L288"/>
+    <mergeCell ref="K291:L291"/>
+    <mergeCell ref="F313:H313"/>
+    <mergeCell ref="F314:H314"/>
+    <mergeCell ref="F328:I328"/>
+    <mergeCell ref="K315:L315"/>
+    <mergeCell ref="K318:L318"/>
+    <mergeCell ref="K321:L321"/>
     <mergeCell ref="L331:O331"/>
     <mergeCell ref="K294:L294"/>
     <mergeCell ref="K297:L297"/>
@@ -20045,19 +20065,6 @@
     <mergeCell ref="K306:L306"/>
     <mergeCell ref="K309:L309"/>
     <mergeCell ref="K312:L312"/>
-    <mergeCell ref="K288:L288"/>
-    <mergeCell ref="K291:L291"/>
-    <mergeCell ref="F313:H313"/>
-    <mergeCell ref="F314:H314"/>
-    <mergeCell ref="F328:I328"/>
-    <mergeCell ref="K315:L315"/>
-    <mergeCell ref="K318:L318"/>
-    <mergeCell ref="K321:L321"/>
-    <mergeCell ref="K275:L275"/>
-    <mergeCell ref="F276:G276"/>
-    <mergeCell ref="K279:L279"/>
-    <mergeCell ref="K282:L282"/>
-    <mergeCell ref="K285:L285"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/forms/app/infant_child.xlsx
+++ b/forms/app/infant_child.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2617" uniqueCount="1653">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2619" uniqueCount="1656">
   <si>
     <t>type</t>
   </si>
@@ -3023,12 +3023,6 @@
   </si>
   <si>
     <t>too_old_note</t>
-  </si>
-  <si>
-    <t>Okay, please continue taking care of your child.</t>
-  </si>
-  <si>
-    <t>Sawa, taafadhali hakikisha unaendelea kumtunza mtoto wako vizuri.</t>
   </si>
   <si>
     <t>selected(${why_not_vaccines_up_to_date},"baby_too_old")</t>
@@ -5429,6 +5423,21 @@
   <si>
     <t>&lt;span style="color:#f58a1f;font-weight: bold"&gt;If possible, ask the mother to breastfeed and observe. If not possible, ask questions below rather than observing.WASH your hands. OBSERVE the mother breastfeeding. Try to UNDERSTAND the situation.Do you notice any problems with breastfeeding? Provide guidance based on what you observe. Try to solve any problems you identify or the mother describes.&lt;/span&gt;
 &lt;span style="color:#f58a1f;display:block;padding-left:1em"&gt;Je umegundua kuna tatizo lolote kwenye kunyonyesha? Toa muongozo kwa kile ulichokiona. Jaribu kutatua tatizo lolote uliloliona au alilolisema mama.&lt;/span&gt;</t>
+  </si>
+  <si>
+    <t>media::audio::en</t>
+  </si>
+  <si>
+    <t>media::audio::sw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Watoto wote chini ya miaka mitano wanaweza kupatiwa chanjo zote, hata kama muda wa chanjo umepita. Tafadhali muwahishe mtoto wako kituo cha afya kwa ajili ya kupatiwa chanjo. </t>
+  </si>
+  <si>
+    <t>All children under 5 are eligible for all vaccines, even if their vaccine dates are overdue. Please take your child to the health facility as soon as possible for vaccination.</t>
+  </si>
+  <si>
+    <t>selected(${has_health_card},"yes") and ${age_years} &lt; 2  or selected(${child_card_available},"yes")</t>
   </si>
 </sst>
 </file>
@@ -5518,7 +5527,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -5568,12 +5577,16 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5873,7 +5886,7 @@
     <col min="18" max="18" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="13">
+    <row r="1" spans="1:21" ht="13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5931,8 +5944,14 @@
       <c r="S1" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="2" spans="1:19" ht="15.75" customHeight="1">
+      <c r="T1" s="46" t="s">
+        <v>1651</v>
+      </c>
+      <c r="U1" s="47" t="s">
+        <v>1652</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>19</v>
       </c>
@@ -5960,7 +5979,7 @@
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
     </row>
-    <row r="3" spans="1:19" ht="15.75" customHeight="1">
+    <row r="3" spans="1:21" ht="15.75" customHeight="1">
       <c r="A3" s="3" t="s">
         <v>24</v>
       </c>
@@ -5985,7 +6004,7 @@
       <c r="P3" s="1"/>
       <c r="Q3" s="1"/>
     </row>
-    <row r="4" spans="1:19" ht="15.75" customHeight="1">
+    <row r="4" spans="1:21" ht="15.75" customHeight="1">
       <c r="A4" s="3" t="s">
         <v>24</v>
       </c>
@@ -6010,7 +6029,7 @@
       <c r="P4" s="1"/>
       <c r="Q4" s="1"/>
     </row>
-    <row r="5" spans="1:19" ht="15.75" customHeight="1">
+    <row r="5" spans="1:21" ht="15.75" customHeight="1">
       <c r="A5" s="3" t="s">
         <v>24</v>
       </c>
@@ -6035,7 +6054,7 @@
       <c r="P5" s="1"/>
       <c r="Q5" s="1"/>
     </row>
-    <row r="6" spans="1:19" ht="15.75" customHeight="1">
+    <row r="6" spans="1:21" ht="15.75" customHeight="1">
       <c r="A6" s="3" t="s">
         <v>24</v>
       </c>
@@ -6060,7 +6079,7 @@
       <c r="P6" s="1"/>
       <c r="Q6" s="1"/>
     </row>
-    <row r="7" spans="1:19" ht="15.75" customHeight="1">
+    <row r="7" spans="1:21" ht="15.75" customHeight="1">
       <c r="A7" s="3" t="s">
         <v>24</v>
       </c>
@@ -6085,7 +6104,7 @@
       <c r="P7" s="1"/>
       <c r="Q7" s="1"/>
     </row>
-    <row r="8" spans="1:19" ht="15.75" customHeight="1">
+    <row r="8" spans="1:21" ht="15.75" customHeight="1">
       <c r="A8" s="3" t="s">
         <v>24</v>
       </c>
@@ -6110,7 +6129,7 @@
       <c r="P8" s="1"/>
       <c r="Q8" s="1"/>
     </row>
-    <row r="9" spans="1:19" ht="15.75" customHeight="1">
+    <row r="9" spans="1:21" ht="15.75" customHeight="1">
       <c r="A9" s="3" t="s">
         <v>24</v>
       </c>
@@ -6135,7 +6154,7 @@
       <c r="P9" s="1"/>
       <c r="Q9" s="1"/>
     </row>
-    <row r="10" spans="1:19" ht="15.75" customHeight="1">
+    <row r="10" spans="1:21" ht="15.75" customHeight="1">
       <c r="A10" s="3" t="s">
         <v>24</v>
       </c>
@@ -6160,7 +6179,7 @@
       <c r="P10" s="1"/>
       <c r="Q10" s="1"/>
     </row>
-    <row r="11" spans="1:19" ht="15.75" customHeight="1">
+    <row r="11" spans="1:21" ht="15.75" customHeight="1">
       <c r="A11" s="3" t="s">
         <v>24</v>
       </c>
@@ -6185,7 +6204,7 @@
       <c r="P11" s="1"/>
       <c r="Q11" s="1"/>
     </row>
-    <row r="12" spans="1:19" ht="15.75" customHeight="1">
+    <row r="12" spans="1:21" ht="15.75" customHeight="1">
       <c r="A12" s="3" t="s">
         <v>24</v>
       </c>
@@ -6210,7 +6229,7 @@
       <c r="P12" s="1"/>
       <c r="Q12" s="1"/>
     </row>
-    <row r="13" spans="1:19" ht="15.75" customHeight="1">
+    <row r="13" spans="1:21" ht="15.75" customHeight="1">
       <c r="A13" s="3" t="s">
         <v>24</v>
       </c>
@@ -6235,7 +6254,7 @@
       <c r="P13" s="1"/>
       <c r="Q13" s="1"/>
     </row>
-    <row r="14" spans="1:19" ht="15.75" customHeight="1">
+    <row r="14" spans="1:21" ht="15.75" customHeight="1">
       <c r="A14" s="3" t="s">
         <v>24</v>
       </c>
@@ -6260,7 +6279,7 @@
       <c r="P14" s="1"/>
       <c r="Q14" s="1"/>
     </row>
-    <row r="15" spans="1:19" ht="15.75" customHeight="1">
+    <row r="15" spans="1:21" ht="15.75" customHeight="1">
       <c r="A15" s="3" t="s">
         <v>24</v>
       </c>
@@ -6285,7 +6304,7 @@
       <c r="P15" s="1"/>
       <c r="Q15" s="1"/>
     </row>
-    <row r="16" spans="1:19" ht="15.75" customHeight="1">
+    <row r="16" spans="1:21" ht="15.75" customHeight="1">
       <c r="A16" s="3" t="s">
         <v>24</v>
       </c>
@@ -11250,8 +11269,8 @@
       <c r="B195" s="1" t="s">
         <v>502</v>
       </c>
-      <c r="C195" s="48" t="s">
-        <v>1652</v>
+      <c r="C195" s="45" t="s">
+        <v>1650</v>
       </c>
       <c r="D195" s="18" t="s">
         <v>503</v>
@@ -13472,7 +13491,7 @@
       <c r="D271" s="33"/>
       <c r="E271" s="29"/>
       <c r="F271" s="28" t="s">
-        <v>725</v>
+        <v>1655</v>
       </c>
       <c r="G271" s="32"/>
       <c r="H271" s="29"/>
@@ -13634,10 +13653,10 @@
       <c r="J275" s="28" t="s">
         <v>742</v>
       </c>
-      <c r="K275" s="45" t="s">
+      <c r="K275" s="50" t="s">
         <v>743</v>
       </c>
-      <c r="L275" s="46"/>
+      <c r="L275" s="51"/>
       <c r="M275" s="29"/>
       <c r="N275" s="29"/>
       <c r="O275" s="29"/>
@@ -13667,10 +13686,10 @@
         <v>746</v>
       </c>
       <c r="E276" s="32"/>
-      <c r="F276" s="45" t="s">
+      <c r="F276" s="50" t="s">
         <v>747</v>
       </c>
-      <c r="G276" s="46"/>
+      <c r="G276" s="51"/>
       <c r="H276" s="29"/>
       <c r="I276" s="32"/>
       <c r="J276" s="32"/>
@@ -13794,10 +13813,10 @@
       <c r="J279" s="28" t="s">
         <v>742</v>
       </c>
-      <c r="K279" s="45" t="s">
+      <c r="K279" s="50" t="s">
         <v>743</v>
       </c>
-      <c r="L279" s="46"/>
+      <c r="L279" s="51"/>
       <c r="M279" s="32"/>
       <c r="N279" s="32"/>
       <c r="O279" s="29"/>
@@ -13916,10 +13935,10 @@
       <c r="J282" s="28" t="s">
         <v>742</v>
       </c>
-      <c r="K282" s="45" t="s">
+      <c r="K282" s="50" t="s">
         <v>743</v>
       </c>
-      <c r="L282" s="46"/>
+      <c r="L282" s="51"/>
       <c r="M282" s="32"/>
       <c r="N282" s="29"/>
       <c r="O282" s="29"/>
@@ -14038,10 +14057,10 @@
       <c r="J285" s="28" t="s">
         <v>742</v>
       </c>
-      <c r="K285" s="45" t="s">
+      <c r="K285" s="50" t="s">
         <v>743</v>
       </c>
-      <c r="L285" s="46"/>
+      <c r="L285" s="51"/>
       <c r="M285" s="29"/>
       <c r="N285" s="29"/>
       <c r="O285" s="29"/>
@@ -14160,10 +14179,10 @@
       <c r="J288" s="28" t="s">
         <v>742</v>
       </c>
-      <c r="K288" s="45" t="s">
+      <c r="K288" s="50" t="s">
         <v>743</v>
       </c>
-      <c r="L288" s="46"/>
+      <c r="L288" s="51"/>
       <c r="M288" s="32"/>
       <c r="N288" s="29"/>
       <c r="O288" s="29"/>
@@ -14282,10 +14301,10 @@
       <c r="J291" s="28" t="s">
         <v>742</v>
       </c>
-      <c r="K291" s="45" t="s">
+      <c r="K291" s="50" t="s">
         <v>743</v>
       </c>
-      <c r="L291" s="46"/>
+      <c r="L291" s="51"/>
       <c r="M291" s="32"/>
       <c r="N291" s="29"/>
       <c r="O291" s="29"/>
@@ -14404,10 +14423,10 @@
       <c r="J294" s="28" t="s">
         <v>742</v>
       </c>
-      <c r="K294" s="45" t="s">
+      <c r="K294" s="50" t="s">
         <v>743</v>
       </c>
-      <c r="L294" s="46"/>
+      <c r="L294" s="51"/>
       <c r="M294" s="32"/>
       <c r="N294" s="29"/>
       <c r="O294" s="29"/>
@@ -14526,10 +14545,10 @@
       <c r="J297" s="28" t="s">
         <v>742</v>
       </c>
-      <c r="K297" s="45" t="s">
+      <c r="K297" s="50" t="s">
         <v>743</v>
       </c>
-      <c r="L297" s="46"/>
+      <c r="L297" s="51"/>
       <c r="M297" s="32"/>
       <c r="N297" s="29"/>
       <c r="O297" s="29"/>
@@ -14648,10 +14667,10 @@
       <c r="J300" s="28" t="s">
         <v>742</v>
       </c>
-      <c r="K300" s="45" t="s">
+      <c r="K300" s="50" t="s">
         <v>743</v>
       </c>
-      <c r="L300" s="46"/>
+      <c r="L300" s="51"/>
       <c r="M300" s="29"/>
       <c r="N300" s="29"/>
       <c r="O300" s="29"/>
@@ -14770,10 +14789,10 @@
       <c r="J303" s="28" t="s">
         <v>742</v>
       </c>
-      <c r="K303" s="45" t="s">
+      <c r="K303" s="50" t="s">
         <v>743</v>
       </c>
-      <c r="L303" s="46"/>
+      <c r="L303" s="51"/>
       <c r="M303" s="32"/>
       <c r="N303" s="29"/>
       <c r="O303" s="29"/>
@@ -14892,10 +14911,10 @@
       <c r="J306" s="28" t="s">
         <v>742</v>
       </c>
-      <c r="K306" s="45" t="s">
+      <c r="K306" s="50" t="s">
         <v>743</v>
       </c>
-      <c r="L306" s="46"/>
+      <c r="L306" s="51"/>
       <c r="M306" s="29"/>
       <c r="N306" s="29"/>
       <c r="O306" s="29"/>
@@ -15014,10 +15033,10 @@
       <c r="J309" s="28" t="s">
         <v>742</v>
       </c>
-      <c r="K309" s="45" t="s">
+      <c r="K309" s="50" t="s">
         <v>743</v>
       </c>
-      <c r="L309" s="46"/>
+      <c r="L309" s="51"/>
       <c r="M309" s="32"/>
       <c r="N309" s="29"/>
       <c r="O309" s="29"/>
@@ -15136,10 +15155,10 @@
       <c r="J312" s="28" t="s">
         <v>742</v>
       </c>
-      <c r="K312" s="45" t="s">
+      <c r="K312" s="50" t="s">
         <v>743</v>
       </c>
-      <c r="L312" s="46"/>
+      <c r="L312" s="51"/>
       <c r="M312" s="29"/>
       <c r="N312" s="29"/>
       <c r="O312" s="29"/>
@@ -15169,11 +15188,11 @@
         <v>731</v>
       </c>
       <c r="E313" s="32"/>
-      <c r="F313" s="45" t="s">
+      <c r="F313" s="50" t="s">
         <v>857</v>
       </c>
-      <c r="G313" s="46"/>
-      <c r="H313" s="46"/>
+      <c r="G313" s="51"/>
+      <c r="H313" s="51"/>
       <c r="I313" s="32"/>
       <c r="J313" s="29"/>
       <c r="K313" s="29"/>
@@ -15209,11 +15228,11 @@
       <c r="E314" s="28" t="s">
         <v>169</v>
       </c>
-      <c r="F314" s="45" t="s">
+      <c r="F314" s="50" t="s">
         <v>857</v>
       </c>
-      <c r="G314" s="46"/>
-      <c r="H314" s="46"/>
+      <c r="G314" s="51"/>
+      <c r="H314" s="51"/>
       <c r="I314" s="29"/>
       <c r="J314" s="29"/>
       <c r="K314" s="29"/>
@@ -15258,10 +15277,10 @@
       <c r="J315" s="28" t="s">
         <v>742</v>
       </c>
-      <c r="K315" s="45" t="s">
+      <c r="K315" s="50" t="s">
         <v>743</v>
       </c>
-      <c r="L315" s="46"/>
+      <c r="L315" s="51"/>
       <c r="M315" s="32"/>
       <c r="N315" s="29"/>
       <c r="O315" s="29"/>
@@ -15380,10 +15399,10 @@
       <c r="J318" s="28" t="s">
         <v>742</v>
       </c>
-      <c r="K318" s="45" t="s">
+      <c r="K318" s="50" t="s">
         <v>743</v>
       </c>
-      <c r="L318" s="46"/>
+      <c r="L318" s="51"/>
       <c r="M318" s="29"/>
       <c r="N318" s="29"/>
       <c r="O318" s="29"/>
@@ -15502,10 +15521,10 @@
       <c r="J321" s="28" t="s">
         <v>742</v>
       </c>
-      <c r="K321" s="45" t="s">
+      <c r="K321" s="50" t="s">
         <v>743</v>
       </c>
-      <c r="L321" s="46"/>
+      <c r="L321" s="51"/>
       <c r="M321" s="32"/>
       <c r="N321" s="29"/>
       <c r="O321" s="29"/>
@@ -15709,69 +15728,69 @@
       <c r="Y326" s="30"/>
       <c r="Z326" s="30"/>
     </row>
-    <row r="327" spans="1:26" ht="15.75" customHeight="1">
+    <row r="327" spans="1:26" s="49" customFormat="1" ht="15.75" customHeight="1">
       <c r="A327" s="35" t="s">
         <v>137</v>
       </c>
-      <c r="B327" s="28" t="s">
-        <v>897</v>
-      </c>
-      <c r="C327" s="28" t="s">
-        <v>898</v>
-      </c>
-      <c r="D327" s="28" t="s">
-        <v>899</v>
-      </c>
-      <c r="E327" s="32"/>
-      <c r="F327" s="28" t="s">
-        <v>900</v>
-      </c>
-      <c r="G327" s="32"/>
-      <c r="H327" s="29"/>
-      <c r="I327" s="32"/>
-      <c r="J327" s="32"/>
-      <c r="K327" s="32"/>
-      <c r="L327" s="32"/>
-      <c r="M327" s="32"/>
-      <c r="N327" s="32"/>
-      <c r="O327" s="29"/>
-      <c r="P327" s="29"/>
-      <c r="Q327" s="29"/>
-      <c r="R327" s="30"/>
-      <c r="S327" s="30"/>
-      <c r="T327" s="30"/>
-      <c r="U327" s="30"/>
-      <c r="V327" s="30"/>
-      <c r="W327" s="30"/>
-      <c r="X327" s="30"/>
-      <c r="Y327" s="30"/>
-      <c r="Z327" s="30"/>
+      <c r="B327" s="48" t="s">
+        <v>905</v>
+      </c>
+      <c r="C327" s="48" t="s">
+        <v>1654</v>
+      </c>
+      <c r="D327" s="48" t="s">
+        <v>1653</v>
+      </c>
+      <c r="E327" s="48"/>
+      <c r="F327" s="48" t="s">
+        <v>906</v>
+      </c>
+      <c r="G327" s="48"/>
+      <c r="H327" s="48"/>
+      <c r="I327" s="48"/>
+      <c r="J327" s="48"/>
+      <c r="K327" s="48"/>
+      <c r="L327" s="48"/>
+      <c r="M327" s="48"/>
+      <c r="N327" s="48"/>
+      <c r="O327" s="48"/>
+      <c r="P327" s="48"/>
+      <c r="Q327" s="48"/>
+      <c r="R327" s="33"/>
+      <c r="S327" s="33"/>
+      <c r="T327" s="33"/>
+      <c r="U327" s="33"/>
+      <c r="V327" s="33"/>
+      <c r="W327" s="33"/>
+      <c r="X327" s="33"/>
+      <c r="Y327" s="33"/>
+      <c r="Z327" s="33"/>
     </row>
     <row r="328" spans="1:26" ht="15.75" customHeight="1">
       <c r="A328" s="35" t="s">
         <v>137</v>
       </c>
       <c r="B328" s="28" t="s">
-        <v>901</v>
+        <v>897</v>
       </c>
       <c r="C328" s="28" t="s">
-        <v>902</v>
+        <v>898</v>
       </c>
       <c r="D328" s="28" t="s">
-        <v>903</v>
-      </c>
-      <c r="E328" s="29"/>
-      <c r="F328" s="45" t="s">
-        <v>904</v>
-      </c>
-      <c r="G328" s="46"/>
-      <c r="H328" s="46"/>
-      <c r="I328" s="46"/>
+        <v>899</v>
+      </c>
+      <c r="E328" s="32"/>
+      <c r="F328" s="28" t="s">
+        <v>900</v>
+      </c>
+      <c r="G328" s="32"/>
+      <c r="H328" s="29"/>
+      <c r="I328" s="32"/>
       <c r="J328" s="32"/>
       <c r="K328" s="32"/>
       <c r="L328" s="32"/>
       <c r="M328" s="32"/>
-      <c r="N328" s="29"/>
+      <c r="N328" s="32"/>
       <c r="O328" s="29"/>
       <c r="P328" s="29"/>
       <c r="Q328" s="29"/>
@@ -15790,25 +15809,25 @@
         <v>137</v>
       </c>
       <c r="B329" s="28" t="s">
-        <v>905</v>
+        <v>901</v>
       </c>
       <c r="C329" s="28" t="s">
-        <v>906</v>
+        <v>902</v>
       </c>
       <c r="D329" s="28" t="s">
-        <v>907</v>
+        <v>903</v>
       </c>
       <c r="E329" s="29"/>
-      <c r="F329" s="28" t="s">
-        <v>908</v>
-      </c>
-      <c r="G329" s="32"/>
-      <c r="H329" s="32"/>
-      <c r="I329" s="29"/>
-      <c r="J329" s="29"/>
-      <c r="K329" s="29"/>
-      <c r="L329" s="29"/>
-      <c r="M329" s="29"/>
+      <c r="F329" s="50" t="s">
+        <v>904</v>
+      </c>
+      <c r="G329" s="51"/>
+      <c r="H329" s="51"/>
+      <c r="I329" s="51"/>
+      <c r="J329" s="32"/>
+      <c r="K329" s="32"/>
+      <c r="L329" s="32"/>
+      <c r="M329" s="32"/>
       <c r="N329" s="29"/>
       <c r="O329" s="29"/>
       <c r="P329" s="29"/>
@@ -15828,17 +15847,17 @@
         <v>137</v>
       </c>
       <c r="B330" s="28" t="s">
+        <v>907</v>
+      </c>
+      <c r="C330" s="28" t="s">
+        <v>908</v>
+      </c>
+      <c r="D330" s="28" t="s">
         <v>909</v>
-      </c>
-      <c r="C330" s="28" t="s">
-        <v>910</v>
-      </c>
-      <c r="D330" s="28" t="s">
-        <v>911</v>
       </c>
       <c r="E330" s="32"/>
       <c r="F330" s="28" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="G330" s="32"/>
       <c r="H330" s="32"/>
@@ -15866,7 +15885,7 @@
         <v>60</v>
       </c>
       <c r="B331" s="28" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="C331" s="32"/>
       <c r="D331" s="32"/>
@@ -15877,12 +15896,12 @@
       <c r="I331" s="32"/>
       <c r="J331" s="32"/>
       <c r="K331" s="32"/>
-      <c r="L331" s="45" t="s">
-        <v>914</v>
-      </c>
-      <c r="M331" s="46"/>
-      <c r="N331" s="46"/>
-      <c r="O331" s="46"/>
+      <c r="L331" s="50" t="s">
+        <v>912</v>
+      </c>
+      <c r="M331" s="51"/>
+      <c r="N331" s="51"/>
+      <c r="O331" s="51"/>
       <c r="P331" s="29"/>
       <c r="Q331" s="29"/>
       <c r="R331" s="30"/>
@@ -15900,13 +15919,13 @@
         <v>137</v>
       </c>
       <c r="B332" s="28" t="s">
+        <v>913</v>
+      </c>
+      <c r="C332" s="28" t="s">
+        <v>914</v>
+      </c>
+      <c r="D332" s="28" t="s">
         <v>915</v>
-      </c>
-      <c r="C332" s="28" t="s">
-        <v>916</v>
-      </c>
-      <c r="D332" s="28" t="s">
-        <v>917</v>
       </c>
       <c r="E332" s="29"/>
       <c r="F332" s="28" t="s">
@@ -15938,17 +15957,17 @@
         <v>137</v>
       </c>
       <c r="B333" s="28" t="s">
+        <v>916</v>
+      </c>
+      <c r="C333" s="28" t="s">
+        <v>917</v>
+      </c>
+      <c r="D333" s="28" t="s">
         <v>918</v>
-      </c>
-      <c r="C333" s="28" t="s">
-        <v>919</v>
-      </c>
-      <c r="D333" s="28" t="s">
-        <v>920</v>
       </c>
       <c r="E333" s="32"/>
       <c r="F333" s="28" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="G333" s="32"/>
       <c r="H333" s="32"/>
@@ -15976,17 +15995,17 @@
         <v>137</v>
       </c>
       <c r="B334" s="28" t="s">
+        <v>920</v>
+      </c>
+      <c r="C334" s="28" t="s">
+        <v>921</v>
+      </c>
+      <c r="D334" s="28" t="s">
         <v>922</v>
-      </c>
-      <c r="C334" s="28" t="s">
-        <v>923</v>
-      </c>
-      <c r="D334" s="28" t="s">
-        <v>924</v>
       </c>
       <c r="E334" s="32"/>
       <c r="F334" s="28" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="G334" s="32"/>
       <c r="H334" s="32"/>
@@ -16046,17 +16065,17 @@
         <v>19</v>
       </c>
       <c r="B336" s="1" t="s">
+        <v>923</v>
+      </c>
+      <c r="C336" s="8" t="s">
+        <v>924</v>
+      </c>
+      <c r="D336" s="18" t="s">
         <v>925</v>
-      </c>
-      <c r="C336" s="8" t="s">
-        <v>926</v>
-      </c>
-      <c r="D336" s="18" t="s">
-        <v>927</v>
       </c>
       <c r="E336" s="1"/>
       <c r="F336" s="3" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="G336" s="1" t="s">
         <v>145</v>
@@ -16074,16 +16093,16 @@
     </row>
     <row r="337" spans="1:17" ht="15.75" customHeight="1">
       <c r="A337" s="1" t="s">
+        <v>927</v>
+      </c>
+      <c r="B337" s="1" t="s">
+        <v>928</v>
+      </c>
+      <c r="C337" s="8" t="s">
         <v>929</v>
       </c>
-      <c r="B337" s="1" t="s">
+      <c r="D337" s="3" t="s">
         <v>930</v>
-      </c>
-      <c r="C337" s="8" t="s">
-        <v>931</v>
-      </c>
-      <c r="D337" s="3" t="s">
-        <v>932</v>
       </c>
       <c r="E337" s="1" t="s">
         <v>169</v>
@@ -16106,17 +16125,17 @@
         <v>137</v>
       </c>
       <c r="B338" s="1" t="s">
+        <v>931</v>
+      </c>
+      <c r="C338" s="8" t="s">
+        <v>932</v>
+      </c>
+      <c r="D338" s="18" t="s">
         <v>933</v>
-      </c>
-      <c r="C338" s="8" t="s">
-        <v>934</v>
-      </c>
-      <c r="D338" s="18" t="s">
-        <v>935</v>
       </c>
       <c r="E338" s="1"/>
       <c r="F338" s="4" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
       <c r="G338" s="6"/>
       <c r="H338" s="1"/>
@@ -16135,13 +16154,13 @@
         <v>137</v>
       </c>
       <c r="B339" s="1" t="s">
+        <v>935</v>
+      </c>
+      <c r="C339" s="8" t="s">
+        <v>936</v>
+      </c>
+      <c r="D339" s="18" t="s">
         <v>937</v>
-      </c>
-      <c r="C339" s="8" t="s">
-        <v>938</v>
-      </c>
-      <c r="D339" s="18" t="s">
-        <v>939</v>
       </c>
       <c r="E339" s="6"/>
       <c r="F339" s="6"/>
@@ -16162,13 +16181,13 @@
         <v>137</v>
       </c>
       <c r="B340" s="1" t="s">
+        <v>938</v>
+      </c>
+      <c r="C340" s="8" t="s">
+        <v>939</v>
+      </c>
+      <c r="D340" s="18" t="s">
         <v>940</v>
-      </c>
-      <c r="C340" s="8" t="s">
-        <v>941</v>
-      </c>
-      <c r="D340" s="18" t="s">
-        <v>942</v>
       </c>
       <c r="E340" s="6"/>
       <c r="F340" s="6"/>
@@ -16189,13 +16208,13 @@
         <v>137</v>
       </c>
       <c r="B341" s="1" t="s">
+        <v>941</v>
+      </c>
+      <c r="C341" s="8" t="s">
+        <v>942</v>
+      </c>
+      <c r="D341" s="18" t="s">
         <v>943</v>
-      </c>
-      <c r="C341" s="8" t="s">
-        <v>944</v>
-      </c>
-      <c r="D341" s="18" t="s">
-        <v>945</v>
       </c>
       <c r="E341" s="6"/>
       <c r="F341" s="6"/>
@@ -16216,7 +16235,7 @@
         <v>60</v>
       </c>
       <c r="B342" s="1" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="C342" s="1"/>
       <c r="D342" s="1"/>
@@ -16228,7 +16247,7 @@
       <c r="J342" s="1"/>
       <c r="K342" s="1"/>
       <c r="L342" s="8" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="M342" s="1"/>
       <c r="N342" s="1"/>
@@ -16241,13 +16260,13 @@
         <v>137</v>
       </c>
       <c r="B343" s="1" t="s">
+        <v>946</v>
+      </c>
+      <c r="C343" s="8" t="s">
+        <v>947</v>
+      </c>
+      <c r="D343" s="18" t="s">
         <v>948</v>
-      </c>
-      <c r="C343" s="8" t="s">
-        <v>949</v>
-      </c>
-      <c r="D343" s="18" t="s">
-        <v>950</v>
       </c>
       <c r="E343" s="6"/>
       <c r="F343" s="6"/>
@@ -16265,16 +16284,16 @@
     </row>
     <row r="344" spans="1:17" ht="15.75" customHeight="1">
       <c r="A344" s="1" t="s">
+        <v>949</v>
+      </c>
+      <c r="B344" s="1" t="s">
+        <v>950</v>
+      </c>
+      <c r="C344" s="8" t="s">
         <v>951</v>
       </c>
-      <c r="B344" s="1" t="s">
+      <c r="D344" s="3" t="s">
         <v>952</v>
-      </c>
-      <c r="C344" s="8" t="s">
-        <v>953</v>
-      </c>
-      <c r="D344" s="3" t="s">
-        <v>954</v>
       </c>
       <c r="E344" s="1" t="s">
         <v>169</v>
@@ -16297,7 +16316,7 @@
         <v>19</v>
       </c>
       <c r="B345" s="1" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="C345" s="3" t="s">
         <v>21</v>
@@ -16305,7 +16324,7 @@
       <c r="D345" s="1"/>
       <c r="E345" s="1"/>
       <c r="F345" s="1" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="G345" s="1" t="s">
         <v>145</v>
@@ -16323,16 +16342,16 @@
     </row>
     <row r="346" spans="1:17" ht="15.75" customHeight="1">
       <c r="A346" s="1" t="s">
+        <v>955</v>
+      </c>
+      <c r="B346" s="1" t="s">
+        <v>956</v>
+      </c>
+      <c r="C346" s="8" t="s">
         <v>957</v>
       </c>
-      <c r="B346" s="1" t="s">
+      <c r="D346" s="3" t="s">
         <v>958</v>
-      </c>
-      <c r="C346" s="8" t="s">
-        <v>959</v>
-      </c>
-      <c r="D346" s="3" t="s">
-        <v>960</v>
       </c>
       <c r="E346" s="1" t="s">
         <v>169</v>
@@ -16341,13 +16360,13 @@
       <c r="G346" s="1"/>
       <c r="H346" s="1"/>
       <c r="I346" s="3" t="s">
+        <v>959</v>
+      </c>
+      <c r="J346" s="3" t="s">
+        <v>960</v>
+      </c>
+      <c r="K346" s="3" t="s">
         <v>961</v>
-      </c>
-      <c r="J346" s="3" t="s">
-        <v>962</v>
-      </c>
-      <c r="K346" s="3" t="s">
-        <v>963</v>
       </c>
       <c r="L346" s="1"/>
       <c r="M346" s="1"/>
@@ -16361,17 +16380,17 @@
         <v>137</v>
       </c>
       <c r="B347" s="1" t="s">
+        <v>962</v>
+      </c>
+      <c r="C347" s="8" t="s">
+        <v>963</v>
+      </c>
+      <c r="D347" s="18" t="s">
         <v>964</v>
-      </c>
-      <c r="C347" s="8" t="s">
-        <v>965</v>
-      </c>
-      <c r="D347" s="18" t="s">
-        <v>966</v>
       </c>
       <c r="E347" s="1"/>
       <c r="F347" s="4" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="G347" s="6"/>
       <c r="H347" s="6"/>
@@ -16390,17 +16409,17 @@
         <v>137</v>
       </c>
       <c r="B348" s="1" t="s">
+        <v>966</v>
+      </c>
+      <c r="C348" s="8" t="s">
+        <v>967</v>
+      </c>
+      <c r="D348" s="18" t="s">
         <v>968</v>
-      </c>
-      <c r="C348" s="8" t="s">
-        <v>969</v>
-      </c>
-      <c r="D348" s="18" t="s">
-        <v>970</v>
       </c>
       <c r="E348" s="1"/>
       <c r="F348" s="4" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="G348" s="6"/>
       <c r="H348" s="1"/>
@@ -16419,13 +16438,13 @@
         <v>137</v>
       </c>
       <c r="B349" s="1" t="s">
+        <v>970</v>
+      </c>
+      <c r="C349" s="8" t="s">
+        <v>971</v>
+      </c>
+      <c r="D349" s="18" t="s">
         <v>972</v>
-      </c>
-      <c r="C349" s="8" t="s">
-        <v>973</v>
-      </c>
-      <c r="D349" s="18" t="s">
-        <v>974</v>
       </c>
       <c r="E349" s="6"/>
       <c r="F349" s="6"/>
@@ -16443,29 +16462,29 @@
     </row>
     <row r="350" spans="1:17" ht="15.75" customHeight="1">
       <c r="A350" s="3" t="s">
+        <v>973</v>
+      </c>
+      <c r="B350" s="3" t="s">
+        <v>974</v>
+      </c>
+      <c r="C350" s="8" t="s">
         <v>975</v>
       </c>
-      <c r="B350" s="3" t="s">
+      <c r="D350" s="3" t="s">
         <v>976</v>
-      </c>
-      <c r="C350" s="8" t="s">
-        <v>977</v>
-      </c>
-      <c r="D350" s="3" t="s">
-        <v>978</v>
       </c>
       <c r="E350" s="1"/>
       <c r="F350" s="1"/>
       <c r="G350" s="1"/>
       <c r="H350" s="1"/>
       <c r="I350" s="3" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="J350" s="3" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="K350" s="3" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="L350" s="1"/>
       <c r="M350" s="1"/>
@@ -16479,17 +16498,17 @@
         <v>137</v>
       </c>
       <c r="B351" s="1" t="s">
+        <v>978</v>
+      </c>
+      <c r="C351" s="8" t="s">
+        <v>979</v>
+      </c>
+      <c r="D351" s="18" t="s">
         <v>980</v>
-      </c>
-      <c r="C351" s="8" t="s">
-        <v>981</v>
-      </c>
-      <c r="D351" s="18" t="s">
-        <v>982</v>
       </c>
       <c r="E351" s="1"/>
       <c r="F351" s="4" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="G351" s="6"/>
       <c r="H351" s="6"/>
@@ -16508,17 +16527,17 @@
         <v>137</v>
       </c>
       <c r="B352" s="1" t="s">
+        <v>982</v>
+      </c>
+      <c r="C352" s="8" t="s">
+        <v>983</v>
+      </c>
+      <c r="D352" s="18" t="s">
         <v>984</v>
-      </c>
-      <c r="C352" s="8" t="s">
-        <v>985</v>
-      </c>
-      <c r="D352" s="18" t="s">
-        <v>986</v>
       </c>
       <c r="E352" s="1"/>
       <c r="F352" s="4" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="G352" s="6"/>
       <c r="H352" s="6"/>
@@ -16537,13 +16556,13 @@
         <v>137</v>
       </c>
       <c r="B353" s="1" t="s">
+        <v>986</v>
+      </c>
+      <c r="C353" s="8" t="s">
+        <v>987</v>
+      </c>
+      <c r="D353" s="18" t="s">
         <v>988</v>
-      </c>
-      <c r="C353" s="8" t="s">
-        <v>989</v>
-      </c>
-      <c r="D353" s="18" t="s">
-        <v>990</v>
       </c>
       <c r="E353" s="6"/>
       <c r="F353" s="6"/>
@@ -16564,7 +16583,7 @@
         <v>53</v>
       </c>
       <c r="B354" s="1" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="C354" s="1"/>
       <c r="D354" s="1"/>
@@ -16587,7 +16606,7 @@
         <v>19</v>
       </c>
       <c r="B355" s="1" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="C355" s="3" t="s">
         <v>21</v>
@@ -16595,7 +16614,7 @@
       <c r="D355" s="1"/>
       <c r="E355" s="1"/>
       <c r="F355" s="1" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="G355" s="1" t="s">
         <v>145</v>
@@ -16616,13 +16635,13 @@
         <v>165</v>
       </c>
       <c r="B356" s="1" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="C356" s="8" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="D356" s="3" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="E356" s="1" t="s">
         <v>169</v>
@@ -16645,17 +16664,17 @@
         <v>137</v>
       </c>
       <c r="B357" s="1" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="C357" s="8" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="D357" s="18" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="E357" s="1"/>
       <c r="F357" s="4" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="G357" s="1"/>
       <c r="H357" s="1"/>
@@ -16674,17 +16693,17 @@
         <v>137</v>
       </c>
       <c r="B358" s="1" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="C358" s="8" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="D358" s="18" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="E358" s="1"/>
       <c r="F358" s="4" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="G358" s="1"/>
       <c r="H358" s="1"/>
@@ -16703,13 +16722,13 @@
         <v>137</v>
       </c>
       <c r="B359" s="1" t="s">
+        <v>999</v>
+      </c>
+      <c r="C359" s="4" t="s">
+        <v>1000</v>
+      </c>
+      <c r="D359" s="18" t="s">
         <v>1001</v>
-      </c>
-      <c r="C359" s="4" t="s">
-        <v>1002</v>
-      </c>
-      <c r="D359" s="18" t="s">
-        <v>1003</v>
       </c>
       <c r="E359" s="6"/>
       <c r="F359" s="6"/>
@@ -16730,17 +16749,17 @@
         <v>137</v>
       </c>
       <c r="B360" s="1" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C360" s="4" t="s">
+        <v>1003</v>
+      </c>
+      <c r="D360" s="18" t="s">
         <v>1004</v>
-      </c>
-      <c r="C360" s="4" t="s">
-        <v>1005</v>
-      </c>
-      <c r="D360" s="18" t="s">
-        <v>1006</v>
       </c>
       <c r="E360" s="1"/>
       <c r="F360" s="4" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="G360" s="6"/>
       <c r="H360" s="6"/>
@@ -16759,17 +16778,17 @@
         <v>137</v>
       </c>
       <c r="B361" s="1" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C361" s="4" t="s">
+        <v>1007</v>
+      </c>
+      <c r="D361" s="18" t="s">
         <v>1008</v>
-      </c>
-      <c r="C361" s="4" t="s">
-        <v>1009</v>
-      </c>
-      <c r="D361" s="18" t="s">
-        <v>1010</v>
       </c>
       <c r="E361" s="1"/>
       <c r="F361" s="4" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="G361" s="6"/>
       <c r="H361" s="6"/>
@@ -16788,17 +16807,17 @@
         <v>137</v>
       </c>
       <c r="B362" s="1" t="s">
+        <v>1010</v>
+      </c>
+      <c r="C362" s="4" t="s">
+        <v>1011</v>
+      </c>
+      <c r="D362" s="18" t="s">
         <v>1012</v>
-      </c>
-      <c r="C362" s="4" t="s">
-        <v>1013</v>
-      </c>
-      <c r="D362" s="18" t="s">
-        <v>1014</v>
       </c>
       <c r="E362" s="1"/>
       <c r="F362" s="4" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="G362" s="6"/>
       <c r="H362" s="6"/>
@@ -16817,17 +16836,17 @@
         <v>137</v>
       </c>
       <c r="B363" s="1" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C363" s="4" t="s">
+        <v>1015</v>
+      </c>
+      <c r="D363" s="18" t="s">
         <v>1016</v>
-      </c>
-      <c r="C363" s="4" t="s">
-        <v>1017</v>
-      </c>
-      <c r="D363" s="18" t="s">
-        <v>1018</v>
       </c>
       <c r="E363" s="1"/>
       <c r="F363" s="4" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="G363" s="6"/>
       <c r="H363" s="1"/>
@@ -16843,29 +16862,29 @@
     </row>
     <row r="364" spans="1:17" ht="15.75" customHeight="1">
       <c r="A364" s="26" t="s">
+        <v>973</v>
+      </c>
+      <c r="B364" s="26" t="s">
+        <v>974</v>
+      </c>
+      <c r="C364" s="8" t="s">
         <v>975</v>
       </c>
-      <c r="B364" s="26" t="s">
+      <c r="D364" s="3" t="s">
         <v>976</v>
-      </c>
-      <c r="C364" s="8" t="s">
-        <v>977</v>
-      </c>
-      <c r="D364" s="3" t="s">
-        <v>978</v>
       </c>
       <c r="E364" s="1"/>
       <c r="F364" s="1"/>
       <c r="G364" s="1"/>
       <c r="H364" s="1"/>
       <c r="I364" s="26" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="J364" s="26" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="K364" s="26" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="L364" s="1"/>
       <c r="M364" s="1"/>
@@ -16879,17 +16898,17 @@
         <v>137</v>
       </c>
       <c r="B365" s="1" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="C365" s="8" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="D365" s="18" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="E365" s="1"/>
       <c r="F365" s="4" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="G365" s="6"/>
       <c r="H365" s="6"/>
@@ -16908,17 +16927,17 @@
         <v>137</v>
       </c>
       <c r="B366" s="1" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="C366" s="8" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="D366" s="18" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="E366" s="1"/>
       <c r="F366" s="4" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="G366" s="6"/>
       <c r="H366" s="6"/>
@@ -16937,13 +16956,13 @@
         <v>137</v>
       </c>
       <c r="B367" s="1" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C367" s="4" t="s">
+        <v>1024</v>
+      </c>
+      <c r="D367" s="18" t="s">
         <v>1025</v>
-      </c>
-      <c r="C367" s="4" t="s">
-        <v>1026</v>
-      </c>
-      <c r="D367" s="18" t="s">
-        <v>1027</v>
       </c>
       <c r="E367" s="6"/>
       <c r="F367" s="1"/>
@@ -16964,17 +16983,17 @@
         <v>137</v>
       </c>
       <c r="B368" s="1" t="s">
+        <v>1026</v>
+      </c>
+      <c r="C368" s="4" t="s">
+        <v>1027</v>
+      </c>
+      <c r="D368" s="18" t="s">
         <v>1028</v>
-      </c>
-      <c r="C368" s="4" t="s">
-        <v>1029</v>
-      </c>
-      <c r="D368" s="18" t="s">
-        <v>1030</v>
       </c>
       <c r="E368" s="1"/>
       <c r="F368" s="4" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="G368" s="6"/>
       <c r="H368" s="6"/>
@@ -16993,17 +17012,17 @@
         <v>137</v>
       </c>
       <c r="B369" s="1" t="s">
+        <v>1029</v>
+      </c>
+      <c r="C369" s="4" t="s">
+        <v>1030</v>
+      </c>
+      <c r="D369" s="18" t="s">
         <v>1031</v>
-      </c>
-      <c r="C369" s="4" t="s">
-        <v>1032</v>
-      </c>
-      <c r="D369" s="18" t="s">
-        <v>1033</v>
       </c>
       <c r="E369" s="1"/>
       <c r="F369" s="4" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="G369" s="6"/>
       <c r="H369" s="6"/>
@@ -17022,17 +17041,17 @@
         <v>137</v>
       </c>
       <c r="B370" s="1" t="s">
+        <v>1032</v>
+      </c>
+      <c r="C370" s="4" t="s">
+        <v>1033</v>
+      </c>
+      <c r="D370" s="18" t="s">
         <v>1034</v>
-      </c>
-      <c r="C370" s="4" t="s">
-        <v>1035</v>
-      </c>
-      <c r="D370" s="18" t="s">
-        <v>1036</v>
       </c>
       <c r="E370" s="1"/>
       <c r="F370" s="4" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="G370" s="6"/>
       <c r="H370" s="6"/>
@@ -17051,17 +17070,17 @@
         <v>137</v>
       </c>
       <c r="B371" s="1" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C371" s="8" t="s">
+        <v>1036</v>
+      </c>
+      <c r="D371" s="18" t="s">
         <v>1037</v>
-      </c>
-      <c r="C371" s="8" t="s">
-        <v>1038</v>
-      </c>
-      <c r="D371" s="18" t="s">
-        <v>1039</v>
       </c>
       <c r="E371" s="1"/>
       <c r="F371" s="4" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="G371" s="6"/>
       <c r="H371" s="1"/>
@@ -17080,7 +17099,7 @@
         <v>53</v>
       </c>
       <c r="B372" s="1" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="C372" s="1"/>
       <c r="D372" s="1"/>
@@ -17103,7 +17122,7 @@
         <v>53</v>
       </c>
       <c r="B373" s="1" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="C373" s="1"/>
       <c r="D373" s="1"/>
@@ -17126,17 +17145,17 @@
         <v>19</v>
       </c>
       <c r="B374" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="C374" s="3" t="s">
+        <v>1039</v>
+      </c>
+      <c r="D374" s="3" t="s">
         <v>1040</v>
-      </c>
-      <c r="C374" s="3" t="s">
-        <v>1041</v>
-      </c>
-      <c r="D374" s="3" t="s">
-        <v>1042</v>
       </c>
       <c r="E374" s="3"/>
       <c r="F374" s="3" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="G374" s="1" t="s">
         <v>145</v>
@@ -17157,13 +17176,13 @@
         <v>137</v>
       </c>
       <c r="B375" s="1" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C375" s="8" t="s">
+        <v>1042</v>
+      </c>
+      <c r="D375" s="18" t="s">
         <v>1043</v>
-      </c>
-      <c r="C375" s="8" t="s">
-        <v>1044</v>
-      </c>
-      <c r="D375" s="18" t="s">
-        <v>1045</v>
       </c>
       <c r="E375" s="6"/>
       <c r="F375" s="6"/>
@@ -17181,16 +17200,16 @@
     </row>
     <row r="376" spans="1:17" ht="15.75" customHeight="1">
       <c r="A376" s="1" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B376" s="1" t="s">
+        <v>1045</v>
+      </c>
+      <c r="C376" s="8" t="s">
         <v>1046</v>
       </c>
-      <c r="B376" s="1" t="s">
+      <c r="D376" s="3" t="s">
         <v>1047</v>
-      </c>
-      <c r="C376" s="8" t="s">
-        <v>1048</v>
-      </c>
-      <c r="D376" s="3" t="s">
-        <v>1049</v>
       </c>
       <c r="E376" s="1" t="s">
         <v>169</v>
@@ -17213,17 +17232,17 @@
         <v>137</v>
       </c>
       <c r="B377" s="1" t="s">
+        <v>1048</v>
+      </c>
+      <c r="C377" s="8" t="s">
+        <v>1049</v>
+      </c>
+      <c r="D377" s="3" t="s">
         <v>1050</v>
-      </c>
-      <c r="C377" s="8" t="s">
-        <v>1051</v>
-      </c>
-      <c r="D377" s="3" t="s">
-        <v>1052</v>
       </c>
       <c r="E377" s="1"/>
       <c r="F377" s="4" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="G377" s="1"/>
       <c r="H377" s="1"/>
@@ -17242,17 +17261,17 @@
         <v>137</v>
       </c>
       <c r="B378" s="1" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C378" s="8" t="s">
+        <v>1053</v>
+      </c>
+      <c r="D378" s="18" t="s">
         <v>1054</v>
-      </c>
-      <c r="C378" s="8" t="s">
-        <v>1055</v>
-      </c>
-      <c r="D378" s="18" t="s">
-        <v>1056</v>
       </c>
       <c r="E378" s="1"/>
       <c r="F378" s="4" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="G378" s="6"/>
       <c r="H378" s="1"/>
@@ -17271,13 +17290,13 @@
         <v>165</v>
       </c>
       <c r="B379" s="1" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C379" s="4" t="s">
+        <v>1057</v>
+      </c>
+      <c r="D379" s="3" t="s">
         <v>1058</v>
-      </c>
-      <c r="C379" s="4" t="s">
-        <v>1059</v>
-      </c>
-      <c r="D379" s="3" t="s">
-        <v>1060</v>
       </c>
       <c r="E379" s="1" t="s">
         <v>169</v>
@@ -17297,22 +17316,22 @@
     </row>
     <row r="380" spans="1:17" ht="15.75" customHeight="1">
       <c r="A380" s="3" t="s">
+        <v>1059</v>
+      </c>
+      <c r="B380" s="3" t="s">
+        <v>1060</v>
+      </c>
+      <c r="C380" s="8" t="s">
         <v>1061</v>
       </c>
-      <c r="B380" s="3" t="s">
+      <c r="D380" s="3" t="s">
         <v>1062</v>
-      </c>
-      <c r="C380" s="8" t="s">
-        <v>1063</v>
-      </c>
-      <c r="D380" s="3" t="s">
-        <v>1064</v>
       </c>
       <c r="E380" s="2" t="s">
         <v>169</v>
       </c>
       <c r="F380" s="19" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="G380" s="1"/>
       <c r="H380" s="1"/>
@@ -17331,16 +17350,16 @@
         <v>137</v>
       </c>
       <c r="B381" s="1" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C381" s="8" t="s">
+        <v>1065</v>
+      </c>
+      <c r="D381" s="3" t="s">
         <v>1066</v>
       </c>
-      <c r="C381" s="8" t="s">
+      <c r="F381" s="8" t="s">
         <v>1067</v>
-      </c>
-      <c r="D381" s="3" t="s">
-        <v>1068</v>
-      </c>
-      <c r="F381" s="8" t="s">
-        <v>1069</v>
       </c>
       <c r="G381" s="1"/>
       <c r="H381" s="1"/>
@@ -17359,16 +17378,16 @@
         <v>137</v>
       </c>
       <c r="B382" s="1" t="s">
+        <v>1068</v>
+      </c>
+      <c r="C382" s="8" t="s">
+        <v>1069</v>
+      </c>
+      <c r="D382" s="3" t="s">
         <v>1070</v>
       </c>
-      <c r="C382" s="8" t="s">
+      <c r="F382" s="8" t="s">
         <v>1071</v>
-      </c>
-      <c r="D382" s="3" t="s">
-        <v>1072</v>
-      </c>
-      <c r="F382" s="8" t="s">
-        <v>1073</v>
       </c>
       <c r="G382" s="1"/>
       <c r="H382" s="1"/>
@@ -17387,19 +17406,19 @@
         <v>165</v>
       </c>
       <c r="B383" s="1" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C383" s="4" t="s">
+        <v>1073</v>
+      </c>
+      <c r="D383" s="3" t="s">
         <v>1074</v>
-      </c>
-      <c r="C383" s="4" t="s">
-        <v>1075</v>
-      </c>
-      <c r="D383" s="3" t="s">
-        <v>1076</v>
       </c>
       <c r="E383" s="1" t="s">
         <v>169</v>
       </c>
       <c r="F383" s="4" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="G383" s="6"/>
       <c r="H383" s="6"/>
@@ -17418,17 +17437,17 @@
         <v>137</v>
       </c>
       <c r="B384" s="1" t="s">
+        <v>1075</v>
+      </c>
+      <c r="C384" s="8" t="s">
+        <v>1076</v>
+      </c>
+      <c r="D384" s="18" t="s">
         <v>1077</v>
-      </c>
-      <c r="C384" s="8" t="s">
-        <v>1078</v>
-      </c>
-      <c r="D384" s="18" t="s">
-        <v>1079</v>
       </c>
       <c r="E384" s="1"/>
       <c r="F384" s="4" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="G384" s="6"/>
       <c r="H384" s="1"/>
@@ -17444,22 +17463,22 @@
     </row>
     <row r="385" spans="1:17" ht="15.75" customHeight="1">
       <c r="A385" s="1" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B385" s="1" t="s">
+        <v>1080</v>
+      </c>
+      <c r="C385" s="4" t="s">
         <v>1081</v>
       </c>
-      <c r="B385" s="1" t="s">
+      <c r="D385" s="3" t="s">
         <v>1082</v>
-      </c>
-      <c r="C385" s="4" t="s">
-        <v>1083</v>
-      </c>
-      <c r="D385" s="3" t="s">
-        <v>1084</v>
       </c>
       <c r="E385" s="1" t="s">
         <v>169</v>
       </c>
       <c r="F385" s="4" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="G385" s="6"/>
       <c r="H385" s="1"/>
@@ -17478,17 +17497,17 @@
         <v>137</v>
       </c>
       <c r="B386" s="1" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C386" s="8" t="s">
+        <v>1085</v>
+      </c>
+      <c r="D386" s="18" t="s">
         <v>1086</v>
-      </c>
-      <c r="C386" s="8" t="s">
-        <v>1087</v>
-      </c>
-      <c r="D386" s="18" t="s">
-        <v>1088</v>
       </c>
       <c r="E386" s="1"/>
       <c r="F386" s="4" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="G386" s="6"/>
       <c r="H386" s="1"/>
@@ -17507,17 +17526,17 @@
         <v>137</v>
       </c>
       <c r="B387" s="1" t="s">
+        <v>1088</v>
+      </c>
+      <c r="C387" s="8" t="s">
+        <v>1089</v>
+      </c>
+      <c r="D387" s="18" t="s">
         <v>1090</v>
-      </c>
-      <c r="C387" s="8" t="s">
-        <v>1091</v>
-      </c>
-      <c r="D387" s="18" t="s">
-        <v>1092</v>
       </c>
       <c r="E387" s="1"/>
       <c r="F387" s="4" t="s">
-        <v>1093</v>
+        <v>1091</v>
       </c>
       <c r="G387" s="1"/>
       <c r="H387" s="1"/>
@@ -17536,7 +17555,7 @@
         <v>53</v>
       </c>
       <c r="B388" s="1" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="C388" s="1"/>
       <c r="D388" s="1"/>
@@ -17559,13 +17578,13 @@
         <v>19</v>
       </c>
       <c r="B389" s="1" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C389" s="3" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D389" s="3" t="s">
         <v>1094</v>
-      </c>
-      <c r="C389" s="3" t="s">
-        <v>1095</v>
-      </c>
-      <c r="D389" s="3" t="s">
-        <v>1096</v>
       </c>
       <c r="E389" s="1"/>
       <c r="F389" s="9" t="s">
@@ -17590,17 +17609,17 @@
         <v>137</v>
       </c>
       <c r="B390" s="1" t="s">
+        <v>1095</v>
+      </c>
+      <c r="C390" s="8" t="s">
+        <v>1096</v>
+      </c>
+      <c r="D390" s="18" t="s">
         <v>1097</v>
-      </c>
-      <c r="C390" s="8" t="s">
-        <v>1098</v>
-      </c>
-      <c r="D390" s="18" t="s">
-        <v>1099</v>
       </c>
       <c r="E390" s="6"/>
       <c r="F390" s="3" t="s">
-        <v>1100</v>
+        <v>1098</v>
       </c>
       <c r="G390" s="6"/>
       <c r="H390" s="6"/>
@@ -17619,19 +17638,19 @@
         <v>165</v>
       </c>
       <c r="B391" s="1" t="s">
+        <v>1099</v>
+      </c>
+      <c r="C391" s="8" t="s">
+        <v>1100</v>
+      </c>
+      <c r="D391" s="3" t="s">
         <v>1101</v>
-      </c>
-      <c r="C391" s="8" t="s">
-        <v>1102</v>
-      </c>
-      <c r="D391" s="3" t="s">
-        <v>1103</v>
       </c>
       <c r="E391" s="1" t="s">
         <v>169</v>
       </c>
       <c r="F391" s="3" t="s">
-        <v>1100</v>
+        <v>1098</v>
       </c>
       <c r="G391" s="1"/>
       <c r="H391" s="1"/>
@@ -17650,17 +17669,17 @@
         <v>137</v>
       </c>
       <c r="B392" s="1" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C392" s="8" t="s">
+        <v>1103</v>
+      </c>
+      <c r="D392" s="18" t="s">
         <v>1104</v>
-      </c>
-      <c r="C392" s="8" t="s">
-        <v>1105</v>
-      </c>
-      <c r="D392" s="18" t="s">
-        <v>1106</v>
       </c>
       <c r="E392" s="1"/>
       <c r="F392" s="4" t="s">
-        <v>1107</v>
+        <v>1105</v>
       </c>
       <c r="G392" s="6"/>
       <c r="H392" s="1"/>
@@ -17679,19 +17698,19 @@
         <v>165</v>
       </c>
       <c r="B393" s="1" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C393" s="8" t="s">
+        <v>1107</v>
+      </c>
+      <c r="D393" s="18" t="s">
         <v>1108</v>
-      </c>
-      <c r="C393" s="8" t="s">
-        <v>1109</v>
-      </c>
-      <c r="D393" s="18" t="s">
-        <v>1110</v>
       </c>
       <c r="E393" s="18" t="s">
         <v>169</v>
       </c>
       <c r="F393" s="3" t="s">
-        <v>1100</v>
+        <v>1098</v>
       </c>
       <c r="G393" s="6"/>
       <c r="H393" s="6"/>
@@ -17710,17 +17729,17 @@
         <v>137</v>
       </c>
       <c r="B394" s="1" t="s">
+        <v>1109</v>
+      </c>
+      <c r="C394" s="8" t="s">
+        <v>1110</v>
+      </c>
+      <c r="D394" s="18" t="s">
         <v>1111</v>
-      </c>
-      <c r="C394" s="8" t="s">
-        <v>1112</v>
-      </c>
-      <c r="D394" s="18" t="s">
-        <v>1113</v>
       </c>
       <c r="E394" s="1"/>
       <c r="F394" s="4" t="s">
-        <v>1114</v>
+        <v>1112</v>
       </c>
       <c r="G394" s="6"/>
       <c r="H394" s="1"/>
@@ -17736,33 +17755,33 @@
     </row>
     <row r="395" spans="1:17" ht="15.75" customHeight="1">
       <c r="A395" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B395" s="1" t="s">
+        <v>1114</v>
+      </c>
+      <c r="C395" s="8" t="s">
         <v>1115</v>
       </c>
-      <c r="B395" s="1" t="s">
+      <c r="D395" s="3" t="s">
         <v>1116</v>
-      </c>
-      <c r="C395" s="8" t="s">
-        <v>1117</v>
-      </c>
-      <c r="D395" s="3" t="s">
-        <v>1118</v>
       </c>
       <c r="E395" s="1" t="s">
         <v>169</v>
       </c>
       <c r="F395" s="8" t="s">
-        <v>1119</v>
+        <v>1117</v>
       </c>
       <c r="G395" s="6"/>
       <c r="H395" s="6"/>
       <c r="I395" s="3" t="s">
+        <v>1118</v>
+      </c>
+      <c r="J395" s="3" t="s">
+        <v>1119</v>
+      </c>
+      <c r="K395" s="18" t="s">
         <v>1120</v>
-      </c>
-      <c r="J395" s="3" t="s">
-        <v>1121</v>
-      </c>
-      <c r="K395" s="18" t="s">
-        <v>1122</v>
       </c>
       <c r="L395" s="6"/>
       <c r="M395" s="6"/>
@@ -17773,22 +17792,22 @@
     </row>
     <row r="396" spans="1:17" ht="15.75" customHeight="1">
       <c r="A396" s="1" t="s">
+        <v>1121</v>
+      </c>
+      <c r="B396" s="1" t="s">
+        <v>1122</v>
+      </c>
+      <c r="C396" s="8" t="s">
         <v>1123</v>
       </c>
-      <c r="B396" s="1" t="s">
+      <c r="D396" s="3" t="s">
         <v>1124</v>
-      </c>
-      <c r="C396" s="8" t="s">
-        <v>1125</v>
-      </c>
-      <c r="D396" s="3" t="s">
-        <v>1126</v>
       </c>
       <c r="E396" s="1" t="s">
         <v>169</v>
       </c>
       <c r="F396" s="8" t="s">
-        <v>1127</v>
+        <v>1125</v>
       </c>
       <c r="G396" s="6"/>
       <c r="H396" s="1"/>
@@ -17804,20 +17823,20 @@
     </row>
     <row r="397" spans="1:17" ht="15.75" customHeight="1">
       <c r="A397" s="3" t="s">
+        <v>1126</v>
+      </c>
+      <c r="B397" s="1" t="s">
+        <v>1127</v>
+      </c>
+      <c r="C397" s="1" t="s">
         <v>1128</v>
       </c>
-      <c r="B397" s="1" t="s">
+      <c r="D397" s="3" t="s">
         <v>1129</v>
-      </c>
-      <c r="C397" s="1" t="s">
-        <v>1130</v>
-      </c>
-      <c r="D397" s="3" t="s">
-        <v>1131</v>
       </c>
       <c r="E397" s="1"/>
       <c r="F397" s="4" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="G397" s="1"/>
       <c r="H397" s="1"/>
@@ -17833,27 +17852,27 @@
     </row>
     <row r="398" spans="1:17" ht="15.75" customHeight="1">
       <c r="A398" s="1" t="s">
+        <v>1131</v>
+      </c>
+      <c r="B398" s="1" t="s">
+        <v>1132</v>
+      </c>
+      <c r="C398" s="8" t="s">
         <v>1133</v>
       </c>
-      <c r="B398" s="1" t="s">
+      <c r="D398" s="18" t="s">
         <v>1134</v>
-      </c>
-      <c r="C398" s="8" t="s">
-        <v>1135</v>
-      </c>
-      <c r="D398" s="18" t="s">
-        <v>1136</v>
       </c>
       <c r="E398" s="3" t="s">
         <v>169</v>
       </c>
       <c r="F398" s="8" t="s">
-        <v>1127</v>
+        <v>1125</v>
       </c>
       <c r="G398" s="6"/>
       <c r="H398" s="1"/>
       <c r="I398" s="4" t="s">
-        <v>1137</v>
+        <v>1135</v>
       </c>
       <c r="J398" s="1"/>
       <c r="K398" s="1"/>
@@ -17869,19 +17888,19 @@
         <v>165</v>
       </c>
       <c r="B399" s="1" t="s">
+        <v>1136</v>
+      </c>
+      <c r="C399" s="8" t="s">
+        <v>1137</v>
+      </c>
+      <c r="D399" s="3" t="s">
         <v>1138</v>
-      </c>
-      <c r="C399" s="8" t="s">
-        <v>1139</v>
-      </c>
-      <c r="D399" s="3" t="s">
-        <v>1140</v>
       </c>
       <c r="E399" s="1" t="s">
         <v>169</v>
       </c>
       <c r="F399" s="3" t="s">
-        <v>1100</v>
+        <v>1098</v>
       </c>
       <c r="G399" s="1"/>
       <c r="H399" s="1"/>
@@ -17900,17 +17919,17 @@
         <v>137</v>
       </c>
       <c r="B400" s="1" t="s">
+        <v>1139</v>
+      </c>
+      <c r="C400" s="8" t="s">
+        <v>1140</v>
+      </c>
+      <c r="D400" s="18" t="s">
         <v>1141</v>
-      </c>
-      <c r="C400" s="8" t="s">
-        <v>1142</v>
-      </c>
-      <c r="D400" s="18" t="s">
-        <v>1143</v>
       </c>
       <c r="E400" s="1"/>
       <c r="F400" s="4" t="s">
-        <v>1144</v>
+        <v>1142</v>
       </c>
       <c r="G400" s="1"/>
       <c r="H400" s="1"/>
@@ -17929,19 +17948,19 @@
         <v>165</v>
       </c>
       <c r="B401" s="1" t="s">
+        <v>1143</v>
+      </c>
+      <c r="C401" s="8" t="s">
+        <v>1144</v>
+      </c>
+      <c r="D401" s="3" t="s">
         <v>1145</v>
-      </c>
-      <c r="C401" s="8" t="s">
-        <v>1146</v>
-      </c>
-      <c r="D401" s="3" t="s">
-        <v>1147</v>
       </c>
       <c r="E401" s="1" t="s">
         <v>169</v>
       </c>
       <c r="F401" s="8" t="s">
-        <v>1119</v>
+        <v>1117</v>
       </c>
       <c r="G401" s="6"/>
       <c r="H401" s="6"/>
@@ -17960,19 +17979,19 @@
         <v>165</v>
       </c>
       <c r="B402" s="1" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C402" s="8" t="s">
+        <v>1147</v>
+      </c>
+      <c r="D402" s="3" t="s">
         <v>1148</v>
-      </c>
-      <c r="C402" s="8" t="s">
-        <v>1149</v>
-      </c>
-      <c r="D402" s="3" t="s">
-        <v>1150</v>
       </c>
       <c r="E402" s="1" t="s">
         <v>169</v>
       </c>
       <c r="F402" s="8" t="s">
-        <v>1119</v>
+        <v>1117</v>
       </c>
       <c r="G402" s="6"/>
       <c r="H402" s="6"/>
@@ -17991,19 +18010,19 @@
         <v>165</v>
       </c>
       <c r="B403" s="1" t="s">
+        <v>1149</v>
+      </c>
+      <c r="C403" s="8" t="s">
+        <v>1150</v>
+      </c>
+      <c r="D403" s="3" t="s">
         <v>1151</v>
-      </c>
-      <c r="C403" s="8" t="s">
-        <v>1152</v>
-      </c>
-      <c r="D403" s="3" t="s">
-        <v>1153</v>
       </c>
       <c r="E403" s="1" t="s">
         <v>169</v>
       </c>
       <c r="F403" s="8" t="s">
-        <v>1119</v>
+        <v>1117</v>
       </c>
       <c r="G403" s="6"/>
       <c r="H403" s="6"/>
@@ -18019,27 +18038,27 @@
     </row>
     <row r="404" spans="1:17" ht="15.75" customHeight="1">
       <c r="A404" s="1" t="s">
-        <v>1133</v>
+        <v>1131</v>
       </c>
       <c r="B404" s="1" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C404" s="8" t="s">
+        <v>1153</v>
+      </c>
+      <c r="D404" s="3" t="s">
         <v>1154</v>
-      </c>
-      <c r="C404" s="8" t="s">
-        <v>1155</v>
-      </c>
-      <c r="D404" s="3" t="s">
-        <v>1156</v>
       </c>
       <c r="E404" s="1" t="s">
         <v>169</v>
       </c>
       <c r="F404" s="8" t="s">
-        <v>1119</v>
+        <v>1117</v>
       </c>
       <c r="G404" s="6"/>
       <c r="H404" s="1"/>
       <c r="I404" s="3" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
       <c r="J404" s="1"/>
       <c r="K404" s="1"/>
@@ -18055,19 +18074,19 @@
         <v>165</v>
       </c>
       <c r="B405" s="1" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C405" s="8" t="s">
+        <v>1157</v>
+      </c>
+      <c r="D405" s="3" t="s">
         <v>1158</v>
-      </c>
-      <c r="C405" s="8" t="s">
-        <v>1159</v>
-      </c>
-      <c r="D405" s="3" t="s">
-        <v>1160</v>
       </c>
       <c r="E405" s="1" t="s">
         <v>169</v>
       </c>
       <c r="F405" s="3" t="s">
-        <v>1100</v>
+        <v>1098</v>
       </c>
       <c r="G405" s="1"/>
       <c r="H405" s="1"/>
@@ -18086,17 +18105,17 @@
         <v>137</v>
       </c>
       <c r="B406" s="1" t="s">
+        <v>1159</v>
+      </c>
+      <c r="C406" s="8" t="s">
+        <v>1160</v>
+      </c>
+      <c r="D406" s="18" t="s">
         <v>1161</v>
-      </c>
-      <c r="C406" s="8" t="s">
-        <v>1162</v>
-      </c>
-      <c r="D406" s="18" t="s">
-        <v>1163</v>
       </c>
       <c r="E406" s="1"/>
       <c r="F406" s="4" t="s">
-        <v>1164</v>
+        <v>1162</v>
       </c>
       <c r="G406" s="6"/>
       <c r="H406" s="1"/>
@@ -18115,17 +18134,17 @@
         <v>137</v>
       </c>
       <c r="B407" s="3" t="s">
+        <v>1163</v>
+      </c>
+      <c r="C407" s="8" t="s">
+        <v>1164</v>
+      </c>
+      <c r="D407" s="3" t="s">
         <v>1165</v>
-      </c>
-      <c r="C407" s="8" t="s">
-        <v>1166</v>
-      </c>
-      <c r="D407" s="3" t="s">
-        <v>1167</v>
       </c>
       <c r="E407" s="1"/>
       <c r="F407" s="8" t="s">
-        <v>1168</v>
+        <v>1166</v>
       </c>
       <c r="G407" s="6"/>
       <c r="H407" s="1"/>
@@ -18141,27 +18160,27 @@
     </row>
     <row r="408" spans="1:17" ht="15.75" customHeight="1">
       <c r="A408" s="1" t="s">
-        <v>1133</v>
+        <v>1131</v>
       </c>
       <c r="B408" s="1" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C408" s="8" t="s">
+        <v>1168</v>
+      </c>
+      <c r="D408" s="3" t="s">
         <v>1169</v>
-      </c>
-      <c r="C408" s="8" t="s">
-        <v>1170</v>
-      </c>
-      <c r="D408" s="3" t="s">
-        <v>1171</v>
       </c>
       <c r="E408" s="1" t="s">
         <v>169</v>
       </c>
       <c r="F408" s="8" t="s">
-        <v>1119</v>
+        <v>1117</v>
       </c>
       <c r="G408" s="6"/>
       <c r="H408" s="1"/>
       <c r="I408" s="1" t="s">
-        <v>1172</v>
+        <v>1170</v>
       </c>
       <c r="J408" s="1"/>
       <c r="K408" s="1"/>
@@ -18174,27 +18193,27 @@
     </row>
     <row r="409" spans="1:17" ht="15.75" customHeight="1">
       <c r="A409" s="1" t="s">
-        <v>1133</v>
+        <v>1131</v>
       </c>
       <c r="B409" s="1" t="s">
+        <v>1171</v>
+      </c>
+      <c r="C409" s="8" t="s">
+        <v>1172</v>
+      </c>
+      <c r="D409" s="3" t="s">
         <v>1173</v>
-      </c>
-      <c r="C409" s="8" t="s">
-        <v>1174</v>
-      </c>
-      <c r="D409" s="3" t="s">
-        <v>1175</v>
       </c>
       <c r="E409" s="1" t="s">
         <v>169</v>
       </c>
       <c r="F409" s="8" t="s">
-        <v>1119</v>
+        <v>1117</v>
       </c>
       <c r="G409" s="6"/>
       <c r="H409" s="1"/>
       <c r="I409" s="1" t="s">
-        <v>1172</v>
+        <v>1170</v>
       </c>
       <c r="J409" s="1"/>
       <c r="K409" s="1"/>
@@ -18210,17 +18229,17 @@
         <v>137</v>
       </c>
       <c r="B410" s="3" t="s">
+        <v>1174</v>
+      </c>
+      <c r="C410" s="12" t="s">
+        <v>1175</v>
+      </c>
+      <c r="D410" s="12" t="s">
         <v>1176</v>
-      </c>
-      <c r="C410" s="12" t="s">
-        <v>1177</v>
-      </c>
-      <c r="D410" s="12" t="s">
-        <v>1178</v>
       </c>
       <c r="E410" s="1"/>
       <c r="F410" s="3" t="s">
-        <v>1100</v>
+        <v>1098</v>
       </c>
       <c r="G410" s="1"/>
       <c r="H410" s="1"/>
@@ -18239,17 +18258,17 @@
         <v>137</v>
       </c>
       <c r="B411" s="1" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C411" s="8" t="s">
+        <v>1178</v>
+      </c>
+      <c r="D411" s="18" t="s">
         <v>1179</v>
-      </c>
-      <c r="C411" s="8" t="s">
-        <v>1180</v>
-      </c>
-      <c r="D411" s="18" t="s">
-        <v>1181</v>
       </c>
       <c r="E411" s="6"/>
       <c r="F411" s="3" t="s">
-        <v>1100</v>
+        <v>1098</v>
       </c>
       <c r="G411" s="6"/>
       <c r="H411" s="6"/>
@@ -18268,17 +18287,17 @@
         <v>137</v>
       </c>
       <c r="B412" s="1" t="s">
+        <v>1180</v>
+      </c>
+      <c r="C412" s="8" t="s">
+        <v>1181</v>
+      </c>
+      <c r="D412" s="18" t="s">
         <v>1182</v>
-      </c>
-      <c r="C412" s="8" t="s">
-        <v>1183</v>
-      </c>
-      <c r="D412" s="18" t="s">
-        <v>1184</v>
       </c>
       <c r="E412" s="6"/>
       <c r="F412" s="3" t="s">
-        <v>1100</v>
+        <v>1098</v>
       </c>
       <c r="G412" s="6"/>
       <c r="H412" s="6"/>
@@ -18297,7 +18316,7 @@
         <v>137</v>
       </c>
       <c r="B413" s="3" t="s">
-        <v>1185</v>
+        <v>1183</v>
       </c>
       <c r="C413" s="9" t="s">
         <v>731</v>
@@ -18307,7 +18326,7 @@
       </c>
       <c r="E413" s="1"/>
       <c r="F413" s="3" t="s">
-        <v>1100</v>
+        <v>1098</v>
       </c>
       <c r="G413" s="1"/>
       <c r="H413" s="1"/>
@@ -18326,19 +18345,19 @@
         <v>165</v>
       </c>
       <c r="B414" s="1" t="s">
+        <v>1184</v>
+      </c>
+      <c r="C414" s="8" t="s">
+        <v>1185</v>
+      </c>
+      <c r="D414" s="3" t="s">
         <v>1186</v>
-      </c>
-      <c r="C414" s="8" t="s">
-        <v>1187</v>
-      </c>
-      <c r="D414" s="3" t="s">
-        <v>1188</v>
       </c>
       <c r="E414" s="1" t="s">
         <v>169</v>
       </c>
       <c r="F414" s="3" t="s">
-        <v>1100</v>
+        <v>1098</v>
       </c>
       <c r="G414" s="1"/>
       <c r="H414" s="1"/>
@@ -18357,17 +18376,17 @@
         <v>137</v>
       </c>
       <c r="B415" s="1" t="s">
+        <v>1187</v>
+      </c>
+      <c r="C415" s="8" t="s">
+        <v>1188</v>
+      </c>
+      <c r="D415" s="18" t="s">
         <v>1189</v>
-      </c>
-      <c r="C415" s="8" t="s">
-        <v>1190</v>
-      </c>
-      <c r="D415" s="18" t="s">
-        <v>1191</v>
       </c>
       <c r="E415" s="1"/>
       <c r="F415" s="4" t="s">
-        <v>1192</v>
+        <v>1190</v>
       </c>
       <c r="G415" s="6"/>
       <c r="H415" s="1"/>
@@ -18386,17 +18405,17 @@
         <v>137</v>
       </c>
       <c r="B416" s="1" t="s">
+        <v>1191</v>
+      </c>
+      <c r="C416" s="8" t="s">
+        <v>1192</v>
+      </c>
+      <c r="D416" s="18" t="s">
         <v>1193</v>
-      </c>
-      <c r="C416" s="8" t="s">
-        <v>1194</v>
-      </c>
-      <c r="D416" s="18" t="s">
-        <v>1195</v>
       </c>
       <c r="E416" s="1"/>
       <c r="F416" s="4" t="s">
-        <v>1192</v>
+        <v>1190</v>
       </c>
       <c r="G416" s="6"/>
       <c r="H416" s="1"/>
@@ -18415,7 +18434,7 @@
         <v>137</v>
       </c>
       <c r="B417" s="3" t="s">
-        <v>1196</v>
+        <v>1194</v>
       </c>
       <c r="C417" s="3" t="s">
         <v>731</v>
@@ -18425,7 +18444,7 @@
       </c>
       <c r="E417" s="1"/>
       <c r="F417" s="3" t="s">
-        <v>1100</v>
+        <v>1098</v>
       </c>
       <c r="G417" s="6"/>
       <c r="H417" s="1"/>
@@ -18444,19 +18463,19 @@
         <v>165</v>
       </c>
       <c r="B418" s="1" t="s">
+        <v>1195</v>
+      </c>
+      <c r="C418" s="8" t="s">
+        <v>1196</v>
+      </c>
+      <c r="D418" s="3" t="s">
         <v>1197</v>
-      </c>
-      <c r="C418" s="8" t="s">
-        <v>1198</v>
-      </c>
-      <c r="D418" s="3" t="s">
-        <v>1199</v>
       </c>
       <c r="E418" s="1" t="s">
         <v>169</v>
       </c>
       <c r="F418" s="3" t="s">
-        <v>1100</v>
+        <v>1098</v>
       </c>
       <c r="G418" s="1"/>
       <c r="H418" s="1"/>
@@ -18475,17 +18494,17 @@
         <v>137</v>
       </c>
       <c r="B419" s="1" t="s">
+        <v>1198</v>
+      </c>
+      <c r="C419" s="8" t="s">
+        <v>1199</v>
+      </c>
+      <c r="D419" s="18" t="s">
         <v>1200</v>
-      </c>
-      <c r="C419" s="8" t="s">
-        <v>1201</v>
-      </c>
-      <c r="D419" s="18" t="s">
-        <v>1202</v>
       </c>
       <c r="E419" s="1"/>
       <c r="F419" s="4" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
       <c r="G419" s="6"/>
       <c r="H419" s="6"/>
@@ -18504,7 +18523,7 @@
         <v>53</v>
       </c>
       <c r="B420" s="1" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="C420" s="8"/>
       <c r="D420" s="3"/>
@@ -18527,17 +18546,17 @@
         <v>19</v>
       </c>
       <c r="B421" s="3" t="s">
+        <v>1202</v>
+      </c>
+      <c r="C421" s="8" t="s">
+        <v>1203</v>
+      </c>
+      <c r="D421" s="3" t="s">
         <v>1204</v>
-      </c>
-      <c r="C421" s="8" t="s">
-        <v>1205</v>
-      </c>
-      <c r="D421" s="3" t="s">
-        <v>1206</v>
       </c>
       <c r="E421" s="1"/>
       <c r="F421" s="3" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="G421" s="3" t="s">
         <v>145</v>
@@ -18558,13 +18577,13 @@
         <v>165</v>
       </c>
       <c r="B422" s="1" t="s">
+        <v>1205</v>
+      </c>
+      <c r="C422" s="8" t="s">
+        <v>1206</v>
+      </c>
+      <c r="D422" s="3" t="s">
         <v>1207</v>
-      </c>
-      <c r="C422" s="8" t="s">
-        <v>1208</v>
-      </c>
-      <c r="D422" s="3" t="s">
-        <v>1209</v>
       </c>
       <c r="E422" s="1" t="s">
         <v>169</v>
@@ -18587,17 +18606,17 @@
         <v>137</v>
       </c>
       <c r="B423" s="1" t="s">
+        <v>1208</v>
+      </c>
+      <c r="C423" s="8" t="s">
+        <v>1209</v>
+      </c>
+      <c r="D423" s="18" t="s">
         <v>1210</v>
-      </c>
-      <c r="C423" s="8" t="s">
-        <v>1211</v>
-      </c>
-      <c r="D423" s="18" t="s">
-        <v>1212</v>
       </c>
       <c r="E423" s="1"/>
       <c r="F423" s="4" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="G423" s="6"/>
       <c r="H423" s="1"/>
@@ -18616,17 +18635,17 @@
         <v>137</v>
       </c>
       <c r="B424" s="1" t="s">
+        <v>1212</v>
+      </c>
+      <c r="C424" s="8" t="s">
+        <v>1213</v>
+      </c>
+      <c r="D424" s="18" t="s">
         <v>1214</v>
-      </c>
-      <c r="C424" s="8" t="s">
-        <v>1215</v>
-      </c>
-      <c r="D424" s="18" t="s">
-        <v>1216</v>
       </c>
       <c r="E424" s="1"/>
       <c r="F424" s="8" t="s">
-        <v>1217</v>
+        <v>1215</v>
       </c>
       <c r="G424" s="6"/>
       <c r="H424" s="6"/>
@@ -18645,17 +18664,17 @@
         <v>165</v>
       </c>
       <c r="B425" s="1" t="s">
+        <v>1216</v>
+      </c>
+      <c r="C425" s="8" t="s">
+        <v>1217</v>
+      </c>
+      <c r="D425" s="28" t="s">
         <v>1218</v>
-      </c>
-      <c r="C425" s="8" t="s">
-        <v>1219</v>
-      </c>
-      <c r="D425" s="28" t="s">
-        <v>1220</v>
       </c>
       <c r="E425" s="1"/>
       <c r="F425" s="8" t="s">
-        <v>1217</v>
+        <v>1215</v>
       </c>
       <c r="G425" s="6"/>
       <c r="H425" s="6"/>
@@ -18674,17 +18693,17 @@
         <v>165</v>
       </c>
       <c r="B426" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="C426" s="8" t="s">
+        <v>1220</v>
+      </c>
+      <c r="D426" s="28" t="s">
         <v>1221</v>
-      </c>
-      <c r="C426" s="8" t="s">
-        <v>1222</v>
-      </c>
-      <c r="D426" s="28" t="s">
-        <v>1223</v>
       </c>
       <c r="E426" s="1"/>
       <c r="F426" s="8" t="s">
-        <v>1217</v>
+        <v>1215</v>
       </c>
       <c r="G426" s="6"/>
       <c r="H426" s="6"/>
@@ -18703,17 +18722,17 @@
         <v>165</v>
       </c>
       <c r="B427" s="1" t="s">
+        <v>1222</v>
+      </c>
+      <c r="C427" s="8" t="s">
+        <v>1223</v>
+      </c>
+      <c r="D427" s="28" t="s">
         <v>1224</v>
-      </c>
-      <c r="C427" s="8" t="s">
-        <v>1225</v>
-      </c>
-      <c r="D427" s="28" t="s">
-        <v>1226</v>
       </c>
       <c r="E427" s="1"/>
       <c r="F427" s="8" t="s">
-        <v>1217</v>
+        <v>1215</v>
       </c>
       <c r="G427" s="6"/>
       <c r="H427" s="6"/>
@@ -18732,17 +18751,17 @@
         <v>165</v>
       </c>
       <c r="B428" s="1" t="s">
+        <v>1225</v>
+      </c>
+      <c r="C428" s="8" t="s">
+        <v>1226</v>
+      </c>
+      <c r="D428" s="28" t="s">
         <v>1227</v>
-      </c>
-      <c r="C428" s="8" t="s">
-        <v>1228</v>
-      </c>
-      <c r="D428" s="28" t="s">
-        <v>1229</v>
       </c>
       <c r="E428" s="1"/>
       <c r="F428" s="8" t="s">
-        <v>1217</v>
+        <v>1215</v>
       </c>
       <c r="G428" s="6"/>
       <c r="H428" s="6"/>
@@ -18761,17 +18780,17 @@
         <v>165</v>
       </c>
       <c r="B429" s="1" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C429" s="8" t="s">
+        <v>1229</v>
+      </c>
+      <c r="D429" s="28" t="s">
         <v>1230</v>
-      </c>
-      <c r="C429" s="8" t="s">
-        <v>1231</v>
-      </c>
-      <c r="D429" s="28" t="s">
-        <v>1232</v>
       </c>
       <c r="E429" s="1"/>
       <c r="F429" s="8" t="s">
-        <v>1217</v>
+        <v>1215</v>
       </c>
       <c r="G429" s="6"/>
       <c r="H429" s="6"/>
@@ -18790,17 +18809,17 @@
         <v>165</v>
       </c>
       <c r="B430" s="1" t="s">
+        <v>1231</v>
+      </c>
+      <c r="C430" s="8" t="s">
+        <v>1232</v>
+      </c>
+      <c r="D430" s="37" t="s">
         <v>1233</v>
-      </c>
-      <c r="C430" s="8" t="s">
-        <v>1234</v>
-      </c>
-      <c r="D430" s="37" t="s">
-        <v>1235</v>
       </c>
       <c r="E430" s="1"/>
       <c r="F430" s="8" t="s">
-        <v>1217</v>
+        <v>1215</v>
       </c>
       <c r="G430" s="6"/>
       <c r="H430" s="6"/>
@@ -18819,17 +18838,17 @@
         <v>165</v>
       </c>
       <c r="B431" s="1" t="s">
+        <v>1234</v>
+      </c>
+      <c r="C431" s="8" t="s">
+        <v>1235</v>
+      </c>
+      <c r="D431" s="28" t="s">
         <v>1236</v>
-      </c>
-      <c r="C431" s="8" t="s">
-        <v>1237</v>
-      </c>
-      <c r="D431" s="28" t="s">
-        <v>1238</v>
       </c>
       <c r="E431" s="1"/>
       <c r="F431" s="8" t="s">
-        <v>1217</v>
+        <v>1215</v>
       </c>
       <c r="G431" s="6"/>
       <c r="H431" s="6"/>
@@ -18848,17 +18867,17 @@
         <v>165</v>
       </c>
       <c r="B432" s="1" t="s">
+        <v>1237</v>
+      </c>
+      <c r="C432" s="8" t="s">
+        <v>1238</v>
+      </c>
+      <c r="D432" s="28" t="s">
         <v>1239</v>
-      </c>
-      <c r="C432" s="8" t="s">
-        <v>1240</v>
-      </c>
-      <c r="D432" s="28" t="s">
-        <v>1241</v>
       </c>
       <c r="E432" s="1"/>
       <c r="F432" s="8" t="s">
-        <v>1217</v>
+        <v>1215</v>
       </c>
       <c r="G432" s="6"/>
       <c r="H432" s="6"/>
@@ -18877,17 +18896,17 @@
         <v>165</v>
       </c>
       <c r="B433" s="1" t="s">
+        <v>1240</v>
+      </c>
+      <c r="C433" s="8" t="s">
+        <v>1241</v>
+      </c>
+      <c r="D433" s="37" t="s">
         <v>1242</v>
-      </c>
-      <c r="C433" s="8" t="s">
-        <v>1243</v>
-      </c>
-      <c r="D433" s="37" t="s">
-        <v>1244</v>
       </c>
       <c r="E433" s="1"/>
       <c r="F433" s="8" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="G433" s="6"/>
       <c r="H433" s="6"/>
@@ -18906,17 +18925,17 @@
         <v>165</v>
       </c>
       <c r="B434" s="1" t="s">
+        <v>1244</v>
+      </c>
+      <c r="C434" s="8" t="s">
+        <v>1245</v>
+      </c>
+      <c r="D434" s="28" t="s">
         <v>1246</v>
-      </c>
-      <c r="C434" s="8" t="s">
-        <v>1247</v>
-      </c>
-      <c r="D434" s="28" t="s">
-        <v>1248</v>
       </c>
       <c r="E434" s="1"/>
       <c r="F434" s="8" t="s">
-        <v>1249</v>
+        <v>1247</v>
       </c>
       <c r="G434" s="6"/>
       <c r="H434" s="6"/>
@@ -18935,17 +18954,17 @@
         <v>165</v>
       </c>
       <c r="B435" s="1" t="s">
+        <v>1248</v>
+      </c>
+      <c r="C435" s="8" t="s">
+        <v>1249</v>
+      </c>
+      <c r="D435" s="28" t="s">
         <v>1250</v>
-      </c>
-      <c r="C435" s="8" t="s">
-        <v>1251</v>
-      </c>
-      <c r="D435" s="28" t="s">
-        <v>1252</v>
       </c>
       <c r="E435" s="1"/>
       <c r="F435" s="8" t="s">
-        <v>1217</v>
+        <v>1215</v>
       </c>
       <c r="G435" s="6"/>
       <c r="H435" s="6"/>
@@ -18964,7 +18983,7 @@
         <v>60</v>
       </c>
       <c r="B436" s="3" t="s">
-        <v>1253</v>
+        <v>1251</v>
       </c>
       <c r="C436" s="1"/>
       <c r="D436" s="1"/>
@@ -18976,7 +18995,7 @@
       <c r="J436" s="1"/>
       <c r="K436" s="1"/>
       <c r="L436" s="4" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="M436" s="6"/>
       <c r="N436" s="6"/>
@@ -18989,17 +19008,17 @@
         <v>137</v>
       </c>
       <c r="B437" s="1" t="s">
+        <v>1253</v>
+      </c>
+      <c r="C437" s="8" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D437" s="18" t="s">
         <v>1255</v>
-      </c>
-      <c r="C437" s="8" t="s">
-        <v>1256</v>
-      </c>
-      <c r="D437" s="18" t="s">
-        <v>1257</v>
       </c>
       <c r="E437" s="1"/>
       <c r="F437" s="8" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
       <c r="G437" s="6"/>
       <c r="H437" s="1"/>
@@ -19018,7 +19037,7 @@
         <v>53</v>
       </c>
       <c r="B438" s="3" t="s">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="C438" s="3"/>
       <c r="D438" s="3"/>
@@ -19041,13 +19060,13 @@
         <v>19</v>
       </c>
       <c r="B439" s="3" t="s">
+        <v>1257</v>
+      </c>
+      <c r="C439" s="3" t="s">
+        <v>1258</v>
+      </c>
+      <c r="D439" s="3" t="s">
         <v>1259</v>
-      </c>
-      <c r="C439" s="3" t="s">
-        <v>1260</v>
-      </c>
-      <c r="D439" s="3" t="s">
-        <v>1261</v>
       </c>
       <c r="E439" s="1"/>
       <c r="F439" s="12" t="s">
@@ -19072,7 +19091,7 @@
         <v>137</v>
       </c>
       <c r="B440" s="3" t="s">
-        <v>1262</v>
+        <v>1260</v>
       </c>
       <c r="C440" s="3" t="s">
         <v>731</v>
@@ -19099,13 +19118,13 @@
         <v>165</v>
       </c>
       <c r="B441" s="1" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C441" s="4" t="s">
+        <v>1262</v>
+      </c>
+      <c r="D441" s="7" t="s">
         <v>1263</v>
-      </c>
-      <c r="C441" s="4" t="s">
-        <v>1264</v>
-      </c>
-      <c r="D441" s="7" t="s">
-        <v>1265</v>
       </c>
       <c r="E441" s="1" t="s">
         <v>169</v>
@@ -19128,7 +19147,7 @@
         <v>137</v>
       </c>
       <c r="B442" s="3" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="C442" s="3" t="s">
         <v>731</v>
@@ -19138,7 +19157,7 @@
       </c>
       <c r="E442" s="1"/>
       <c r="F442" s="9" t="s">
-        <v>1267</v>
+        <v>1265</v>
       </c>
       <c r="G442" s="1"/>
       <c r="H442" s="1"/>
@@ -19157,19 +19176,19 @@
         <v>165</v>
       </c>
       <c r="B443" s="1" t="s">
+        <v>1266</v>
+      </c>
+      <c r="C443" s="4" t="s">
+        <v>1267</v>
+      </c>
+      <c r="D443" s="3" t="s">
         <v>1268</v>
-      </c>
-      <c r="C443" s="4" t="s">
-        <v>1269</v>
-      </c>
-      <c r="D443" s="3" t="s">
-        <v>1270</v>
       </c>
       <c r="E443" s="1" t="s">
         <v>169</v>
       </c>
       <c r="F443" s="9" t="s">
-        <v>1267</v>
+        <v>1265</v>
       </c>
       <c r="G443" s="6"/>
       <c r="H443" s="1"/>
@@ -19188,17 +19207,17 @@
         <v>137</v>
       </c>
       <c r="B444" s="3" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="C444" s="3" t="s">
-        <v>1272</v>
+        <v>1270</v>
       </c>
       <c r="D444" s="3" t="s">
-        <v>1272</v>
+        <v>1270</v>
       </c>
       <c r="E444" s="1"/>
       <c r="F444" s="8" t="s">
-        <v>1273</v>
+        <v>1271</v>
       </c>
       <c r="G444" s="6"/>
       <c r="H444" s="1"/>
@@ -19214,22 +19233,22 @@
     </row>
     <row r="445" spans="1:17" ht="15.75" customHeight="1">
       <c r="A445" s="3" t="s">
+        <v>1272</v>
+      </c>
+      <c r="B445" s="1" t="s">
+        <v>1273</v>
+      </c>
+      <c r="C445" s="4" t="s">
         <v>1274</v>
       </c>
-      <c r="B445" s="1" t="s">
+      <c r="D445" s="3" t="s">
         <v>1275</v>
-      </c>
-      <c r="C445" s="4" t="s">
-        <v>1276</v>
-      </c>
-      <c r="D445" s="3" t="s">
-        <v>1277</v>
       </c>
       <c r="E445" s="1" t="s">
         <v>169</v>
       </c>
       <c r="F445" s="8" t="s">
-        <v>1273</v>
+        <v>1271</v>
       </c>
       <c r="G445" s="6"/>
       <c r="H445" s="1"/>
@@ -19248,7 +19267,7 @@
         <v>53</v>
       </c>
       <c r="B446" s="3" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="C446" s="3"/>
       <c r="D446" s="3"/>
@@ -19271,17 +19290,17 @@
         <v>19</v>
       </c>
       <c r="B447" s="1" t="s">
+        <v>1276</v>
+      </c>
+      <c r="C447" s="3" t="s">
+        <v>1277</v>
+      </c>
+      <c r="D447" s="3" t="s">
         <v>1278</v>
-      </c>
-      <c r="C447" s="3" t="s">
-        <v>1279</v>
-      </c>
-      <c r="D447" s="3" t="s">
-        <v>1280</v>
       </c>
       <c r="E447" s="1"/>
       <c r="F447" s="3" t="s">
-        <v>1281</v>
+        <v>1279</v>
       </c>
       <c r="G447" s="1" t="s">
         <v>145</v>
@@ -19302,13 +19321,13 @@
         <v>137</v>
       </c>
       <c r="B448" s="1" t="s">
+        <v>1280</v>
+      </c>
+      <c r="C448" s="8" t="s">
+        <v>1281</v>
+      </c>
+      <c r="D448" s="18" t="s">
         <v>1282</v>
-      </c>
-      <c r="C448" s="8" t="s">
-        <v>1283</v>
-      </c>
-      <c r="D448" s="18" t="s">
-        <v>1284</v>
       </c>
       <c r="E448" s="6"/>
       <c r="F448" s="6"/>
@@ -19329,19 +19348,19 @@
         <v>165</v>
       </c>
       <c r="B449" s="1" t="s">
+        <v>1283</v>
+      </c>
+      <c r="C449" s="8" t="s">
+        <v>1284</v>
+      </c>
+      <c r="D449" s="3" t="s">
         <v>1285</v>
-      </c>
-      <c r="C449" s="8" t="s">
-        <v>1286</v>
-      </c>
-      <c r="D449" s="3" t="s">
-        <v>1287</v>
       </c>
       <c r="E449" s="1" t="s">
         <v>169</v>
       </c>
       <c r="F449" s="8" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
       <c r="G449" s="6"/>
       <c r="H449" s="1"/>
@@ -19357,22 +19376,22 @@
     </row>
     <row r="450" spans="1:26" ht="15.75" customHeight="1">
       <c r="A450" s="3" t="s">
+        <v>1287</v>
+      </c>
+      <c r="B450" s="1" t="s">
+        <v>1288</v>
+      </c>
+      <c r="C450" s="8" t="s">
         <v>1289</v>
       </c>
-      <c r="B450" s="1" t="s">
+      <c r="D450" s="3" t="s">
         <v>1290</v>
-      </c>
-      <c r="C450" s="8" t="s">
-        <v>1291</v>
-      </c>
-      <c r="D450" s="3" t="s">
-        <v>1292</v>
       </c>
       <c r="E450" s="1" t="s">
         <v>169</v>
       </c>
       <c r="F450" s="4" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="G450" s="1"/>
       <c r="H450" s="1"/>
@@ -19391,17 +19410,17 @@
         <v>137</v>
       </c>
       <c r="B451" s="1" t="s">
+        <v>1292</v>
+      </c>
+      <c r="C451" s="8" t="s">
+        <v>1293</v>
+      </c>
+      <c r="D451" s="18" t="s">
         <v>1294</v>
-      </c>
-      <c r="C451" s="8" t="s">
-        <v>1295</v>
-      </c>
-      <c r="D451" s="18" t="s">
-        <v>1296</v>
       </c>
       <c r="E451" s="1"/>
       <c r="F451" s="4" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
       <c r="G451" s="1"/>
       <c r="H451" s="1"/>
@@ -19420,13 +19439,13 @@
         <v>137</v>
       </c>
       <c r="B452" s="1" t="s">
+        <v>1296</v>
+      </c>
+      <c r="C452" s="8" t="s">
+        <v>1297</v>
+      </c>
+      <c r="D452" s="18" t="s">
         <v>1298</v>
-      </c>
-      <c r="C452" s="8" t="s">
-        <v>1299</v>
-      </c>
-      <c r="D452" s="18" t="s">
-        <v>1300</v>
       </c>
       <c r="E452" s="6"/>
       <c r="F452" s="6"/>
@@ -19447,7 +19466,7 @@
         <v>53</v>
       </c>
       <c r="B453" s="1" t="s">
-        <v>1278</v>
+        <v>1276</v>
       </c>
       <c r="C453" s="1"/>
       <c r="D453" s="1"/>
@@ -19470,13 +19489,13 @@
         <v>19</v>
       </c>
       <c r="B454" s="1" t="s">
+        <v>1299</v>
+      </c>
+      <c r="C454" s="3" t="s">
+        <v>1300</v>
+      </c>
+      <c r="D454" s="3" t="s">
         <v>1301</v>
-      </c>
-      <c r="C454" s="3" t="s">
-        <v>1302</v>
-      </c>
-      <c r="D454" s="3" t="s">
-        <v>1303</v>
       </c>
       <c r="E454" s="1"/>
       <c r="F454" s="3" t="s">
@@ -19501,13 +19520,13 @@
         <v>137</v>
       </c>
       <c r="B455" s="1" t="s">
+        <v>1302</v>
+      </c>
+      <c r="C455" s="8" t="s">
+        <v>1303</v>
+      </c>
+      <c r="D455" s="18" t="s">
         <v>1304</v>
-      </c>
-      <c r="C455" s="8" t="s">
-        <v>1305</v>
-      </c>
-      <c r="D455" s="18" t="s">
-        <v>1306</v>
       </c>
       <c r="E455" s="6"/>
       <c r="F455" s="6"/>
@@ -19528,13 +19547,13 @@
         <v>165</v>
       </c>
       <c r="B456" s="1" t="s">
+        <v>1305</v>
+      </c>
+      <c r="C456" s="8" t="s">
+        <v>1306</v>
+      </c>
+      <c r="D456" s="3" t="s">
         <v>1307</v>
-      </c>
-      <c r="C456" s="8" t="s">
-        <v>1308</v>
-      </c>
-      <c r="D456" s="3" t="s">
-        <v>1309</v>
       </c>
       <c r="E456" s="1" t="s">
         <v>169</v>
@@ -19557,17 +19576,17 @@
         <v>137</v>
       </c>
       <c r="B457" s="1" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C457" s="8" t="s">
+        <v>1309</v>
+      </c>
+      <c r="D457" s="18" t="s">
         <v>1310</v>
-      </c>
-      <c r="C457" s="8" t="s">
-        <v>1311</v>
-      </c>
-      <c r="D457" s="18" t="s">
-        <v>1312</v>
       </c>
       <c r="E457" s="1"/>
       <c r="F457" s="3" t="s">
-        <v>1313</v>
+        <v>1311</v>
       </c>
       <c r="G457" s="1"/>
       <c r="H457" s="1"/>
@@ -19586,7 +19605,7 @@
         <v>53</v>
       </c>
       <c r="B458" s="1" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
       <c r="C458" s="1"/>
       <c r="D458" s="1"/>
@@ -19609,17 +19628,17 @@
         <v>19</v>
       </c>
       <c r="B459" s="38" t="s">
+        <v>1312</v>
+      </c>
+      <c r="C459" s="3" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D459" s="3" t="s">
         <v>1314</v>
-      </c>
-      <c r="C459" s="3" t="s">
-        <v>1315</v>
-      </c>
-      <c r="D459" s="3" t="s">
-        <v>1316</v>
       </c>
       <c r="E459" s="1"/>
       <c r="F459" s="3" t="s">
-        <v>1317</v>
+        <v>1315</v>
       </c>
       <c r="G459" s="20" t="s">
         <v>145</v>
@@ -19649,17 +19668,17 @@
         <v>137</v>
       </c>
       <c r="B460" s="38" t="s">
+        <v>1316</v>
+      </c>
+      <c r="C460" s="3" t="s">
+        <v>1317</v>
+      </c>
+      <c r="D460" s="8" t="s">
         <v>1318</v>
-      </c>
-      <c r="C460" s="3" t="s">
-        <v>1319</v>
-      </c>
-      <c r="D460" s="8" t="s">
-        <v>1320</v>
       </c>
       <c r="E460" s="6"/>
       <c r="F460" s="12" t="s">
-        <v>1321</v>
+        <v>1319</v>
       </c>
       <c r="G460" s="39"/>
       <c r="H460" s="6"/>
@@ -19687,17 +19706,17 @@
         <v>137</v>
       </c>
       <c r="B461" s="7" t="s">
+        <v>1320</v>
+      </c>
+      <c r="C461" s="3" t="s">
+        <v>1321</v>
+      </c>
+      <c r="D461" s="3" t="s">
         <v>1322</v>
-      </c>
-      <c r="C461" s="3" t="s">
-        <v>1323</v>
-      </c>
-      <c r="D461" s="3" t="s">
-        <v>1324</v>
       </c>
       <c r="E461" s="1"/>
       <c r="F461" s="12" t="s">
-        <v>1325</v>
+        <v>1323</v>
       </c>
       <c r="G461" s="20"/>
       <c r="H461" s="1"/>
@@ -19725,7 +19744,7 @@
         <v>53</v>
       </c>
       <c r="B462" s="38" t="s">
-        <v>1314</v>
+        <v>1312</v>
       </c>
       <c r="C462" s="20"/>
       <c r="D462" s="20"/>
@@ -19757,13 +19776,13 @@
         <v>19</v>
       </c>
       <c r="B463" s="2" t="s">
+        <v>1324</v>
+      </c>
+      <c r="C463" s="2" t="s">
+        <v>1325</v>
+      </c>
+      <c r="D463" s="2" t="s">
         <v>1326</v>
-      </c>
-      <c r="C463" s="2" t="s">
-        <v>1327</v>
-      </c>
-      <c r="D463" s="2" t="s">
-        <v>1328</v>
       </c>
       <c r="G463" s="2" t="s">
         <v>145</v>
@@ -19774,16 +19793,16 @@
         <v>137</v>
       </c>
       <c r="B464" s="2" t="s">
+        <v>1327</v>
+      </c>
+      <c r="C464" s="2" t="s">
+        <v>1328</v>
+      </c>
+      <c r="D464" s="2" t="s">
         <v>1329</v>
       </c>
-      <c r="C464" s="2" t="s">
+      <c r="F464" s="2" t="s">
         <v>1330</v>
-      </c>
-      <c r="D464" s="2" t="s">
-        <v>1331</v>
-      </c>
-      <c r="F464" s="2" t="s">
-        <v>1332</v>
       </c>
     </row>
     <row r="465" spans="1:12" ht="15.75" customHeight="1">
@@ -19791,10 +19810,10 @@
         <v>60</v>
       </c>
       <c r="B465" s="2" t="s">
-        <v>1333</v>
+        <v>1331</v>
       </c>
       <c r="L465" s="2" t="s">
-        <v>1334</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="466" spans="1:12" ht="13">
@@ -19802,16 +19821,16 @@
         <v>137</v>
       </c>
       <c r="B466" s="2" t="s">
+        <v>1333</v>
+      </c>
+      <c r="C466" s="2" t="s">
+        <v>1334</v>
+      </c>
+      <c r="D466" s="2" t="s">
         <v>1335</v>
       </c>
-      <c r="C466" s="2" t="s">
+      <c r="F466" s="2" t="s">
         <v>1336</v>
-      </c>
-      <c r="D466" s="2" t="s">
-        <v>1337</v>
-      </c>
-      <c r="F466" s="2" t="s">
-        <v>1338</v>
       </c>
     </row>
     <row r="467" spans="1:12" ht="13">
@@ -19819,16 +19838,16 @@
         <v>137</v>
       </c>
       <c r="B467" s="2" t="s">
+        <v>1337</v>
+      </c>
+      <c r="C467" s="2" t="s">
+        <v>1338</v>
+      </c>
+      <c r="D467" s="2" t="s">
         <v>1339</v>
       </c>
-      <c r="C467" s="2" t="s">
+      <c r="F467" s="2" t="s">
         <v>1340</v>
-      </c>
-      <c r="D467" s="2" t="s">
-        <v>1341</v>
-      </c>
-      <c r="F467" s="2" t="s">
-        <v>1342</v>
       </c>
     </row>
     <row r="468" spans="1:12" ht="14.25">
@@ -19836,19 +19855,19 @@
         <v>137</v>
       </c>
       <c r="B468" s="2" t="s">
+        <v>1341</v>
+      </c>
+      <c r="C468" s="2" t="s">
+        <v>1342</v>
+      </c>
+      <c r="D468" s="2" t="s">
         <v>1343</v>
       </c>
-      <c r="C468" s="2" t="s">
+      <c r="F468" s="40" t="s">
         <v>1344</v>
       </c>
-      <c r="D468" s="2" t="s">
+      <c r="G468" s="2" t="s">
         <v>1345</v>
-      </c>
-      <c r="F468" s="40" t="s">
-        <v>1346</v>
-      </c>
-      <c r="G468" s="2" t="s">
-        <v>1347</v>
       </c>
     </row>
     <row r="469" spans="1:12" ht="14.25">
@@ -19856,19 +19875,19 @@
         <v>137</v>
       </c>
       <c r="B469" s="2" t="s">
+        <v>1346</v>
+      </c>
+      <c r="C469" s="2" t="s">
+        <v>1347</v>
+      </c>
+      <c r="D469" s="2" t="s">
         <v>1348</v>
-      </c>
-      <c r="C469" s="2" t="s">
-        <v>1349</v>
-      </c>
-      <c r="D469" s="2" t="s">
-        <v>1350</v>
       </c>
       <c r="F469" s="40" t="s">
         <v>279</v>
       </c>
       <c r="G469" s="2" t="s">
-        <v>1347</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="470" spans="1:12" ht="14.25">
@@ -19876,19 +19895,19 @@
         <v>137</v>
       </c>
       <c r="B470" s="2" t="s">
+        <v>1349</v>
+      </c>
+      <c r="C470" s="2" t="s">
+        <v>1350</v>
+      </c>
+      <c r="D470" s="2" t="s">
         <v>1351</v>
-      </c>
-      <c r="C470" s="2" t="s">
-        <v>1352</v>
-      </c>
-      <c r="D470" s="2" t="s">
-        <v>1353</v>
       </c>
       <c r="F470" s="40" t="s">
         <v>328</v>
       </c>
       <c r="G470" s="2" t="s">
-        <v>1347</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="471" spans="1:12" ht="14.25">
@@ -19896,19 +19915,19 @@
         <v>137</v>
       </c>
       <c r="B471" s="2" t="s">
+        <v>1352</v>
+      </c>
+      <c r="C471" s="2" t="s">
+        <v>1353</v>
+      </c>
+      <c r="D471" s="2" t="s">
         <v>1354</v>
-      </c>
-      <c r="C471" s="2" t="s">
-        <v>1355</v>
-      </c>
-      <c r="D471" s="2" t="s">
-        <v>1356</v>
       </c>
       <c r="F471" s="40" t="s">
         <v>361</v>
       </c>
       <c r="G471" s="2" t="s">
-        <v>1347</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="472" spans="1:12" ht="14.25">
@@ -19916,19 +19935,19 @@
         <v>137</v>
       </c>
       <c r="B472" s="2" t="s">
+        <v>1355</v>
+      </c>
+      <c r="C472" s="2" t="s">
+        <v>1356</v>
+      </c>
+      <c r="D472" s="2" t="s">
         <v>1357</v>
-      </c>
-      <c r="C472" s="2" t="s">
-        <v>1358</v>
-      </c>
-      <c r="D472" s="2" t="s">
-        <v>1359</v>
       </c>
       <c r="F472" s="40" t="s">
         <v>391</v>
       </c>
       <c r="G472" s="2" t="s">
-        <v>1347</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="473" spans="1:12" ht="14.25">
@@ -19936,19 +19955,19 @@
         <v>137</v>
       </c>
       <c r="B473" s="2" t="s">
+        <v>1358</v>
+      </c>
+      <c r="C473" s="2" t="s">
+        <v>1359</v>
+      </c>
+      <c r="D473" s="2" t="s">
         <v>1360</v>
       </c>
-      <c r="C473" s="2" t="s">
+      <c r="F473" s="40" t="s">
         <v>1361</v>
       </c>
-      <c r="D473" s="2" t="s">
-        <v>1362</v>
-      </c>
-      <c r="F473" s="40" t="s">
-        <v>1363</v>
-      </c>
       <c r="G473" s="2" t="s">
-        <v>1347</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="474" spans="1:12" ht="14.25">
@@ -19956,19 +19975,19 @@
         <v>137</v>
       </c>
       <c r="B474" s="2" t="s">
+        <v>1362</v>
+      </c>
+      <c r="C474" s="2" t="s">
+        <v>1363</v>
+      </c>
+      <c r="D474" s="2" t="s">
         <v>1364</v>
       </c>
-      <c r="C474" s="2" t="s">
+      <c r="F474" s="40" t="s">
         <v>1365</v>
       </c>
-      <c r="D474" s="2" t="s">
-        <v>1366</v>
-      </c>
-      <c r="F474" s="40" t="s">
-        <v>1367</v>
-      </c>
       <c r="G474" s="2" t="s">
-        <v>1347</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="475" spans="1:12" ht="14.25">
@@ -19976,19 +19995,19 @@
         <v>137</v>
       </c>
       <c r="B475" s="2" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C475" s="2" t="s">
+        <v>1367</v>
+      </c>
+      <c r="D475" s="2" t="s">
         <v>1368</v>
       </c>
-      <c r="C475" s="2" t="s">
+      <c r="F475" s="40" t="s">
         <v>1369</v>
       </c>
-      <c r="D475" s="2" t="s">
-        <v>1370</v>
-      </c>
-      <c r="F475" s="40" t="s">
-        <v>1371</v>
-      </c>
       <c r="G475" s="2" t="s">
-        <v>1347</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="476" spans="1:12" ht="14.25">
@@ -19996,19 +20015,19 @@
         <v>137</v>
       </c>
       <c r="B476" s="2" t="s">
+        <v>1370</v>
+      </c>
+      <c r="C476" s="2" t="s">
+        <v>1371</v>
+      </c>
+      <c r="D476" s="2" t="s">
         <v>1372</v>
       </c>
-      <c r="C476" s="2" t="s">
+      <c r="F476" s="40" t="s">
         <v>1373</v>
       </c>
-      <c r="D476" s="2" t="s">
-        <v>1374</v>
-      </c>
-      <c r="F476" s="40" t="s">
-        <v>1375</v>
-      </c>
       <c r="G476" s="2" t="s">
-        <v>1347</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="477" spans="1:12" ht="13">
@@ -20016,16 +20035,16 @@
         <v>137</v>
       </c>
       <c r="B477" s="2" t="s">
+        <v>1374</v>
+      </c>
+      <c r="C477" s="2" t="s">
+        <v>1375</v>
+      </c>
+      <c r="D477" s="2" t="s">
         <v>1376</v>
       </c>
-      <c r="C477" s="2" t="s">
-        <v>1377</v>
-      </c>
-      <c r="D477" s="2" t="s">
-        <v>1378</v>
-      </c>
       <c r="F477" s="2" t="s">
-        <v>1342</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="478" spans="1:12" ht="13">
@@ -20033,7 +20052,7 @@
         <v>53</v>
       </c>
       <c r="B478" s="2" t="s">
-        <v>1326</v>
+        <v>1324</v>
       </c>
     </row>
   </sheetData>
@@ -20053,7 +20072,7 @@
     <mergeCell ref="K291:L291"/>
     <mergeCell ref="F313:H313"/>
     <mergeCell ref="F314:H314"/>
-    <mergeCell ref="F328:I328"/>
+    <mergeCell ref="F329:I329"/>
     <mergeCell ref="K315:L315"/>
     <mergeCell ref="K318:L318"/>
     <mergeCell ref="K321:L321"/>
@@ -20085,7 +20104,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>1379</v>
+        <v>1377</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -20099,30 +20118,30 @@
     </row>
     <row r="2" spans="1:4" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>1380</v>
+        <v>1378</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>169</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>1381</v>
+        <v>1379</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>1382</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="15.75" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>1380</v>
+        <v>1378</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>1381</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>1382</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>1383</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>1384</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>1385</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15.75" customHeight="1">
@@ -20130,13 +20149,13 @@
         <v>179</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>1384</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>1385</v>
+      </c>
+      <c r="D4" s="37" t="s">
         <v>1386</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>1387</v>
-      </c>
-      <c r="D4" s="37" t="s">
-        <v>1388</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15.75" customHeight="1">
@@ -20144,13 +20163,13 @@
         <v>179</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>1387</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>1388</v>
+      </c>
+      <c r="D5" s="37" t="s">
         <v>1389</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>1390</v>
-      </c>
-      <c r="D5" s="37" t="s">
-        <v>1391</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15.75" customHeight="1">
@@ -20158,153 +20177,153 @@
         <v>179</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>1390</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>1391</v>
+      </c>
+      <c r="D6" s="37" t="s">
         <v>1392</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>1393</v>
-      </c>
-      <c r="D6" s="37" t="s">
-        <v>1394</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15.75" customHeight="1">
       <c r="A7" s="1" t="s">
+        <v>1393</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>1394</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>1395</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="D7" s="37" t="s">
         <v>1396</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>1397</v>
-      </c>
-      <c r="D7" s="37" t="s">
-        <v>1398</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15.75" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>1395</v>
+        <v>1393</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>1397</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>1398</v>
+      </c>
+      <c r="D8" s="37" t="s">
         <v>1399</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>1400</v>
-      </c>
-      <c r="D8" s="37" t="s">
-        <v>1401</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15.75" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>1395</v>
+        <v>1393</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>1401</v>
+      </c>
+      <c r="D9" s="37" t="s">
         <v>1402</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>1403</v>
-      </c>
-      <c r="D9" s="37" t="s">
-        <v>1404</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15.75" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>1403</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>1404</v>
+      </c>
+      <c r="D10" s="37" t="s">
         <v>1405</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>1406</v>
-      </c>
-      <c r="D10" s="37" t="s">
-        <v>1407</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="15.75" customHeight="1">
       <c r="A11" s="1" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>1406</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>1407</v>
+      </c>
+      <c r="D11" s="37" t="s">
         <v>1408</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>1409</v>
-      </c>
-      <c r="D11" s="37" t="s">
-        <v>1410</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15.75" customHeight="1">
       <c r="A12" s="1" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>1410</v>
+      </c>
+      <c r="D12" s="37" t="s">
         <v>1411</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>1412</v>
-      </c>
-      <c r="D12" s="37" t="s">
-        <v>1413</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="15.75" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>1413</v>
+      </c>
+      <c r="D13" s="37" t="s">
         <v>1414</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>1415</v>
-      </c>
-      <c r="D13" s="37" t="s">
-        <v>1416</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="15.75" customHeight="1">
       <c r="A14" s="1" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>1415</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>1416</v>
+      </c>
+      <c r="D14" s="37" t="s">
         <v>1417</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>1418</v>
-      </c>
-      <c r="D14" s="37" t="s">
-        <v>1419</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="15.75" customHeight="1">
       <c r="A15" s="1" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>1418</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>1419</v>
+      </c>
+      <c r="D15" s="37" t="s">
         <v>1420</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>1421</v>
-      </c>
-      <c r="D15" s="37" t="s">
-        <v>1422</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="15.75" customHeight="1">
       <c r="A16" s="1" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>1421</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>1422</v>
+      </c>
+      <c r="D16" s="37" t="s">
         <v>1423</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>1424</v>
-      </c>
-      <c r="D16" s="37" t="s">
-        <v>1425</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="15.75" customHeight="1">
@@ -20312,13 +20331,13 @@
         <v>405</v>
       </c>
       <c r="B17" s="1" t="s">
+        <v>1424</v>
+      </c>
+      <c r="C17" s="41" t="s">
+        <v>1425</v>
+      </c>
+      <c r="D17" s="37" t="s">
         <v>1426</v>
-      </c>
-      <c r="C17" s="41" t="s">
-        <v>1427</v>
-      </c>
-      <c r="D17" s="37" t="s">
-        <v>1428</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="15.75" customHeight="1">
@@ -20326,13 +20345,13 @@
         <v>405</v>
       </c>
       <c r="B18" s="1" t="s">
+        <v>1427</v>
+      </c>
+      <c r="C18" s="42" t="s">
+        <v>1428</v>
+      </c>
+      <c r="D18" s="37" t="s">
         <v>1429</v>
-      </c>
-      <c r="C18" s="42" t="s">
-        <v>1430</v>
-      </c>
-      <c r="D18" s="37" t="s">
-        <v>1431</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="13">
@@ -20340,13 +20359,13 @@
         <v>405</v>
       </c>
       <c r="B19" s="1" t="s">
+        <v>1430</v>
+      </c>
+      <c r="C19" s="42" t="s">
+        <v>1431</v>
+      </c>
+      <c r="D19" s="37" t="s">
         <v>1432</v>
-      </c>
-      <c r="C19" s="42" t="s">
-        <v>1433</v>
-      </c>
-      <c r="D19" s="37" t="s">
-        <v>1434</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="13">
@@ -20354,13 +20373,13 @@
         <v>405</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>1433</v>
+      </c>
+      <c r="C20" s="41" t="s">
+        <v>1434</v>
+      </c>
+      <c r="D20" s="37" t="s">
         <v>1435</v>
-      </c>
-      <c r="C20" s="41" t="s">
-        <v>1436</v>
-      </c>
-      <c r="D20" s="37" t="s">
-        <v>1437</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="13">
@@ -20368,55 +20387,55 @@
         <v>405</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>1436</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>1437</v>
+      </c>
+      <c r="D21" s="37" t="s">
         <v>1438</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>1439</v>
-      </c>
-      <c r="D21" s="37" t="s">
-        <v>1440</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="13">
       <c r="A22" s="1" t="s">
+        <v>1439</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>1440</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>1441</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="D22" s="37" t="s">
         <v>1442</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>1443</v>
-      </c>
-      <c r="D22" s="37" t="s">
-        <v>1444</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="13">
       <c r="A23" s="1" t="s">
-        <v>1441</v>
+        <v>1439</v>
       </c>
       <c r="B23" s="1" t="s">
+        <v>1443</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>1444</v>
+      </c>
+      <c r="D23" s="37" t="s">
         <v>1445</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>1446</v>
-      </c>
-      <c r="D23" s="37" t="s">
-        <v>1447</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="13">
       <c r="A24" s="1" t="s">
-        <v>1441</v>
+        <v>1439</v>
       </c>
       <c r="B24" s="1" t="s">
+        <v>1446</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>1447</v>
+      </c>
+      <c r="D24" s="37" t="s">
         <v>1448</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>1449</v>
-      </c>
-      <c r="D24" s="37" t="s">
-        <v>1450</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="13">
@@ -20424,13 +20443,13 @@
         <v>438</v>
       </c>
       <c r="B25" s="1" t="s">
+        <v>1449</v>
+      </c>
+      <c r="C25" s="42" t="s">
+        <v>1450</v>
+      </c>
+      <c r="D25" s="37" t="s">
         <v>1451</v>
-      </c>
-      <c r="C25" s="42" t="s">
-        <v>1452</v>
-      </c>
-      <c r="D25" s="37" t="s">
-        <v>1453</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="13">
@@ -20438,97 +20457,97 @@
         <v>438</v>
       </c>
       <c r="B26" s="1" t="s">
+        <v>1452</v>
+      </c>
+      <c r="C26" s="42" t="s">
+        <v>1453</v>
+      </c>
+      <c r="D26" s="37" t="s">
         <v>1454</v>
-      </c>
-      <c r="C26" s="42" t="s">
-        <v>1455</v>
-      </c>
-      <c r="D26" s="37" t="s">
-        <v>1456</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="13">
       <c r="A27" s="1" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="B27" s="1" t="s">
+        <v>1455</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>1456</v>
+      </c>
+      <c r="D27" s="37" t="s">
         <v>1457</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>1458</v>
-      </c>
-      <c r="D27" s="37" t="s">
-        <v>1459</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="13">
       <c r="A28" s="1" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="B28" s="1" t="s">
+        <v>1458</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>1459</v>
+      </c>
+      <c r="D28" s="37" t="s">
         <v>1460</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>1461</v>
-      </c>
-      <c r="D28" s="37" t="s">
-        <v>1462</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="13">
       <c r="A29" s="1" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="B29" s="1" t="s">
+        <v>1461</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>1462</v>
+      </c>
+      <c r="D29" s="37" t="s">
         <v>1463</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>1464</v>
-      </c>
-      <c r="D29" s="37" t="s">
-        <v>1465</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="13">
       <c r="A30" s="3" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="B30" s="3" t="s">
+        <v>1464</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>1465</v>
+      </c>
+      <c r="D30" s="37" t="s">
         <v>1466</v>
-      </c>
-      <c r="C30" s="8" t="s">
-        <v>1467</v>
-      </c>
-      <c r="D30" s="37" t="s">
-        <v>1468</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="13">
       <c r="A31" s="3" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="B31" s="3" t="s">
+        <v>1467</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>1468</v>
+      </c>
+      <c r="D31" s="37" t="s">
         <v>1469</v>
-      </c>
-      <c r="C31" s="8" t="s">
-        <v>1470</v>
-      </c>
-      <c r="D31" s="37" t="s">
-        <v>1471</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="13">
       <c r="A32" s="3" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="B32" s="3" t="s">
+        <v>1470</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>1471</v>
+      </c>
+      <c r="D32" s="37" t="s">
         <v>1472</v>
-      </c>
-      <c r="C32" s="8" t="s">
-        <v>1473</v>
-      </c>
-      <c r="D32" s="37" t="s">
-        <v>1474</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="13">
@@ -20536,13 +20555,13 @@
         <v>488</v>
       </c>
       <c r="B33" s="1" t="s">
+        <v>1473</v>
+      </c>
+      <c r="C33" s="41" t="s">
+        <v>1474</v>
+      </c>
+      <c r="D33" s="37" t="s">
         <v>1475</v>
-      </c>
-      <c r="C33" s="41" t="s">
-        <v>1476</v>
-      </c>
-      <c r="D33" s="37" t="s">
-        <v>1477</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="13">
@@ -20550,13 +20569,13 @@
         <v>488</v>
       </c>
       <c r="B34" s="1" t="s">
+        <v>1476</v>
+      </c>
+      <c r="C34" s="41" t="s">
+        <v>1477</v>
+      </c>
+      <c r="D34" s="37" t="s">
         <v>1478</v>
-      </c>
-      <c r="C34" s="41" t="s">
-        <v>1479</v>
-      </c>
-      <c r="D34" s="37" t="s">
-        <v>1480</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="13">
@@ -20564,13 +20583,13 @@
         <v>488</v>
       </c>
       <c r="B35" s="1" t="s">
+        <v>1479</v>
+      </c>
+      <c r="C35" s="41" t="s">
+        <v>1480</v>
+      </c>
+      <c r="D35" s="37" t="s">
         <v>1481</v>
-      </c>
-      <c r="C35" s="41" t="s">
-        <v>1482</v>
-      </c>
-      <c r="D35" s="37" t="s">
-        <v>1483</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="13">
@@ -20578,815 +20597,815 @@
         <v>488</v>
       </c>
       <c r="B36" s="1" t="s">
+        <v>1482</v>
+      </c>
+      <c r="C36" s="41" t="s">
+        <v>1483</v>
+      </c>
+      <c r="D36" s="37" t="s">
         <v>1484</v>
-      </c>
-      <c r="C36" s="41" t="s">
-        <v>1485</v>
-      </c>
-      <c r="D36" s="37" t="s">
-        <v>1486</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="13">
       <c r="A37" s="1" t="s">
+        <v>1485</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>1486</v>
+      </c>
+      <c r="C37" s="41" t="s">
         <v>1487</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="D37" s="28" t="s">
         <v>1488</v>
-      </c>
-      <c r="C37" s="41" t="s">
-        <v>1489</v>
-      </c>
-      <c r="D37" s="28" t="s">
-        <v>1490</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="13">
       <c r="A38" s="1" t="s">
-        <v>1487</v>
+        <v>1485</v>
       </c>
       <c r="B38" s="1" t="s">
+        <v>1489</v>
+      </c>
+      <c r="C38" s="41" t="s">
+        <v>1490</v>
+      </c>
+      <c r="D38" s="37" t="s">
         <v>1491</v>
-      </c>
-      <c r="C38" s="41" t="s">
-        <v>1492</v>
-      </c>
-      <c r="D38" s="37" t="s">
-        <v>1493</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="13">
       <c r="A39" s="1" t="s">
-        <v>1487</v>
+        <v>1485</v>
       </c>
       <c r="B39" s="1" t="s">
+        <v>1492</v>
+      </c>
+      <c r="C39" s="41" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D39" s="37" t="s">
         <v>1494</v>
-      </c>
-      <c r="C39" s="41" t="s">
-        <v>1495</v>
-      </c>
-      <c r="D39" s="37" t="s">
-        <v>1496</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="13">
       <c r="A40" s="1" t="s">
-        <v>1487</v>
+        <v>1485</v>
       </c>
       <c r="B40" s="1" t="s">
+        <v>1495</v>
+      </c>
+      <c r="C40" s="41" t="s">
+        <v>1496</v>
+      </c>
+      <c r="D40" s="37" t="s">
         <v>1497</v>
-      </c>
-      <c r="C40" s="41" t="s">
-        <v>1498</v>
-      </c>
-      <c r="D40" s="37" t="s">
-        <v>1499</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="13">
       <c r="A41" s="1" t="s">
-        <v>1487</v>
+        <v>1485</v>
       </c>
       <c r="B41" s="1" t="s">
+        <v>1498</v>
+      </c>
+      <c r="C41" s="42" t="s">
+        <v>1499</v>
+      </c>
+      <c r="D41" s="37" t="s">
         <v>1500</v>
-      </c>
-      <c r="C41" s="42" t="s">
-        <v>1501</v>
-      </c>
-      <c r="D41" s="37" t="s">
-        <v>1502</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="13">
       <c r="A42" s="1" t="s">
-        <v>1487</v>
+        <v>1485</v>
       </c>
       <c r="B42" s="1" t="s">
+        <v>1501</v>
+      </c>
+      <c r="C42" s="41" t="s">
+        <v>1502</v>
+      </c>
+      <c r="D42" s="37" t="s">
         <v>1503</v>
-      </c>
-      <c r="C42" s="41" t="s">
-        <v>1504</v>
-      </c>
-      <c r="D42" s="37" t="s">
-        <v>1505</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="13">
       <c r="A43" s="1" t="s">
-        <v>1487</v>
+        <v>1485</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>1408</v>
+        <v>1406</v>
       </c>
       <c r="C43" s="41" t="s">
-        <v>1506</v>
+        <v>1504</v>
       </c>
       <c r="D43" s="37" t="s">
-        <v>1507</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="13">
       <c r="A44" s="1" t="s">
-        <v>1487</v>
+        <v>1485</v>
       </c>
       <c r="B44" s="1" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C44" s="42" t="s">
+        <v>1507</v>
+      </c>
+      <c r="D44" s="37" t="s">
         <v>1508</v>
-      </c>
-      <c r="C44" s="42" t="s">
-        <v>1509</v>
-      </c>
-      <c r="D44" s="37" t="s">
-        <v>1510</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="13">
       <c r="A45" s="1" t="s">
+        <v>1509</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>1464</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>1510</v>
+      </c>
+      <c r="D45" s="37" t="s">
         <v>1511</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>1466</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>1512</v>
-      </c>
-      <c r="D45" s="37" t="s">
-        <v>1513</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="13">
       <c r="A46" s="1" t="s">
-        <v>1511</v>
+        <v>1509</v>
       </c>
       <c r="B46" s="1" t="s">
+        <v>1512</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>1513</v>
+      </c>
+      <c r="D46" s="37" t="s">
         <v>1514</v>
-      </c>
-      <c r="C46" s="4" t="s">
-        <v>1515</v>
-      </c>
-      <c r="D46" s="37" t="s">
-        <v>1516</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="13">
       <c r="A47" s="1" t="s">
-        <v>1511</v>
+        <v>1509</v>
       </c>
       <c r="B47" s="1" t="s">
+        <v>1515</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>1516</v>
+      </c>
+      <c r="D47" s="37" t="s">
         <v>1517</v>
-      </c>
-      <c r="C47" s="4" t="s">
-        <v>1518</v>
-      </c>
-      <c r="D47" s="37" t="s">
-        <v>1519</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="13">
       <c r="A48" s="1" t="s">
-        <v>1511</v>
+        <v>1509</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>1472</v>
+        <v>1470</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>1520</v>
+        <v>1518</v>
       </c>
       <c r="D48" s="37" t="s">
-        <v>1521</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="13">
       <c r="A49" s="1" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="B49" s="1" t="s">
+        <v>1520</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>1521</v>
+      </c>
+      <c r="D49" s="37" t="s">
         <v>1522</v>
-      </c>
-      <c r="C49" s="4" t="s">
-        <v>1523</v>
-      </c>
-      <c r="D49" s="37" t="s">
-        <v>1524</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="13">
       <c r="A50" s="1" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="B50" s="1" t="s">
+        <v>1523</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>1524</v>
+      </c>
+      <c r="D50" s="37" t="s">
         <v>1525</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>1526</v>
-      </c>
-      <c r="D50" s="37" t="s">
-        <v>1527</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="13">
       <c r="A51" s="1" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>1466</v>
+        <v>1464</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>1528</v>
+        <v>1526</v>
       </c>
       <c r="D51" s="37" t="s">
-        <v>1529</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="13">
       <c r="A52" s="1" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="B52" s="1" t="s">
+        <v>1528</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>1529</v>
+      </c>
+      <c r="D52" s="37" t="s">
         <v>1530</v>
-      </c>
-      <c r="C52" s="4" t="s">
-        <v>1531</v>
-      </c>
-      <c r="D52" s="37" t="s">
-        <v>1532</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="13">
       <c r="A53" s="1" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="B53" s="1" t="s">
+        <v>1531</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>1532</v>
+      </c>
+      <c r="D53" s="37" t="s">
         <v>1533</v>
-      </c>
-      <c r="C53" s="4" t="s">
-        <v>1534</v>
-      </c>
-      <c r="D53" s="37" t="s">
-        <v>1535</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="13">
       <c r="A54" s="1" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="B54" s="1" t="s">
+        <v>1534</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>1535</v>
+      </c>
+      <c r="D54" s="37" t="s">
         <v>1536</v>
-      </c>
-      <c r="C54" s="4" t="s">
-        <v>1537</v>
-      </c>
-      <c r="D54" s="37" t="s">
-        <v>1538</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="13">
       <c r="A55" s="1" t="s">
+        <v>1537</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>1538</v>
+      </c>
+      <c r="C55" s="41" t="s">
         <v>1539</v>
       </c>
-      <c r="B55" s="1" t="s">
+      <c r="D55" s="37" t="s">
         <v>1540</v>
-      </c>
-      <c r="C55" s="41" t="s">
-        <v>1541</v>
-      </c>
-      <c r="D55" s="37" t="s">
-        <v>1542</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="13">
       <c r="A56" s="1" t="s">
-        <v>1539</v>
+        <v>1537</v>
       </c>
       <c r="B56" s="1" t="s">
+        <v>1541</v>
+      </c>
+      <c r="C56" s="42" t="s">
+        <v>1542</v>
+      </c>
+      <c r="D56" s="37" t="s">
         <v>1543</v>
-      </c>
-      <c r="C56" s="42" t="s">
-        <v>1544</v>
-      </c>
-      <c r="D56" s="37" t="s">
-        <v>1545</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="13">
       <c r="A57" s="1" t="s">
-        <v>1539</v>
+        <v>1537</v>
       </c>
       <c r="B57" s="1" t="s">
+        <v>1544</v>
+      </c>
+      <c r="C57" s="41" t="s">
+        <v>1545</v>
+      </c>
+      <c r="D57" s="37" t="s">
         <v>1546</v>
-      </c>
-      <c r="C57" s="41" t="s">
-        <v>1547</v>
-      </c>
-      <c r="D57" s="37" t="s">
-        <v>1548</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="13">
       <c r="A58" s="1" t="s">
-        <v>1539</v>
+        <v>1537</v>
       </c>
       <c r="B58" s="1" t="s">
+        <v>1547</v>
+      </c>
+      <c r="C58" s="42" t="s">
+        <v>1548</v>
+      </c>
+      <c r="D58" s="37" t="s">
         <v>1549</v>
-      </c>
-      <c r="C58" s="42" t="s">
-        <v>1550</v>
-      </c>
-      <c r="D58" s="37" t="s">
-        <v>1551</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="13">
       <c r="A59" s="1" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="B59" s="1" t="s">
+        <v>1550</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>1551</v>
+      </c>
+      <c r="D59" s="37" t="s">
         <v>1552</v>
-      </c>
-      <c r="C59" s="4" t="s">
-        <v>1553</v>
-      </c>
-      <c r="D59" s="37" t="s">
-        <v>1554</v>
       </c>
     </row>
     <row r="60" spans="1:4" ht="13">
       <c r="A60" s="1" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="B60" s="1" t="s">
+        <v>1553</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>1554</v>
+      </c>
+      <c r="D60" s="37" t="s">
         <v>1555</v>
-      </c>
-      <c r="C60" s="4" t="s">
-        <v>1556</v>
-      </c>
-      <c r="D60" s="37" t="s">
-        <v>1557</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="13">
       <c r="A61" s="1" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="B61" s="1" t="s">
+        <v>1556</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>1557</v>
+      </c>
+      <c r="D61" s="37" t="s">
         <v>1558</v>
-      </c>
-      <c r="C61" s="4" t="s">
-        <v>1559</v>
-      </c>
-      <c r="D61" s="37" t="s">
-        <v>1560</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="13">
       <c r="A62" s="1" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="B62" s="1" t="s">
+        <v>1559</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>1560</v>
+      </c>
+      <c r="D62" s="37" t="s">
         <v>1561</v>
-      </c>
-      <c r="C62" s="4" t="s">
-        <v>1562</v>
-      </c>
-      <c r="D62" s="37" t="s">
-        <v>1563</v>
       </c>
     </row>
     <row r="63" spans="1:4" ht="13">
       <c r="A63" s="1" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="B63" s="1" t="s">
+        <v>1562</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>1563</v>
+      </c>
+      <c r="D63" s="37" t="s">
         <v>1564</v>
-      </c>
-      <c r="C63" s="4" t="s">
-        <v>1565</v>
-      </c>
-      <c r="D63" s="37" t="s">
-        <v>1566</v>
       </c>
     </row>
     <row r="64" spans="1:4" ht="13">
       <c r="A64" s="1" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="B64" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>1566</v>
+      </c>
+      <c r="D64" s="37" t="s">
         <v>1567</v>
-      </c>
-      <c r="C64" s="4" t="s">
-        <v>1568</v>
-      </c>
-      <c r="D64" s="37" t="s">
-        <v>1569</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="13">
       <c r="A65" s="1" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="B65" s="1" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>1507</v>
+      </c>
+      <c r="D65" s="37" t="s">
         <v>1508</v>
-      </c>
-      <c r="C65" s="4" t="s">
-        <v>1509</v>
-      </c>
-      <c r="D65" s="37" t="s">
-        <v>1510</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="13">
       <c r="A66" s="1" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>1405</v>
+        <v>1403</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="D66" s="37" t="s">
-        <v>1570</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="13">
       <c r="A67" s="1" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
       <c r="B67" s="1" t="s">
+        <v>1569</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>1570</v>
+      </c>
+      <c r="D67" s="37" t="s">
         <v>1571</v>
-      </c>
-      <c r="C67" s="4" t="s">
-        <v>1572</v>
-      </c>
-      <c r="D67" s="37" t="s">
-        <v>1573</v>
       </c>
     </row>
     <row r="68" spans="1:4" ht="13">
       <c r="A68" s="1" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
       <c r="B68" s="1" t="s">
+        <v>1572</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>1573</v>
+      </c>
+      <c r="D68" s="37" t="s">
         <v>1574</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>1575</v>
-      </c>
-      <c r="D68" s="37" t="s">
-        <v>1576</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="13">
       <c r="A69" s="1" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
       <c r="B69" s="1" t="s">
+        <v>1575</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>1576</v>
+      </c>
+      <c r="D69" s="37" t="s">
         <v>1577</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>1578</v>
-      </c>
-      <c r="D69" s="37" t="s">
-        <v>1579</v>
       </c>
     </row>
     <row r="70" spans="1:4" ht="13">
       <c r="A70" s="1" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>1408</v>
+        <v>1406</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>1580</v>
+        <v>1578</v>
       </c>
       <c r="D70" s="37" t="s">
-        <v>1581</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="71" spans="1:4" ht="13">
       <c r="A71" s="41" t="s">
+        <v>1580</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>1581</v>
+      </c>
+      <c r="C71" s="41" t="s">
         <v>1582</v>
       </c>
-      <c r="B71" s="1" t="s">
+      <c r="D71" s="37" t="s">
         <v>1583</v>
-      </c>
-      <c r="C71" s="41" t="s">
-        <v>1584</v>
-      </c>
-      <c r="D71" s="37" t="s">
-        <v>1585</v>
       </c>
     </row>
     <row r="72" spans="1:4" ht="13">
       <c r="A72" s="41" t="s">
-        <v>1582</v>
+        <v>1580</v>
       </c>
       <c r="B72" s="1" t="s">
+        <v>1584</v>
+      </c>
+      <c r="C72" s="42" t="s">
+        <v>1585</v>
+      </c>
+      <c r="D72" s="37" t="s">
         <v>1586</v>
-      </c>
-      <c r="C72" s="42" t="s">
-        <v>1587</v>
-      </c>
-      <c r="D72" s="37" t="s">
-        <v>1588</v>
       </c>
     </row>
     <row r="73" spans="1:4" ht="13">
       <c r="A73" s="41" t="s">
-        <v>1582</v>
+        <v>1580</v>
       </c>
       <c r="B73" s="1" t="s">
+        <v>1587</v>
+      </c>
+      <c r="C73" s="42" t="s">
+        <v>1588</v>
+      </c>
+      <c r="D73" s="37" t="s">
         <v>1589</v>
-      </c>
-      <c r="C73" s="42" t="s">
-        <v>1590</v>
-      </c>
-      <c r="D73" s="37" t="s">
-        <v>1591</v>
       </c>
     </row>
     <row r="74" spans="1:4" ht="13">
       <c r="A74" s="41" t="s">
-        <v>1582</v>
+        <v>1580</v>
       </c>
       <c r="B74" s="1" t="s">
+        <v>1590</v>
+      </c>
+      <c r="C74" s="42" t="s">
+        <v>1591</v>
+      </c>
+      <c r="D74" s="37" t="s">
         <v>1592</v>
-      </c>
-      <c r="C74" s="42" t="s">
-        <v>1593</v>
-      </c>
-      <c r="D74" s="37" t="s">
-        <v>1594</v>
       </c>
     </row>
     <row r="75" spans="1:4" ht="13">
       <c r="A75" s="41" t="s">
-        <v>1582</v>
+        <v>1580</v>
       </c>
       <c r="B75" s="1" t="s">
+        <v>1593</v>
+      </c>
+      <c r="C75" s="42" t="s">
+        <v>1594</v>
+      </c>
+      <c r="D75" s="37" t="s">
         <v>1595</v>
-      </c>
-      <c r="C75" s="42" t="s">
-        <v>1596</v>
-      </c>
-      <c r="D75" s="37" t="s">
-        <v>1597</v>
       </c>
     </row>
     <row r="76" spans="1:4" ht="13">
       <c r="A76" s="1" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
       <c r="B76" s="1" t="s">
+        <v>1596</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>1597</v>
+      </c>
+      <c r="D76" s="37" t="s">
         <v>1598</v>
-      </c>
-      <c r="C76" s="4" t="s">
-        <v>1599</v>
-      </c>
-      <c r="D76" s="37" t="s">
-        <v>1600</v>
       </c>
     </row>
     <row r="77" spans="1:4" ht="13">
       <c r="A77" s="1" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
       <c r="B77" s="1" t="s">
+        <v>1599</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>1600</v>
+      </c>
+      <c r="D77" s="37" t="s">
         <v>1601</v>
-      </c>
-      <c r="C77" s="4" t="s">
-        <v>1602</v>
-      </c>
-      <c r="D77" s="37" t="s">
-        <v>1603</v>
       </c>
     </row>
     <row r="78" spans="1:4" ht="13">
       <c r="A78" s="1" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
       <c r="B78" s="1" t="s">
+        <v>1602</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>1603</v>
+      </c>
+      <c r="D78" s="37" t="s">
         <v>1604</v>
-      </c>
-      <c r="C78" s="4" t="s">
-        <v>1605</v>
-      </c>
-      <c r="D78" s="37" t="s">
-        <v>1606</v>
       </c>
     </row>
     <row r="79" spans="1:4" ht="13">
       <c r="A79" s="1" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
       <c r="B79" s="1" t="s">
+        <v>1605</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>1606</v>
+      </c>
+      <c r="D79" s="37" t="s">
         <v>1607</v>
-      </c>
-      <c r="C79" s="4" t="s">
-        <v>1608</v>
-      </c>
-      <c r="D79" s="37" t="s">
-        <v>1609</v>
       </c>
     </row>
     <row r="80" spans="1:4" ht="13">
       <c r="A80" s="1" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
       <c r="B80" s="1" t="s">
+        <v>1608</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>1609</v>
+      </c>
+      <c r="D80" s="37" t="s">
         <v>1610</v>
-      </c>
-      <c r="C80" s="4" t="s">
-        <v>1611</v>
-      </c>
-      <c r="D80" s="37" t="s">
-        <v>1612</v>
       </c>
     </row>
     <row r="81" spans="1:6" ht="13">
       <c r="A81" s="1" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
       <c r="B81" s="1" t="s">
+        <v>1611</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>1612</v>
+      </c>
+      <c r="D81" s="37" t="s">
         <v>1613</v>
-      </c>
-      <c r="C81" s="4" t="s">
-        <v>1614</v>
-      </c>
-      <c r="D81" s="37" t="s">
-        <v>1615</v>
       </c>
     </row>
     <row r="82" spans="1:6" ht="13">
       <c r="A82" s="1" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
       <c r="B82" s="1" t="s">
+        <v>1614</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>1615</v>
+      </c>
+      <c r="D82" s="37" t="s">
         <v>1616</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>1617</v>
-      </c>
-      <c r="D82" s="37" t="s">
-        <v>1618</v>
       </c>
     </row>
     <row r="83" spans="1:6" ht="13">
       <c r="A83" s="1" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>1619</v>
+        <v>1617</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>1580</v>
+        <v>1578</v>
       </c>
       <c r="D83" s="37" t="s">
-        <v>1620</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="84" spans="1:6" ht="13">
       <c r="A84" s="43" t="s">
-        <v>1621</v>
+        <v>1619</v>
       </c>
       <c r="B84" s="43">
         <v>1</v>
       </c>
       <c r="C84" s="43" t="s">
-        <v>1622</v>
-      </c>
-      <c r="D84" s="47" t="s">
-        <v>1623</v>
-      </c>
-      <c r="E84" s="46"/>
+        <v>1620</v>
+      </c>
+      <c r="D84" s="52" t="s">
+        <v>1621</v>
+      </c>
+      <c r="E84" s="51"/>
     </row>
     <row r="85" spans="1:6" ht="13">
       <c r="A85" s="43" t="s">
-        <v>1621</v>
+        <v>1619</v>
       </c>
       <c r="B85" s="43">
         <v>2</v>
       </c>
       <c r="C85" s="43" t="s">
-        <v>1624</v>
-      </c>
-      <c r="D85" s="47" t="s">
-        <v>1625</v>
-      </c>
-      <c r="E85" s="46"/>
-      <c r="F85" s="46"/>
+        <v>1622</v>
+      </c>
+      <c r="D85" s="52" t="s">
+        <v>1623</v>
+      </c>
+      <c r="E85" s="51"/>
+      <c r="F85" s="51"/>
     </row>
     <row r="86" spans="1:6" ht="13">
       <c r="A86" s="43" t="s">
-        <v>1621</v>
+        <v>1619</v>
       </c>
       <c r="B86" s="43">
         <v>3</v>
       </c>
       <c r="C86" s="43" t="s">
-        <v>1626</v>
+        <v>1624</v>
       </c>
       <c r="D86" s="43" t="s">
-        <v>1627</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="87" spans="1:6" ht="13">
       <c r="A87" s="43" t="s">
-        <v>1621</v>
+        <v>1619</v>
       </c>
       <c r="B87" s="43">
         <v>4</v>
       </c>
       <c r="C87" s="43" t="s">
-        <v>1628</v>
-      </c>
-      <c r="D87" s="47" t="s">
-        <v>1629</v>
-      </c>
-      <c r="E87" s="46"/>
+        <v>1626</v>
+      </c>
+      <c r="D87" s="52" t="s">
+        <v>1627</v>
+      </c>
+      <c r="E87" s="51"/>
     </row>
     <row r="88" spans="1:6" ht="13">
       <c r="A88" s="43" t="s">
-        <v>1621</v>
+        <v>1619</v>
       </c>
       <c r="B88" s="43">
         <v>5</v>
       </c>
       <c r="C88" s="43" t="s">
-        <v>1630</v>
+        <v>1628</v>
       </c>
       <c r="D88" s="43" t="s">
-        <v>1631</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="89" spans="1:6" ht="13">
       <c r="A89" s="43" t="s">
-        <v>1621</v>
+        <v>1619</v>
       </c>
       <c r="B89" s="43">
         <v>6</v>
       </c>
       <c r="C89" s="43" t="s">
-        <v>1632</v>
+        <v>1630</v>
       </c>
       <c r="D89" s="43" t="s">
-        <v>1633</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="90" spans="1:6" ht="13">
       <c r="A90" s="43" t="s">
-        <v>1621</v>
+        <v>1619</v>
       </c>
       <c r="B90" s="43">
         <v>7</v>
       </c>
       <c r="C90" s="43" t="s">
-        <v>1634</v>
+        <v>1632</v>
       </c>
       <c r="D90" s="43" t="s">
-        <v>1635</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="91" spans="1:6" ht="13">
       <c r="A91" s="43" t="s">
-        <v>1636</v>
+        <v>1634</v>
       </c>
       <c r="B91" s="43">
         <v>1</v>
       </c>
       <c r="C91" s="43" t="s">
-        <v>1637</v>
+        <v>1635</v>
       </c>
       <c r="D91" s="43" t="s">
-        <v>1638</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="92" spans="1:6" ht="13">
       <c r="A92" s="43" t="s">
-        <v>1636</v>
+        <v>1634</v>
       </c>
       <c r="B92" s="43">
         <v>0</v>
       </c>
       <c r="C92" s="43" t="s">
-        <v>1639</v>
+        <v>1637</v>
       </c>
       <c r="D92" s="43" t="s">
-        <v>1639</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="93" spans="1:6" ht="13">
       <c r="A93" s="43" t="s">
-        <v>1636</v>
+        <v>1634</v>
       </c>
       <c r="B93" s="43">
         <v>99</v>
       </c>
       <c r="C93" s="43" t="s">
-        <v>1640</v>
+        <v>1638</v>
       </c>
       <c r="D93" s="43" t="s">
-        <v>1641</v>
+        <v>1639</v>
       </c>
     </row>
   </sheetData>
@@ -21417,39 +21436,39 @@
   <sheetData>
     <row r="1" spans="1:6" ht="15.75" customHeight="1">
       <c r="A1" s="2" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1641</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>1642</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>1643</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>1644</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>1645</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>1646</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>1647</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="15.75" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>1648</v>
+        <v>1646</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1649</v>
+        <v>1647</v>
       </c>
       <c r="C2" s="44">
         <v>43580</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1650</v>
+        <v>1648</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>1651</v>
+        <v>1649</v>
       </c>
     </row>
   </sheetData>

--- a/forms/app/infant_child.xlsx
+++ b/forms/app/infant_child.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2568" uniqueCount="1633">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2569" uniqueCount="1633">
   <si>
     <t>type</t>
   </si>
@@ -5230,9 +5230,6 @@
     <t xml:space="preserve">Essential New Born Care: Breastfeeding </t>
   </si>
   <si>
-    <t>not(selected(${child_consent_today},"no")) and ${age_days} &lt;= (${month} * 24) and ${refer_neonatal_danger_sign_flag}=0 and ${refer_child_danger_sign_flag}=0</t>
-  </si>
-  <si>
     <t>small_baby_intro</t>
   </si>
   <si>
@@ -5274,9 +5271,6 @@
   </si>
   <si>
     <t xml:space="preserve">Zungumza na mama kuhusu tatizo na msaidie kulitatua. </t>
-  </si>
-  <si>
-    <t>selected(${baby_breastfeed_well},"no") and  ${small_baby_ever}=1 and  ${age_days} &lt;= (${month} * 6)</t>
   </si>
   <si>
     <t>not_breastfeeding_well</t>
@@ -5336,9 +5330,6 @@
     <t>${n_child_visits} = 0 and ${age_days} &lt; (${month} * 6)</t>
   </si>
   <si>
-    <t>selected(${baby_breastfeed_well},"no") and  (${small_baby_ever}=0 or ${small_baby_ever}=1 and  ${age_days} &lt;= (${month} * 6))</t>
-  </si>
-  <si>
     <t>selected(${baby_times_breastfed_daily},"five_more_times_day")</t>
   </si>
   <si>
@@ -5361,6 +5352,15 @@
   </si>
   <si>
     <t>selected(${currently_breastfeeding},"yes") and ${age_days} &lt; (${month} * 6) and ${random_value} &gt; 5</t>
+  </si>
+  <si>
+    <t>selected(${baby_breastfeed_well},"no") and  ${small_baby_ever}=1 and  ${age_days} &lt; (${month} * 6)</t>
+  </si>
+  <si>
+    <t>selected(${baby_breastfeed_well},"no") and  (${small_baby_ever}=0 or ${small_baby_ever}=1 and  ${age_days} &lt; (${month} * 6))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">${age_days} &lt;= (${month} * 24) </t>
   </si>
 </sst>
 </file>
@@ -5371,7 +5371,7 @@
     <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
     <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -5407,6 +5407,11 @@
       <name val="Arial"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -5440,7 +5445,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
@@ -5476,6 +5481,8 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -11028,8 +11035,8 @@
       <c r="D188" s="2" t="s">
         <v>479</v>
       </c>
-      <c r="F188" s="19" t="s">
-        <v>1592</v>
+      <c r="F188" s="23" t="s">
+        <v>401</v>
       </c>
     </row>
     <row r="189" spans="1:17" ht="78">
@@ -11037,16 +11044,16 @@
         <v>139</v>
       </c>
       <c r="B189" s="1" t="s">
+        <v>1592</v>
+      </c>
+      <c r="C189" s="18" t="s">
+        <v>1594</v>
+      </c>
+      <c r="D189" s="10" t="s">
         <v>1593</v>
       </c>
-      <c r="C189" s="18" t="s">
-        <v>1595</v>
-      </c>
-      <c r="D189" s="10" t="s">
-        <v>1594</v>
-      </c>
       <c r="F189" s="19" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="190" spans="1:17" ht="65">
@@ -11064,7 +11071,7 @@
       </c>
       <c r="E190" s="1"/>
       <c r="F190" s="2" t="s">
-        <v>1622</v>
+        <v>1620</v>
       </c>
       <c r="G190" s="1"/>
       <c r="H190" s="1"/>
@@ -11095,7 +11102,7 @@
         <v>171</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="G191" s="1"/>
       <c r="H191" s="1"/>
@@ -11156,7 +11163,9 @@
       <c r="E193" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="F193" s="1"/>
+      <c r="F193" s="24" t="s">
+        <v>1632</v>
+      </c>
       <c r="G193" s="1"/>
       <c r="H193" s="1"/>
       <c r="I193" s="1"/>
@@ -11206,10 +11215,10 @@
         <v>498</v>
       </c>
       <c r="C195" s="10" t="s">
+        <v>1596</v>
+      </c>
+      <c r="D195" s="10" t="s">
         <v>1597</v>
-      </c>
-      <c r="D195" s="10" t="s">
-        <v>1598</v>
       </c>
       <c r="E195" s="1"/>
       <c r="F195" s="2" t="s">
@@ -11235,7 +11244,7 @@
         <v>499</v>
       </c>
       <c r="C196" s="10" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="D196" s="10" t="s">
         <v>500</v>
@@ -11261,7 +11270,7 @@
         <v>167</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="C197" s="3" t="s">
         <v>566</v>
@@ -11290,16 +11299,16 @@
         <v>139</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>1606</v>
+        <v>1604</v>
       </c>
       <c r="C198" s="20" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
       <c r="D198" s="20" t="s">
-        <v>1607</v>
+        <v>1605</v>
       </c>
       <c r="F198" s="19" t="s">
-        <v>1624</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="199" spans="1:17">
@@ -11307,16 +11316,16 @@
         <v>139</v>
       </c>
       <c r="B199" s="1" t="s">
+        <v>1601</v>
+      </c>
+      <c r="C199" s="18" t="s">
         <v>1602</v>
       </c>
-      <c r="C199" s="18" t="s">
+      <c r="D199" s="18" t="s">
         <v>1603</v>
       </c>
-      <c r="D199" s="18" t="s">
-        <v>1604</v>
-      </c>
       <c r="F199" s="19" t="s">
-        <v>1605</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="200" spans="1:17">
@@ -11324,13 +11333,13 @@
         <v>62</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>1608</v>
+        <v>1606</v>
       </c>
       <c r="C200" s="18"/>
       <c r="D200" s="18"/>
       <c r="F200" s="19"/>
       <c r="L200" t="s">
-        <v>1630</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="201" spans="1:17">
@@ -11338,7 +11347,7 @@
         <v>167</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>1627</v>
+        <v>1624</v>
       </c>
       <c r="C201" s="2" t="s">
         <v>501</v>
@@ -11350,7 +11359,7 @@
         <v>171</v>
       </c>
       <c r="F201" s="2" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
       <c r="G201" s="2"/>
       <c r="H201" s="1"/>
@@ -11366,19 +11375,19 @@
     </row>
     <row r="202" spans="1:17">
       <c r="A202" s="1" t="s">
-        <v>1612</v>
+        <v>1610</v>
       </c>
       <c r="B202" s="1" t="s">
+        <v>1607</v>
+      </c>
+      <c r="C202" t="s">
+        <v>1608</v>
+      </c>
+      <c r="D202" t="s">
         <v>1609</v>
       </c>
-      <c r="C202" t="s">
-        <v>1610</v>
-      </c>
-      <c r="D202" t="s">
-        <v>1611</v>
-      </c>
       <c r="F202" s="2" t="s">
-        <v>1632</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="203" spans="1:17">
@@ -11386,16 +11395,16 @@
         <v>139</v>
       </c>
       <c r="B203" s="1" t="s">
+        <v>1611</v>
+      </c>
+      <c r="C203" t="s">
+        <v>1612</v>
+      </c>
+      <c r="D203" t="s">
         <v>1613</v>
       </c>
-      <c r="C203" t="s">
+      <c r="F203" s="19" t="s">
         <v>1614</v>
-      </c>
-      <c r="D203" t="s">
-        <v>1615</v>
-      </c>
-      <c r="F203" s="19" t="s">
-        <v>1616</v>
       </c>
     </row>
     <row r="204" spans="1:17">
@@ -11403,7 +11412,7 @@
         <v>561</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>1618</v>
+        <v>1616</v>
       </c>
       <c r="C204" s="3" t="s">
         <v>562</v>
@@ -11415,7 +11424,7 @@
         <v>171</v>
       </c>
       <c r="F204" s="2" t="s">
-        <v>1617</v>
+        <v>1615</v>
       </c>
       <c r="G204" s="2"/>
       <c r="H204" s="2"/>
@@ -11434,7 +11443,7 @@
         <v>139</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>1619</v>
+        <v>1617</v>
       </c>
       <c r="C205" s="10" t="s">
         <v>564</v>
@@ -11444,7 +11453,7 @@
       </c>
       <c r="E205" s="1"/>
       <c r="F205" s="2" t="s">
-        <v>1625</v>
+        <v>1622</v>
       </c>
       <c r="G205" s="2"/>
       <c r="H205" s="2"/>
@@ -11463,13 +11472,13 @@
         <v>139</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>1620</v>
+        <v>1618</v>
       </c>
       <c r="C206" t="s">
-        <v>1621</v>
+        <v>1619</v>
       </c>
       <c r="F206" s="2" t="s">
-        <v>1626</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="207" spans="1:17">
@@ -12777,7 +12786,7 @@
         <v>139</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
       <c r="C254" s="10"/>
       <c r="D254" s="10"/>
@@ -12797,10 +12806,10 @@
       <c r="P254" s="1"/>
       <c r="Q254" s="1"/>
       <c r="T254" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
       <c r="U254" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="255" spans="1:26">
@@ -19626,27 +19635,27 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="K266:L266"/>
-    <mergeCell ref="F267:G267"/>
-    <mergeCell ref="K270:L270"/>
-    <mergeCell ref="K273:L273"/>
-    <mergeCell ref="K276:L276"/>
-    <mergeCell ref="K279:L279"/>
-    <mergeCell ref="K282:L282"/>
-    <mergeCell ref="K285:L285"/>
-    <mergeCell ref="K288:L288"/>
-    <mergeCell ref="K291:L291"/>
-    <mergeCell ref="K294:L294"/>
-    <mergeCell ref="K297:L297"/>
-    <mergeCell ref="K300:L300"/>
-    <mergeCell ref="K303:L303"/>
-    <mergeCell ref="F304:H304"/>
     <mergeCell ref="L322:O322"/>
     <mergeCell ref="F305:H305"/>
     <mergeCell ref="K306:L306"/>
     <mergeCell ref="K309:L309"/>
     <mergeCell ref="K312:L312"/>
     <mergeCell ref="F320:I320"/>
+    <mergeCell ref="K294:L294"/>
+    <mergeCell ref="K297:L297"/>
+    <mergeCell ref="K300:L300"/>
+    <mergeCell ref="K303:L303"/>
+    <mergeCell ref="F304:H304"/>
+    <mergeCell ref="K279:L279"/>
+    <mergeCell ref="K282:L282"/>
+    <mergeCell ref="K285:L285"/>
+    <mergeCell ref="K288:L288"/>
+    <mergeCell ref="K291:L291"/>
+    <mergeCell ref="K266:L266"/>
+    <mergeCell ref="F267:G267"/>
+    <mergeCell ref="K270:L270"/>
+    <mergeCell ref="K273:L273"/>
+    <mergeCell ref="K276:L276"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
   <pageSetup firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/forms/app/infant_child.xlsx
+++ b/forms/app/infant_child.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2569" uniqueCount="1633">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2570" uniqueCount="1633">
   <si>
     <t>type</t>
   </si>
@@ -5333,9 +5333,6 @@
     <t>selected(${baby_times_breastfed_daily},"five_more_times_day")</t>
   </si>
   <si>
-    <t>not(selected(${baby_times_breastfed_daily},"five_more_times_day")) and (not(selected(${exclusive_breastfeeding},"yes")) or not(selected(${exclusive_breastfeeding_multiple_choice},"none")))</t>
-  </si>
-  <si>
     <t>exclusive_breastfeeding</t>
   </si>
   <si>
@@ -5361,6 +5358,9 @@
   </si>
   <si>
     <t xml:space="preserve">${age_days} &lt;= (${month} * 24) </t>
+  </si>
+  <si>
+    <t>not(selected(${baby_times_breastfed_daily},"five_more_times_day")) and ${age_days} &lt; (${month} * 6) and (not(selected(${exclusive_breastfeeding},"yes")) or not(selected(${exclusive_breastfeeding_multiple_choice},"none")))</t>
   </si>
 </sst>
 </file>
@@ -5480,9 +5480,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -11035,7 +11035,7 @@
       <c r="D188" s="2" t="s">
         <v>479</v>
       </c>
-      <c r="F188" s="23" t="s">
+      <c r="F188" s="22" t="s">
         <v>401</v>
       </c>
     </row>
@@ -11163,8 +11163,8 @@
       <c r="E193" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="F193" s="24" t="s">
-        <v>1632</v>
+      <c r="F193" s="23" t="s">
+        <v>1631</v>
       </c>
       <c r="G193" s="1"/>
       <c r="H193" s="1"/>
@@ -11281,7 +11281,9 @@
       <c r="E197" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="F197" s="2"/>
+      <c r="F197" s="23" t="s">
+        <v>1631</v>
+      </c>
       <c r="G197" s="2"/>
       <c r="H197" s="2"/>
       <c r="I197" s="1"/>
@@ -11308,7 +11310,7 @@
         <v>1605</v>
       </c>
       <c r="F198" s="19" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="199" spans="1:17">
@@ -11325,7 +11327,7 @@
         <v>1603</v>
       </c>
       <c r="F199" s="19" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="200" spans="1:17">
@@ -11339,7 +11341,7 @@
       <c r="D200" s="18"/>
       <c r="F200" s="19"/>
       <c r="L200" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="201" spans="1:17">
@@ -11347,7 +11349,7 @@
         <v>167</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="C201" s="2" t="s">
         <v>501</v>
@@ -11359,7 +11361,7 @@
         <v>171</v>
       </c>
       <c r="F201" s="2" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="G201" s="2"/>
       <c r="H201" s="1"/>
@@ -11387,7 +11389,7 @@
         <v>1609</v>
       </c>
       <c r="F202" s="2" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="203" spans="1:17">
@@ -11478,7 +11480,7 @@
         <v>1619</v>
       </c>
       <c r="F206" s="2" t="s">
-        <v>1623</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="207" spans="1:17">
@@ -12786,7 +12788,7 @@
         <v>139</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="C254" s="10"/>
       <c r="D254" s="10"/>
@@ -12806,10 +12808,10 @@
       <c r="P254" s="1"/>
       <c r="Q254" s="1"/>
       <c r="T254" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="U254" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="255" spans="1:26">
@@ -13240,10 +13242,10 @@
       <c r="J266" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="K266" s="22" t="s">
+      <c r="K266" s="24" t="s">
         <v>681</v>
       </c>
-      <c r="L266" s="22"/>
+      <c r="L266" s="24"/>
       <c r="M266" s="1"/>
       <c r="N266" s="1"/>
       <c r="O266" s="1"/>
@@ -13273,10 +13275,10 @@
         <v>684</v>
       </c>
       <c r="E267" s="1"/>
-      <c r="F267" s="22" t="s">
+      <c r="F267" s="24" t="s">
         <v>685</v>
       </c>
-      <c r="G267" s="22"/>
+      <c r="G267" s="24"/>
       <c r="H267" s="1"/>
       <c r="I267" s="1"/>
       <c r="J267" s="1"/>
@@ -13400,10 +13402,10 @@
       <c r="J270" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="K270" s="22" t="s">
+      <c r="K270" s="24" t="s">
         <v>681</v>
       </c>
-      <c r="L270" s="22"/>
+      <c r="L270" s="24"/>
       <c r="M270" s="1"/>
       <c r="N270" s="1"/>
       <c r="O270" s="1"/>
@@ -13522,10 +13524,10 @@
       <c r="J273" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="K273" s="22" t="s">
+      <c r="K273" s="24" t="s">
         <v>681</v>
       </c>
-      <c r="L273" s="22"/>
+      <c r="L273" s="24"/>
       <c r="M273" s="1"/>
       <c r="N273" s="1"/>
       <c r="O273" s="1"/>
@@ -13644,10 +13646,10 @@
       <c r="J276" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="K276" s="22" t="s">
+      <c r="K276" s="24" t="s">
         <v>681</v>
       </c>
-      <c r="L276" s="22"/>
+      <c r="L276" s="24"/>
       <c r="M276" s="1"/>
       <c r="N276" s="1"/>
       <c r="O276" s="1"/>
@@ -13766,10 +13768,10 @@
       <c r="J279" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="K279" s="22" t="s">
+      <c r="K279" s="24" t="s">
         <v>681</v>
       </c>
-      <c r="L279" s="22"/>
+      <c r="L279" s="24"/>
       <c r="M279" s="1"/>
       <c r="N279" s="1"/>
       <c r="O279" s="1"/>
@@ -13888,10 +13890,10 @@
       <c r="J282" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="K282" s="22" t="s">
+      <c r="K282" s="24" t="s">
         <v>681</v>
       </c>
-      <c r="L282" s="22"/>
+      <c r="L282" s="24"/>
       <c r="M282" s="1"/>
       <c r="N282" s="1"/>
       <c r="O282" s="1"/>
@@ -14010,10 +14012,10 @@
       <c r="J285" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="K285" s="22" t="s">
+      <c r="K285" s="24" t="s">
         <v>681</v>
       </c>
-      <c r="L285" s="22"/>
+      <c r="L285" s="24"/>
       <c r="M285" s="1"/>
       <c r="N285" s="1"/>
       <c r="O285" s="1"/>
@@ -14132,10 +14134,10 @@
       <c r="J288" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="K288" s="22" t="s">
+      <c r="K288" s="24" t="s">
         <v>681</v>
       </c>
-      <c r="L288" s="22"/>
+      <c r="L288" s="24"/>
       <c r="M288" s="1"/>
       <c r="N288" s="1"/>
       <c r="O288" s="1"/>
@@ -14254,10 +14256,10 @@
       <c r="J291" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="K291" s="22" t="s">
+      <c r="K291" s="24" t="s">
         <v>681</v>
       </c>
-      <c r="L291" s="22"/>
+      <c r="L291" s="24"/>
       <c r="M291" s="1"/>
       <c r="N291" s="1"/>
       <c r="O291" s="1"/>
@@ -14376,10 +14378,10 @@
       <c r="J294" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="K294" s="22" t="s">
+      <c r="K294" s="24" t="s">
         <v>681</v>
       </c>
-      <c r="L294" s="22"/>
+      <c r="L294" s="24"/>
       <c r="M294" s="1"/>
       <c r="N294" s="1"/>
       <c r="O294" s="1"/>
@@ -14498,10 +14500,10 @@
       <c r="J297" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="K297" s="22" t="s">
+      <c r="K297" s="24" t="s">
         <v>681</v>
       </c>
-      <c r="L297" s="22"/>
+      <c r="L297" s="24"/>
       <c r="M297" s="1"/>
       <c r="N297" s="1"/>
       <c r="O297" s="1"/>
@@ -14620,10 +14622,10 @@
       <c r="J300" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="K300" s="22" t="s">
+      <c r="K300" s="24" t="s">
         <v>681</v>
       </c>
-      <c r="L300" s="22"/>
+      <c r="L300" s="24"/>
       <c r="M300" s="1"/>
       <c r="N300" s="1"/>
       <c r="O300" s="1"/>
@@ -14742,10 +14744,10 @@
       <c r="J303" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="K303" s="22" t="s">
+      <c r="K303" s="24" t="s">
         <v>681</v>
       </c>
-      <c r="L303" s="22"/>
+      <c r="L303" s="24"/>
       <c r="M303" s="1"/>
       <c r="N303" s="1"/>
       <c r="O303" s="1"/>
@@ -14775,11 +14777,11 @@
         <v>669</v>
       </c>
       <c r="E304" s="1"/>
-      <c r="F304" s="22" t="s">
+      <c r="F304" s="24" t="s">
         <v>795</v>
       </c>
-      <c r="G304" s="22"/>
-      <c r="H304" s="22"/>
+      <c r="G304" s="24"/>
+      <c r="H304" s="24"/>
       <c r="I304" s="1"/>
       <c r="J304" s="1"/>
       <c r="K304" s="1"/>
@@ -14815,11 +14817,11 @@
       <c r="E305" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="F305" s="22" t="s">
+      <c r="F305" s="24" t="s">
         <v>795</v>
       </c>
-      <c r="G305" s="22"/>
-      <c r="H305" s="22"/>
+      <c r="G305" s="24"/>
+      <c r="H305" s="24"/>
       <c r="I305" s="1"/>
       <c r="J305" s="1"/>
       <c r="K305" s="1"/>
@@ -14864,10 +14866,10 @@
       <c r="J306" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="K306" s="22" t="s">
+      <c r="K306" s="24" t="s">
         <v>681</v>
       </c>
-      <c r="L306" s="22"/>
+      <c r="L306" s="24"/>
       <c r="M306" s="1"/>
       <c r="N306" s="1"/>
       <c r="O306" s="1"/>
@@ -14986,10 +14988,10 @@
       <c r="J309" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="K309" s="22" t="s">
+      <c r="K309" s="24" t="s">
         <v>681</v>
       </c>
-      <c r="L309" s="22"/>
+      <c r="L309" s="24"/>
       <c r="M309" s="1"/>
       <c r="N309" s="1"/>
       <c r="O309" s="1"/>
@@ -15108,10 +15110,10 @@
       <c r="J312" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="K312" s="22" t="s">
+      <c r="K312" s="24" t="s">
         <v>681</v>
       </c>
-      <c r="L312" s="22"/>
+      <c r="L312" s="24"/>
       <c r="M312" s="1"/>
       <c r="N312" s="1"/>
       <c r="O312" s="1"/>
@@ -15396,12 +15398,12 @@
         <v>845</v>
       </c>
       <c r="E320" s="1"/>
-      <c r="F320" s="22" t="s">
+      <c r="F320" s="24" t="s">
         <v>846</v>
       </c>
-      <c r="G320" s="22"/>
-      <c r="H320" s="22"/>
-      <c r="I320" s="22"/>
+      <c r="G320" s="24"/>
+      <c r="H320" s="24"/>
+      <c r="I320" s="24"/>
       <c r="J320" s="1"/>
       <c r="K320" s="1"/>
       <c r="L320" s="1"/>
@@ -15474,12 +15476,12 @@
       <c r="I322" s="1"/>
       <c r="J322" s="1"/>
       <c r="K322" s="1"/>
-      <c r="L322" s="22" t="s">
+      <c r="L322" s="24" t="s">
         <v>852</v>
       </c>
-      <c r="M322" s="22"/>
-      <c r="N322" s="22"/>
-      <c r="O322" s="22"/>
+      <c r="M322" s="24"/>
+      <c r="N322" s="24"/>
+      <c r="O322" s="24"/>
       <c r="P322" s="1"/>
       <c r="Q322" s="1"/>
       <c r="R322" s="6"/>
@@ -19635,27 +19637,27 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="K266:L266"/>
+    <mergeCell ref="F267:G267"/>
+    <mergeCell ref="K270:L270"/>
+    <mergeCell ref="K273:L273"/>
+    <mergeCell ref="K276:L276"/>
+    <mergeCell ref="K279:L279"/>
+    <mergeCell ref="K282:L282"/>
+    <mergeCell ref="K285:L285"/>
+    <mergeCell ref="K288:L288"/>
+    <mergeCell ref="K291:L291"/>
+    <mergeCell ref="K294:L294"/>
+    <mergeCell ref="K297:L297"/>
+    <mergeCell ref="K300:L300"/>
+    <mergeCell ref="K303:L303"/>
+    <mergeCell ref="F304:H304"/>
     <mergeCell ref="L322:O322"/>
     <mergeCell ref="F305:H305"/>
     <mergeCell ref="K306:L306"/>
     <mergeCell ref="K309:L309"/>
     <mergeCell ref="K312:L312"/>
     <mergeCell ref="F320:I320"/>
-    <mergeCell ref="K294:L294"/>
-    <mergeCell ref="K297:L297"/>
-    <mergeCell ref="K300:L300"/>
-    <mergeCell ref="K303:L303"/>
-    <mergeCell ref="F304:H304"/>
-    <mergeCell ref="K279:L279"/>
-    <mergeCell ref="K282:L282"/>
-    <mergeCell ref="K285:L285"/>
-    <mergeCell ref="K288:L288"/>
-    <mergeCell ref="K291:L291"/>
-    <mergeCell ref="K266:L266"/>
-    <mergeCell ref="F267:G267"/>
-    <mergeCell ref="K270:L270"/>
-    <mergeCell ref="K273:L273"/>
-    <mergeCell ref="K276:L276"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
   <pageSetup firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -20845,10 +20847,10 @@
       <c r="C84" s="1" t="s">
         <v>1561</v>
       </c>
-      <c r="D84" s="22" t="s">
+      <c r="D84" s="24" t="s">
         <v>1562</v>
       </c>
-      <c r="E84" s="22"/>
+      <c r="E84" s="24"/>
     </row>
     <row r="85" spans="1:6">
       <c r="A85" s="1" t="s">
@@ -20860,11 +20862,11 @@
       <c r="C85" s="1" t="s">
         <v>1563</v>
       </c>
-      <c r="D85" s="22" t="s">
+      <c r="D85" s="24" t="s">
         <v>1564</v>
       </c>
-      <c r="E85" s="22"/>
-      <c r="F85" s="22"/>
+      <c r="E85" s="24"/>
+      <c r="F85" s="24"/>
     </row>
     <row r="86" spans="1:6">
       <c r="A86" s="1" t="s">
@@ -20890,10 +20892,10 @@
       <c r="C87" s="1" t="s">
         <v>1567</v>
       </c>
-      <c r="D87" s="22" t="s">
+      <c r="D87" s="24" t="s">
         <v>1568</v>
       </c>
-      <c r="E87" s="22"/>
+      <c r="E87" s="24"/>
     </row>
     <row r="88" spans="1:6">
       <c r="A88" s="1" t="s">

--- a/forms/app/infant_child.xlsx
+++ b/forms/app/infant_child.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2570" uniqueCount="1633">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2570" uniqueCount="1634">
   <si>
     <t>type</t>
   </si>
@@ -5361,6 +5361,9 @@
   </si>
   <si>
     <t>not(selected(${baby_times_breastfed_daily},"five_more_times_day")) and ${age_days} &lt; (${month} * 6) and (not(selected(${exclusive_breastfeeding},"yes")) or not(selected(${exclusive_breastfeeding_multiple_choice},"none")))</t>
+  </si>
+  <si>
+    <t>${age_days} &lt;= (${month} * 24) and selected(${currently_breastfeeding},"yes")</t>
   </si>
 </sst>
 </file>
@@ -11282,7 +11285,7 @@
         <v>171</v>
       </c>
       <c r="F197" s="23" t="s">
-        <v>1631</v>
+        <v>1633</v>
       </c>
       <c r="G197" s="2"/>
       <c r="H197" s="2"/>
@@ -19637,27 +19640,27 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="K266:L266"/>
-    <mergeCell ref="F267:G267"/>
-    <mergeCell ref="K270:L270"/>
-    <mergeCell ref="K273:L273"/>
-    <mergeCell ref="K276:L276"/>
-    <mergeCell ref="K279:L279"/>
-    <mergeCell ref="K282:L282"/>
-    <mergeCell ref="K285:L285"/>
-    <mergeCell ref="K288:L288"/>
-    <mergeCell ref="K291:L291"/>
-    <mergeCell ref="K294:L294"/>
-    <mergeCell ref="K297:L297"/>
-    <mergeCell ref="K300:L300"/>
-    <mergeCell ref="K303:L303"/>
-    <mergeCell ref="F304:H304"/>
     <mergeCell ref="L322:O322"/>
     <mergeCell ref="F305:H305"/>
     <mergeCell ref="K306:L306"/>
     <mergeCell ref="K309:L309"/>
     <mergeCell ref="K312:L312"/>
     <mergeCell ref="F320:I320"/>
+    <mergeCell ref="K294:L294"/>
+    <mergeCell ref="K297:L297"/>
+    <mergeCell ref="K300:L300"/>
+    <mergeCell ref="K303:L303"/>
+    <mergeCell ref="F304:H304"/>
+    <mergeCell ref="K279:L279"/>
+    <mergeCell ref="K282:L282"/>
+    <mergeCell ref="K285:L285"/>
+    <mergeCell ref="K288:L288"/>
+    <mergeCell ref="K291:L291"/>
+    <mergeCell ref="K266:L266"/>
+    <mergeCell ref="F267:G267"/>
+    <mergeCell ref="K270:L270"/>
+    <mergeCell ref="K273:L273"/>
+    <mergeCell ref="K276:L276"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
   <pageSetup firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/forms/app/infant_child.xlsx
+++ b/forms/app/infant_child.xlsx
@@ -5356,10 +5356,10 @@
 ${refer_slow_to_learn_specifics_flag}=1, 1, 0)</t>
   </si>
   <si>
-    <t>I’m now going to screen your baby for neonatal danger signs. If your child has dange signs, I shall refer you to a nearest health facility so that they can receive the appropriate medical attention.  Has your baby exhibited any of these symptoms within the past 24 hours?</t>
-  </si>
-  <si>
     <t>Nahitaji kumchunguza mtoto wako dalili za hatari.  Iwapo mtoto ataonesha ana dalili za hatari, atapatiwa rufaa (kwenda kituo cha afya) na kuunganishwa na mtoa huduma kwenye kituo kilicho karibu naye. Je, mwanao ameonesha dalili zote kati ya hizi katika masaa 24 yaliyo pita?</t>
+  </si>
+  <si>
+    <t>I’m now going to screen your baby for neonatal danger signs. If your child has danger signs, I shall refer him/her to a nearest health facility so that they can receive the appropriate medical attention.  Has your baby exhibited any of these symptoms within the past 24 hours?</t>
   </si>
 </sst>
 </file>
@@ -8701,10 +8701,10 @@
         <v>240</v>
       </c>
       <c r="C106" s="2" t="s">
+        <v>1632</v>
+      </c>
+      <c r="D106" s="2" t="s">
         <v>1631</v>
-      </c>
-      <c r="D106" s="2" t="s">
-        <v>1632</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" s="1"/>
@@ -19621,6 +19621,11 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="F305:H305"/>
+    <mergeCell ref="K306:L306"/>
+    <mergeCell ref="K309:L309"/>
+    <mergeCell ref="K312:L312"/>
+    <mergeCell ref="F320:I320"/>
     <mergeCell ref="F322:I322"/>
     <mergeCell ref="K266:L266"/>
     <mergeCell ref="F267:G267"/>
@@ -19637,11 +19642,6 @@
     <mergeCell ref="K300:L300"/>
     <mergeCell ref="K303:L303"/>
     <mergeCell ref="F304:H304"/>
-    <mergeCell ref="F305:H305"/>
-    <mergeCell ref="K306:L306"/>
-    <mergeCell ref="K309:L309"/>
-    <mergeCell ref="K312:L312"/>
-    <mergeCell ref="F320:I320"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
   <pageSetup firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/forms/app/infant_child.xlsx
+++ b/forms/app/infant_child.xlsx
@@ -5337,12 +5337,6 @@
     <t>missing_vaccine_note</t>
   </si>
   <si>
-    <t xml:space="preserve">Please take your child to health facility to get the appropriate vaccinations. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tafadhali mpeleke mwanao kituo cha afya ili apatiwe chanjo kamili. </t>
-  </si>
-  <si>
     <t>selected(${has_health_card},"no") and ${age_years} &lt; 2 or selected(${vaccines_up_to_date},"no")</t>
   </si>
   <si>
@@ -5360,6 +5354,14 @@
   </si>
   <si>
     <t>I’m now going to screen your baby for neonatal danger signs. If your child has danger signs, I shall refer him/her to a nearest health facility so that they can receive the appropriate medical attention.  Has your baby exhibited any of these symptoms within the past 24 hours?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">At this stage, your child is supposed to get the vaccine. Make sure you go to  the facility to seek the vaccine for your child. In case you go and don't find one  because of un avoided conditions, make sure you return once again so that your kid could be vaccinated. This is really
+important for your child's health.
+</t>
+  </si>
+  <si>
+    <t>Katika hatua hii mtoto wako anapaswa kupatiwa chanjo, Hakikisha unaenda kituo cha afya ili apatiwe. Ikitokea hakupatiwa kutokana na sababu zisizoepukika, hakikisha unamrudisha tena Kituoni ili apatiwe chanjo.Hii ni muhimu sana kwa afya ya mtoto wako</t>
   </si>
 </sst>
 </file>
@@ -8701,10 +8703,10 @@
         <v>240</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>1632</v>
+        <v>1630</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>1631</v>
+        <v>1629</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" s="1"/>
@@ -15460,22 +15462,22 @@
       <c r="Y321" s="6"/>
       <c r="Z321" s="6"/>
     </row>
-    <row r="322" spans="1:26">
+    <row r="322" spans="1:26" ht="65">
       <c r="A322" s="13" t="s">
         <v>139</v>
       </c>
       <c r="B322" s="1" t="s">
         <v>1626</v>
       </c>
-      <c r="C322" s="1" t="s">
-        <v>1627</v>
+      <c r="C322" s="9" t="s">
+        <v>1631</v>
       </c>
       <c r="D322" s="1" t="s">
-        <v>1628</v>
+        <v>1632</v>
       </c>
       <c r="E322" s="1"/>
       <c r="F322" s="25" t="s">
-        <v>1629</v>
+        <v>1627</v>
       </c>
       <c r="G322" s="25"/>
       <c r="H322" s="25"/>
@@ -19397,7 +19399,7 @@
         <v>1269</v>
       </c>
       <c r="L456" s="9" t="s">
-        <v>1630</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="457" spans="1:26">

--- a/forms/app/infant_child.xlsx
+++ b/forms/app/infant_child.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20377"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20384"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\D-tree\config-dtree-newrepo\config-dtree\forms\app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACD102F3-5614-4ABD-B004-664E272E2A52}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DF0196B-5104-4C82-8159-5385F0B79D0A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16385" windowHeight="8190" tabRatio="392" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,15 +18,15 @@
     <sheet name="settings" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">survey!$B$1:$B$494</definedName>
-    <definedName name="Z_781EBA2C_D8B1_4B7C_8F0C_A942CACA9398_.wvu.FilterData" localSheetId="0">survey!$A$406:$Z$437</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">survey!$B$1:$B$495</definedName>
+    <definedName name="Z_781EBA2C_D8B1_4B7C_8F0C_A942CACA9398_.wvu.FilterData" localSheetId="0">survey!$A$407:$Z$438</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2652" uniqueCount="1675">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2654" uniqueCount="1676">
   <si>
     <t>type</t>
   </si>
@@ -5538,6 +5538,9 @@
   </si>
   <si>
     <t>${age_days} &gt; (${month} * 6)</t>
+  </si>
+  <si>
+    <t>confirm_nutrition_counseling_c</t>
   </si>
 </sst>
 </file>
@@ -5638,7 +5641,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
@@ -5685,6 +5688,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6034,7 +6038,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z494"/>
+  <dimension ref="A1:Z495"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="28.6796875" customWidth="1"/>
@@ -13673,21 +13677,23 @@
     </row>
     <row r="281" spans="1:26">
       <c r="A281" s="1" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B281" s="1" t="s">
-        <v>590</v>
-      </c>
-      <c r="C281" s="1"/>
-      <c r="D281" s="1"/>
+        <v>1675</v>
+      </c>
+      <c r="C281" s="10"/>
+      <c r="D281" s="10"/>
       <c r="E281" s="1"/>
-      <c r="F281" s="1"/>
+      <c r="F281" s="30"/>
       <c r="G281" s="1"/>
       <c r="H281" s="1"/>
       <c r="I281" s="1"/>
       <c r="J281" s="1"/>
       <c r="K281" s="1"/>
-      <c r="L281" s="1"/>
+      <c r="L281" s="1">
+        <v>1</v>
+      </c>
       <c r="M281" s="1"/>
       <c r="N281" s="1"/>
       <c r="O281" s="1"/>
@@ -13696,24 +13702,16 @@
     </row>
     <row r="282" spans="1:26">
       <c r="A282" s="1" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>614</v>
-      </c>
-      <c r="C282" s="1" t="s">
-        <v>615</v>
-      </c>
-      <c r="D282" s="1" t="s">
-        <v>616</v>
-      </c>
+        <v>590</v>
+      </c>
+      <c r="C282" s="1"/>
+      <c r="D282" s="1"/>
       <c r="E282" s="1"/>
-      <c r="F282" s="1" t="s">
-        <v>460</v>
-      </c>
-      <c r="G282" s="1" t="s">
-        <v>147</v>
-      </c>
+      <c r="F282" s="1"/>
+      <c r="G282" s="1"/>
       <c r="H282" s="1"/>
       <c r="I282" s="1"/>
       <c r="J282" s="1"/>
@@ -13724,34 +13722,27 @@
       <c r="O282" s="1"/>
       <c r="P282" s="1"/>
       <c r="Q282" s="1"/>
-      <c r="R282" s="6"/>
-      <c r="S282" s="6"/>
-      <c r="T282" s="6"/>
-      <c r="U282" s="6"/>
-      <c r="V282" s="6"/>
-      <c r="W282" s="6"/>
-      <c r="X282" s="6"/>
-      <c r="Y282" s="6"/>
-      <c r="Z282" s="6"/>
     </row>
     <row r="283" spans="1:26">
       <c r="A283" s="1" t="s">
-        <v>139</v>
+        <v>21</v>
       </c>
       <c r="B283" s="1" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="C283" s="1" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="E283" s="1"/>
       <c r="F283" s="1" t="s">
-        <v>620</v>
-      </c>
-      <c r="G283" s="1"/>
+        <v>460</v>
+      </c>
+      <c r="G283" s="1" t="s">
+        <v>147</v>
+      </c>
       <c r="H283" s="1"/>
       <c r="I283" s="1"/>
       <c r="J283" s="1"/>
@@ -13777,13 +13768,13 @@
         <v>139</v>
       </c>
       <c r="B284" s="1" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="C284" s="1" t="s">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="E284" s="1"/>
       <c r="F284" s="1" t="s">
@@ -13815,16 +13806,18 @@
         <v>139</v>
       </c>
       <c r="B285" s="1" t="s">
-        <v>624</v>
-      </c>
-      <c r="C285" s="11" t="s">
-        <v>625</v>
-      </c>
-      <c r="D285" s="11" t="s">
-        <v>626</v>
+        <v>621</v>
+      </c>
+      <c r="C285" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="D285" s="1" t="s">
+        <v>623</v>
       </c>
       <c r="E285" s="1"/>
-      <c r="F285" s="1"/>
+      <c r="F285" s="1" t="s">
+        <v>620</v>
+      </c>
       <c r="G285" s="1"/>
       <c r="H285" s="1"/>
       <c r="I285" s="1"/>
@@ -13848,23 +13841,19 @@
     </row>
     <row r="286" spans="1:26">
       <c r="A286" s="1" t="s">
-        <v>166</v>
+        <v>139</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>627</v>
-      </c>
-      <c r="C286" s="1" t="s">
-        <v>628</v>
-      </c>
-      <c r="D286" s="1" t="s">
-        <v>629</v>
-      </c>
-      <c r="E286" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F286" s="1" t="s">
-        <v>630</v>
-      </c>
+        <v>624</v>
+      </c>
+      <c r="C286" s="11" t="s">
+        <v>625</v>
+      </c>
+      <c r="D286" s="11" t="s">
+        <v>626</v>
+      </c>
+      <c r="E286" s="1"/>
+      <c r="F286" s="1"/>
       <c r="G286" s="1"/>
       <c r="H286" s="1"/>
       <c r="I286" s="1"/>
@@ -13888,20 +13877,22 @@
     </row>
     <row r="287" spans="1:26">
       <c r="A287" s="1" t="s">
-        <v>139</v>
+        <v>166</v>
       </c>
       <c r="B287" s="1" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="C287" s="1" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>633</v>
-      </c>
-      <c r="E287" s="1"/>
+        <v>629</v>
+      </c>
+      <c r="E287" s="1" t="s">
+        <v>170</v>
+      </c>
       <c r="F287" s="1" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="G287" s="1"/>
       <c r="H287" s="1"/>
@@ -13926,18 +13917,20 @@
     </row>
     <row r="288" spans="1:26">
       <c r="A288" s="1" t="s">
-        <v>21</v>
+        <v>139</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="C288" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D288" s="6"/>
+        <v>632</v>
+      </c>
+      <c r="D288" s="1" t="s">
+        <v>633</v>
+      </c>
       <c r="E288" s="1"/>
       <c r="F288" s="1" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="G288" s="1"/>
       <c r="H288" s="1"/>
@@ -13962,19 +13955,19 @@
     </row>
     <row r="289" spans="1:26">
       <c r="A289" s="1" t="s">
-        <v>139</v>
+        <v>21</v>
       </c>
       <c r="B289" s="1" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="C289" s="1" t="s">
-        <v>638</v>
-      </c>
-      <c r="D289" s="1" t="s">
-        <v>639</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="D289" s="6"/>
       <c r="E289" s="1"/>
-      <c r="F289" s="1"/>
+      <c r="F289" s="1" t="s">
+        <v>636</v>
+      </c>
       <c r="G289" s="1"/>
       <c r="H289" s="1"/>
       <c r="I289" s="1"/>
@@ -14001,18 +13994,16 @@
         <v>139</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="C290" s="1" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="E290" s="1"/>
-      <c r="F290" s="1" t="s">
-        <v>643</v>
-      </c>
+      <c r="F290" s="1"/>
       <c r="G290" s="1"/>
       <c r="H290" s="1"/>
       <c r="I290" s="1"/>
@@ -14036,16 +14027,16 @@
     </row>
     <row r="291" spans="1:26">
       <c r="A291" s="1" t="s">
-        <v>166</v>
+        <v>139</v>
       </c>
       <c r="B291" s="1" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="C291" s="1" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="E291" s="1"/>
       <c r="F291" s="1" t="s">
@@ -14074,35 +14065,27 @@
     </row>
     <row r="292" spans="1:26">
       <c r="A292" s="1" t="s">
-        <v>647</v>
+        <v>166</v>
       </c>
       <c r="B292" s="1" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="C292" s="1" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>650</v>
-      </c>
-      <c r="E292" s="1" t="s">
-        <v>170</v>
-      </c>
+        <v>646</v>
+      </c>
+      <c r="E292" s="1"/>
       <c r="F292" s="1" t="s">
-        <v>651</v>
+        <v>643</v>
       </c>
       <c r="G292" s="1"/>
       <c r="H292" s="1"/>
-      <c r="I292" s="1" t="s">
-        <v>652</v>
-      </c>
-      <c r="J292" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="K292" s="30" t="s">
-        <v>654</v>
-      </c>
-      <c r="L292" s="30"/>
+      <c r="I292" s="1"/>
+      <c r="J292" s="1"/>
+      <c r="K292" s="1"/>
+      <c r="L292" s="1"/>
       <c r="M292" s="1"/>
       <c r="N292" s="1"/>
       <c r="O292" s="1"/>
@@ -14120,27 +14103,35 @@
     </row>
     <row r="293" spans="1:26">
       <c r="A293" s="1" t="s">
-        <v>139</v>
+        <v>647</v>
       </c>
       <c r="B293" s="1" t="s">
-        <v>655</v>
-      </c>
-      <c r="C293" s="4" t="s">
-        <v>656</v>
-      </c>
-      <c r="D293" s="4" t="s">
-        <v>657</v>
-      </c>
-      <c r="E293" s="1"/>
-      <c r="F293" s="30" t="s">
-        <v>658</v>
-      </c>
-      <c r="G293" s="30"/>
+        <v>648</v>
+      </c>
+      <c r="C293" s="1" t="s">
+        <v>649</v>
+      </c>
+      <c r="D293" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="E293" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F293" s="1" t="s">
+        <v>651</v>
+      </c>
+      <c r="G293" s="1"/>
       <c r="H293" s="1"/>
-      <c r="I293" s="1"/>
-      <c r="J293" s="1"/>
-      <c r="K293" s="1"/>
-      <c r="L293" s="1"/>
+      <c r="I293" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="J293" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="K293" s="32" t="s">
+        <v>654</v>
+      </c>
+      <c r="L293" s="32"/>
       <c r="M293" s="1"/>
       <c r="N293" s="1"/>
       <c r="O293" s="1"/>
@@ -14161,19 +14152,19 @@
         <v>139</v>
       </c>
       <c r="B294" s="1" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="C294" s="4" t="s">
-        <v>642</v>
+        <v>656</v>
       </c>
       <c r="D294" s="4" t="s">
-        <v>642</v>
+        <v>657</v>
       </c>
       <c r="E294" s="1"/>
-      <c r="F294" s="1" t="s">
-        <v>660</v>
-      </c>
-      <c r="G294" s="1"/>
+      <c r="F294" s="32" t="s">
+        <v>658</v>
+      </c>
+      <c r="G294" s="32"/>
       <c r="H294" s="1"/>
       <c r="I294" s="1"/>
       <c r="J294" s="1"/>
@@ -14196,20 +14187,18 @@
     </row>
     <row r="295" spans="1:26">
       <c r="A295" s="1" t="s">
-        <v>166</v>
+        <v>139</v>
       </c>
       <c r="B295" s="1" t="s">
-        <v>661</v>
-      </c>
-      <c r="C295" s="13" t="s">
-        <v>662</v>
-      </c>
-      <c r="D295" s="1" t="s">
-        <v>663</v>
-      </c>
-      <c r="E295" s="1" t="s">
-        <v>170</v>
-      </c>
+        <v>659</v>
+      </c>
+      <c r="C295" s="4" t="s">
+        <v>642</v>
+      </c>
+      <c r="D295" s="4" t="s">
+        <v>642</v>
+      </c>
+      <c r="E295" s="1"/>
       <c r="F295" s="1" t="s">
         <v>660</v>
       </c>
@@ -14236,33 +14225,29 @@
     </row>
     <row r="296" spans="1:26">
       <c r="A296" s="1" t="s">
-        <v>647</v>
+        <v>166</v>
       </c>
       <c r="B296" s="1" t="s">
-        <v>664</v>
-      </c>
-      <c r="C296" s="1" t="s">
-        <v>665</v>
+        <v>661</v>
+      </c>
+      <c r="C296" s="13" t="s">
+        <v>662</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>666</v>
-      </c>
-      <c r="E296" s="1"/>
+        <v>663</v>
+      </c>
+      <c r="E296" s="1" t="s">
+        <v>170</v>
+      </c>
       <c r="F296" s="1" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="G296" s="1"/>
       <c r="H296" s="1"/>
-      <c r="I296" s="1" t="s">
-        <v>652</v>
-      </c>
-      <c r="J296" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="K296" s="30" t="s">
-        <v>654</v>
-      </c>
-      <c r="L296" s="30"/>
+      <c r="I296" s="1"/>
+      <c r="J296" s="1"/>
+      <c r="K296" s="1"/>
+      <c r="L296" s="1"/>
       <c r="M296" s="1"/>
       <c r="N296" s="1"/>
       <c r="O296" s="1"/>
@@ -14280,27 +14265,33 @@
     </row>
     <row r="297" spans="1:26">
       <c r="A297" s="1" t="s">
-        <v>139</v>
+        <v>647</v>
       </c>
       <c r="B297" s="1" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="C297" s="1" t="s">
-        <v>641</v>
+        <v>665</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>641</v>
+        <v>666</v>
       </c>
       <c r="E297" s="1"/>
       <c r="F297" s="1" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="G297" s="1"/>
       <c r="H297" s="1"/>
-      <c r="I297" s="1"/>
-      <c r="J297" s="1"/>
-      <c r="K297" s="1"/>
-      <c r="L297" s="1"/>
+      <c r="I297" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="J297" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="K297" s="32" t="s">
+        <v>654</v>
+      </c>
+      <c r="L297" s="32"/>
       <c r="M297" s="1"/>
       <c r="N297" s="1"/>
       <c r="O297" s="1"/>
@@ -14318,26 +14309,24 @@
     </row>
     <row r="298" spans="1:26">
       <c r="A298" s="1" t="s">
-        <v>166</v>
+        <v>139</v>
       </c>
       <c r="B298" s="1" t="s">
-        <v>670</v>
-      </c>
-      <c r="C298" s="13" t="s">
-        <v>671</v>
+        <v>668</v>
+      </c>
+      <c r="C298" s="1" t="s">
+        <v>641</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>672</v>
-      </c>
-      <c r="E298" s="1" t="s">
-        <v>170</v>
-      </c>
+        <v>641</v>
+      </c>
+      <c r="E298" s="1"/>
       <c r="F298" s="1" t="s">
         <v>669</v>
       </c>
       <c r="G298" s="1"/>
       <c r="H298" s="1"/>
-      <c r="I298" s="6"/>
+      <c r="I298" s="1"/>
       <c r="J298" s="1"/>
       <c r="K298" s="1"/>
       <c r="L298" s="1"/>
@@ -14358,33 +14347,29 @@
     </row>
     <row r="299" spans="1:26">
       <c r="A299" s="1" t="s">
-        <v>647</v>
+        <v>166</v>
       </c>
       <c r="B299" s="1" t="s">
-        <v>673</v>
-      </c>
-      <c r="C299" s="1" t="s">
-        <v>674</v>
+        <v>670</v>
+      </c>
+      <c r="C299" s="13" t="s">
+        <v>671</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>675</v>
-      </c>
-      <c r="E299" s="1"/>
+        <v>672</v>
+      </c>
+      <c r="E299" s="1" t="s">
+        <v>170</v>
+      </c>
       <c r="F299" s="1" t="s">
-        <v>676</v>
+        <v>669</v>
       </c>
       <c r="G299" s="1"/>
       <c r="H299" s="1"/>
-      <c r="I299" s="1" t="s">
-        <v>652</v>
-      </c>
-      <c r="J299" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="K299" s="30" t="s">
-        <v>654</v>
-      </c>
-      <c r="L299" s="30"/>
+      <c r="I299" s="6"/>
+      <c r="J299" s="1"/>
+      <c r="K299" s="1"/>
+      <c r="L299" s="1"/>
       <c r="M299" s="1"/>
       <c r="N299" s="1"/>
       <c r="O299" s="1"/>
@@ -14402,27 +14387,33 @@
     </row>
     <row r="300" spans="1:26">
       <c r="A300" s="1" t="s">
-        <v>139</v>
+        <v>647</v>
       </c>
       <c r="B300" s="1" t="s">
-        <v>677</v>
-      </c>
-      <c r="C300" s="4" t="s">
-        <v>642</v>
-      </c>
-      <c r="D300" s="4" t="s">
-        <v>642</v>
+        <v>673</v>
+      </c>
+      <c r="C300" s="1" t="s">
+        <v>674</v>
+      </c>
+      <c r="D300" s="1" t="s">
+        <v>675</v>
       </c>
       <c r="E300" s="1"/>
       <c r="F300" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="G300" s="1"/>
       <c r="H300" s="1"/>
-      <c r="I300" s="1"/>
-      <c r="J300" s="1"/>
-      <c r="K300" s="1"/>
-      <c r="L300" s="1"/>
+      <c r="I300" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="J300" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="K300" s="32" t="s">
+        <v>654</v>
+      </c>
+      <c r="L300" s="32"/>
       <c r="M300" s="1"/>
       <c r="N300" s="1"/>
       <c r="O300" s="1"/>
@@ -14440,20 +14431,18 @@
     </row>
     <row r="301" spans="1:26">
       <c r="A301" s="1" t="s">
-        <v>166</v>
+        <v>139</v>
       </c>
       <c r="B301" s="1" t="s">
-        <v>679</v>
-      </c>
-      <c r="C301" s="13" t="s">
-        <v>680</v>
-      </c>
-      <c r="D301" s="1" t="s">
-        <v>681</v>
-      </c>
-      <c r="E301" s="1" t="s">
-        <v>170</v>
-      </c>
+        <v>677</v>
+      </c>
+      <c r="C301" s="4" t="s">
+        <v>642</v>
+      </c>
+      <c r="D301" s="4" t="s">
+        <v>642</v>
+      </c>
+      <c r="E301" s="1"/>
       <c r="F301" s="1" t="s">
         <v>678</v>
       </c>
@@ -14480,33 +14469,29 @@
     </row>
     <row r="302" spans="1:26">
       <c r="A302" s="1" t="s">
-        <v>647</v>
+        <v>166</v>
       </c>
       <c r="B302" s="1" t="s">
-        <v>682</v>
-      </c>
-      <c r="C302" s="1" t="s">
-        <v>683</v>
+        <v>679</v>
+      </c>
+      <c r="C302" s="13" t="s">
+        <v>680</v>
       </c>
       <c r="D302" s="1" t="s">
-        <v>684</v>
-      </c>
-      <c r="E302" s="1"/>
+        <v>681</v>
+      </c>
+      <c r="E302" s="1" t="s">
+        <v>170</v>
+      </c>
       <c r="F302" s="1" t="s">
-        <v>685</v>
+        <v>678</v>
       </c>
       <c r="G302" s="1"/>
       <c r="H302" s="1"/>
-      <c r="I302" s="1" t="s">
-        <v>652</v>
-      </c>
-      <c r="J302" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="K302" s="30" t="s">
-        <v>654</v>
-      </c>
-      <c r="L302" s="30"/>
+      <c r="I302" s="1"/>
+      <c r="J302" s="1"/>
+      <c r="K302" s="1"/>
+      <c r="L302" s="1"/>
       <c r="M302" s="1"/>
       <c r="N302" s="1"/>
       <c r="O302" s="1"/>
@@ -14524,27 +14509,33 @@
     </row>
     <row r="303" spans="1:26">
       <c r="A303" s="1" t="s">
-        <v>139</v>
+        <v>647</v>
       </c>
       <c r="B303" s="1" t="s">
-        <v>686</v>
-      </c>
-      <c r="C303" s="4" t="s">
-        <v>642</v>
-      </c>
-      <c r="D303" s="4" t="s">
-        <v>642</v>
+        <v>682</v>
+      </c>
+      <c r="C303" s="1" t="s">
+        <v>683</v>
+      </c>
+      <c r="D303" s="1" t="s">
+        <v>684</v>
       </c>
       <c r="E303" s="1"/>
       <c r="F303" s="1" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="G303" s="1"/>
       <c r="H303" s="1"/>
-      <c r="I303" s="1"/>
-      <c r="J303" s="1"/>
-      <c r="K303" s="1"/>
-      <c r="L303" s="1"/>
+      <c r="I303" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="J303" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="K303" s="32" t="s">
+        <v>654</v>
+      </c>
+      <c r="L303" s="32"/>
       <c r="M303" s="1"/>
       <c r="N303" s="1"/>
       <c r="O303" s="1"/>
@@ -14562,20 +14553,18 @@
     </row>
     <row r="304" spans="1:26">
       <c r="A304" s="1" t="s">
-        <v>166</v>
+        <v>139</v>
       </c>
       <c r="B304" s="1" t="s">
-        <v>688</v>
-      </c>
-      <c r="C304" s="13" t="s">
-        <v>689</v>
-      </c>
-      <c r="D304" s="1" t="s">
-        <v>690</v>
-      </c>
-      <c r="E304" s="1" t="s">
-        <v>170</v>
-      </c>
+        <v>686</v>
+      </c>
+      <c r="C304" s="4" t="s">
+        <v>642</v>
+      </c>
+      <c r="D304" s="4" t="s">
+        <v>642</v>
+      </c>
+      <c r="E304" s="1"/>
       <c r="F304" s="1" t="s">
         <v>687</v>
       </c>
@@ -14602,33 +14591,29 @@
     </row>
     <row r="305" spans="1:26">
       <c r="A305" s="1" t="s">
-        <v>647</v>
+        <v>166</v>
       </c>
       <c r="B305" s="1" t="s">
-        <v>691</v>
-      </c>
-      <c r="C305" s="1" t="s">
-        <v>692</v>
+        <v>688</v>
+      </c>
+      <c r="C305" s="13" t="s">
+        <v>689</v>
       </c>
       <c r="D305" s="1" t="s">
-        <v>693</v>
-      </c>
-      <c r="E305" s="1"/>
+        <v>690</v>
+      </c>
+      <c r="E305" s="1" t="s">
+        <v>170</v>
+      </c>
       <c r="F305" s="1" t="s">
-        <v>694</v>
+        <v>687</v>
       </c>
       <c r="G305" s="1"/>
       <c r="H305" s="1"/>
-      <c r="I305" s="1" t="s">
-        <v>652</v>
-      </c>
-      <c r="J305" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="K305" s="30" t="s">
-        <v>654</v>
-      </c>
-      <c r="L305" s="30"/>
+      <c r="I305" s="1"/>
+      <c r="J305" s="1"/>
+      <c r="K305" s="1"/>
+      <c r="L305" s="1"/>
       <c r="M305" s="1"/>
       <c r="N305" s="1"/>
       <c r="O305" s="1"/>
@@ -14646,27 +14631,33 @@
     </row>
     <row r="306" spans="1:26">
       <c r="A306" s="1" t="s">
-        <v>139</v>
+        <v>647</v>
       </c>
       <c r="B306" s="1" t="s">
-        <v>695</v>
-      </c>
-      <c r="C306" s="4" t="s">
-        <v>642</v>
-      </c>
-      <c r="D306" s="4" t="s">
-        <v>642</v>
+        <v>691</v>
+      </c>
+      <c r="C306" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="D306" s="1" t="s">
+        <v>693</v>
       </c>
       <c r="E306" s="1"/>
       <c r="F306" s="1" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="G306" s="1"/>
       <c r="H306" s="1"/>
-      <c r="I306" s="1"/>
-      <c r="J306" s="6"/>
-      <c r="K306" s="1"/>
-      <c r="L306" s="1"/>
+      <c r="I306" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="J306" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="K306" s="32" t="s">
+        <v>654</v>
+      </c>
+      <c r="L306" s="32"/>
       <c r="M306" s="1"/>
       <c r="N306" s="1"/>
       <c r="O306" s="1"/>
@@ -14684,27 +14675,25 @@
     </row>
     <row r="307" spans="1:26">
       <c r="A307" s="1" t="s">
-        <v>166</v>
+        <v>139</v>
       </c>
       <c r="B307" s="1" t="s">
-        <v>697</v>
-      </c>
-      <c r="C307" s="13" t="s">
-        <v>698</v>
-      </c>
-      <c r="D307" s="1" t="s">
-        <v>699</v>
-      </c>
-      <c r="E307" s="1" t="s">
-        <v>170</v>
-      </c>
+        <v>695</v>
+      </c>
+      <c r="C307" s="4" t="s">
+        <v>642</v>
+      </c>
+      <c r="D307" s="4" t="s">
+        <v>642</v>
+      </c>
+      <c r="E307" s="1"/>
       <c r="F307" s="1" t="s">
         <v>696</v>
       </c>
       <c r="G307" s="1"/>
       <c r="H307" s="1"/>
       <c r="I307" s="1"/>
-      <c r="J307" s="1"/>
+      <c r="J307" s="6"/>
       <c r="K307" s="1"/>
       <c r="L307" s="1"/>
       <c r="M307" s="1"/>
@@ -14724,33 +14713,29 @@
     </row>
     <row r="308" spans="1:26">
       <c r="A308" s="1" t="s">
-        <v>647</v>
+        <v>166</v>
       </c>
       <c r="B308" s="1" t="s">
-        <v>700</v>
-      </c>
-      <c r="C308" s="1" t="s">
-        <v>701</v>
+        <v>697</v>
+      </c>
+      <c r="C308" s="13" t="s">
+        <v>698</v>
       </c>
       <c r="D308" s="1" t="s">
-        <v>702</v>
-      </c>
-      <c r="E308" s="1"/>
+        <v>699</v>
+      </c>
+      <c r="E308" s="1" t="s">
+        <v>170</v>
+      </c>
       <c r="F308" s="1" t="s">
-        <v>703</v>
+        <v>696</v>
       </c>
       <c r="G308" s="1"/>
       <c r="H308" s="1"/>
-      <c r="I308" s="1" t="s">
-        <v>652</v>
-      </c>
-      <c r="J308" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="K308" s="30" t="s">
-        <v>654</v>
-      </c>
-      <c r="L308" s="30"/>
+      <c r="I308" s="1"/>
+      <c r="J308" s="1"/>
+      <c r="K308" s="1"/>
+      <c r="L308" s="1"/>
       <c r="M308" s="1"/>
       <c r="N308" s="1"/>
       <c r="O308" s="1"/>
@@ -14768,27 +14753,33 @@
     </row>
     <row r="309" spans="1:26">
       <c r="A309" s="1" t="s">
-        <v>139</v>
+        <v>647</v>
       </c>
       <c r="B309" s="1" t="s">
-        <v>704</v>
-      </c>
-      <c r="C309" s="4" t="s">
-        <v>642</v>
-      </c>
-      <c r="D309" s="4" t="s">
-        <v>642</v>
+        <v>700</v>
+      </c>
+      <c r="C309" s="1" t="s">
+        <v>701</v>
+      </c>
+      <c r="D309" s="1" t="s">
+        <v>702</v>
       </c>
       <c r="E309" s="1"/>
       <c r="F309" s="1" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="G309" s="1"/>
       <c r="H309" s="1"/>
-      <c r="I309" s="1"/>
-      <c r="J309" s="1"/>
-      <c r="K309" s="1"/>
-      <c r="L309" s="1"/>
+      <c r="I309" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="J309" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="K309" s="32" t="s">
+        <v>654</v>
+      </c>
+      <c r="L309" s="32"/>
       <c r="M309" s="1"/>
       <c r="N309" s="1"/>
       <c r="O309" s="1"/>
@@ -14806,20 +14797,18 @@
     </row>
     <row r="310" spans="1:26">
       <c r="A310" s="1" t="s">
-        <v>166</v>
+        <v>139</v>
       </c>
       <c r="B310" s="1" t="s">
-        <v>706</v>
-      </c>
-      <c r="C310" s="13" t="s">
-        <v>707</v>
-      </c>
-      <c r="D310" s="1" t="s">
-        <v>708</v>
-      </c>
-      <c r="E310" s="1" t="s">
-        <v>170</v>
-      </c>
+        <v>704</v>
+      </c>
+      <c r="C310" s="4" t="s">
+        <v>642</v>
+      </c>
+      <c r="D310" s="4" t="s">
+        <v>642</v>
+      </c>
+      <c r="E310" s="1"/>
       <c r="F310" s="1" t="s">
         <v>705</v>
       </c>
@@ -14846,33 +14835,29 @@
     </row>
     <row r="311" spans="1:26">
       <c r="A311" s="1" t="s">
-        <v>647</v>
+        <v>166</v>
       </c>
       <c r="B311" s="1" t="s">
-        <v>709</v>
-      </c>
-      <c r="C311" s="1" t="s">
-        <v>710</v>
+        <v>706</v>
+      </c>
+      <c r="C311" s="13" t="s">
+        <v>707</v>
       </c>
       <c r="D311" s="1" t="s">
-        <v>711</v>
-      </c>
-      <c r="E311" s="1"/>
+        <v>708</v>
+      </c>
+      <c r="E311" s="1" t="s">
+        <v>170</v>
+      </c>
       <c r="F311" s="1" t="s">
-        <v>712</v>
+        <v>705</v>
       </c>
       <c r="G311" s="1"/>
       <c r="H311" s="1"/>
-      <c r="I311" s="1" t="s">
-        <v>652</v>
-      </c>
-      <c r="J311" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="K311" s="30" t="s">
-        <v>654</v>
-      </c>
-      <c r="L311" s="30"/>
+      <c r="I311" s="1"/>
+      <c r="J311" s="1"/>
+      <c r="K311" s="1"/>
+      <c r="L311" s="1"/>
       <c r="M311" s="1"/>
       <c r="N311" s="1"/>
       <c r="O311" s="1"/>
@@ -14890,27 +14875,33 @@
     </row>
     <row r="312" spans="1:26">
       <c r="A312" s="1" t="s">
-        <v>139</v>
+        <v>647</v>
       </c>
       <c r="B312" s="1" t="s">
-        <v>713</v>
-      </c>
-      <c r="C312" s="4" t="s">
-        <v>642</v>
-      </c>
-      <c r="D312" s="4" t="s">
-        <v>642</v>
+        <v>709</v>
+      </c>
+      <c r="C312" s="1" t="s">
+        <v>710</v>
+      </c>
+      <c r="D312" s="1" t="s">
+        <v>711</v>
       </c>
       <c r="E312" s="1"/>
       <c r="F312" s="1" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="G312" s="1"/>
       <c r="H312" s="1"/>
-      <c r="I312" s="1"/>
-      <c r="J312" s="1"/>
-      <c r="K312" s="1"/>
-      <c r="L312" s="1"/>
+      <c r="I312" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="J312" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="K312" s="32" t="s">
+        <v>654</v>
+      </c>
+      <c r="L312" s="32"/>
       <c r="M312" s="1"/>
       <c r="N312" s="1"/>
       <c r="O312" s="1"/>
@@ -14928,20 +14919,18 @@
     </row>
     <row r="313" spans="1:26">
       <c r="A313" s="1" t="s">
-        <v>166</v>
+        <v>139</v>
       </c>
       <c r="B313" s="1" t="s">
-        <v>715</v>
-      </c>
-      <c r="C313" s="13" t="s">
-        <v>716</v>
-      </c>
-      <c r="D313" s="1" t="s">
-        <v>717</v>
-      </c>
-      <c r="E313" s="1" t="s">
-        <v>170</v>
-      </c>
+        <v>713</v>
+      </c>
+      <c r="C313" s="4" t="s">
+        <v>642</v>
+      </c>
+      <c r="D313" s="4" t="s">
+        <v>642</v>
+      </c>
+      <c r="E313" s="1"/>
       <c r="F313" s="1" t="s">
         <v>714</v>
       </c>
@@ -14968,33 +14957,29 @@
     </row>
     <row r="314" spans="1:26">
       <c r="A314" s="1" t="s">
-        <v>647</v>
+        <v>166</v>
       </c>
       <c r="B314" s="1" t="s">
-        <v>718</v>
-      </c>
-      <c r="C314" s="1" t="s">
-        <v>719</v>
+        <v>715</v>
+      </c>
+      <c r="C314" s="13" t="s">
+        <v>716</v>
       </c>
       <c r="D314" s="1" t="s">
-        <v>720</v>
-      </c>
-      <c r="E314" s="1"/>
+        <v>717</v>
+      </c>
+      <c r="E314" s="1" t="s">
+        <v>170</v>
+      </c>
       <c r="F314" s="1" t="s">
-        <v>721</v>
+        <v>714</v>
       </c>
       <c r="G314" s="1"/>
       <c r="H314" s="1"/>
-      <c r="I314" s="1" t="s">
-        <v>652</v>
-      </c>
-      <c r="J314" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="K314" s="30" t="s">
-        <v>654</v>
-      </c>
-      <c r="L314" s="30"/>
+      <c r="I314" s="1"/>
+      <c r="J314" s="1"/>
+      <c r="K314" s="1"/>
+      <c r="L314" s="1"/>
       <c r="M314" s="1"/>
       <c r="N314" s="1"/>
       <c r="O314" s="1"/>
@@ -15012,27 +14997,33 @@
     </row>
     <row r="315" spans="1:26">
       <c r="A315" s="1" t="s">
-        <v>139</v>
+        <v>647</v>
       </c>
       <c r="B315" s="1" t="s">
-        <v>722</v>
-      </c>
-      <c r="C315" s="14" t="s">
-        <v>642</v>
-      </c>
-      <c r="D315" s="4" t="s">
-        <v>642</v>
+        <v>718</v>
+      </c>
+      <c r="C315" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="D315" s="1" t="s">
+        <v>720</v>
       </c>
       <c r="E315" s="1"/>
       <c r="F315" s="1" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="G315" s="1"/>
       <c r="H315" s="1"/>
-      <c r="I315" s="1"/>
-      <c r="J315" s="1"/>
-      <c r="K315" s="1"/>
-      <c r="L315" s="1"/>
+      <c r="I315" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="J315" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="K315" s="32" t="s">
+        <v>654</v>
+      </c>
+      <c r="L315" s="32"/>
       <c r="M315" s="1"/>
       <c r="N315" s="1"/>
       <c r="O315" s="1"/>
@@ -15050,20 +15041,18 @@
     </row>
     <row r="316" spans="1:26">
       <c r="A316" s="1" t="s">
-        <v>166</v>
+        <v>139</v>
       </c>
       <c r="B316" s="1" t="s">
-        <v>724</v>
-      </c>
-      <c r="C316" s="13" t="s">
-        <v>725</v>
-      </c>
-      <c r="D316" s="1" t="s">
-        <v>726</v>
-      </c>
-      <c r="E316" s="1" t="s">
-        <v>170</v>
-      </c>
+        <v>722</v>
+      </c>
+      <c r="C316" s="14" t="s">
+        <v>642</v>
+      </c>
+      <c r="D316" s="4" t="s">
+        <v>642</v>
+      </c>
+      <c r="E316" s="1"/>
       <c r="F316" s="1" t="s">
         <v>723</v>
       </c>
@@ -15090,33 +15079,29 @@
     </row>
     <row r="317" spans="1:26">
       <c r="A317" s="1" t="s">
-        <v>647</v>
+        <v>166</v>
       </c>
       <c r="B317" s="1" t="s">
-        <v>727</v>
-      </c>
-      <c r="C317" s="1" t="s">
-        <v>728</v>
+        <v>724</v>
+      </c>
+      <c r="C317" s="13" t="s">
+        <v>725</v>
       </c>
       <c r="D317" s="1" t="s">
-        <v>729</v>
-      </c>
-      <c r="E317" s="1"/>
+        <v>726</v>
+      </c>
+      <c r="E317" s="1" t="s">
+        <v>170</v>
+      </c>
       <c r="F317" s="1" t="s">
-        <v>730</v>
+        <v>723</v>
       </c>
       <c r="G317" s="1"/>
       <c r="H317" s="1"/>
-      <c r="I317" s="1" t="s">
-        <v>652</v>
-      </c>
-      <c r="J317" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="K317" s="30" t="s">
-        <v>654</v>
-      </c>
-      <c r="L317" s="30"/>
+      <c r="I317" s="1"/>
+      <c r="J317" s="1"/>
+      <c r="K317" s="1"/>
+      <c r="L317" s="1"/>
       <c r="M317" s="1"/>
       <c r="N317" s="1"/>
       <c r="O317" s="1"/>
@@ -15134,27 +15119,33 @@
     </row>
     <row r="318" spans="1:26">
       <c r="A318" s="1" t="s">
-        <v>139</v>
+        <v>647</v>
       </c>
       <c r="B318" s="1" t="s">
-        <v>731</v>
-      </c>
-      <c r="C318" s="13" t="s">
-        <v>642</v>
-      </c>
-      <c r="D318" s="14" t="s">
-        <v>642</v>
+        <v>727</v>
+      </c>
+      <c r="C318" s="1" t="s">
+        <v>728</v>
+      </c>
+      <c r="D318" s="1" t="s">
+        <v>729</v>
       </c>
       <c r="E318" s="1"/>
       <c r="F318" s="1" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="G318" s="1"/>
       <c r="H318" s="1"/>
-      <c r="I318" s="1"/>
-      <c r="J318" s="1"/>
-      <c r="K318" s="1"/>
-      <c r="L318" s="1"/>
+      <c r="I318" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="J318" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="K318" s="32" t="s">
+        <v>654</v>
+      </c>
+      <c r="L318" s="32"/>
       <c r="M318" s="1"/>
       <c r="N318" s="1"/>
       <c r="O318" s="1"/>
@@ -15172,20 +15163,18 @@
     </row>
     <row r="319" spans="1:26">
       <c r="A319" s="1" t="s">
-        <v>166</v>
+        <v>139</v>
       </c>
       <c r="B319" s="1" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="C319" s="13" t="s">
-        <v>734</v>
-      </c>
-      <c r="D319" s="1" t="s">
-        <v>735</v>
-      </c>
-      <c r="E319" s="1" t="s">
-        <v>170</v>
-      </c>
+        <v>642</v>
+      </c>
+      <c r="D319" s="14" t="s">
+        <v>642</v>
+      </c>
+      <c r="E319" s="1"/>
       <c r="F319" s="1" t="s">
         <v>732</v>
       </c>
@@ -15212,33 +15201,29 @@
     </row>
     <row r="320" spans="1:26">
       <c r="A320" s="1" t="s">
-        <v>647</v>
+        <v>166</v>
       </c>
       <c r="B320" s="1" t="s">
-        <v>736</v>
-      </c>
-      <c r="C320" s="1" t="s">
-        <v>737</v>
+        <v>733</v>
+      </c>
+      <c r="C320" s="13" t="s">
+        <v>734</v>
       </c>
       <c r="D320" s="1" t="s">
-        <v>738</v>
-      </c>
-      <c r="E320" s="1"/>
+        <v>735</v>
+      </c>
+      <c r="E320" s="1" t="s">
+        <v>170</v>
+      </c>
       <c r="F320" s="1" t="s">
-        <v>739</v>
+        <v>732</v>
       </c>
       <c r="G320" s="1"/>
       <c r="H320" s="1"/>
-      <c r="I320" s="1" t="s">
-        <v>652</v>
-      </c>
-      <c r="J320" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="K320" s="30" t="s">
-        <v>654</v>
-      </c>
-      <c r="L320" s="30"/>
+      <c r="I320" s="1"/>
+      <c r="J320" s="1"/>
+      <c r="K320" s="1"/>
+      <c r="L320" s="1"/>
       <c r="M320" s="1"/>
       <c r="N320" s="1"/>
       <c r="O320" s="1"/>
@@ -15256,27 +15241,33 @@
     </row>
     <row r="321" spans="1:26">
       <c r="A321" s="1" t="s">
-        <v>139</v>
+        <v>647</v>
       </c>
       <c r="B321" s="1" t="s">
-        <v>740</v>
-      </c>
-      <c r="C321" s="13" t="s">
-        <v>642</v>
-      </c>
-      <c r="D321" s="13" t="s">
-        <v>642</v>
+        <v>736</v>
+      </c>
+      <c r="C321" s="1" t="s">
+        <v>737</v>
+      </c>
+      <c r="D321" s="1" t="s">
+        <v>738</v>
       </c>
       <c r="E321" s="1"/>
       <c r="F321" s="1" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="G321" s="1"/>
       <c r="H321" s="1"/>
-      <c r="I321" s="1"/>
-      <c r="J321" s="1"/>
-      <c r="K321" s="1"/>
-      <c r="L321" s="1"/>
+      <c r="I321" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="J321" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="K321" s="32" t="s">
+        <v>654</v>
+      </c>
+      <c r="L321" s="32"/>
       <c r="M321" s="1"/>
       <c r="N321" s="1"/>
       <c r="O321" s="1"/>
@@ -15294,20 +15285,18 @@
     </row>
     <row r="322" spans="1:26">
       <c r="A322" s="1" t="s">
-        <v>166</v>
+        <v>139</v>
       </c>
       <c r="B322" s="1" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="C322" s="13" t="s">
-        <v>743</v>
-      </c>
-      <c r="D322" s="1" t="s">
-        <v>744</v>
-      </c>
-      <c r="E322" s="1" t="s">
-        <v>170</v>
-      </c>
+        <v>642</v>
+      </c>
+      <c r="D322" s="13" t="s">
+        <v>642</v>
+      </c>
+      <c r="E322" s="1"/>
       <c r="F322" s="1" t="s">
         <v>741</v>
       </c>
@@ -15334,33 +15323,29 @@
     </row>
     <row r="323" spans="1:26">
       <c r="A323" s="1" t="s">
-        <v>647</v>
+        <v>166</v>
       </c>
       <c r="B323" s="1" t="s">
-        <v>745</v>
-      </c>
-      <c r="C323" s="1" t="s">
-        <v>746</v>
+        <v>742</v>
+      </c>
+      <c r="C323" s="13" t="s">
+        <v>743</v>
       </c>
       <c r="D323" s="1" t="s">
-        <v>747</v>
-      </c>
-      <c r="E323" s="1"/>
+        <v>744</v>
+      </c>
+      <c r="E323" s="1" t="s">
+        <v>170</v>
+      </c>
       <c r="F323" s="1" t="s">
-        <v>748</v>
+        <v>741</v>
       </c>
       <c r="G323" s="1"/>
       <c r="H323" s="1"/>
-      <c r="I323" s="1" t="s">
-        <v>652</v>
-      </c>
-      <c r="J323" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="K323" s="30" t="s">
-        <v>654</v>
-      </c>
-      <c r="L323" s="30"/>
+      <c r="I323" s="1"/>
+      <c r="J323" s="1"/>
+      <c r="K323" s="1"/>
+      <c r="L323" s="1"/>
       <c r="M323" s="1"/>
       <c r="N323" s="1"/>
       <c r="O323" s="1"/>
@@ -15378,27 +15363,33 @@
     </row>
     <row r="324" spans="1:26">
       <c r="A324" s="1" t="s">
-        <v>139</v>
+        <v>647</v>
       </c>
       <c r="B324" s="1" t="s">
-        <v>749</v>
-      </c>
-      <c r="C324" s="13" t="s">
-        <v>642</v>
-      </c>
-      <c r="D324" s="13" t="s">
-        <v>642</v>
+        <v>745</v>
+      </c>
+      <c r="C324" s="1" t="s">
+        <v>746</v>
+      </c>
+      <c r="D324" s="1" t="s">
+        <v>747</v>
       </c>
       <c r="E324" s="1"/>
       <c r="F324" s="1" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="G324" s="1"/>
       <c r="H324" s="1"/>
-      <c r="I324" s="1"/>
-      <c r="J324" s="1"/>
-      <c r="K324" s="1"/>
-      <c r="L324" s="1"/>
+      <c r="I324" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="J324" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="K324" s="32" t="s">
+        <v>654</v>
+      </c>
+      <c r="L324" s="32"/>
       <c r="M324" s="1"/>
       <c r="N324" s="1"/>
       <c r="O324" s="1"/>
@@ -15416,20 +15407,18 @@
     </row>
     <row r="325" spans="1:26">
       <c r="A325" s="1" t="s">
-        <v>166</v>
+        <v>139</v>
       </c>
       <c r="B325" s="1" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="C325" s="13" t="s">
-        <v>752</v>
-      </c>
-      <c r="D325" s="1" t="s">
-        <v>753</v>
-      </c>
-      <c r="E325" s="1" t="s">
-        <v>170</v>
-      </c>
+        <v>642</v>
+      </c>
+      <c r="D325" s="13" t="s">
+        <v>642</v>
+      </c>
+      <c r="E325" s="1"/>
       <c r="F325" s="1" t="s">
         <v>750</v>
       </c>
@@ -15456,33 +15445,29 @@
     </row>
     <row r="326" spans="1:26">
       <c r="A326" s="1" t="s">
-        <v>647</v>
+        <v>166</v>
       </c>
       <c r="B326" s="1" t="s">
-        <v>754</v>
-      </c>
-      <c r="C326" s="1" t="s">
-        <v>755</v>
+        <v>751</v>
+      </c>
+      <c r="C326" s="13" t="s">
+        <v>752</v>
       </c>
       <c r="D326" s="1" t="s">
-        <v>756</v>
-      </c>
-      <c r="E326" s="1"/>
+        <v>753</v>
+      </c>
+      <c r="E326" s="1" t="s">
+        <v>170</v>
+      </c>
       <c r="F326" s="1" t="s">
-        <v>757</v>
+        <v>750</v>
       </c>
       <c r="G326" s="1"/>
       <c r="H326" s="1"/>
-      <c r="I326" s="1" t="s">
-        <v>652</v>
-      </c>
-      <c r="J326" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="K326" s="30" t="s">
-        <v>654</v>
-      </c>
-      <c r="L326" s="30"/>
+      <c r="I326" s="1"/>
+      <c r="J326" s="1"/>
+      <c r="K326" s="1"/>
+      <c r="L326" s="1"/>
       <c r="M326" s="1"/>
       <c r="N326" s="1"/>
       <c r="O326" s="1"/>
@@ -15500,27 +15485,33 @@
     </row>
     <row r="327" spans="1:26">
       <c r="A327" s="1" t="s">
-        <v>139</v>
+        <v>647</v>
       </c>
       <c r="B327" s="1" t="s">
-        <v>758</v>
-      </c>
-      <c r="C327" s="13" t="s">
-        <v>642</v>
-      </c>
-      <c r="D327" s="13" t="s">
-        <v>642</v>
+        <v>754</v>
+      </c>
+      <c r="C327" s="1" t="s">
+        <v>755</v>
+      </c>
+      <c r="D327" s="1" t="s">
+        <v>756</v>
       </c>
       <c r="E327" s="1"/>
       <c r="F327" s="1" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="G327" s="1"/>
       <c r="H327" s="1"/>
-      <c r="I327" s="1"/>
-      <c r="J327" s="1"/>
-      <c r="K327" s="1"/>
-      <c r="L327" s="1"/>
+      <c r="I327" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="J327" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="K327" s="32" t="s">
+        <v>654</v>
+      </c>
+      <c r="L327" s="32"/>
       <c r="M327" s="1"/>
       <c r="N327" s="1"/>
       <c r="O327" s="1"/>
@@ -15538,20 +15529,18 @@
     </row>
     <row r="328" spans="1:26">
       <c r="A328" s="1" t="s">
-        <v>166</v>
+        <v>139</v>
       </c>
       <c r="B328" s="1" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="C328" s="13" t="s">
-        <v>761</v>
-      </c>
-      <c r="D328" s="1" t="s">
-        <v>762</v>
-      </c>
-      <c r="E328" s="1" t="s">
-        <v>170</v>
-      </c>
+        <v>642</v>
+      </c>
+      <c r="D328" s="13" t="s">
+        <v>642</v>
+      </c>
+      <c r="E328" s="1"/>
       <c r="F328" s="1" t="s">
         <v>759</v>
       </c>
@@ -15578,33 +15567,29 @@
     </row>
     <row r="329" spans="1:26">
       <c r="A329" s="1" t="s">
-        <v>647</v>
+        <v>166</v>
       </c>
       <c r="B329" s="1" t="s">
-        <v>763</v>
-      </c>
-      <c r="C329" s="1" t="s">
-        <v>764</v>
+        <v>760</v>
+      </c>
+      <c r="C329" s="13" t="s">
+        <v>761</v>
       </c>
       <c r="D329" s="1" t="s">
-        <v>765</v>
-      </c>
-      <c r="E329" s="1"/>
+        <v>762</v>
+      </c>
+      <c r="E329" s="1" t="s">
+        <v>170</v>
+      </c>
       <c r="F329" s="1" t="s">
-        <v>766</v>
+        <v>759</v>
       </c>
       <c r="G329" s="1"/>
       <c r="H329" s="1"/>
-      <c r="I329" s="1" t="s">
-        <v>652</v>
-      </c>
-      <c r="J329" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="K329" s="30" t="s">
-        <v>654</v>
-      </c>
-      <c r="L329" s="30"/>
+      <c r="I329" s="1"/>
+      <c r="J329" s="1"/>
+      <c r="K329" s="1"/>
+      <c r="L329" s="1"/>
       <c r="M329" s="1"/>
       <c r="N329" s="1"/>
       <c r="O329" s="1"/>
@@ -15622,27 +15607,33 @@
     </row>
     <row r="330" spans="1:26">
       <c r="A330" s="1" t="s">
-        <v>139</v>
+        <v>647</v>
       </c>
       <c r="B330" s="1" t="s">
-        <v>767</v>
-      </c>
-      <c r="C330" s="13" t="s">
-        <v>642</v>
-      </c>
-      <c r="D330" s="13" t="s">
-        <v>642</v>
+        <v>763</v>
+      </c>
+      <c r="C330" s="1" t="s">
+        <v>764</v>
+      </c>
+      <c r="D330" s="1" t="s">
+        <v>765</v>
       </c>
       <c r="E330" s="1"/>
-      <c r="F330" s="30" t="s">
-        <v>768</v>
-      </c>
-      <c r="G330" s="30"/>
-      <c r="H330" s="30"/>
-      <c r="I330" s="1"/>
-      <c r="J330" s="1"/>
-      <c r="K330" s="1"/>
-      <c r="L330" s="1"/>
+      <c r="F330" s="1" t="s">
+        <v>766</v>
+      </c>
+      <c r="G330" s="1"/>
+      <c r="H330" s="1"/>
+      <c r="I330" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="J330" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="K330" s="32" t="s">
+        <v>654</v>
+      </c>
+      <c r="L330" s="32"/>
       <c r="M330" s="1"/>
       <c r="N330" s="1"/>
       <c r="O330" s="1"/>
@@ -15660,25 +15651,23 @@
     </row>
     <row r="331" spans="1:26">
       <c r="A331" s="1" t="s">
-        <v>166</v>
+        <v>139</v>
       </c>
       <c r="B331" s="1" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="C331" s="13" t="s">
-        <v>770</v>
-      </c>
-      <c r="D331" s="1" t="s">
-        <v>771</v>
-      </c>
-      <c r="E331" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F331" s="30" t="s">
+        <v>642</v>
+      </c>
+      <c r="D331" s="13" t="s">
+        <v>642</v>
+      </c>
+      <c r="E331" s="1"/>
+      <c r="F331" s="32" t="s">
         <v>768</v>
       </c>
-      <c r="G331" s="30"/>
-      <c r="H331" s="30"/>
+      <c r="G331" s="32"/>
+      <c r="H331" s="32"/>
       <c r="I331" s="1"/>
       <c r="J331" s="1"/>
       <c r="K331" s="1"/>
@@ -15700,33 +15689,29 @@
     </row>
     <row r="332" spans="1:26">
       <c r="A332" s="1" t="s">
-        <v>647</v>
+        <v>166</v>
       </c>
       <c r="B332" s="1" t="s">
-        <v>772</v>
-      </c>
-      <c r="C332" s="1" t="s">
-        <v>773</v>
+        <v>769</v>
+      </c>
+      <c r="C332" s="13" t="s">
+        <v>770</v>
       </c>
       <c r="D332" s="1" t="s">
-        <v>774</v>
-      </c>
-      <c r="E332" s="1"/>
-      <c r="F332" s="1" t="s">
-        <v>775</v>
-      </c>
-      <c r="G332" s="1"/>
-      <c r="H332" s="1"/>
-      <c r="I332" s="1" t="s">
-        <v>652</v>
-      </c>
-      <c r="J332" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="K332" s="30" t="s">
-        <v>654</v>
-      </c>
-      <c r="L332" s="30"/>
+        <v>771</v>
+      </c>
+      <c r="E332" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F332" s="32" t="s">
+        <v>768</v>
+      </c>
+      <c r="G332" s="32"/>
+      <c r="H332" s="32"/>
+      <c r="I332" s="1"/>
+      <c r="J332" s="1"/>
+      <c r="K332" s="1"/>
+      <c r="L332" s="1"/>
       <c r="M332" s="1"/>
       <c r="N332" s="1"/>
       <c r="O332" s="1"/>
@@ -15744,27 +15729,33 @@
     </row>
     <row r="333" spans="1:26">
       <c r="A333" s="1" t="s">
-        <v>139</v>
+        <v>647</v>
       </c>
       <c r="B333" s="1" t="s">
-        <v>776</v>
-      </c>
-      <c r="C333" s="13" t="s">
-        <v>642</v>
-      </c>
-      <c r="D333" s="13" t="s">
-        <v>642</v>
+        <v>772</v>
+      </c>
+      <c r="C333" s="1" t="s">
+        <v>773</v>
+      </c>
+      <c r="D333" s="1" t="s">
+        <v>774</v>
       </c>
       <c r="E333" s="1"/>
       <c r="F333" s="1" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="G333" s="1"/>
       <c r="H333" s="1"/>
-      <c r="I333" s="1"/>
-      <c r="J333" s="1"/>
-      <c r="K333" s="1"/>
-      <c r="L333" s="1"/>
+      <c r="I333" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="J333" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="K333" s="32" t="s">
+        <v>654</v>
+      </c>
+      <c r="L333" s="32"/>
       <c r="M333" s="1"/>
       <c r="N333" s="1"/>
       <c r="O333" s="1"/>
@@ -15782,20 +15773,18 @@
     </row>
     <row r="334" spans="1:26">
       <c r="A334" s="1" t="s">
-        <v>166</v>
+        <v>139</v>
       </c>
       <c r="B334" s="1" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="C334" s="13" t="s">
-        <v>779</v>
-      </c>
-      <c r="D334" s="1" t="s">
-        <v>780</v>
-      </c>
-      <c r="E334" s="1" t="s">
-        <v>170</v>
-      </c>
+        <v>642</v>
+      </c>
+      <c r="D334" s="13" t="s">
+        <v>642</v>
+      </c>
+      <c r="E334" s="1"/>
       <c r="F334" s="1" t="s">
         <v>777</v>
       </c>
@@ -15822,33 +15811,29 @@
     </row>
     <row r="335" spans="1:26">
       <c r="A335" s="1" t="s">
-        <v>647</v>
+        <v>166</v>
       </c>
       <c r="B335" s="1" t="s">
-        <v>781</v>
-      </c>
-      <c r="C335" s="1" t="s">
-        <v>782</v>
+        <v>778</v>
+      </c>
+      <c r="C335" s="13" t="s">
+        <v>779</v>
       </c>
       <c r="D335" s="1" t="s">
-        <v>783</v>
-      </c>
-      <c r="E335" s="1"/>
+        <v>780</v>
+      </c>
+      <c r="E335" s="1" t="s">
+        <v>170</v>
+      </c>
       <c r="F335" s="1" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="G335" s="1"/>
       <c r="H335" s="1"/>
-      <c r="I335" s="1" t="s">
-        <v>652</v>
-      </c>
-      <c r="J335" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="K335" s="30" t="s">
-        <v>654</v>
-      </c>
-      <c r="L335" s="30"/>
+      <c r="I335" s="1"/>
+      <c r="J335" s="1"/>
+      <c r="K335" s="1"/>
+      <c r="L335" s="1"/>
       <c r="M335" s="1"/>
       <c r="N335" s="1"/>
       <c r="O335" s="1"/>
@@ -15865,28 +15850,34 @@
       <c r="Z335" s="6"/>
     </row>
     <row r="336" spans="1:26">
-      <c r="A336" s="13" t="s">
-        <v>139</v>
+      <c r="A336" s="1" t="s">
+        <v>647</v>
       </c>
       <c r="B336" s="1" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
       <c r="C336" s="1" t="s">
-        <v>642</v>
+        <v>782</v>
       </c>
       <c r="D336" s="1" t="s">
-        <v>642</v>
+        <v>783</v>
       </c>
       <c r="E336" s="1"/>
       <c r="F336" s="1" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="G336" s="1"/>
       <c r="H336" s="1"/>
-      <c r="I336" s="1"/>
-      <c r="J336" s="1"/>
-      <c r="K336" s="1"/>
-      <c r="L336" s="1"/>
+      <c r="I336" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="J336" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="K336" s="32" t="s">
+        <v>654</v>
+      </c>
+      <c r="L336" s="32"/>
       <c r="M336" s="1"/>
       <c r="N336" s="1"/>
       <c r="O336" s="1"/>
@@ -15904,20 +15895,18 @@
     </row>
     <row r="337" spans="1:26">
       <c r="A337" s="13" t="s">
-        <v>166</v>
+        <v>139</v>
       </c>
       <c r="B337" s="1" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="C337" s="1" t="s">
-        <v>788</v>
+        <v>642</v>
       </c>
       <c r="D337" s="1" t="s">
-        <v>789</v>
-      </c>
-      <c r="E337" s="1" t="s">
-        <v>170</v>
-      </c>
+        <v>642</v>
+      </c>
+      <c r="E337" s="1"/>
       <c r="F337" s="1" t="s">
         <v>786</v>
       </c>
@@ -15944,33 +15933,29 @@
     </row>
     <row r="338" spans="1:26">
       <c r="A338" s="13" t="s">
-        <v>647</v>
+        <v>166</v>
       </c>
       <c r="B338" s="1" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="C338" s="1" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="D338" s="1" t="s">
-        <v>792</v>
-      </c>
-      <c r="E338" s="1"/>
+        <v>789</v>
+      </c>
+      <c r="E338" s="1" t="s">
+        <v>170</v>
+      </c>
       <c r="F338" s="1" t="s">
-        <v>793</v>
+        <v>786</v>
       </c>
       <c r="G338" s="1"/>
       <c r="H338" s="1"/>
-      <c r="I338" s="1" t="s">
-        <v>652</v>
-      </c>
-      <c r="J338" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="K338" s="30" t="s">
-        <v>654</v>
-      </c>
-      <c r="L338" s="30"/>
+      <c r="I338" s="1"/>
+      <c r="J338" s="1"/>
+      <c r="K338" s="1"/>
+      <c r="L338" s="1"/>
       <c r="M338" s="1"/>
       <c r="N338" s="1"/>
       <c r="O338" s="1"/>
@@ -15988,21 +15973,33 @@
     </row>
     <row r="339" spans="1:26">
       <c r="A339" s="13" t="s">
-        <v>55</v>
+        <v>647</v>
       </c>
       <c r="B339" s="1" t="s">
-        <v>635</v>
-      </c>
-      <c r="C339" s="1"/>
-      <c r="D339" s="1"/>
+        <v>790</v>
+      </c>
+      <c r="C339" s="1" t="s">
+        <v>791</v>
+      </c>
+      <c r="D339" s="1" t="s">
+        <v>792</v>
+      </c>
       <c r="E339" s="1"/>
-      <c r="F339" s="1"/>
+      <c r="F339" s="1" t="s">
+        <v>793</v>
+      </c>
       <c r="G339" s="1"/>
       <c r="H339" s="1"/>
-      <c r="I339" s="1"/>
-      <c r="J339" s="1"/>
-      <c r="K339" s="1"/>
-      <c r="L339" s="1"/>
+      <c r="I339" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="J339" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="K339" s="32" t="s">
+        <v>654</v>
+      </c>
+      <c r="L339" s="32"/>
       <c r="M339" s="1"/>
       <c r="N339" s="1"/>
       <c r="O339" s="1"/>
@@ -16020,21 +16017,15 @@
     </row>
     <row r="340" spans="1:26">
       <c r="A340" s="13" t="s">
-        <v>139</v>
+        <v>55</v>
       </c>
       <c r="B340" s="1" t="s">
-        <v>794</v>
-      </c>
-      <c r="C340" s="1" t="s">
-        <v>642</v>
-      </c>
-      <c r="D340" s="1" t="s">
-        <v>642</v>
-      </c>
+        <v>635</v>
+      </c>
+      <c r="C340" s="1"/>
+      <c r="D340" s="1"/>
       <c r="E340" s="1"/>
-      <c r="F340" s="1" t="s">
-        <v>795</v>
-      </c>
+      <c r="F340" s="1"/>
       <c r="G340" s="1"/>
       <c r="H340" s="1"/>
       <c r="I340" s="1"/>
@@ -16058,20 +16049,18 @@
     </row>
     <row r="341" spans="1:26">
       <c r="A341" s="13" t="s">
-        <v>166</v>
+        <v>139</v>
       </c>
       <c r="B341" s="1" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="C341" s="1" t="s">
-        <v>797</v>
+        <v>642</v>
       </c>
       <c r="D341" s="1" t="s">
-        <v>798</v>
-      </c>
-      <c r="E341" s="1" t="s">
-        <v>170</v>
-      </c>
+        <v>642</v>
+      </c>
+      <c r="E341" s="1"/>
       <c r="F341" s="1" t="s">
         <v>795</v>
       </c>
@@ -16098,20 +16087,22 @@
     </row>
     <row r="342" spans="1:26">
       <c r="A342" s="13" t="s">
-        <v>139</v>
+        <v>166</v>
       </c>
       <c r="B342" s="1" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="C342" s="1" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="D342" s="1" t="s">
-        <v>801</v>
-      </c>
-      <c r="E342" s="1"/>
+        <v>798</v>
+      </c>
+      <c r="E342" s="1" t="s">
+        <v>170</v>
+      </c>
       <c r="F342" s="1" t="s">
-        <v>802</v>
+        <v>795</v>
       </c>
       <c r="G342" s="1"/>
       <c r="H342" s="1"/>
@@ -16136,22 +16127,20 @@
     </row>
     <row r="343" spans="1:26">
       <c r="A343" s="13" t="s">
-        <v>803</v>
+        <v>139</v>
       </c>
       <c r="B343" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C343" s="1" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
       <c r="D343" s="1" t="s">
-        <v>806</v>
-      </c>
-      <c r="E343" s="1" t="s">
-        <v>170</v>
-      </c>
+        <v>801</v>
+      </c>
+      <c r="E343" s="1"/>
       <c r="F343" s="1" t="s">
-        <v>807</v>
+        <v>802</v>
       </c>
       <c r="G343" s="1"/>
       <c r="H343" s="1"/>
@@ -16174,22 +16163,24 @@
       <c r="Y343" s="6"/>
       <c r="Z343" s="6"/>
     </row>
-    <row r="344" spans="1:26" s="6" customFormat="1">
+    <row r="344" spans="1:26">
       <c r="A344" s="13" t="s">
-        <v>139</v>
+        <v>803</v>
       </c>
       <c r="B344" s="1" t="s">
-        <v>808</v>
+        <v>804</v>
       </c>
       <c r="C344" s="1" t="s">
-        <v>809</v>
+        <v>805</v>
       </c>
       <c r="D344" s="1" t="s">
-        <v>810</v>
-      </c>
-      <c r="E344" s="1"/>
+        <v>806</v>
+      </c>
+      <c r="E344" s="1" t="s">
+        <v>170</v>
+      </c>
       <c r="F344" s="1" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="G344" s="1"/>
       <c r="H344" s="1"/>
@@ -16202,23 +16193,32 @@
       <c r="O344" s="1"/>
       <c r="P344" s="1"/>
       <c r="Q344" s="1"/>
-    </row>
-    <row r="345" spans="1:26">
+      <c r="R344" s="6"/>
+      <c r="S344" s="6"/>
+      <c r="T344" s="6"/>
+      <c r="U344" s="6"/>
+      <c r="V344" s="6"/>
+      <c r="W344" s="6"/>
+      <c r="X344" s="6"/>
+      <c r="Y344" s="6"/>
+      <c r="Z344" s="6"/>
+    </row>
+    <row r="345" spans="1:26" s="6" customFormat="1">
       <c r="A345" s="13" t="s">
         <v>139</v>
       </c>
       <c r="B345" s="1" t="s">
-        <v>812</v>
+        <v>808</v>
       </c>
       <c r="C345" s="1" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
       <c r="D345" s="1" t="s">
-        <v>814</v>
+        <v>810</v>
       </c>
       <c r="E345" s="1"/>
       <c r="F345" s="1" t="s">
-        <v>815</v>
+        <v>811</v>
       </c>
       <c r="G345" s="1"/>
       <c r="H345" s="1"/>
@@ -16231,36 +16231,27 @@
       <c r="O345" s="1"/>
       <c r="P345" s="1"/>
       <c r="Q345" s="1"/>
-      <c r="R345" s="6"/>
-      <c r="S345" s="6"/>
-      <c r="T345" s="6"/>
-      <c r="U345" s="6"/>
-      <c r="V345" s="6"/>
-      <c r="W345" s="6"/>
-      <c r="X345" s="6"/>
-      <c r="Y345" s="6"/>
-      <c r="Z345" s="6"/>
     </row>
     <row r="346" spans="1:26">
       <c r="A346" s="13" t="s">
         <v>139</v>
       </c>
       <c r="B346" s="1" t="s">
-        <v>816</v>
+        <v>812</v>
       </c>
       <c r="C346" s="1" t="s">
-        <v>817</v>
+        <v>813</v>
       </c>
       <c r="D346" s="1" t="s">
-        <v>818</v>
+        <v>814</v>
       </c>
       <c r="E346" s="1"/>
-      <c r="F346" s="30" t="s">
-        <v>819</v>
-      </c>
-      <c r="G346" s="30"/>
-      <c r="H346" s="30"/>
-      <c r="I346" s="30"/>
+      <c r="F346" s="1" t="s">
+        <v>815</v>
+      </c>
+      <c r="G346" s="1"/>
+      <c r="H346" s="1"/>
+      <c r="I346" s="1"/>
       <c r="J346" s="1"/>
       <c r="K346" s="1"/>
       <c r="L346" s="1"/>
@@ -16284,21 +16275,21 @@
         <v>139</v>
       </c>
       <c r="B347" s="1" t="s">
-        <v>820</v>
+        <v>816</v>
       </c>
       <c r="C347" s="1" t="s">
-        <v>821</v>
+        <v>817</v>
       </c>
       <c r="D347" s="1" t="s">
-        <v>822</v>
+        <v>818</v>
       </c>
       <c r="E347" s="1"/>
-      <c r="F347" s="1" t="s">
-        <v>823</v>
-      </c>
-      <c r="G347" s="1"/>
-      <c r="H347" s="1"/>
-      <c r="I347" s="1"/>
+      <c r="F347" s="32" t="s">
+        <v>819</v>
+      </c>
+      <c r="G347" s="32"/>
+      <c r="H347" s="32"/>
+      <c r="I347" s="32"/>
       <c r="J347" s="1"/>
       <c r="K347" s="1"/>
       <c r="L347" s="1"/>
@@ -16317,32 +16308,32 @@
       <c r="Y347" s="6"/>
       <c r="Z347" s="6"/>
     </row>
-    <row r="348" spans="1:26" ht="65">
+    <row r="348" spans="1:26">
       <c r="A348" s="13" t="s">
         <v>139</v>
       </c>
       <c r="B348" s="1" t="s">
-        <v>1589</v>
-      </c>
-      <c r="C348" s="9" t="s">
-        <v>1594</v>
+        <v>820</v>
+      </c>
+      <c r="C348" s="1" t="s">
+        <v>821</v>
       </c>
       <c r="D348" s="1" t="s">
-        <v>1595</v>
+        <v>822</v>
       </c>
       <c r="E348" s="1"/>
-      <c r="F348" s="30" t="s">
-        <v>1590</v>
-      </c>
-      <c r="G348" s="30"/>
-      <c r="H348" s="30"/>
-      <c r="I348" s="30"/>
+      <c r="F348" s="1" t="s">
+        <v>823</v>
+      </c>
+      <c r="G348" s="1"/>
+      <c r="H348" s="1"/>
+      <c r="I348" s="1"/>
       <c r="J348" s="1"/>
       <c r="K348" s="1"/>
-      <c r="L348" s="24"/>
-      <c r="M348" s="24"/>
-      <c r="N348" s="24"/>
-      <c r="O348" s="24"/>
+      <c r="L348" s="1"/>
+      <c r="M348" s="1"/>
+      <c r="N348" s="1"/>
+      <c r="O348" s="1"/>
       <c r="P348" s="1"/>
       <c r="Q348" s="1"/>
       <c r="R348" s="6"/>
@@ -16355,32 +16346,32 @@
       <c r="Y348" s="6"/>
       <c r="Z348" s="6"/>
     </row>
-    <row r="349" spans="1:26">
+    <row r="349" spans="1:26" ht="65">
       <c r="A349" s="13" t="s">
         <v>139</v>
       </c>
       <c r="B349" s="1" t="s">
-        <v>824</v>
-      </c>
-      <c r="C349" s="1" t="s">
-        <v>825</v>
+        <v>1589</v>
+      </c>
+      <c r="C349" s="9" t="s">
+        <v>1594</v>
       </c>
       <c r="D349" s="1" t="s">
-        <v>826</v>
+        <v>1595</v>
       </c>
       <c r="E349" s="1"/>
-      <c r="F349" s="1" t="s">
-        <v>827</v>
-      </c>
-      <c r="G349" s="1"/>
-      <c r="H349" s="1"/>
-      <c r="I349" s="1"/>
+      <c r="F349" s="32" t="s">
+        <v>1590</v>
+      </c>
+      <c r="G349" s="32"/>
+      <c r="H349" s="32"/>
+      <c r="I349" s="32"/>
       <c r="J349" s="1"/>
       <c r="K349" s="1"/>
-      <c r="L349" s="1"/>
-      <c r="M349" s="1"/>
-      <c r="N349" s="1"/>
-      <c r="O349" s="1"/>
+      <c r="L349" s="24"/>
+      <c r="M349" s="24"/>
+      <c r="N349" s="24"/>
+      <c r="O349" s="24"/>
       <c r="P349" s="1"/>
       <c r="Q349" s="1"/>
       <c r="R349" s="6"/>
@@ -16398,17 +16389,17 @@
         <v>139</v>
       </c>
       <c r="B350" s="1" t="s">
-        <v>828</v>
+        <v>824</v>
       </c>
       <c r="C350" s="1" t="s">
-        <v>829</v>
+        <v>825</v>
       </c>
       <c r="D350" s="1" t="s">
-        <v>830</v>
+        <v>826</v>
       </c>
       <c r="E350" s="1"/>
       <c r="F350" s="1" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
       <c r="G350" s="1"/>
       <c r="H350" s="1"/>
@@ -16436,13 +16427,13 @@
         <v>139</v>
       </c>
       <c r="B351" s="1" t="s">
-        <v>832</v>
+        <v>828</v>
       </c>
       <c r="C351" s="1" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="D351" s="1" t="s">
-        <v>834</v>
+        <v>830</v>
       </c>
       <c r="E351" s="1"/>
       <c r="F351" s="1" t="s">
@@ -16471,15 +16462,21 @@
     </row>
     <row r="352" spans="1:26">
       <c r="A352" s="13" t="s">
-        <v>55</v>
+        <v>139</v>
       </c>
       <c r="B352" s="1" t="s">
-        <v>614</v>
-      </c>
-      <c r="C352" s="1"/>
-      <c r="D352" s="1"/>
+        <v>832</v>
+      </c>
+      <c r="C352" s="1" t="s">
+        <v>833</v>
+      </c>
+      <c r="D352" s="1" t="s">
+        <v>834</v>
+      </c>
       <c r="E352" s="1"/>
-      <c r="F352" s="1"/>
+      <c r="F352" s="1" t="s">
+        <v>831</v>
+      </c>
       <c r="G352" s="1"/>
       <c r="H352" s="1"/>
       <c r="I352" s="1"/>
@@ -16501,26 +16498,18 @@
       <c r="Y352" s="6"/>
       <c r="Z352" s="6"/>
     </row>
-    <row r="353" spans="1:17">
-      <c r="A353" s="1" t="s">
-        <v>21</v>
+    <row r="353" spans="1:26">
+      <c r="A353" s="13" t="s">
+        <v>55</v>
       </c>
       <c r="B353" s="1" t="s">
-        <v>835</v>
-      </c>
-      <c r="C353" s="2" t="s">
-        <v>836</v>
-      </c>
-      <c r="D353" s="2" t="s">
-        <v>837</v>
-      </c>
+        <v>614</v>
+      </c>
+      <c r="C353" s="1"/>
+      <c r="D353" s="1"/>
       <c r="E353" s="1"/>
-      <c r="F353" s="1" t="s">
-        <v>838</v>
-      </c>
-      <c r="G353" s="1" t="s">
-        <v>147</v>
-      </c>
+      <c r="F353" s="1"/>
+      <c r="G353" s="1"/>
       <c r="H353" s="1"/>
       <c r="I353" s="1"/>
       <c r="J353" s="1"/>
@@ -16531,25 +16520,36 @@
       <c r="O353" s="1"/>
       <c r="P353" s="1"/>
       <c r="Q353" s="1"/>
-    </row>
-    <row r="354" spans="1:17">
+      <c r="R353" s="6"/>
+      <c r="S353" s="6"/>
+      <c r="T353" s="6"/>
+      <c r="U353" s="6"/>
+      <c r="V353" s="6"/>
+      <c r="W353" s="6"/>
+      <c r="X353" s="6"/>
+      <c r="Y353" s="6"/>
+      <c r="Z353" s="6"/>
+    </row>
+    <row r="354" spans="1:26">
       <c r="A354" s="1" t="s">
-        <v>839</v>
+        <v>21</v>
       </c>
       <c r="B354" s="1" t="s">
-        <v>840</v>
+        <v>835</v>
       </c>
       <c r="C354" s="2" t="s">
-        <v>841</v>
-      </c>
-      <c r="D354" s="1" t="s">
-        <v>842</v>
-      </c>
-      <c r="E354" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F354" s="1"/>
-      <c r="G354" s="1"/>
+        <v>836</v>
+      </c>
+      <c r="D354" s="2" t="s">
+        <v>837</v>
+      </c>
+      <c r="E354" s="1"/>
+      <c r="F354" s="1" t="s">
+        <v>838</v>
+      </c>
+      <c r="G354" s="1" t="s">
+        <v>147</v>
+      </c>
       <c r="H354" s="1"/>
       <c r="I354" s="1"/>
       <c r="J354" s="1"/>
@@ -16561,24 +16561,24 @@
       <c r="P354" s="1"/>
       <c r="Q354" s="1"/>
     </row>
-    <row r="355" spans="1:17">
+    <row r="355" spans="1:26">
       <c r="A355" s="1" t="s">
-        <v>139</v>
+        <v>839</v>
       </c>
       <c r="B355" s="1" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
       <c r="C355" s="2" t="s">
-        <v>844</v>
-      </c>
-      <c r="D355" s="2" t="s">
-        <v>845</v>
-      </c>
-      <c r="E355" s="1"/>
-      <c r="F355" s="2" t="s">
-        <v>846</v>
-      </c>
-      <c r="G355" s="2"/>
+        <v>841</v>
+      </c>
+      <c r="D355" s="1" t="s">
+        <v>842</v>
+      </c>
+      <c r="E355" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F355" s="1"/>
+      <c r="G355" s="1"/>
       <c r="H355" s="1"/>
       <c r="I355" s="1"/>
       <c r="J355" s="1"/>
@@ -16590,25 +16590,27 @@
       <c r="P355" s="1"/>
       <c r="Q355" s="1"/>
     </row>
-    <row r="356" spans="1:17" ht="65">
+    <row r="356" spans="1:26">
       <c r="A356" s="1" t="s">
         <v>139</v>
       </c>
       <c r="B356" s="1" t="s">
-        <v>847</v>
-      </c>
-      <c r="C356" s="10" t="s">
-        <v>848</v>
-      </c>
-      <c r="D356" s="10" t="s">
-        <v>849</v>
-      </c>
-      <c r="E356" s="2"/>
-      <c r="F356" s="2"/>
+        <v>843</v>
+      </c>
+      <c r="C356" s="2" t="s">
+        <v>844</v>
+      </c>
+      <c r="D356" s="2" t="s">
+        <v>845</v>
+      </c>
+      <c r="E356" s="1"/>
+      <c r="F356" s="2" t="s">
+        <v>846</v>
+      </c>
       <c r="G356" s="2"/>
-      <c r="H356" s="2"/>
-      <c r="I356" s="2"/>
-      <c r="J356" s="2"/>
+      <c r="H356" s="1"/>
+      <c r="I356" s="1"/>
+      <c r="J356" s="1"/>
       <c r="K356" s="1"/>
       <c r="L356" s="1"/>
       <c r="M356" s="1"/>
@@ -16617,18 +16619,18 @@
       <c r="P356" s="1"/>
       <c r="Q356" s="1"/>
     </row>
-    <row r="357" spans="1:17">
+    <row r="357" spans="1:26" ht="65">
       <c r="A357" s="1" t="s">
         <v>139</v>
       </c>
       <c r="B357" s="1" t="s">
-        <v>850</v>
-      </c>
-      <c r="C357" s="2" t="s">
-        <v>851</v>
-      </c>
-      <c r="D357" s="2" t="s">
-        <v>852</v>
+        <v>847</v>
+      </c>
+      <c r="C357" s="10" t="s">
+        <v>848</v>
+      </c>
+      <c r="D357" s="10" t="s">
+        <v>849</v>
       </c>
       <c r="E357" s="2"/>
       <c r="F357" s="2"/>
@@ -16636,26 +16638,26 @@
       <c r="H357" s="2"/>
       <c r="I357" s="2"/>
       <c r="J357" s="2"/>
-      <c r="K357" s="2"/>
-      <c r="L357" s="2"/>
-      <c r="M357" s="2"/>
-      <c r="N357" s="2"/>
-      <c r="O357" s="2"/>
-      <c r="P357" s="2"/>
-      <c r="Q357" s="2"/>
-    </row>
-    <row r="358" spans="1:17">
+      <c r="K357" s="1"/>
+      <c r="L357" s="1"/>
+      <c r="M357" s="1"/>
+      <c r="N357" s="1"/>
+      <c r="O357" s="1"/>
+      <c r="P357" s="1"/>
+      <c r="Q357" s="1"/>
+    </row>
+    <row r="358" spans="1:26">
       <c r="A358" s="1" t="s">
         <v>139</v>
       </c>
       <c r="B358" s="1" t="s">
-        <v>853</v>
+        <v>850</v>
       </c>
       <c r="C358" s="2" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="D358" s="2" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="E358" s="2"/>
       <c r="F358" s="2"/>
@@ -16664,85 +16666,83 @@
       <c r="I358" s="2"/>
       <c r="J358" s="2"/>
       <c r="K358" s="2"/>
-      <c r="L358" s="1"/>
-      <c r="M358" s="1"/>
-      <c r="N358" s="1"/>
-      <c r="O358" s="1"/>
-      <c r="P358" s="1"/>
-      <c r="Q358" s="1"/>
-    </row>
-    <row r="359" spans="1:17">
+      <c r="L358" s="2"/>
+      <c r="M358" s="2"/>
+      <c r="N358" s="2"/>
+      <c r="O358" s="2"/>
+      <c r="P358" s="2"/>
+      <c r="Q358" s="2"/>
+    </row>
+    <row r="359" spans="1:26">
       <c r="A359" s="1" t="s">
-        <v>62</v>
+        <v>139</v>
       </c>
       <c r="B359" s="1" t="s">
-        <v>856</v>
-      </c>
-      <c r="C359" s="1"/>
-      <c r="D359" s="1"/>
-      <c r="E359" s="1"/>
-      <c r="F359" s="1"/>
-      <c r="G359" s="1"/>
-      <c r="H359" s="1"/>
-      <c r="I359" s="1"/>
-      <c r="J359" s="1"/>
-      <c r="K359" s="1"/>
-      <c r="L359" s="2" t="s">
-        <v>857</v>
-      </c>
+        <v>853</v>
+      </c>
+      <c r="C359" s="2" t="s">
+        <v>854</v>
+      </c>
+      <c r="D359" s="2" t="s">
+        <v>855</v>
+      </c>
+      <c r="E359" s="2"/>
+      <c r="F359" s="2"/>
+      <c r="G359" s="2"/>
+      <c r="H359" s="2"/>
+      <c r="I359" s="2"/>
+      <c r="J359" s="2"/>
+      <c r="K359" s="2"/>
+      <c r="L359" s="1"/>
       <c r="M359" s="1"/>
       <c r="N359" s="1"/>
       <c r="O359" s="1"/>
       <c r="P359" s="1"/>
       <c r="Q359" s="1"/>
     </row>
-    <row r="360" spans="1:17" ht="409.5">
+    <row r="360" spans="1:26">
       <c r="A360" s="1" t="s">
-        <v>139</v>
+        <v>62</v>
       </c>
       <c r="B360" s="1" t="s">
-        <v>858</v>
-      </c>
-      <c r="C360" s="10" t="s">
-        <v>859</v>
-      </c>
-      <c r="D360" s="10" t="s">
-        <v>860</v>
-      </c>
-      <c r="E360" s="2"/>
-      <c r="F360" s="2"/>
-      <c r="G360" s="2"/>
-      <c r="H360" s="2"/>
-      <c r="I360" s="2"/>
+        <v>856</v>
+      </c>
+      <c r="C360" s="1"/>
+      <c r="D360" s="1"/>
+      <c r="E360" s="1"/>
+      <c r="F360" s="1"/>
+      <c r="G360" s="1"/>
+      <c r="H360" s="1"/>
+      <c r="I360" s="1"/>
       <c r="J360" s="1"/>
       <c r="K360" s="1"/>
-      <c r="L360" s="1"/>
+      <c r="L360" s="2" t="s">
+        <v>857</v>
+      </c>
       <c r="M360" s="1"/>
       <c r="N360" s="1"/>
       <c r="O360" s="1"/>
       <c r="P360" s="1"/>
       <c r="Q360" s="1"/>
     </row>
-    <row r="361" spans="1:17">
+    <row r="361" spans="1:26" ht="409.5">
       <c r="A361" s="1" t="s">
-        <v>861</v>
+        <v>139</v>
       </c>
       <c r="B361" s="1" t="s">
-        <v>862</v>
-      </c>
-      <c r="C361" s="2" t="s">
-        <v>863</v>
-      </c>
-      <c r="D361" s="1" t="s">
-        <v>864</v>
-      </c>
-      <c r="E361" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F361" s="1"/>
-      <c r="G361" s="1"/>
-      <c r="H361" s="1"/>
-      <c r="I361" s="1"/>
+        <v>858</v>
+      </c>
+      <c r="C361" s="10" t="s">
+        <v>859</v>
+      </c>
+      <c r="D361" s="10" t="s">
+        <v>860</v>
+      </c>
+      <c r="E361" s="2"/>
+      <c r="F361" s="2"/>
+      <c r="G361" s="2"/>
+      <c r="H361" s="2"/>
+      <c r="I361" s="2"/>
       <c r="J361" s="1"/>
       <c r="K361" s="1"/>
       <c r="L361" s="1"/>
@@ -16752,24 +16752,24 @@
       <c r="P361" s="1"/>
       <c r="Q361" s="1"/>
     </row>
-    <row r="362" spans="1:17">
+    <row r="362" spans="1:26">
       <c r="A362" s="1" t="s">
-        <v>21</v>
+        <v>861</v>
       </c>
       <c r="B362" s="1" t="s">
-        <v>865</v>
-      </c>
-      <c r="C362" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D362" s="1"/>
-      <c r="E362" s="1"/>
-      <c r="F362" s="1" t="s">
-        <v>866</v>
-      </c>
-      <c r="G362" s="1" t="s">
-        <v>147</v>
-      </c>
+        <v>862</v>
+      </c>
+      <c r="C362" s="2" t="s">
+        <v>863</v>
+      </c>
+      <c r="D362" s="1" t="s">
+        <v>864</v>
+      </c>
+      <c r="E362" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F362" s="1"/>
+      <c r="G362" s="1"/>
       <c r="H362" s="1"/>
       <c r="I362" s="1"/>
       <c r="J362" s="1"/>
@@ -16781,34 +16781,28 @@
       <c r="P362" s="1"/>
       <c r="Q362" s="1"/>
     </row>
-    <row r="363" spans="1:17" ht="52">
+    <row r="363" spans="1:26">
       <c r="A363" s="1" t="s">
-        <v>867</v>
+        <v>21</v>
       </c>
       <c r="B363" s="1" t="s">
-        <v>868</v>
-      </c>
-      <c r="C363" s="10" t="s">
-        <v>869</v>
-      </c>
-      <c r="D363" s="9" t="s">
-        <v>870</v>
-      </c>
-      <c r="E363" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F363" s="1"/>
-      <c r="G363" s="1"/>
+        <v>865</v>
+      </c>
+      <c r="C363" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D363" s="1"/>
+      <c r="E363" s="1"/>
+      <c r="F363" s="1" t="s">
+        <v>866</v>
+      </c>
+      <c r="G363" s="1" t="s">
+        <v>147</v>
+      </c>
       <c r="H363" s="1"/>
-      <c r="I363" s="1" t="s">
-        <v>871</v>
-      </c>
-      <c r="J363" s="1" t="s">
-        <v>872</v>
-      </c>
-      <c r="K363" s="1" t="s">
-        <v>873</v>
-      </c>
+      <c r="I363" s="1"/>
+      <c r="J363" s="1"/>
+      <c r="K363" s="1"/>
       <c r="L363" s="1"/>
       <c r="M363" s="1"/>
       <c r="N363" s="1"/>
@@ -16816,28 +16810,34 @@
       <c r="P363" s="1"/>
       <c r="Q363" s="1"/>
     </row>
-    <row r="364" spans="1:17" ht="78">
+    <row r="364" spans="1:26" ht="52">
       <c r="A364" s="1" t="s">
-        <v>139</v>
+        <v>867</v>
       </c>
       <c r="B364" s="1" t="s">
-        <v>874</v>
+        <v>868</v>
       </c>
       <c r="C364" s="10" t="s">
-        <v>875</v>
-      </c>
-      <c r="D364" s="10" t="s">
-        <v>876</v>
-      </c>
-      <c r="E364" s="1"/>
-      <c r="F364" s="2" t="s">
-        <v>877</v>
-      </c>
-      <c r="G364" s="2"/>
-      <c r="H364" s="2"/>
-      <c r="I364" s="2"/>
-      <c r="J364" s="1"/>
-      <c r="K364" s="1"/>
+        <v>869</v>
+      </c>
+      <c r="D364" s="9" t="s">
+        <v>870</v>
+      </c>
+      <c r="E364" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F364" s="1"/>
+      <c r="G364" s="1"/>
+      <c r="H364" s="1"/>
+      <c r="I364" s="1" t="s">
+        <v>871</v>
+      </c>
+      <c r="J364" s="1" t="s">
+        <v>872</v>
+      </c>
+      <c r="K364" s="1" t="s">
+        <v>873</v>
+      </c>
       <c r="L364" s="1"/>
       <c r="M364" s="1"/>
       <c r="N364" s="1"/>
@@ -16845,26 +16845,26 @@
       <c r="P364" s="1"/>
       <c r="Q364" s="1"/>
     </row>
-    <row r="365" spans="1:17" ht="104">
+    <row r="365" spans="1:26" ht="78">
       <c r="A365" s="1" t="s">
         <v>139</v>
       </c>
       <c r="B365" s="1" t="s">
-        <v>878</v>
+        <v>874</v>
       </c>
       <c r="C365" s="10" t="s">
-        <v>879</v>
+        <v>875</v>
       </c>
       <c r="D365" s="10" t="s">
-        <v>880</v>
+        <v>876</v>
       </c>
       <c r="E365" s="1"/>
       <c r="F365" s="2" t="s">
-        <v>881</v>
+        <v>877</v>
       </c>
       <c r="G365" s="2"/>
-      <c r="H365" s="1"/>
-      <c r="I365" s="1"/>
+      <c r="H365" s="2"/>
+      <c r="I365" s="2"/>
       <c r="J365" s="1"/>
       <c r="K365" s="1"/>
       <c r="L365" s="1"/>
@@ -16874,88 +16874,88 @@
       <c r="P365" s="1"/>
       <c r="Q365" s="1"/>
     </row>
-    <row r="366" spans="1:17" ht="169">
+    <row r="366" spans="1:26" ht="104">
       <c r="A366" s="1" t="s">
         <v>139</v>
       </c>
       <c r="B366" s="1" t="s">
+        <v>878</v>
+      </c>
+      <c r="C366" s="10" t="s">
+        <v>879</v>
+      </c>
+      <c r="D366" s="10" t="s">
+        <v>880</v>
+      </c>
+      <c r="E366" s="1"/>
+      <c r="F366" s="2" t="s">
+        <v>881</v>
+      </c>
+      <c r="G366" s="2"/>
+      <c r="H366" s="1"/>
+      <c r="I366" s="1"/>
+      <c r="J366" s="1"/>
+      <c r="K366" s="1"/>
+      <c r="L366" s="1"/>
+      <c r="M366" s="1"/>
+      <c r="N366" s="1"/>
+      <c r="O366" s="1"/>
+      <c r="P366" s="1"/>
+      <c r="Q366" s="1"/>
+    </row>
+    <row r="367" spans="1:26" ht="169">
+      <c r="A367" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B367" s="1" t="s">
         <v>882</v>
       </c>
-      <c r="C366" s="10" t="s">
+      <c r="C367" s="10" t="s">
         <v>883</v>
       </c>
-      <c r="D366" s="10" t="s">
+      <c r="D367" s="10" t="s">
         <v>884</v>
       </c>
-      <c r="E366" s="2"/>
-      <c r="F366" s="2"/>
-      <c r="G366" s="2"/>
-      <c r="H366" s="2"/>
-      <c r="I366" s="2"/>
-      <c r="J366" s="2"/>
-      <c r="K366" s="2"/>
-      <c r="L366" s="2"/>
-      <c r="M366" s="2"/>
-      <c r="N366" s="2"/>
-      <c r="O366" s="2"/>
-      <c r="P366" s="2"/>
-      <c r="Q366" s="2"/>
-    </row>
-    <row r="367" spans="1:17">
-      <c r="A367" s="1" t="s">
+      <c r="E367" s="2"/>
+      <c r="F367" s="2"/>
+      <c r="G367" s="2"/>
+      <c r="H367" s="2"/>
+      <c r="I367" s="2"/>
+      <c r="J367" s="2"/>
+      <c r="K367" s="2"/>
+      <c r="L367" s="2"/>
+      <c r="M367" s="2"/>
+      <c r="N367" s="2"/>
+      <c r="O367" s="2"/>
+      <c r="P367" s="2"/>
+      <c r="Q367" s="2"/>
+    </row>
+    <row r="368" spans="1:26">
+      <c r="A368" s="1" t="s">
         <v>885</v>
       </c>
-      <c r="B367" s="1" t="s">
+      <c r="B368" s="1" t="s">
         <v>886</v>
       </c>
-      <c r="C367" s="2" t="s">
+      <c r="C368" s="2" t="s">
         <v>887</v>
       </c>
-      <c r="D367" s="1" t="s">
+      <c r="D368" s="1" t="s">
         <v>888</v>
       </c>
-      <c r="E367" s="1"/>
-      <c r="F367" s="1"/>
-      <c r="G367" s="1"/>
-      <c r="H367" s="1"/>
-      <c r="I367" s="1" t="s">
+      <c r="E368" s="1"/>
+      <c r="F368" s="1"/>
+      <c r="G368" s="1"/>
+      <c r="H368" s="1"/>
+      <c r="I368" s="1" t="s">
         <v>889</v>
       </c>
-      <c r="J367" s="1" t="s">
+      <c r="J368" s="1" t="s">
         <v>872</v>
       </c>
-      <c r="K367" s="1" t="s">
+      <c r="K368" s="1" t="s">
         <v>873</v>
       </c>
-      <c r="L367" s="1"/>
-      <c r="M367" s="1"/>
-      <c r="N367" s="1"/>
-      <c r="O367" s="1"/>
-      <c r="P367" s="1"/>
-      <c r="Q367" s="1"/>
-    </row>
-    <row r="368" spans="1:17" ht="91">
-      <c r="A368" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="B368" s="1" t="s">
-        <v>890</v>
-      </c>
-      <c r="C368" s="10" t="s">
-        <v>891</v>
-      </c>
-      <c r="D368" s="10" t="s">
-        <v>892</v>
-      </c>
-      <c r="E368" s="1"/>
-      <c r="F368" s="2" t="s">
-        <v>893</v>
-      </c>
-      <c r="G368" s="2"/>
-      <c r="H368" s="2"/>
-      <c r="I368" s="2"/>
-      <c r="J368" s="2"/>
-      <c r="K368" s="1"/>
       <c r="L368" s="1"/>
       <c r="M368" s="1"/>
       <c r="N368" s="1"/>
@@ -16968,17 +16968,17 @@
         <v>139</v>
       </c>
       <c r="B369" s="1" t="s">
-        <v>894</v>
+        <v>890</v>
       </c>
       <c r="C369" s="10" t="s">
-        <v>895</v>
+        <v>891</v>
       </c>
       <c r="D369" s="10" t="s">
-        <v>896</v>
+        <v>892</v>
       </c>
       <c r="E369" s="1"/>
       <c r="F369" s="2" t="s">
-        <v>897</v>
+        <v>893</v>
       </c>
       <c r="G369" s="2"/>
       <c r="H369" s="2"/>
@@ -16992,74 +16992,74 @@
       <c r="P369" s="1"/>
       <c r="Q369" s="1"/>
     </row>
-    <row r="370" spans="1:17" ht="130">
+    <row r="370" spans="1:17" ht="91">
       <c r="A370" s="1" t="s">
         <v>139</v>
       </c>
       <c r="B370" s="1" t="s">
-        <v>898</v>
+        <v>894</v>
       </c>
       <c r="C370" s="10" t="s">
-        <v>899</v>
+        <v>895</v>
       </c>
       <c r="D370" s="10" t="s">
-        <v>900</v>
-      </c>
-      <c r="E370" s="2"/>
-      <c r="F370" s="2"/>
+        <v>896</v>
+      </c>
+      <c r="E370" s="1"/>
+      <c r="F370" s="2" t="s">
+        <v>897</v>
+      </c>
       <c r="G370" s="2"/>
       <c r="H370" s="2"/>
       <c r="I370" s="2"/>
       <c r="J370" s="2"/>
-      <c r="K370" s="2"/>
-      <c r="L370" s="2"/>
-      <c r="M370" s="2"/>
-      <c r="N370" s="2"/>
-      <c r="O370" s="2"/>
-      <c r="P370" s="2"/>
-      <c r="Q370" s="2"/>
-    </row>
-    <row r="371" spans="1:17">
+      <c r="K370" s="1"/>
+      <c r="L370" s="1"/>
+      <c r="M370" s="1"/>
+      <c r="N370" s="1"/>
+      <c r="O370" s="1"/>
+      <c r="P370" s="1"/>
+      <c r="Q370" s="1"/>
+    </row>
+    <row r="371" spans="1:17" ht="130">
       <c r="A371" s="1" t="s">
-        <v>55</v>
+        <v>139</v>
       </c>
       <c r="B371" s="1" t="s">
-        <v>865</v>
-      </c>
-      <c r="C371" s="1"/>
-      <c r="D371" s="1"/>
-      <c r="E371" s="1"/>
-      <c r="F371" s="1"/>
-      <c r="G371" s="1"/>
-      <c r="H371" s="1"/>
-      <c r="I371" s="1"/>
-      <c r="J371" s="1"/>
-      <c r="K371" s="1"/>
-      <c r="L371" s="1"/>
-      <c r="M371" s="1"/>
-      <c r="N371" s="1"/>
-      <c r="O371" s="1"/>
-      <c r="P371" s="1"/>
-      <c r="Q371" s="1"/>
+        <v>898</v>
+      </c>
+      <c r="C371" s="10" t="s">
+        <v>899</v>
+      </c>
+      <c r="D371" s="10" t="s">
+        <v>900</v>
+      </c>
+      <c r="E371" s="2"/>
+      <c r="F371" s="2"/>
+      <c r="G371" s="2"/>
+      <c r="H371" s="2"/>
+      <c r="I371" s="2"/>
+      <c r="J371" s="2"/>
+      <c r="K371" s="2"/>
+      <c r="L371" s="2"/>
+      <c r="M371" s="2"/>
+      <c r="N371" s="2"/>
+      <c r="O371" s="2"/>
+      <c r="P371" s="2"/>
+      <c r="Q371" s="2"/>
     </row>
     <row r="372" spans="1:17">
       <c r="A372" s="1" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="B372" s="1" t="s">
-        <v>901</v>
-      </c>
-      <c r="C372" s="1" t="s">
-        <v>23</v>
-      </c>
+        <v>865</v>
+      </c>
+      <c r="C372" s="1"/>
       <c r="D372" s="1"/>
       <c r="E372" s="1"/>
-      <c r="F372" s="1" t="s">
-        <v>902</v>
-      </c>
-      <c r="G372" s="1" t="s">
-        <v>147</v>
-      </c>
+      <c r="F372" s="1"/>
+      <c r="G372" s="1"/>
       <c r="H372" s="1"/>
       <c r="I372" s="1"/>
       <c r="J372" s="1"/>
@@ -17071,24 +17071,24 @@
       <c r="P372" s="1"/>
       <c r="Q372" s="1"/>
     </row>
-    <row r="373" spans="1:17" ht="52">
+    <row r="373" spans="1:17">
       <c r="A373" s="1" t="s">
-        <v>166</v>
+        <v>21</v>
       </c>
       <c r="B373" s="1" t="s">
-        <v>868</v>
-      </c>
-      <c r="C373" s="10" t="s">
-        <v>903</v>
-      </c>
-      <c r="D373" s="9" t="s">
-        <v>904</v>
-      </c>
-      <c r="E373" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F373" s="1"/>
-      <c r="G373" s="1"/>
+        <v>901</v>
+      </c>
+      <c r="C373" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D373" s="1"/>
+      <c r="E373" s="1"/>
+      <c r="F373" s="1" t="s">
+        <v>902</v>
+      </c>
+      <c r="G373" s="1" t="s">
+        <v>147</v>
+      </c>
       <c r="H373" s="1"/>
       <c r="I373" s="1"/>
       <c r="J373" s="1"/>
@@ -17100,23 +17100,23 @@
       <c r="P373" s="1"/>
       <c r="Q373" s="1"/>
     </row>
-    <row r="374" spans="1:17" ht="104">
+    <row r="374" spans="1:17" ht="52">
       <c r="A374" s="1" t="s">
-        <v>139</v>
+        <v>166</v>
       </c>
       <c r="B374" s="1" t="s">
-        <v>874</v>
+        <v>868</v>
       </c>
       <c r="C374" s="10" t="s">
-        <v>905</v>
-      </c>
-      <c r="D374" s="10" t="s">
-        <v>906</v>
-      </c>
-      <c r="E374" s="1"/>
-      <c r="F374" s="2" t="s">
-        <v>907</v>
-      </c>
+        <v>903</v>
+      </c>
+      <c r="D374" s="9" t="s">
+        <v>904</v>
+      </c>
+      <c r="E374" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F374" s="1"/>
       <c r="G374" s="1"/>
       <c r="H374" s="1"/>
       <c r="I374" s="1"/>
@@ -17129,22 +17129,22 @@
       <c r="P374" s="1"/>
       <c r="Q374" s="1"/>
     </row>
-    <row r="375" spans="1:17">
+    <row r="375" spans="1:17" ht="104">
       <c r="A375" s="1" t="s">
         <v>139</v>
       </c>
       <c r="B375" s="1" t="s">
-        <v>878</v>
-      </c>
-      <c r="C375" s="2" t="s">
-        <v>908</v>
-      </c>
-      <c r="D375" s="2" t="s">
-        <v>909</v>
+        <v>874</v>
+      </c>
+      <c r="C375" s="10" t="s">
+        <v>905</v>
+      </c>
+      <c r="D375" s="10" t="s">
+        <v>906</v>
       </c>
       <c r="E375" s="1"/>
       <c r="F375" s="2" t="s">
-        <v>910</v>
+        <v>907</v>
       </c>
       <c r="G375" s="1"/>
       <c r="H375" s="1"/>
@@ -17163,18 +17163,20 @@
         <v>139</v>
       </c>
       <c r="B376" s="1" t="s">
-        <v>911</v>
+        <v>878</v>
       </c>
       <c r="C376" s="2" t="s">
-        <v>912</v>
+        <v>908</v>
       </c>
       <c r="D376" s="2" t="s">
-        <v>913</v>
-      </c>
-      <c r="E376" s="2"/>
-      <c r="F376" s="2"/>
-      <c r="G376" s="2"/>
-      <c r="H376" s="2"/>
+        <v>909</v>
+      </c>
+      <c r="E376" s="1"/>
+      <c r="F376" s="2" t="s">
+        <v>910</v>
+      </c>
+      <c r="G376" s="1"/>
+      <c r="H376" s="1"/>
       <c r="I376" s="1"/>
       <c r="J376" s="1"/>
       <c r="K376" s="1"/>
@@ -17190,18 +17192,16 @@
         <v>139</v>
       </c>
       <c r="B377" s="1" t="s">
-        <v>914</v>
+        <v>911</v>
       </c>
       <c r="C377" s="2" t="s">
-        <v>915</v>
+        <v>912</v>
       </c>
       <c r="D377" s="2" t="s">
-        <v>916</v>
-      </c>
-      <c r="E377" s="1"/>
-      <c r="F377" s="2" t="s">
-        <v>917</v>
-      </c>
+        <v>913</v>
+      </c>
+      <c r="E377" s="2"/>
+      <c r="F377" s="2"/>
       <c r="G377" s="2"/>
       <c r="H377" s="2"/>
       <c r="I377" s="1"/>
@@ -17219,17 +17219,17 @@
         <v>139</v>
       </c>
       <c r="B378" s="1" t="s">
-        <v>918</v>
+        <v>914</v>
       </c>
       <c r="C378" s="2" t="s">
-        <v>919</v>
+        <v>915</v>
       </c>
       <c r="D378" s="2" t="s">
-        <v>920</v>
+        <v>916</v>
       </c>
       <c r="E378" s="1"/>
       <c r="F378" s="2" t="s">
-        <v>921</v>
+        <v>917</v>
       </c>
       <c r="G378" s="2"/>
       <c r="H378" s="2"/>
@@ -17248,17 +17248,17 @@
         <v>139</v>
       </c>
       <c r="B379" s="1" t="s">
-        <v>922</v>
+        <v>918</v>
       </c>
       <c r="C379" s="2" t="s">
-        <v>923</v>
+        <v>919</v>
       </c>
       <c r="D379" s="2" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="E379" s="1"/>
       <c r="F379" s="2" t="s">
-        <v>925</v>
+        <v>921</v>
       </c>
       <c r="G379" s="2"/>
       <c r="H379" s="2"/>
@@ -17277,20 +17277,20 @@
         <v>139</v>
       </c>
       <c r="B380" s="1" t="s">
-        <v>926</v>
+        <v>922</v>
       </c>
       <c r="C380" s="2" t="s">
-        <v>927</v>
+        <v>923</v>
       </c>
       <c r="D380" s="2" t="s">
-        <v>928</v>
+        <v>924</v>
       </c>
       <c r="E380" s="1"/>
       <c r="F380" s="2" t="s">
-        <v>929</v>
+        <v>925</v>
       </c>
       <c r="G380" s="2"/>
-      <c r="H380" s="1"/>
+      <c r="H380" s="2"/>
       <c r="I380" s="1"/>
       <c r="J380" s="1"/>
       <c r="K380" s="1"/>
@@ -17303,30 +17303,26 @@
     </row>
     <row r="381" spans="1:17">
       <c r="A381" s="1" t="s">
-        <v>885</v>
+        <v>139</v>
       </c>
       <c r="B381" s="1" t="s">
-        <v>886</v>
+        <v>926</v>
       </c>
       <c r="C381" s="2" t="s">
-        <v>887</v>
-      </c>
-      <c r="D381" s="1" t="s">
-        <v>888</v>
+        <v>927</v>
+      </c>
+      <c r="D381" s="2" t="s">
+        <v>928</v>
       </c>
       <c r="E381" s="1"/>
-      <c r="F381" s="1"/>
-      <c r="G381" s="1"/>
+      <c r="F381" s="2" t="s">
+        <v>929</v>
+      </c>
+      <c r="G381" s="2"/>
       <c r="H381" s="1"/>
-      <c r="I381" s="1" t="s">
-        <v>889</v>
-      </c>
-      <c r="J381" s="1" t="s">
-        <v>872</v>
-      </c>
-      <c r="K381" s="1" t="s">
-        <v>873</v>
-      </c>
+      <c r="I381" s="1"/>
+      <c r="J381" s="1"/>
+      <c r="K381" s="1"/>
       <c r="L381" s="1"/>
       <c r="M381" s="1"/>
       <c r="N381" s="1"/>
@@ -17336,26 +17332,30 @@
     </row>
     <row r="382" spans="1:17">
       <c r="A382" s="1" t="s">
-        <v>139</v>
+        <v>885</v>
       </c>
       <c r="B382" s="1" t="s">
-        <v>890</v>
+        <v>886</v>
       </c>
       <c r="C382" s="2" t="s">
-        <v>930</v>
-      </c>
-      <c r="D382" s="2" t="s">
-        <v>931</v>
+        <v>887</v>
+      </c>
+      <c r="D382" s="1" t="s">
+        <v>888</v>
       </c>
       <c r="E382" s="1"/>
-      <c r="F382" s="2" t="s">
-        <v>932</v>
-      </c>
-      <c r="G382" s="2"/>
-      <c r="H382" s="2"/>
-      <c r="I382" s="2"/>
-      <c r="J382" s="2"/>
-      <c r="K382" s="1"/>
+      <c r="F382" s="1"/>
+      <c r="G382" s="1"/>
+      <c r="H382" s="1"/>
+      <c r="I382" s="1" t="s">
+        <v>889</v>
+      </c>
+      <c r="J382" s="1" t="s">
+        <v>872</v>
+      </c>
+      <c r="K382" s="1" t="s">
+        <v>873</v>
+      </c>
       <c r="L382" s="1"/>
       <c r="M382" s="1"/>
       <c r="N382" s="1"/>
@@ -17368,17 +17368,17 @@
         <v>139</v>
       </c>
       <c r="B383" s="1" t="s">
-        <v>894</v>
+        <v>890</v>
       </c>
       <c r="C383" s="2" t="s">
-        <v>933</v>
+        <v>930</v>
       </c>
       <c r="D383" s="2" t="s">
-        <v>934</v>
+        <v>931</v>
       </c>
       <c r="E383" s="1"/>
       <c r="F383" s="2" t="s">
-        <v>897</v>
+        <v>932</v>
       </c>
       <c r="G383" s="2"/>
       <c r="H383" s="2"/>
@@ -17397,20 +17397,22 @@
         <v>139</v>
       </c>
       <c r="B384" s="1" t="s">
-        <v>935</v>
+        <v>894</v>
       </c>
       <c r="C384" s="2" t="s">
-        <v>936</v>
+        <v>933</v>
       </c>
       <c r="D384" s="2" t="s">
-        <v>937</v>
-      </c>
-      <c r="E384" s="2"/>
-      <c r="F384" s="1"/>
-      <c r="G384" s="1"/>
-      <c r="H384" s="1"/>
-      <c r="I384" s="1"/>
-      <c r="J384" s="1"/>
+        <v>934</v>
+      </c>
+      <c r="E384" s="1"/>
+      <c r="F384" s="2" t="s">
+        <v>897</v>
+      </c>
+      <c r="G384" s="2"/>
+      <c r="H384" s="2"/>
+      <c r="I384" s="2"/>
+      <c r="J384" s="2"/>
       <c r="K384" s="1"/>
       <c r="L384" s="1"/>
       <c r="M384" s="1"/>
@@ -17424,20 +17426,18 @@
         <v>139</v>
       </c>
       <c r="B385" s="1" t="s">
-        <v>938</v>
+        <v>935</v>
       </c>
       <c r="C385" s="2" t="s">
-        <v>939</v>
+        <v>936</v>
       </c>
       <c r="D385" s="2" t="s">
-        <v>940</v>
-      </c>
-      <c r="E385" s="1"/>
-      <c r="F385" s="2" t="s">
-        <v>917</v>
-      </c>
-      <c r="G385" s="2"/>
-      <c r="H385" s="2"/>
+        <v>937</v>
+      </c>
+      <c r="E385" s="2"/>
+      <c r="F385" s="1"/>
+      <c r="G385" s="1"/>
+      <c r="H385" s="1"/>
       <c r="I385" s="1"/>
       <c r="J385" s="1"/>
       <c r="K385" s="1"/>
@@ -17453,17 +17453,17 @@
         <v>139</v>
       </c>
       <c r="B386" s="1" t="s">
-        <v>941</v>
+        <v>938</v>
       </c>
       <c r="C386" s="2" t="s">
-        <v>942</v>
+        <v>939</v>
       </c>
       <c r="D386" s="2" t="s">
-        <v>943</v>
+        <v>940</v>
       </c>
       <c r="E386" s="1"/>
       <c r="F386" s="2" t="s">
-        <v>921</v>
+        <v>917</v>
       </c>
       <c r="G386" s="2"/>
       <c r="H386" s="2"/>
@@ -17482,17 +17482,17 @@
         <v>139</v>
       </c>
       <c r="B387" s="1" t="s">
-        <v>944</v>
+        <v>941</v>
       </c>
       <c r="C387" s="2" t="s">
-        <v>945</v>
+        <v>942</v>
       </c>
       <c r="D387" s="2" t="s">
-        <v>946</v>
+        <v>943</v>
       </c>
       <c r="E387" s="1"/>
       <c r="F387" s="2" t="s">
-        <v>925</v>
+        <v>921</v>
       </c>
       <c r="G387" s="2"/>
       <c r="H387" s="2"/>
@@ -17506,25 +17506,25 @@
       <c r="P387" s="1"/>
       <c r="Q387" s="1"/>
     </row>
-    <row r="388" spans="1:17" ht="104">
+    <row r="388" spans="1:17">
       <c r="A388" s="1" t="s">
         <v>139</v>
       </c>
       <c r="B388" s="1" t="s">
-        <v>947</v>
-      </c>
-      <c r="C388" s="10" t="s">
-        <v>948</v>
-      </c>
-      <c r="D388" s="10" t="s">
-        <v>949</v>
+        <v>944</v>
+      </c>
+      <c r="C388" s="2" t="s">
+        <v>945</v>
+      </c>
+      <c r="D388" s="2" t="s">
+        <v>946</v>
       </c>
       <c r="E388" s="1"/>
       <c r="F388" s="2" t="s">
-        <v>929</v>
+        <v>925</v>
       </c>
       <c r="G388" s="2"/>
-      <c r="H388" s="1"/>
+      <c r="H388" s="2"/>
       <c r="I388" s="1"/>
       <c r="J388" s="1"/>
       <c r="K388" s="1"/>
@@ -17535,18 +17535,24 @@
       <c r="P388" s="1"/>
       <c r="Q388" s="1"/>
     </row>
-    <row r="389" spans="1:17">
+    <row r="389" spans="1:17" ht="104">
       <c r="A389" s="1" t="s">
-        <v>55</v>
+        <v>139</v>
       </c>
       <c r="B389" s="1" t="s">
-        <v>901</v>
-      </c>
-      <c r="C389" s="1"/>
-      <c r="D389" s="1"/>
+        <v>947</v>
+      </c>
+      <c r="C389" s="10" t="s">
+        <v>948</v>
+      </c>
+      <c r="D389" s="10" t="s">
+        <v>949</v>
+      </c>
       <c r="E389" s="1"/>
-      <c r="F389" s="1"/>
-      <c r="G389" s="1"/>
+      <c r="F389" s="2" t="s">
+        <v>929</v>
+      </c>
+      <c r="G389" s="2"/>
       <c r="H389" s="1"/>
       <c r="I389" s="1"/>
       <c r="J389" s="1"/>
@@ -17563,7 +17569,7 @@
         <v>55</v>
       </c>
       <c r="B390" s="1" t="s">
-        <v>835</v>
+        <v>901</v>
       </c>
       <c r="C390" s="1"/>
       <c r="D390" s="1"/>
@@ -17583,24 +17589,16 @@
     </row>
     <row r="391" spans="1:17">
       <c r="A391" s="1" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="B391" s="1" t="s">
-        <v>950</v>
-      </c>
-      <c r="C391" s="1" t="s">
-        <v>951</v>
-      </c>
-      <c r="D391" s="1" t="s">
-        <v>952</v>
-      </c>
+        <v>835</v>
+      </c>
+      <c r="C391" s="1"/>
+      <c r="D391" s="1"/>
       <c r="E391" s="1"/>
-      <c r="F391" s="1" t="s">
-        <v>838</v>
-      </c>
-      <c r="G391" s="1" t="s">
-        <v>147</v>
-      </c>
+      <c r="F391" s="1"/>
+      <c r="G391" s="1"/>
       <c r="H391" s="1"/>
       <c r="I391" s="1"/>
       <c r="J391" s="1"/>
@@ -17614,25 +17612,29 @@
     </row>
     <row r="392" spans="1:17">
       <c r="A392" s="1" t="s">
-        <v>139</v>
+        <v>21</v>
       </c>
       <c r="B392" s="1" t="s">
-        <v>953</v>
-      </c>
-      <c r="C392" s="2" t="s">
-        <v>954</v>
-      </c>
-      <c r="D392" s="2" t="s">
-        <v>955</v>
-      </c>
-      <c r="E392" s="2"/>
-      <c r="F392" s="2"/>
-      <c r="G392" s="2"/>
-      <c r="H392" s="2"/>
-      <c r="I392" s="2"/>
-      <c r="J392" s="2"/>
-      <c r="K392" s="2"/>
-      <c r="L392" s="2"/>
+        <v>950</v>
+      </c>
+      <c r="C392" s="1" t="s">
+        <v>951</v>
+      </c>
+      <c r="D392" s="1" t="s">
+        <v>952</v>
+      </c>
+      <c r="E392" s="1"/>
+      <c r="F392" s="1" t="s">
+        <v>838</v>
+      </c>
+      <c r="G392" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="H392" s="1"/>
+      <c r="I392" s="1"/>
+      <c r="J392" s="1"/>
+      <c r="K392" s="1"/>
+      <c r="L392" s="1"/>
       <c r="M392" s="1"/>
       <c r="N392" s="1"/>
       <c r="O392" s="1"/>
@@ -17641,27 +17643,25 @@
     </row>
     <row r="393" spans="1:17">
       <c r="A393" s="1" t="s">
-        <v>956</v>
+        <v>139</v>
       </c>
       <c r="B393" s="1" t="s">
-        <v>957</v>
+        <v>953</v>
       </c>
       <c r="C393" s="2" t="s">
-        <v>958</v>
-      </c>
-      <c r="D393" s="1" t="s">
-        <v>959</v>
-      </c>
-      <c r="E393" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F393" s="1"/>
-      <c r="G393" s="1"/>
-      <c r="H393" s="1"/>
-      <c r="I393" s="1"/>
-      <c r="J393" s="1"/>
-      <c r="K393" s="1"/>
-      <c r="L393" s="1"/>
+        <v>954</v>
+      </c>
+      <c r="D393" s="2" t="s">
+        <v>955</v>
+      </c>
+      <c r="E393" s="2"/>
+      <c r="F393" s="2"/>
+      <c r="G393" s="2"/>
+      <c r="H393" s="2"/>
+      <c r="I393" s="2"/>
+      <c r="J393" s="2"/>
+      <c r="K393" s="2"/>
+      <c r="L393" s="2"/>
       <c r="M393" s="1"/>
       <c r="N393" s="1"/>
       <c r="O393" s="1"/>
@@ -17670,21 +17670,21 @@
     </row>
     <row r="394" spans="1:17">
       <c r="A394" s="1" t="s">
-        <v>139</v>
+        <v>956</v>
       </c>
       <c r="B394" s="1" t="s">
-        <v>960</v>
+        <v>957</v>
       </c>
       <c r="C394" s="2" t="s">
-        <v>961</v>
+        <v>958</v>
       </c>
       <c r="D394" s="1" t="s">
-        <v>962</v>
-      </c>
-      <c r="E394" s="1"/>
-      <c r="F394" s="2" t="s">
-        <v>963</v>
-      </c>
+        <v>959</v>
+      </c>
+      <c r="E394" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F394" s="1"/>
       <c r="G394" s="1"/>
       <c r="H394" s="1"/>
       <c r="I394" s="1"/>
@@ -17702,19 +17702,19 @@
         <v>139</v>
       </c>
       <c r="B395" s="1" t="s">
-        <v>964</v>
+        <v>960</v>
       </c>
       <c r="C395" s="2" t="s">
-        <v>965</v>
-      </c>
-      <c r="D395" s="2" t="s">
-        <v>966</v>
+        <v>961</v>
+      </c>
+      <c r="D395" s="1" t="s">
+        <v>962</v>
       </c>
       <c r="E395" s="1"/>
       <c r="F395" s="2" t="s">
-        <v>967</v>
-      </c>
-      <c r="G395" s="2"/>
+        <v>963</v>
+      </c>
+      <c r="G395" s="1"/>
       <c r="H395" s="1"/>
       <c r="I395" s="1"/>
       <c r="J395" s="1"/>
@@ -17728,22 +17728,22 @@
     </row>
     <row r="396" spans="1:17">
       <c r="A396" s="1" t="s">
-        <v>166</v>
+        <v>139</v>
       </c>
       <c r="B396" s="1" t="s">
-        <v>968</v>
+        <v>964</v>
       </c>
       <c r="C396" s="2" t="s">
-        <v>969</v>
-      </c>
-      <c r="D396" s="1" t="s">
-        <v>970</v>
-      </c>
-      <c r="E396" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F396" s="1"/>
-      <c r="G396" s="1"/>
+        <v>965</v>
+      </c>
+      <c r="D396" s="2" t="s">
+        <v>966</v>
+      </c>
+      <c r="E396" s="1"/>
+      <c r="F396" s="2" t="s">
+        <v>967</v>
+      </c>
+      <c r="G396" s="2"/>
       <c r="H396" s="1"/>
       <c r="I396" s="1"/>
       <c r="J396" s="1"/>
@@ -17757,23 +17757,21 @@
     </row>
     <row r="397" spans="1:17">
       <c r="A397" s="1" t="s">
-        <v>971</v>
+        <v>166</v>
       </c>
       <c r="B397" s="1" t="s">
-        <v>972</v>
+        <v>968</v>
       </c>
       <c r="C397" s="2" t="s">
-        <v>973</v>
+        <v>969</v>
       </c>
       <c r="D397" s="1" t="s">
-        <v>974</v>
+        <v>970</v>
       </c>
       <c r="E397" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="F397" s="1" t="s">
-        <v>975</v>
-      </c>
+      <c r="F397" s="1"/>
       <c r="G397" s="1"/>
       <c r="H397" s="1"/>
       <c r="I397" s="1"/>
@@ -17788,19 +17786,22 @@
     </row>
     <row r="398" spans="1:17">
       <c r="A398" s="1" t="s">
-        <v>139</v>
+        <v>971</v>
       </c>
       <c r="B398" s="1" t="s">
-        <v>976</v>
+        <v>972</v>
       </c>
       <c r="C398" s="2" t="s">
-        <v>977</v>
+        <v>973</v>
       </c>
       <c r="D398" s="1" t="s">
-        <v>978</v>
-      </c>
-      <c r="F398" s="2" t="s">
-        <v>979</v>
+        <v>974</v>
+      </c>
+      <c r="E398" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F398" s="1" t="s">
+        <v>975</v>
       </c>
       <c r="G398" s="1"/>
       <c r="H398" s="1"/>
@@ -17814,21 +17815,21 @@
       <c r="P398" s="1"/>
       <c r="Q398" s="1"/>
     </row>
-    <row r="399" spans="1:17" ht="65">
+    <row r="399" spans="1:17">
       <c r="A399" s="1" t="s">
         <v>139</v>
       </c>
       <c r="B399" s="1" t="s">
-        <v>980</v>
-      </c>
-      <c r="C399" s="10" t="s">
-        <v>981</v>
-      </c>
-      <c r="D399" s="9" t="s">
-        <v>982</v>
+        <v>976</v>
+      </c>
+      <c r="C399" s="2" t="s">
+        <v>977</v>
+      </c>
+      <c r="D399" s="1" t="s">
+        <v>978</v>
       </c>
       <c r="F399" s="2" t="s">
-        <v>983</v>
+        <v>979</v>
       </c>
       <c r="G399" s="1"/>
       <c r="H399" s="1"/>
@@ -17842,27 +17843,24 @@
       <c r="P399" s="1"/>
       <c r="Q399" s="1"/>
     </row>
-    <row r="400" spans="1:17">
+    <row r="400" spans="1:17" ht="65">
       <c r="A400" s="1" t="s">
-        <v>166</v>
+        <v>139</v>
       </c>
       <c r="B400" s="1" t="s">
-        <v>984</v>
-      </c>
-      <c r="C400" s="2" t="s">
-        <v>985</v>
-      </c>
-      <c r="D400" s="1" t="s">
-        <v>986</v>
-      </c>
-      <c r="E400" s="1" t="s">
-        <v>170</v>
+        <v>980</v>
+      </c>
+      <c r="C400" s="10" t="s">
+        <v>981</v>
+      </c>
+      <c r="D400" s="9" t="s">
+        <v>982</v>
       </c>
       <c r="F400" s="2" t="s">
-        <v>902</v>
-      </c>
-      <c r="G400" s="2"/>
-      <c r="H400" s="2"/>
+        <v>983</v>
+      </c>
+      <c r="G400" s="1"/>
+      <c r="H400" s="1"/>
       <c r="I400" s="1"/>
       <c r="J400" s="1"/>
       <c r="K400" s="1"/>
@@ -17875,23 +17873,25 @@
     </row>
     <row r="401" spans="1:17">
       <c r="A401" s="1" t="s">
-        <v>139</v>
+        <v>166</v>
       </c>
       <c r="B401" s="1" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="C401" s="2" t="s">
-        <v>988</v>
-      </c>
-      <c r="D401" s="2" t="s">
-        <v>989</v>
-      </c>
-      <c r="E401" s="1"/>
+        <v>985</v>
+      </c>
+      <c r="D401" s="1" t="s">
+        <v>986</v>
+      </c>
+      <c r="E401" s="1" t="s">
+        <v>170</v>
+      </c>
       <c r="F401" s="2" t="s">
-        <v>990</v>
+        <v>902</v>
       </c>
       <c r="G401" s="2"/>
-      <c r="H401" s="1"/>
+      <c r="H401" s="2"/>
       <c r="I401" s="1"/>
       <c r="J401" s="1"/>
       <c r="K401" s="1"/>
@@ -17904,22 +17904,20 @@
     </row>
     <row r="402" spans="1:17">
       <c r="A402" s="1" t="s">
-        <v>991</v>
+        <v>139</v>
       </c>
       <c r="B402" s="1" t="s">
-        <v>992</v>
+        <v>987</v>
       </c>
       <c r="C402" s="2" t="s">
-        <v>993</v>
-      </c>
-      <c r="D402" s="1" t="s">
-        <v>994</v>
-      </c>
-      <c r="E402" s="1" t="s">
-        <v>170</v>
-      </c>
+        <v>988</v>
+      </c>
+      <c r="D402" s="2" t="s">
+        <v>989</v>
+      </c>
+      <c r="E402" s="1"/>
       <c r="F402" s="2" t="s">
-        <v>995</v>
+        <v>990</v>
       </c>
       <c r="G402" s="2"/>
       <c r="H402" s="1"/>
@@ -17935,20 +17933,22 @@
     </row>
     <row r="403" spans="1:17">
       <c r="A403" s="1" t="s">
-        <v>139</v>
+        <v>991</v>
       </c>
       <c r="B403" s="1" t="s">
-        <v>996</v>
+        <v>992</v>
       </c>
       <c r="C403" s="2" t="s">
-        <v>997</v>
-      </c>
-      <c r="D403" s="2" t="s">
-        <v>998</v>
-      </c>
-      <c r="E403" s="1"/>
+        <v>993</v>
+      </c>
+      <c r="D403" s="1" t="s">
+        <v>994</v>
+      </c>
+      <c r="E403" s="1" t="s">
+        <v>170</v>
+      </c>
       <c r="F403" s="2" t="s">
-        <v>999</v>
+        <v>995</v>
       </c>
       <c r="G403" s="2"/>
       <c r="H403" s="1"/>
@@ -17962,24 +17962,24 @@
       <c r="P403" s="1"/>
       <c r="Q403" s="1"/>
     </row>
-    <row r="404" spans="1:17" ht="91">
+    <row r="404" spans="1:17">
       <c r="A404" s="1" t="s">
         <v>139</v>
       </c>
       <c r="B404" s="1" t="s">
-        <v>1000</v>
-      </c>
-      <c r="C404" s="10" t="s">
-        <v>1001</v>
-      </c>
-      <c r="D404" s="10" t="s">
-        <v>1002</v>
+        <v>996</v>
+      </c>
+      <c r="C404" s="2" t="s">
+        <v>997</v>
+      </c>
+      <c r="D404" s="2" t="s">
+        <v>998</v>
       </c>
       <c r="E404" s="1"/>
       <c r="F404" s="2" t="s">
-        <v>1003</v>
-      </c>
-      <c r="G404" s="1"/>
+        <v>999</v>
+      </c>
+      <c r="G404" s="2"/>
       <c r="H404" s="1"/>
       <c r="I404" s="1"/>
       <c r="J404" s="1"/>
@@ -17991,17 +17991,23 @@
       <c r="P404" s="1"/>
       <c r="Q404" s="1"/>
     </row>
-    <row r="405" spans="1:17">
+    <row r="405" spans="1:17" ht="91">
       <c r="A405" s="1" t="s">
-        <v>55</v>
+        <v>139</v>
       </c>
       <c r="B405" s="1" t="s">
-        <v>950</v>
-      </c>
-      <c r="C405" s="1"/>
-      <c r="D405" s="1"/>
+        <v>1000</v>
+      </c>
+      <c r="C405" s="10" t="s">
+        <v>1001</v>
+      </c>
+      <c r="D405" s="10" t="s">
+        <v>1002</v>
+      </c>
       <c r="E405" s="1"/>
-      <c r="F405" s="1"/>
+      <c r="F405" s="2" t="s">
+        <v>1003</v>
+      </c>
       <c r="G405" s="1"/>
       <c r="H405" s="1"/>
       <c r="I405" s="1"/>
@@ -18016,24 +18022,16 @@
     </row>
     <row r="406" spans="1:17">
       <c r="A406" s="1" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="B406" s="1" t="s">
-        <v>1004</v>
-      </c>
-      <c r="C406" s="1" t="s">
-        <v>1005</v>
-      </c>
-      <c r="D406" s="1" t="s">
-        <v>1006</v>
-      </c>
+        <v>950</v>
+      </c>
+      <c r="C406" s="1"/>
+      <c r="D406" s="1"/>
       <c r="E406" s="1"/>
-      <c r="F406" s="4" t="s">
-        <v>460</v>
-      </c>
-      <c r="G406" s="1" t="s">
-        <v>147</v>
-      </c>
+      <c r="F406" s="1"/>
+      <c r="G406" s="1"/>
       <c r="H406" s="1"/>
       <c r="I406" s="1"/>
       <c r="J406" s="1"/>
@@ -18045,30 +18043,32 @@
       <c r="P406" s="1"/>
       <c r="Q406" s="1"/>
     </row>
-    <row r="407" spans="1:17" ht="52">
+    <row r="407" spans="1:17">
       <c r="A407" s="1" t="s">
-        <v>139</v>
+        <v>21</v>
       </c>
       <c r="B407" s="1" t="s">
-        <v>1007</v>
-      </c>
-      <c r="C407" s="2" t="s">
-        <v>1008</v>
-      </c>
-      <c r="D407" s="2" t="s">
-        <v>1009</v>
-      </c>
-      <c r="E407" s="2"/>
-      <c r="F407" s="9" t="s">
-        <v>1010</v>
-      </c>
-      <c r="G407" s="2"/>
-      <c r="H407" s="2"/>
-      <c r="I407" s="2"/>
-      <c r="J407" s="2"/>
-      <c r="K407" s="2"/>
-      <c r="L407" s="2"/>
-      <c r="M407" s="2"/>
+        <v>1004</v>
+      </c>
+      <c r="C407" s="1" t="s">
+        <v>1005</v>
+      </c>
+      <c r="D407" s="1" t="s">
+        <v>1006</v>
+      </c>
+      <c r="E407" s="1"/>
+      <c r="F407" s="4" t="s">
+        <v>460</v>
+      </c>
+      <c r="G407" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="H407" s="1"/>
+      <c r="I407" s="1"/>
+      <c r="J407" s="1"/>
+      <c r="K407" s="1"/>
+      <c r="L407" s="1"/>
+      <c r="M407" s="1"/>
       <c r="N407" s="1"/>
       <c r="O407" s="1"/>
       <c r="P407" s="1"/>
@@ -18076,53 +18076,53 @@
     </row>
     <row r="408" spans="1:17" ht="52">
       <c r="A408" s="1" t="s">
-        <v>166</v>
+        <v>139</v>
       </c>
       <c r="B408" s="1" t="s">
-        <v>1011</v>
+        <v>1007</v>
       </c>
       <c r="C408" s="2" t="s">
-        <v>1012</v>
-      </c>
-      <c r="D408" s="1" t="s">
-        <v>1013</v>
-      </c>
-      <c r="E408" s="1" t="s">
-        <v>170</v>
-      </c>
+        <v>1008</v>
+      </c>
+      <c r="D408" s="2" t="s">
+        <v>1009</v>
+      </c>
+      <c r="E408" s="2"/>
       <c r="F408" s="9" t="s">
         <v>1010</v>
       </c>
-      <c r="G408" s="1"/>
-      <c r="H408" s="1"/>
-      <c r="I408" s="1"/>
-      <c r="J408" s="1"/>
-      <c r="K408" s="1"/>
-      <c r="L408" s="1"/>
-      <c r="M408" s="1"/>
+      <c r="G408" s="2"/>
+      <c r="H408" s="2"/>
+      <c r="I408" s="2"/>
+      <c r="J408" s="2"/>
+      <c r="K408" s="2"/>
+      <c r="L408" s="2"/>
+      <c r="M408" s="2"/>
       <c r="N408" s="1"/>
       <c r="O408" s="1"/>
       <c r="P408" s="1"/>
       <c r="Q408" s="1"/>
     </row>
-    <row r="409" spans="1:17" ht="104">
+    <row r="409" spans="1:17" ht="52">
       <c r="A409" s="1" t="s">
-        <v>139</v>
+        <v>166</v>
       </c>
       <c r="B409" s="1" t="s">
-        <v>1014</v>
-      </c>
-      <c r="C409" s="10" t="s">
-        <v>1015</v>
-      </c>
-      <c r="D409" s="10" t="s">
-        <v>1016</v>
-      </c>
-      <c r="E409" s="1"/>
-      <c r="F409" s="2" t="s">
-        <v>1017</v>
-      </c>
-      <c r="G409" s="2"/>
+        <v>1011</v>
+      </c>
+      <c r="C409" s="2" t="s">
+        <v>1012</v>
+      </c>
+      <c r="D409" s="1" t="s">
+        <v>1013</v>
+      </c>
+      <c r="E409" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F409" s="9" t="s">
+        <v>1010</v>
+      </c>
+      <c r="G409" s="1"/>
       <c r="H409" s="1"/>
       <c r="I409" s="1"/>
       <c r="J409" s="1"/>
@@ -18134,28 +18134,26 @@
       <c r="P409" s="1"/>
       <c r="Q409" s="1"/>
     </row>
-    <row r="410" spans="1:17" ht="52">
+    <row r="410" spans="1:17" ht="104">
       <c r="A410" s="1" t="s">
-        <v>166</v>
+        <v>139</v>
       </c>
       <c r="B410" s="1" t="s">
-        <v>1018</v>
-      </c>
-      <c r="C410" s="2" t="s">
-        <v>1019</v>
-      </c>
-      <c r="D410" s="2" t="s">
-        <v>1020</v>
-      </c>
-      <c r="E410" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="F410" s="9" t="s">
-        <v>1010</v>
+        <v>1014</v>
+      </c>
+      <c r="C410" s="10" t="s">
+        <v>1015</v>
+      </c>
+      <c r="D410" s="10" t="s">
+        <v>1016</v>
+      </c>
+      <c r="E410" s="1"/>
+      <c r="F410" s="2" t="s">
+        <v>1017</v>
       </c>
       <c r="G410" s="2"/>
-      <c r="H410" s="2"/>
-      <c r="I410" s="2"/>
+      <c r="H410" s="1"/>
+      <c r="I410" s="1"/>
       <c r="J410" s="1"/>
       <c r="K410" s="1"/>
       <c r="L410" s="1"/>
@@ -18165,26 +18163,28 @@
       <c r="P410" s="1"/>
       <c r="Q410" s="1"/>
     </row>
-    <row r="411" spans="1:17" ht="117">
+    <row r="411" spans="1:17" ht="52">
       <c r="A411" s="1" t="s">
-        <v>139</v>
+        <v>166</v>
       </c>
       <c r="B411" s="1" t="s">
-        <v>1021</v>
-      </c>
-      <c r="C411" s="10" t="s">
-        <v>1022</v>
-      </c>
-      <c r="D411" s="10" t="s">
-        <v>1023</v>
-      </c>
-      <c r="E411" s="1"/>
-      <c r="F411" s="2" t="s">
-        <v>1024</v>
+        <v>1018</v>
+      </c>
+      <c r="C411" s="2" t="s">
+        <v>1019</v>
+      </c>
+      <c r="D411" s="2" t="s">
+        <v>1020</v>
+      </c>
+      <c r="E411" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="F411" s="9" t="s">
+        <v>1010</v>
       </c>
       <c r="G411" s="2"/>
-      <c r="H411" s="1"/>
-      <c r="I411" s="1"/>
+      <c r="H411" s="2"/>
+      <c r="I411" s="2"/>
       <c r="J411" s="1"/>
       <c r="K411" s="1"/>
       <c r="L411" s="1"/>
@@ -18194,92 +18194,92 @@
       <c r="P411" s="1"/>
       <c r="Q411" s="1"/>
     </row>
-    <row r="412" spans="1:17">
+    <row r="412" spans="1:17" ht="117">
       <c r="A412" s="1" t="s">
-        <v>1025</v>
+        <v>139</v>
       </c>
       <c r="B412" s="1" t="s">
-        <v>1026</v>
-      </c>
-      <c r="C412" s="2" t="s">
-        <v>1027</v>
-      </c>
-      <c r="D412" s="1" t="s">
-        <v>1028</v>
-      </c>
-      <c r="E412" s="1" t="s">
-        <v>170</v>
-      </c>
+        <v>1021</v>
+      </c>
+      <c r="C412" s="10" t="s">
+        <v>1022</v>
+      </c>
+      <c r="D412" s="10" t="s">
+        <v>1023</v>
+      </c>
+      <c r="E412" s="1"/>
       <c r="F412" s="2" t="s">
-        <v>1029</v>
+        <v>1024</v>
       </c>
       <c r="G412" s="2"/>
-      <c r="H412" s="2"/>
-      <c r="I412" s="1" t="s">
-        <v>1030</v>
-      </c>
-      <c r="J412" s="1" t="s">
-        <v>1031</v>
-      </c>
-      <c r="K412" s="2" t="s">
-        <v>1032</v>
-      </c>
-      <c r="L412" s="2"/>
-      <c r="M412" s="2"/>
-      <c r="N412" s="2"/>
+      <c r="H412" s="1"/>
+      <c r="I412" s="1"/>
+      <c r="J412" s="1"/>
+      <c r="K412" s="1"/>
+      <c r="L412" s="1"/>
+      <c r="M412" s="1"/>
+      <c r="N412" s="1"/>
       <c r="O412" s="1"/>
       <c r="P412" s="1"/>
       <c r="Q412" s="1"/>
     </row>
-    <row r="413" spans="1:17" ht="78">
+    <row r="413" spans="1:17">
       <c r="A413" s="1" t="s">
-        <v>1033</v>
+        <v>1025</v>
       </c>
       <c r="B413" s="1" t="s">
-        <v>1034</v>
+        <v>1026</v>
       </c>
       <c r="C413" s="2" t="s">
-        <v>1035</v>
+        <v>1027</v>
       </c>
       <c r="D413" s="1" t="s">
-        <v>1036</v>
+        <v>1028</v>
       </c>
       <c r="E413" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="F413" s="10" t="s">
-        <v>1037</v>
+      <c r="F413" s="2" t="s">
+        <v>1029</v>
       </c>
       <c r="G413" s="2"/>
-      <c r="H413" s="1"/>
-      <c r="I413" s="1"/>
-      <c r="J413" s="1"/>
-      <c r="K413" s="1"/>
-      <c r="L413" s="1"/>
-      <c r="M413" s="1"/>
-      <c r="N413" s="1"/>
+      <c r="H413" s="2"/>
+      <c r="I413" s="1" t="s">
+        <v>1030</v>
+      </c>
+      <c r="J413" s="1" t="s">
+        <v>1031</v>
+      </c>
+      <c r="K413" s="2" t="s">
+        <v>1032</v>
+      </c>
+      <c r="L413" s="2"/>
+      <c r="M413" s="2"/>
+      <c r="N413" s="2"/>
       <c r="O413" s="1"/>
       <c r="P413" s="1"/>
       <c r="Q413" s="1"/>
     </row>
-    <row r="414" spans="1:17">
+    <row r="414" spans="1:17" ht="78">
       <c r="A414" s="1" t="s">
-        <v>1038</v>
+        <v>1033</v>
       </c>
       <c r="B414" s="1" t="s">
-        <v>1039</v>
-      </c>
-      <c r="C414" s="1" t="s">
-        <v>1040</v>
+        <v>1034</v>
+      </c>
+      <c r="C414" s="2" t="s">
+        <v>1035</v>
       </c>
       <c r="D414" s="1" t="s">
-        <v>1041</v>
-      </c>
-      <c r="E414" s="1"/>
-      <c r="F414" s="2" t="s">
-        <v>1042</v>
-      </c>
-      <c r="G414" s="1"/>
+        <v>1036</v>
+      </c>
+      <c r="E414" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F414" s="10" t="s">
+        <v>1037</v>
+      </c>
+      <c r="G414" s="2"/>
       <c r="H414" s="1"/>
       <c r="I414" s="1"/>
       <c r="J414" s="1"/>
@@ -18291,30 +18291,26 @@
       <c r="P414" s="1"/>
       <c r="Q414" s="1"/>
     </row>
-    <row r="415" spans="1:17" ht="78">
+    <row r="415" spans="1:17">
       <c r="A415" s="1" t="s">
-        <v>1043</v>
+        <v>1038</v>
       </c>
       <c r="B415" s="1" t="s">
-        <v>1044</v>
-      </c>
-      <c r="C415" s="2" t="s">
-        <v>1045</v>
-      </c>
-      <c r="D415" s="2" t="s">
-        <v>1046</v>
-      </c>
-      <c r="E415" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F415" s="10" t="s">
-        <v>1037</v>
-      </c>
-      <c r="G415" s="2"/>
+        <v>1039</v>
+      </c>
+      <c r="C415" s="1" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D415" s="1" t="s">
+        <v>1041</v>
+      </c>
+      <c r="E415" s="1"/>
+      <c r="F415" s="2" t="s">
+        <v>1042</v>
+      </c>
+      <c r="G415" s="1"/>
       <c r="H415" s="1"/>
-      <c r="I415" s="2" t="s">
-        <v>1047</v>
-      </c>
+      <c r="I415" s="1"/>
       <c r="J415" s="1"/>
       <c r="K415" s="1"/>
       <c r="L415" s="1"/>
@@ -18324,28 +18320,30 @@
       <c r="P415" s="1"/>
       <c r="Q415" s="1"/>
     </row>
-    <row r="416" spans="1:17" ht="52">
+    <row r="416" spans="1:17" ht="78">
       <c r="A416" s="1" t="s">
-        <v>166</v>
+        <v>1043</v>
       </c>
       <c r="B416" s="1" t="s">
-        <v>1048</v>
+        <v>1044</v>
       </c>
       <c r="C416" s="2" t="s">
-        <v>1049</v>
-      </c>
-      <c r="D416" s="1" t="s">
-        <v>1050</v>
+        <v>1045</v>
+      </c>
+      <c r="D416" s="2" t="s">
+        <v>1046</v>
       </c>
       <c r="E416" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="F416" s="9" t="s">
-        <v>1010</v>
-      </c>
-      <c r="G416" s="1"/>
+      <c r="F416" s="10" t="s">
+        <v>1037</v>
+      </c>
+      <c r="G416" s="2"/>
       <c r="H416" s="1"/>
-      <c r="I416" s="1"/>
+      <c r="I416" s="2" t="s">
+        <v>1047</v>
+      </c>
       <c r="J416" s="1"/>
       <c r="K416" s="1"/>
       <c r="L416" s="1"/>
@@ -18355,22 +18353,24 @@
       <c r="P416" s="1"/>
       <c r="Q416" s="1"/>
     </row>
-    <row r="417" spans="1:17" ht="143">
+    <row r="417" spans="1:17" ht="52">
       <c r="A417" s="1" t="s">
-        <v>139</v>
+        <v>166</v>
       </c>
       <c r="B417" s="1" t="s">
-        <v>1051</v>
-      </c>
-      <c r="C417" s="10" t="s">
-        <v>1052</v>
-      </c>
-      <c r="D417" s="10" t="s">
-        <v>1053</v>
-      </c>
-      <c r="E417" s="1"/>
-      <c r="F417" s="2" t="s">
-        <v>1054</v>
+        <v>1048</v>
+      </c>
+      <c r="C417" s="2" t="s">
+        <v>1049</v>
+      </c>
+      <c r="D417" s="1" t="s">
+        <v>1050</v>
+      </c>
+      <c r="E417" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F417" s="9" t="s">
+        <v>1010</v>
       </c>
       <c r="G417" s="1"/>
       <c r="H417" s="1"/>
@@ -18384,33 +18384,31 @@
       <c r="P417" s="1"/>
       <c r="Q417" s="1"/>
     </row>
-    <row r="418" spans="1:17">
+    <row r="418" spans="1:17" ht="143">
       <c r="A418" s="1" t="s">
-        <v>166</v>
+        <v>139</v>
       </c>
       <c r="B418" s="1" t="s">
-        <v>1055</v>
-      </c>
-      <c r="C418" s="2" t="s">
-        <v>1056</v>
-      </c>
-      <c r="D418" s="1" t="s">
-        <v>1057</v>
-      </c>
-      <c r="E418" s="1" t="s">
-        <v>170</v>
-      </c>
+        <v>1051</v>
+      </c>
+      <c r="C418" s="10" t="s">
+        <v>1052</v>
+      </c>
+      <c r="D418" s="10" t="s">
+        <v>1053</v>
+      </c>
+      <c r="E418" s="1"/>
       <c r="F418" s="2" t="s">
-        <v>1029</v>
-      </c>
-      <c r="G418" s="2"/>
-      <c r="H418" s="2"/>
-      <c r="I418" s="2"/>
-      <c r="J418" s="2"/>
-      <c r="K418" s="2"/>
-      <c r="L418" s="2"/>
-      <c r="M418" s="2"/>
-      <c r="N418" s="2"/>
+        <v>1054</v>
+      </c>
+      <c r="G418" s="1"/>
+      <c r="H418" s="1"/>
+      <c r="I418" s="1"/>
+      <c r="J418" s="1"/>
+      <c r="K418" s="1"/>
+      <c r="L418" s="1"/>
+      <c r="M418" s="1"/>
+      <c r="N418" s="1"/>
       <c r="O418" s="1"/>
       <c r="P418" s="1"/>
       <c r="Q418" s="1"/>
@@ -18420,13 +18418,13 @@
         <v>166</v>
       </c>
       <c r="B419" s="1" t="s">
-        <v>1058</v>
+        <v>1055</v>
       </c>
       <c r="C419" s="2" t="s">
-        <v>1059</v>
+        <v>1056</v>
       </c>
       <c r="D419" s="1" t="s">
-        <v>1060</v>
+        <v>1057</v>
       </c>
       <c r="E419" s="1" t="s">
         <v>170</v>
@@ -18451,13 +18449,13 @@
         <v>166</v>
       </c>
       <c r="B420" s="1" t="s">
-        <v>1061</v>
+        <v>1058</v>
       </c>
       <c r="C420" s="2" t="s">
-        <v>1062</v>
+        <v>1059</v>
       </c>
       <c r="D420" s="1" t="s">
-        <v>1063</v>
+        <v>1060</v>
       </c>
       <c r="E420" s="1" t="s">
         <v>170</v>
@@ -18479,16 +18477,16 @@
     </row>
     <row r="421" spans="1:17">
       <c r="A421" s="1" t="s">
-        <v>1043</v>
+        <v>166</v>
       </c>
       <c r="B421" s="1" t="s">
-        <v>1064</v>
+        <v>1061</v>
       </c>
       <c r="C421" s="2" t="s">
-        <v>1065</v>
+        <v>1062</v>
       </c>
       <c r="D421" s="1" t="s">
-        <v>1066</v>
+        <v>1063</v>
       </c>
       <c r="E421" s="1" t="s">
         <v>170</v>
@@ -18497,41 +18495,41 @@
         <v>1029</v>
       </c>
       <c r="G421" s="2"/>
-      <c r="H421" s="1"/>
-      <c r="I421" s="1" t="s">
-        <v>1067</v>
-      </c>
-      <c r="J421" s="1"/>
-      <c r="K421" s="1"/>
-      <c r="L421" s="1"/>
-      <c r="M421" s="1"/>
-      <c r="N421" s="1"/>
+      <c r="H421" s="2"/>
+      <c r="I421" s="2"/>
+      <c r="J421" s="2"/>
+      <c r="K421" s="2"/>
+      <c r="L421" s="2"/>
+      <c r="M421" s="2"/>
+      <c r="N421" s="2"/>
       <c r="O421" s="1"/>
       <c r="P421" s="1"/>
       <c r="Q421" s="1"/>
     </row>
-    <row r="422" spans="1:17" ht="52">
+    <row r="422" spans="1:17">
       <c r="A422" s="1" t="s">
-        <v>166</v>
+        <v>1043</v>
       </c>
       <c r="B422" s="1" t="s">
-        <v>1068</v>
+        <v>1064</v>
       </c>
       <c r="C422" s="2" t="s">
-        <v>1069</v>
+        <v>1065</v>
       </c>
       <c r="D422" s="1" t="s">
-        <v>1070</v>
+        <v>1066</v>
       </c>
       <c r="E422" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="F422" s="9" t="s">
-        <v>1010</v>
-      </c>
-      <c r="G422" s="1"/>
+      <c r="F422" s="2" t="s">
+        <v>1029</v>
+      </c>
+      <c r="G422" s="2"/>
       <c r="H422" s="1"/>
-      <c r="I422" s="1"/>
+      <c r="I422" s="1" t="s">
+        <v>1067</v>
+      </c>
       <c r="J422" s="1"/>
       <c r="K422" s="1"/>
       <c r="L422" s="1"/>
@@ -18541,24 +18539,26 @@
       <c r="P422" s="1"/>
       <c r="Q422" s="1"/>
     </row>
-    <row r="423" spans="1:17" ht="143">
+    <row r="423" spans="1:17" ht="52">
       <c r="A423" s="1" t="s">
-        <v>139</v>
+        <v>166</v>
       </c>
       <c r="B423" s="1" t="s">
-        <v>1071</v>
-      </c>
-      <c r="C423" s="10" t="s">
-        <v>1072</v>
-      </c>
-      <c r="D423" s="10" t="s">
-        <v>1073</v>
-      </c>
-      <c r="E423" s="1"/>
-      <c r="F423" s="2" t="s">
-        <v>1074</v>
-      </c>
-      <c r="G423" s="2"/>
+        <v>1068</v>
+      </c>
+      <c r="C423" s="2" t="s">
+        <v>1069</v>
+      </c>
+      <c r="D423" s="1" t="s">
+        <v>1070</v>
+      </c>
+      <c r="E423" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F423" s="9" t="s">
+        <v>1010</v>
+      </c>
+      <c r="G423" s="1"/>
       <c r="H423" s="1"/>
       <c r="I423" s="1"/>
       <c r="J423" s="1"/>
@@ -18570,22 +18570,22 @@
       <c r="P423" s="1"/>
       <c r="Q423" s="1"/>
     </row>
-    <row r="424" spans="1:17">
+    <row r="424" spans="1:17" ht="143">
       <c r="A424" s="1" t="s">
         <v>139</v>
       </c>
       <c r="B424" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="C424" s="2" t="s">
-        <v>1076</v>
-      </c>
-      <c r="D424" s="1" t="s">
-        <v>1077</v>
+        <v>1071</v>
+      </c>
+      <c r="C424" s="10" t="s">
+        <v>1072</v>
+      </c>
+      <c r="D424" s="10" t="s">
+        <v>1073</v>
       </c>
       <c r="E424" s="1"/>
       <c r="F424" s="2" t="s">
-        <v>1078</v>
+        <v>1074</v>
       </c>
       <c r="G424" s="2"/>
       <c r="H424" s="1"/>
@@ -18599,30 +18599,26 @@
       <c r="P424" s="1"/>
       <c r="Q424" s="1"/>
     </row>
-    <row r="425" spans="1:17" ht="52">
+    <row r="425" spans="1:17">
       <c r="A425" s="1" t="s">
-        <v>1043</v>
+        <v>139</v>
       </c>
       <c r="B425" s="1" t="s">
-        <v>1079</v>
-      </c>
-      <c r="C425" s="10" t="s">
-        <v>1080</v>
-      </c>
-      <c r="D425" s="9" t="s">
-        <v>1081</v>
-      </c>
-      <c r="E425" s="1" t="s">
-        <v>170</v>
-      </c>
+        <v>1075</v>
+      </c>
+      <c r="C425" s="2" t="s">
+        <v>1076</v>
+      </c>
+      <c r="D425" s="1" t="s">
+        <v>1077</v>
+      </c>
+      <c r="E425" s="1"/>
       <c r="F425" s="2" t="s">
-        <v>1029</v>
+        <v>1078</v>
       </c>
       <c r="G425" s="2"/>
       <c r="H425" s="1"/>
-      <c r="I425" s="1" t="s">
-        <v>1082</v>
-      </c>
+      <c r="I425" s="1"/>
       <c r="J425" s="1"/>
       <c r="K425" s="1"/>
       <c r="L425" s="1"/>
@@ -18632,18 +18628,18 @@
       <c r="P425" s="1"/>
       <c r="Q425" s="1"/>
     </row>
-    <row r="426" spans="1:17">
+    <row r="426" spans="1:17" ht="52">
       <c r="A426" s="1" t="s">
         <v>1043</v>
       </c>
       <c r="B426" s="1" t="s">
-        <v>1083</v>
-      </c>
-      <c r="C426" s="2" t="s">
-        <v>1084</v>
-      </c>
-      <c r="D426" s="1" t="s">
-        <v>1085</v>
+        <v>1079</v>
+      </c>
+      <c r="C426" s="10" t="s">
+        <v>1080</v>
+      </c>
+      <c r="D426" s="9" t="s">
+        <v>1081</v>
       </c>
       <c r="E426" s="1" t="s">
         <v>170</v>
@@ -18665,26 +18661,30 @@
       <c r="P426" s="1"/>
       <c r="Q426" s="1"/>
     </row>
-    <row r="427" spans="1:17" ht="52">
+    <row r="427" spans="1:17">
       <c r="A427" s="1" t="s">
-        <v>139</v>
+        <v>1043</v>
       </c>
       <c r="B427" s="1" t="s">
-        <v>1086</v>
-      </c>
-      <c r="C427" s="7" t="s">
-        <v>1087</v>
-      </c>
-      <c r="D427" s="7" t="s">
-        <v>1088</v>
-      </c>
-      <c r="E427" s="1"/>
-      <c r="F427" s="9" t="s">
-        <v>1010</v>
-      </c>
-      <c r="G427" s="1"/>
+        <v>1083</v>
+      </c>
+      <c r="C427" s="2" t="s">
+        <v>1084</v>
+      </c>
+      <c r="D427" s="1" t="s">
+        <v>1085</v>
+      </c>
+      <c r="E427" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F427" s="2" t="s">
+        <v>1029</v>
+      </c>
+      <c r="G427" s="2"/>
       <c r="H427" s="1"/>
-      <c r="I427" s="1"/>
+      <c r="I427" s="1" t="s">
+        <v>1082</v>
+      </c>
       <c r="J427" s="1"/>
       <c r="K427" s="1"/>
       <c r="L427" s="1"/>
@@ -18699,23 +18699,23 @@
         <v>139</v>
       </c>
       <c r="B428" s="1" t="s">
-        <v>1089</v>
-      </c>
-      <c r="C428" s="2" t="s">
-        <v>1090</v>
-      </c>
-      <c r="D428" s="2" t="s">
-        <v>1091</v>
-      </c>
-      <c r="E428" s="2"/>
+        <v>1086</v>
+      </c>
+      <c r="C428" s="7" t="s">
+        <v>1087</v>
+      </c>
+      <c r="D428" s="7" t="s">
+        <v>1088</v>
+      </c>
+      <c r="E428" s="1"/>
       <c r="F428" s="9" t="s">
         <v>1010</v>
       </c>
-      <c r="G428" s="2"/>
-      <c r="H428" s="2"/>
-      <c r="I428" s="2"/>
-      <c r="J428" s="2"/>
-      <c r="K428" s="2"/>
+      <c r="G428" s="1"/>
+      <c r="H428" s="1"/>
+      <c r="I428" s="1"/>
+      <c r="J428" s="1"/>
+      <c r="K428" s="1"/>
       <c r="L428" s="1"/>
       <c r="M428" s="1"/>
       <c r="N428" s="1"/>
@@ -18723,18 +18723,18 @@
       <c r="P428" s="1"/>
       <c r="Q428" s="1"/>
     </row>
-    <row r="429" spans="1:17" ht="221">
+    <row r="429" spans="1:17" ht="52">
       <c r="A429" s="1" t="s">
         <v>139</v>
       </c>
       <c r="B429" s="1" t="s">
-        <v>1092</v>
-      </c>
-      <c r="C429" s="10" t="s">
-        <v>1093</v>
-      </c>
-      <c r="D429" s="10" t="s">
-        <v>1094</v>
+        <v>1089</v>
+      </c>
+      <c r="C429" s="2" t="s">
+        <v>1090</v>
+      </c>
+      <c r="D429" s="2" t="s">
+        <v>1091</v>
       </c>
       <c r="E429" s="2"/>
       <c r="F429" s="9" t="s">
@@ -18745,58 +18745,56 @@
       <c r="I429" s="2"/>
       <c r="J429" s="2"/>
       <c r="K429" s="2"/>
-      <c r="L429" s="2"/>
-      <c r="M429" s="2"/>
-      <c r="N429" s="2"/>
-      <c r="O429" s="2"/>
-      <c r="P429" s="2"/>
-      <c r="Q429" s="2"/>
-    </row>
-    <row r="430" spans="1:17" ht="52">
+      <c r="L429" s="1"/>
+      <c r="M429" s="1"/>
+      <c r="N429" s="1"/>
+      <c r="O429" s="1"/>
+      <c r="P429" s="1"/>
+      <c r="Q429" s="1"/>
+    </row>
+    <row r="430" spans="1:17" ht="221">
       <c r="A430" s="1" t="s">
         <v>139</v>
       </c>
       <c r="B430" s="1" t="s">
-        <v>1095</v>
-      </c>
-      <c r="C430" s="4" t="s">
-        <v>642</v>
-      </c>
-      <c r="D430" s="1" t="s">
-        <v>642</v>
-      </c>
-      <c r="E430" s="1"/>
+        <v>1092</v>
+      </c>
+      <c r="C430" s="10" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D430" s="10" t="s">
+        <v>1094</v>
+      </c>
+      <c r="E430" s="2"/>
       <c r="F430" s="9" t="s">
         <v>1010</v>
       </c>
-      <c r="G430" s="1"/>
-      <c r="H430" s="1"/>
-      <c r="I430" s="1"/>
-      <c r="J430" s="1"/>
-      <c r="K430" s="1"/>
-      <c r="L430" s="1"/>
-      <c r="M430" s="1"/>
-      <c r="N430" s="1"/>
-      <c r="O430" s="1"/>
-      <c r="P430" s="1"/>
-      <c r="Q430" s="1"/>
+      <c r="G430" s="2"/>
+      <c r="H430" s="2"/>
+      <c r="I430" s="2"/>
+      <c r="J430" s="2"/>
+      <c r="K430" s="2"/>
+      <c r="L430" s="2"/>
+      <c r="M430" s="2"/>
+      <c r="N430" s="2"/>
+      <c r="O430" s="2"/>
+      <c r="P430" s="2"/>
+      <c r="Q430" s="2"/>
     </row>
     <row r="431" spans="1:17" ht="52">
       <c r="A431" s="1" t="s">
-        <v>166</v>
+        <v>139</v>
       </c>
       <c r="B431" s="1" t="s">
-        <v>1096</v>
-      </c>
-      <c r="C431" s="2" t="s">
-        <v>1097</v>
+        <v>1095</v>
+      </c>
+      <c r="C431" s="4" t="s">
+        <v>642</v>
       </c>
       <c r="D431" s="1" t="s">
-        <v>1098</v>
-      </c>
-      <c r="E431" s="1" t="s">
-        <v>170</v>
-      </c>
+        <v>642</v>
+      </c>
+      <c r="E431" s="1"/>
       <c r="F431" s="9" t="s">
         <v>1010</v>
       </c>
@@ -18812,24 +18810,26 @@
       <c r="P431" s="1"/>
       <c r="Q431" s="1"/>
     </row>
-    <row r="432" spans="1:17" ht="39">
+    <row r="432" spans="1:17" ht="52">
       <c r="A432" s="1" t="s">
-        <v>139</v>
+        <v>166</v>
       </c>
       <c r="B432" s="1" t="s">
-        <v>1099</v>
+        <v>1096</v>
       </c>
       <c r="C432" s="2" t="s">
-        <v>1100</v>
-      </c>
-      <c r="D432" s="10" t="s">
-        <v>1101</v>
-      </c>
-      <c r="E432" s="1"/>
-      <c r="F432" s="2" t="s">
-        <v>1102</v>
-      </c>
-      <c r="G432" s="2"/>
+        <v>1097</v>
+      </c>
+      <c r="D432" s="1" t="s">
+        <v>1098</v>
+      </c>
+      <c r="E432" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F432" s="9" t="s">
+        <v>1010</v>
+      </c>
+      <c r="G432" s="1"/>
       <c r="H432" s="1"/>
       <c r="I432" s="1"/>
       <c r="J432" s="1"/>
@@ -18841,18 +18841,18 @@
       <c r="P432" s="1"/>
       <c r="Q432" s="1"/>
     </row>
-    <row r="433" spans="1:17">
+    <row r="433" spans="1:17" ht="39">
       <c r="A433" s="1" t="s">
         <v>139</v>
       </c>
       <c r="B433" s="1" t="s">
-        <v>1103</v>
+        <v>1099</v>
       </c>
       <c r="C433" s="2" t="s">
-        <v>1104</v>
-      </c>
-      <c r="D433" s="2" t="s">
-        <v>1105</v>
+        <v>1100</v>
+      </c>
+      <c r="D433" s="10" t="s">
+        <v>1101</v>
       </c>
       <c r="E433" s="1"/>
       <c r="F433" s="2" t="s">
@@ -18870,22 +18870,22 @@
       <c r="P433" s="1"/>
       <c r="Q433" s="1"/>
     </row>
-    <row r="434" spans="1:17" ht="52">
+    <row r="434" spans="1:17">
       <c r="A434" s="1" t="s">
         <v>139</v>
       </c>
       <c r="B434" s="1" t="s">
-        <v>1106</v>
-      </c>
-      <c r="C434" s="1" t="s">
-        <v>642</v>
-      </c>
-      <c r="D434" s="1" t="s">
-        <v>642</v>
+        <v>1103</v>
+      </c>
+      <c r="C434" s="2" t="s">
+        <v>1104</v>
+      </c>
+      <c r="D434" s="2" t="s">
+        <v>1105</v>
       </c>
       <c r="E434" s="1"/>
-      <c r="F434" s="9" t="s">
-        <v>1010</v>
+      <c r="F434" s="2" t="s">
+        <v>1102</v>
       </c>
       <c r="G434" s="2"/>
       <c r="H434" s="1"/>
@@ -18901,24 +18901,22 @@
     </row>
     <row r="435" spans="1:17" ht="52">
       <c r="A435" s="1" t="s">
-        <v>166</v>
+        <v>139</v>
       </c>
       <c r="B435" s="1" t="s">
-        <v>1107</v>
-      </c>
-      <c r="C435" s="2" t="s">
-        <v>1108</v>
+        <v>1106</v>
+      </c>
+      <c r="C435" s="1" t="s">
+        <v>642</v>
       </c>
       <c r="D435" s="1" t="s">
-        <v>1109</v>
-      </c>
-      <c r="E435" s="1" t="s">
-        <v>170</v>
-      </c>
+        <v>642</v>
+      </c>
+      <c r="E435" s="1"/>
       <c r="F435" s="9" t="s">
         <v>1010</v>
       </c>
-      <c r="G435" s="1"/>
+      <c r="G435" s="2"/>
       <c r="H435" s="1"/>
       <c r="I435" s="1"/>
       <c r="J435" s="1"/>
@@ -18930,25 +18928,27 @@
       <c r="P435" s="1"/>
       <c r="Q435" s="1"/>
     </row>
-    <row r="436" spans="1:17" ht="78">
+    <row r="436" spans="1:17" ht="52">
       <c r="A436" s="1" t="s">
-        <v>139</v>
+        <v>166</v>
       </c>
       <c r="B436" s="1" t="s">
-        <v>1110</v>
-      </c>
-      <c r="C436" s="10" t="s">
-        <v>1111</v>
-      </c>
-      <c r="D436" s="10" t="s">
-        <v>1112</v>
-      </c>
-      <c r="E436" s="1"/>
-      <c r="F436" s="2" t="s">
-        <v>1113</v>
-      </c>
-      <c r="G436" s="2"/>
-      <c r="H436" s="2"/>
+        <v>1107</v>
+      </c>
+      <c r="C436" s="2" t="s">
+        <v>1108</v>
+      </c>
+      <c r="D436" s="1" t="s">
+        <v>1109</v>
+      </c>
+      <c r="E436" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F436" s="9" t="s">
+        <v>1010</v>
+      </c>
+      <c r="G436" s="1"/>
+      <c r="H436" s="1"/>
       <c r="I436" s="1"/>
       <c r="J436" s="1"/>
       <c r="K436" s="1"/>
@@ -18959,19 +18959,25 @@
       <c r="P436" s="1"/>
       <c r="Q436" s="1"/>
     </row>
-    <row r="437" spans="1:17">
+    <row r="437" spans="1:17" ht="78">
       <c r="A437" s="1" t="s">
-        <v>55</v>
+        <v>139</v>
       </c>
       <c r="B437" s="1" t="s">
-        <v>1004</v>
-      </c>
-      <c r="C437" s="2"/>
-      <c r="D437" s="1"/>
+        <v>1110</v>
+      </c>
+      <c r="C437" s="10" t="s">
+        <v>1111</v>
+      </c>
+      <c r="D437" s="10" t="s">
+        <v>1112</v>
+      </c>
       <c r="E437" s="1"/>
-      <c r="F437" s="1"/>
-      <c r="G437" s="1"/>
-      <c r="H437" s="1"/>
+      <c r="F437" s="2" t="s">
+        <v>1113</v>
+      </c>
+      <c r="G437" s="2"/>
+      <c r="H437" s="2"/>
       <c r="I437" s="1"/>
       <c r="J437" s="1"/>
       <c r="K437" s="1"/>
@@ -18984,24 +18990,16 @@
     </row>
     <row r="438" spans="1:17">
       <c r="A438" s="1" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="B438" s="1" t="s">
-        <v>1114</v>
-      </c>
-      <c r="C438" s="2" t="s">
-        <v>1115</v>
-      </c>
-      <c r="D438" s="1" t="s">
-        <v>1116</v>
-      </c>
+        <v>1004</v>
+      </c>
+      <c r="C438" s="2"/>
+      <c r="D438" s="1"/>
       <c r="E438" s="1"/>
-      <c r="F438" s="1" t="s">
-        <v>838</v>
-      </c>
-      <c r="G438" s="1" t="s">
-        <v>147</v>
-      </c>
+      <c r="F438" s="1"/>
+      <c r="G438" s="1"/>
       <c r="H438" s="1"/>
       <c r="I438" s="1"/>
       <c r="J438" s="1"/>
@@ -19015,22 +19013,24 @@
     </row>
     <row r="439" spans="1:17">
       <c r="A439" s="1" t="s">
-        <v>166</v>
+        <v>21</v>
       </c>
       <c r="B439" s="1" t="s">
-        <v>1117</v>
+        <v>1114</v>
       </c>
       <c r="C439" s="2" t="s">
-        <v>1118</v>
+        <v>1115</v>
       </c>
       <c r="D439" s="1" t="s">
-        <v>1119</v>
-      </c>
-      <c r="E439" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F439" s="1"/>
-      <c r="G439" s="1"/>
+        <v>1116</v>
+      </c>
+      <c r="E439" s="1"/>
+      <c r="F439" s="1" t="s">
+        <v>838</v>
+      </c>
+      <c r="G439" s="1" t="s">
+        <v>147</v>
+      </c>
       <c r="H439" s="1"/>
       <c r="I439" s="1"/>
       <c r="J439" s="1"/>
@@ -19044,22 +19044,22 @@
     </row>
     <row r="440" spans="1:17">
       <c r="A440" s="1" t="s">
-        <v>139</v>
+        <v>166</v>
       </c>
       <c r="B440" s="1" t="s">
-        <v>1120</v>
+        <v>1117</v>
       </c>
       <c r="C440" s="2" t="s">
-        <v>1121</v>
-      </c>
-      <c r="D440" s="2" t="s">
-        <v>1122</v>
-      </c>
-      <c r="E440" s="1"/>
-      <c r="F440" s="2" t="s">
-        <v>1123</v>
-      </c>
-      <c r="G440" s="2"/>
+        <v>1118</v>
+      </c>
+      <c r="D440" s="1" t="s">
+        <v>1119</v>
+      </c>
+      <c r="E440" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F440" s="1"/>
+      <c r="G440" s="1"/>
       <c r="H440" s="1"/>
       <c r="I440" s="1"/>
       <c r="J440" s="1"/>
@@ -19076,20 +19076,20 @@
         <v>139</v>
       </c>
       <c r="B441" s="1" t="s">
-        <v>1124</v>
+        <v>1120</v>
       </c>
       <c r="C441" s="2" t="s">
-        <v>1125</v>
+        <v>1121</v>
       </c>
       <c r="D441" s="2" t="s">
-        <v>1126</v>
+        <v>1122</v>
       </c>
       <c r="E441" s="1"/>
       <c r="F441" s="2" t="s">
-        <v>1127</v>
+        <v>1123</v>
       </c>
       <c r="G441" s="2"/>
-      <c r="H441" s="2"/>
+      <c r="H441" s="1"/>
       <c r="I441" s="1"/>
       <c r="J441" s="1"/>
       <c r="K441" s="1"/>
@@ -19102,16 +19102,16 @@
     </row>
     <row r="442" spans="1:17">
       <c r="A442" s="1" t="s">
-        <v>166</v>
+        <v>139</v>
       </c>
       <c r="B442" s="1" t="s">
-        <v>1128</v>
+        <v>1124</v>
       </c>
       <c r="C442" s="2" t="s">
-        <v>1129</v>
-      </c>
-      <c r="D442" s="1" t="s">
-        <v>1130</v>
+        <v>1125</v>
+      </c>
+      <c r="D442" s="2" t="s">
+        <v>1126</v>
       </c>
       <c r="E442" s="1"/>
       <c r="F442" s="2" t="s">
@@ -19134,13 +19134,13 @@
         <v>166</v>
       </c>
       <c r="B443" s="1" t="s">
-        <v>1131</v>
+        <v>1128</v>
       </c>
       <c r="C443" s="2" t="s">
-        <v>1132</v>
+        <v>1129</v>
       </c>
       <c r="D443" s="1" t="s">
-        <v>1133</v>
+        <v>1130</v>
       </c>
       <c r="E443" s="1"/>
       <c r="F443" s="2" t="s">
@@ -19158,18 +19158,18 @@
       <c r="P443" s="1"/>
       <c r="Q443" s="1"/>
     </row>
-    <row r="444" spans="1:17" ht="26">
+    <row r="444" spans="1:17">
       <c r="A444" s="1" t="s">
         <v>166</v>
       </c>
       <c r="B444" s="1" t="s">
-        <v>1134</v>
+        <v>1131</v>
       </c>
       <c r="C444" s="2" t="s">
-        <v>1135</v>
-      </c>
-      <c r="D444" s="9" t="s">
-        <v>1136</v>
+        <v>1132</v>
+      </c>
+      <c r="D444" s="1" t="s">
+        <v>1133</v>
       </c>
       <c r="E444" s="1"/>
       <c r="F444" s="2" t="s">
@@ -19187,18 +19187,18 @@
       <c r="P444" s="1"/>
       <c r="Q444" s="1"/>
     </row>
-    <row r="445" spans="1:17">
+    <row r="445" spans="1:17" ht="26">
       <c r="A445" s="1" t="s">
         <v>166</v>
       </c>
       <c r="B445" s="1" t="s">
-        <v>1137</v>
+        <v>1134</v>
       </c>
       <c r="C445" s="2" t="s">
-        <v>1138</v>
-      </c>
-      <c r="D445" s="1" t="s">
-        <v>1139</v>
+        <v>1135</v>
+      </c>
+      <c r="D445" s="9" t="s">
+        <v>1136</v>
       </c>
       <c r="E445" s="1"/>
       <c r="F445" s="2" t="s">
@@ -19221,13 +19221,13 @@
         <v>166</v>
       </c>
       <c r="B446" s="1" t="s">
-        <v>1140</v>
+        <v>1137</v>
       </c>
       <c r="C446" s="2" t="s">
-        <v>1141</v>
+        <v>1138</v>
       </c>
       <c r="D446" s="1" t="s">
-        <v>1142</v>
+        <v>1139</v>
       </c>
       <c r="E446" s="1"/>
       <c r="F446" s="2" t="s">
@@ -19250,13 +19250,13 @@
         <v>166</v>
       </c>
       <c r="B447" s="1" t="s">
-        <v>1143</v>
+        <v>1140</v>
       </c>
       <c r="C447" s="2" t="s">
-        <v>1144</v>
+        <v>1141</v>
       </c>
       <c r="D447" s="1" t="s">
-        <v>1145</v>
+        <v>1142</v>
       </c>
       <c r="E447" s="1"/>
       <c r="F447" s="2" t="s">
@@ -19274,18 +19274,18 @@
       <c r="P447" s="1"/>
       <c r="Q447" s="1"/>
     </row>
-    <row r="448" spans="1:17" ht="26">
+    <row r="448" spans="1:17">
       <c r="A448" s="1" t="s">
         <v>166</v>
       </c>
       <c r="B448" s="1" t="s">
-        <v>1146</v>
+        <v>1143</v>
       </c>
       <c r="C448" s="2" t="s">
-        <v>1147</v>
-      </c>
-      <c r="D448" s="9" t="s">
-        <v>1148</v>
+        <v>1144</v>
+      </c>
+      <c r="D448" s="1" t="s">
+        <v>1145</v>
       </c>
       <c r="E448" s="1"/>
       <c r="F448" s="2" t="s">
@@ -19308,13 +19308,13 @@
         <v>166</v>
       </c>
       <c r="B449" s="1" t="s">
-        <v>1149</v>
+        <v>1146</v>
       </c>
       <c r="C449" s="2" t="s">
-        <v>1150</v>
+        <v>1147</v>
       </c>
       <c r="D449" s="9" t="s">
-        <v>1151</v>
+        <v>1148</v>
       </c>
       <c r="E449" s="1"/>
       <c r="F449" s="2" t="s">
@@ -19337,17 +19337,17 @@
         <v>166</v>
       </c>
       <c r="B450" s="1" t="s">
-        <v>1152</v>
+        <v>1149</v>
       </c>
       <c r="C450" s="2" t="s">
-        <v>1153</v>
+        <v>1150</v>
       </c>
       <c r="D450" s="9" t="s">
-        <v>1154</v>
+        <v>1151</v>
       </c>
       <c r="E450" s="1"/>
       <c r="F450" s="2" t="s">
-        <v>1155</v>
+        <v>1127</v>
       </c>
       <c r="G450" s="2"/>
       <c r="H450" s="2"/>
@@ -19366,22 +19366,22 @@
         <v>166</v>
       </c>
       <c r="B451" s="1" t="s">
-        <v>1156</v>
+        <v>1152</v>
       </c>
       <c r="C451" s="2" t="s">
-        <v>1157</v>
+        <v>1153</v>
       </c>
       <c r="D451" s="9" t="s">
-        <v>1158</v>
+        <v>1154</v>
       </c>
       <c r="E451" s="1"/>
       <c r="F451" s="2" t="s">
-        <v>1159</v>
+        <v>1155</v>
       </c>
       <c r="G451" s="2"/>
       <c r="H451" s="2"/>
-      <c r="I451" s="2"/>
-      <c r="J451" s="2"/>
+      <c r="I451" s="1"/>
+      <c r="J451" s="1"/>
       <c r="K451" s="1"/>
       <c r="L451" s="1"/>
       <c r="M451" s="1"/>
@@ -19390,27 +19390,27 @@
       <c r="P451" s="1"/>
       <c r="Q451" s="1"/>
     </row>
-    <row r="452" spans="1:17">
+    <row r="452" spans="1:17" ht="26">
       <c r="A452" s="1" t="s">
         <v>166</v>
       </c>
       <c r="B452" s="1" t="s">
-        <v>1160</v>
+        <v>1156</v>
       </c>
       <c r="C452" s="2" t="s">
-        <v>1161</v>
-      </c>
-      <c r="D452" s="1" t="s">
-        <v>1162</v>
+        <v>1157</v>
+      </c>
+      <c r="D452" s="9" t="s">
+        <v>1158</v>
       </c>
       <c r="E452" s="1"/>
       <c r="F452" s="2" t="s">
-        <v>1127</v>
+        <v>1159</v>
       </c>
       <c r="G452" s="2"/>
       <c r="H452" s="2"/>
-      <c r="I452" s="1"/>
-      <c r="J452" s="1"/>
+      <c r="I452" s="2"/>
+      <c r="J452" s="2"/>
       <c r="K452" s="1"/>
       <c r="L452" s="1"/>
       <c r="M452" s="1"/>
@@ -19421,70 +19421,76 @@
     </row>
     <row r="453" spans="1:17">
       <c r="A453" s="1" t="s">
-        <v>62</v>
+        <v>166</v>
       </c>
       <c r="B453" s="1" t="s">
-        <v>1163</v>
-      </c>
-      <c r="C453" s="1"/>
-      <c r="D453" s="1"/>
+        <v>1160</v>
+      </c>
+      <c r="C453" s="2" t="s">
+        <v>1161</v>
+      </c>
+      <c r="D453" s="1" t="s">
+        <v>1162</v>
+      </c>
       <c r="E453" s="1"/>
-      <c r="F453" s="1"/>
-      <c r="G453" s="1"/>
-      <c r="H453" s="1"/>
+      <c r="F453" s="2" t="s">
+        <v>1127</v>
+      </c>
+      <c r="G453" s="2"/>
+      <c r="H453" s="2"/>
       <c r="I453" s="1"/>
       <c r="J453" s="1"/>
       <c r="K453" s="1"/>
-      <c r="L453" s="2" t="s">
-        <v>1164</v>
-      </c>
-      <c r="M453" s="2"/>
-      <c r="N453" s="2"/>
-      <c r="O453" s="2"/>
-      <c r="P453" s="2"/>
-      <c r="Q453" s="2"/>
-    </row>
-    <row r="454" spans="1:17" ht="91">
+      <c r="L453" s="1"/>
+      <c r="M453" s="1"/>
+      <c r="N453" s="1"/>
+      <c r="O453" s="1"/>
+      <c r="P453" s="1"/>
+      <c r="Q453" s="1"/>
+    </row>
+    <row r="454" spans="1:17">
       <c r="A454" s="1" t="s">
-        <v>139</v>
+        <v>62</v>
       </c>
       <c r="B454" s="1" t="s">
-        <v>1165</v>
-      </c>
-      <c r="C454" s="10" t="s">
-        <v>1166</v>
-      </c>
-      <c r="D454" s="10" t="s">
-        <v>1167</v>
-      </c>
+        <v>1163</v>
+      </c>
+      <c r="C454" s="1"/>
+      <c r="D454" s="1"/>
       <c r="E454" s="1"/>
-      <c r="F454" s="2" t="s">
-        <v>1168</v>
-      </c>
-      <c r="G454" s="2"/>
+      <c r="F454" s="1"/>
+      <c r="G454" s="1"/>
       <c r="H454" s="1"/>
       <c r="I454" s="1"/>
       <c r="J454" s="1"/>
       <c r="K454" s="1"/>
-      <c r="L454" s="1"/>
-      <c r="M454" s="1"/>
-      <c r="N454" s="1"/>
-      <c r="O454" s="1"/>
-      <c r="P454" s="1"/>
-      <c r="Q454" s="1"/>
-    </row>
-    <row r="455" spans="1:17">
+      <c r="L454" s="2" t="s">
+        <v>1164</v>
+      </c>
+      <c r="M454" s="2"/>
+      <c r="N454" s="2"/>
+      <c r="O454" s="2"/>
+      <c r="P454" s="2"/>
+      <c r="Q454" s="2"/>
+    </row>
+    <row r="455" spans="1:17" ht="91">
       <c r="A455" s="1" t="s">
-        <v>55</v>
+        <v>139</v>
       </c>
       <c r="B455" s="1" t="s">
-        <v>1114</v>
-      </c>
-      <c r="C455" s="1"/>
-      <c r="D455" s="1"/>
+        <v>1165</v>
+      </c>
+      <c r="C455" s="10" t="s">
+        <v>1166</v>
+      </c>
+      <c r="D455" s="10" t="s">
+        <v>1167</v>
+      </c>
       <c r="E455" s="1"/>
-      <c r="F455" s="1"/>
-      <c r="G455" s="1"/>
+      <c r="F455" s="2" t="s">
+        <v>1168</v>
+      </c>
+      <c r="G455" s="2"/>
       <c r="H455" s="1"/>
       <c r="I455" s="1"/>
       <c r="J455" s="1"/>
@@ -19498,24 +19504,16 @@
     </row>
     <row r="456" spans="1:17">
       <c r="A456" s="1" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="B456" s="1" t="s">
-        <v>1169</v>
-      </c>
-      <c r="C456" s="1" t="s">
-        <v>1170</v>
-      </c>
-      <c r="D456" s="1" t="s">
-        <v>1171</v>
-      </c>
+        <v>1114</v>
+      </c>
+      <c r="C456" s="1"/>
+      <c r="D456" s="1"/>
       <c r="E456" s="1"/>
-      <c r="F456" s="7" t="s">
-        <v>460</v>
-      </c>
-      <c r="G456" s="1" t="s">
-        <v>147</v>
-      </c>
+      <c r="F456" s="1"/>
+      <c r="G456" s="1"/>
       <c r="H456" s="1"/>
       <c r="I456" s="1"/>
       <c r="J456" s="1"/>
@@ -19529,20 +19527,24 @@
     </row>
     <row r="457" spans="1:17">
       <c r="A457" s="1" t="s">
-        <v>139</v>
+        <v>21</v>
       </c>
       <c r="B457" s="1" t="s">
-        <v>1172</v>
+        <v>1169</v>
       </c>
       <c r="C457" s="1" t="s">
-        <v>642</v>
+        <v>1170</v>
       </c>
       <c r="D457" s="1" t="s">
-        <v>642</v>
+        <v>1171</v>
       </c>
       <c r="E457" s="1"/>
-      <c r="F457" s="1"/>
-      <c r="G457" s="1"/>
+      <c r="F457" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="G457" s="1" t="s">
+        <v>147</v>
+      </c>
       <c r="H457" s="1"/>
       <c r="I457" s="1"/>
       <c r="J457" s="1"/>
@@ -19556,20 +19558,18 @@
     </row>
     <row r="458" spans="1:17">
       <c r="A458" s="1" t="s">
-        <v>166</v>
+        <v>139</v>
       </c>
       <c r="B458" s="1" t="s">
-        <v>1173</v>
-      </c>
-      <c r="C458" s="2" t="s">
-        <v>1174</v>
+        <v>1172</v>
+      </c>
+      <c r="C458" s="1" t="s">
+        <v>642</v>
       </c>
       <c r="D458" s="1" t="s">
-        <v>1175</v>
-      </c>
-      <c r="E458" s="1" t="s">
-        <v>170</v>
-      </c>
+        <v>642</v>
+      </c>
+      <c r="E458" s="1"/>
       <c r="F458" s="1"/>
       <c r="G458" s="1"/>
       <c r="H458" s="1"/>
@@ -19585,21 +19585,21 @@
     </row>
     <row r="459" spans="1:17">
       <c r="A459" s="1" t="s">
-        <v>139</v>
+        <v>166</v>
       </c>
       <c r="B459" s="1" t="s">
-        <v>1176</v>
-      </c>
-      <c r="C459" s="1" t="s">
-        <v>642</v>
+        <v>1173</v>
+      </c>
+      <c r="C459" s="2" t="s">
+        <v>1174</v>
       </c>
       <c r="D459" s="1" t="s">
-        <v>642</v>
-      </c>
-      <c r="E459" s="1"/>
-      <c r="F459" s="4" t="s">
-        <v>1177</v>
-      </c>
+        <v>1175</v>
+      </c>
+      <c r="E459" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F459" s="1"/>
       <c r="G459" s="1"/>
       <c r="H459" s="1"/>
       <c r="I459" s="1"/>
@@ -19614,24 +19614,22 @@
     </row>
     <row r="460" spans="1:17">
       <c r="A460" s="1" t="s">
-        <v>166</v>
+        <v>139</v>
       </c>
       <c r="B460" s="1" t="s">
-        <v>1178</v>
-      </c>
-      <c r="C460" s="2" t="s">
-        <v>1179</v>
+        <v>1176</v>
+      </c>
+      <c r="C460" s="1" t="s">
+        <v>642</v>
       </c>
       <c r="D460" s="1" t="s">
-        <v>1180</v>
-      </c>
-      <c r="E460" s="1" t="s">
-        <v>170</v>
-      </c>
+        <v>642</v>
+      </c>
+      <c r="E460" s="1"/>
       <c r="F460" s="4" t="s">
         <v>1177</v>
       </c>
-      <c r="G460" s="2"/>
+      <c r="G460" s="1"/>
       <c r="H460" s="1"/>
       <c r="I460" s="1"/>
       <c r="J460" s="1"/>
@@ -19645,20 +19643,22 @@
     </row>
     <row r="461" spans="1:17">
       <c r="A461" s="1" t="s">
-        <v>139</v>
+        <v>166</v>
       </c>
       <c r="B461" s="1" t="s">
-        <v>1181</v>
-      </c>
-      <c r="C461" s="1" t="s">
-        <v>1182</v>
+        <v>1178</v>
+      </c>
+      <c r="C461" s="2" t="s">
+        <v>1179</v>
       </c>
       <c r="D461" s="1" t="s">
-        <v>1182</v>
-      </c>
-      <c r="E461" s="1"/>
-      <c r="F461" s="2" t="s">
-        <v>1183</v>
+        <v>1180</v>
+      </c>
+      <c r="E461" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F461" s="4" t="s">
+        <v>1177</v>
       </c>
       <c r="G461" s="2"/>
       <c r="H461" s="1"/>
@@ -19674,20 +19674,18 @@
     </row>
     <row r="462" spans="1:17">
       <c r="A462" s="1" t="s">
-        <v>1184</v>
+        <v>139</v>
       </c>
       <c r="B462" s="1" t="s">
-        <v>1185</v>
-      </c>
-      <c r="C462" s="2" t="s">
-        <v>1186</v>
+        <v>1181</v>
+      </c>
+      <c r="C462" s="1" t="s">
+        <v>1182</v>
       </c>
       <c r="D462" s="1" t="s">
-        <v>1187</v>
-      </c>
-      <c r="E462" s="1" t="s">
-        <v>170</v>
-      </c>
+        <v>1182</v>
+      </c>
+      <c r="E462" s="1"/>
       <c r="F462" s="2" t="s">
         <v>1183</v>
       </c>
@@ -19705,16 +19703,24 @@
     </row>
     <row r="463" spans="1:17">
       <c r="A463" s="1" t="s">
-        <v>55</v>
+        <v>1184</v>
       </c>
       <c r="B463" s="1" t="s">
-        <v>1169</v>
-      </c>
-      <c r="C463" s="1"/>
-      <c r="D463" s="1"/>
-      <c r="E463" s="1"/>
-      <c r="F463" s="1"/>
-      <c r="G463" s="1"/>
+        <v>1185</v>
+      </c>
+      <c r="C463" s="2" t="s">
+        <v>1186</v>
+      </c>
+      <c r="D463" s="1" t="s">
+        <v>1187</v>
+      </c>
+      <c r="E463" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F463" s="2" t="s">
+        <v>1183</v>
+      </c>
+      <c r="G463" s="2"/>
       <c r="H463" s="1"/>
       <c r="I463" s="1"/>
       <c r="J463" s="1"/>
@@ -19728,24 +19734,16 @@
     </row>
     <row r="464" spans="1:17">
       <c r="A464" s="1" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="B464" s="1" t="s">
-        <v>1188</v>
-      </c>
-      <c r="C464" s="1" t="s">
-        <v>1189</v>
-      </c>
-      <c r="D464" s="1" t="s">
-        <v>1190</v>
-      </c>
+        <v>1169</v>
+      </c>
+      <c r="C464" s="1"/>
+      <c r="D464" s="1"/>
       <c r="E464" s="1"/>
-      <c r="F464" s="1" t="s">
-        <v>1191</v>
-      </c>
-      <c r="G464" s="1" t="s">
-        <v>147</v>
-      </c>
+      <c r="F464" s="1"/>
+      <c r="G464" s="1"/>
       <c r="H464" s="1"/>
       <c r="I464" s="1"/>
       <c r="J464" s="1"/>
@@ -19757,23 +19755,27 @@
       <c r="P464" s="1"/>
       <c r="Q464" s="1"/>
     </row>
-    <row r="465" spans="1:26" ht="52">
+    <row r="465" spans="1:26">
       <c r="A465" s="1" t="s">
-        <v>139</v>
+        <v>21</v>
       </c>
       <c r="B465" s="1" t="s">
-        <v>1192</v>
-      </c>
-      <c r="C465" s="10" t="s">
-        <v>1193</v>
-      </c>
-      <c r="D465" s="10" t="s">
-        <v>1194</v>
-      </c>
-      <c r="E465" s="2"/>
-      <c r="F465" s="2"/>
-      <c r="G465" s="2"/>
-      <c r="H465" s="2"/>
+        <v>1188</v>
+      </c>
+      <c r="C465" s="1" t="s">
+        <v>1189</v>
+      </c>
+      <c r="D465" s="1" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E465" s="1"/>
+      <c r="F465" s="1" t="s">
+        <v>1191</v>
+      </c>
+      <c r="G465" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="H465" s="1"/>
       <c r="I465" s="1"/>
       <c r="J465" s="1"/>
       <c r="K465" s="1"/>
@@ -19784,27 +19786,23 @@
       <c r="P465" s="1"/>
       <c r="Q465" s="1"/>
     </row>
-    <row r="466" spans="1:26">
+    <row r="466" spans="1:26" ht="52">
       <c r="A466" s="1" t="s">
-        <v>166</v>
+        <v>139</v>
       </c>
       <c r="B466" s="1" t="s">
-        <v>1195</v>
-      </c>
-      <c r="C466" s="2" t="s">
-        <v>1196</v>
-      </c>
-      <c r="D466" s="1" t="s">
-        <v>1197</v>
-      </c>
-      <c r="E466" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F466" s="2" t="s">
-        <v>1198</v>
-      </c>
+        <v>1192</v>
+      </c>
+      <c r="C466" s="10" t="s">
+        <v>1193</v>
+      </c>
+      <c r="D466" s="10" t="s">
+        <v>1194</v>
+      </c>
+      <c r="E466" s="2"/>
+      <c r="F466" s="2"/>
       <c r="G466" s="2"/>
-      <c r="H466" s="1"/>
+      <c r="H466" s="2"/>
       <c r="I466" s="1"/>
       <c r="J466" s="1"/>
       <c r="K466" s="1"/>
@@ -19817,24 +19815,24 @@
     </row>
     <row r="467" spans="1:26">
       <c r="A467" s="1" t="s">
-        <v>1199</v>
+        <v>166</v>
       </c>
       <c r="B467" s="1" t="s">
-        <v>1200</v>
+        <v>1195</v>
       </c>
       <c r="C467" s="2" t="s">
-        <v>1201</v>
+        <v>1196</v>
       </c>
       <c r="D467" s="1" t="s">
-        <v>1202</v>
+        <v>1197</v>
       </c>
       <c r="E467" s="1" t="s">
         <v>170</v>
       </c>
       <c r="F467" s="2" t="s">
-        <v>1203</v>
-      </c>
-      <c r="G467" s="1"/>
+        <v>1198</v>
+      </c>
+      <c r="G467" s="2"/>
       <c r="H467" s="1"/>
       <c r="I467" s="1"/>
       <c r="J467" s="1"/>
@@ -19848,20 +19846,22 @@
     </row>
     <row r="468" spans="1:26">
       <c r="A468" s="1" t="s">
-        <v>139</v>
+        <v>1199</v>
       </c>
       <c r="B468" s="1" t="s">
-        <v>1204</v>
+        <v>1200</v>
       </c>
       <c r="C468" s="2" t="s">
-        <v>1205</v>
-      </c>
-      <c r="D468" s="2" t="s">
-        <v>1206</v>
-      </c>
-      <c r="E468" s="1"/>
+        <v>1201</v>
+      </c>
+      <c r="D468" s="1" t="s">
+        <v>1202</v>
+      </c>
+      <c r="E468" s="1" t="s">
+        <v>170</v>
+      </c>
       <c r="F468" s="2" t="s">
-        <v>1207</v>
+        <v>1203</v>
       </c>
       <c r="G468" s="1"/>
       <c r="H468" s="1"/>
@@ -19875,50 +19875,56 @@
       <c r="P468" s="1"/>
       <c r="Q468" s="1"/>
     </row>
-    <row r="469" spans="1:26" ht="156">
+    <row r="469" spans="1:26">
       <c r="A469" s="1" t="s">
         <v>139</v>
       </c>
       <c r="B469" s="1" t="s">
-        <v>1208</v>
-      </c>
-      <c r="C469" s="10" t="s">
-        <v>1209</v>
-      </c>
-      <c r="D469" s="10" t="s">
-        <v>1210</v>
-      </c>
-      <c r="E469" s="2"/>
-      <c r="F469" s="2"/>
-      <c r="G469" s="2"/>
-      <c r="H469" s="2"/>
-      <c r="I469" s="2"/>
-      <c r="J469" s="2"/>
-      <c r="K469" s="2"/>
-      <c r="L469" s="2"/>
+        <v>1204</v>
+      </c>
+      <c r="C469" s="2" t="s">
+        <v>1205</v>
+      </c>
+      <c r="D469" s="2" t="s">
+        <v>1206</v>
+      </c>
+      <c r="E469" s="1"/>
+      <c r="F469" s="2" t="s">
+        <v>1207</v>
+      </c>
+      <c r="G469" s="1"/>
+      <c r="H469" s="1"/>
+      <c r="I469" s="1"/>
+      <c r="J469" s="1"/>
+      <c r="K469" s="1"/>
+      <c r="L469" s="1"/>
       <c r="M469" s="1"/>
       <c r="N469" s="1"/>
       <c r="O469" s="1"/>
       <c r="P469" s="1"/>
       <c r="Q469" s="1"/>
     </row>
-    <row r="470" spans="1:26">
+    <row r="470" spans="1:26" ht="156">
       <c r="A470" s="1" t="s">
-        <v>55</v>
+        <v>139</v>
       </c>
       <c r="B470" s="1" t="s">
-        <v>1188</v>
-      </c>
-      <c r="C470" s="1"/>
-      <c r="D470" s="1"/>
-      <c r="E470" s="1"/>
-      <c r="F470" s="1"/>
-      <c r="G470" s="1"/>
-      <c r="H470" s="1"/>
-      <c r="I470" s="1"/>
-      <c r="J470" s="1"/>
-      <c r="K470" s="1"/>
-      <c r="L470" s="1"/>
+        <v>1208</v>
+      </c>
+      <c r="C470" s="10" t="s">
+        <v>1209</v>
+      </c>
+      <c r="D470" s="10" t="s">
+        <v>1210</v>
+      </c>
+      <c r="E470" s="2"/>
+      <c r="F470" s="2"/>
+      <c r="G470" s="2"/>
+      <c r="H470" s="2"/>
+      <c r="I470" s="2"/>
+      <c r="J470" s="2"/>
+      <c r="K470" s="2"/>
+      <c r="L470" s="2"/>
       <c r="M470" s="1"/>
       <c r="N470" s="1"/>
       <c r="O470" s="1"/>
@@ -19927,24 +19933,16 @@
     </row>
     <row r="471" spans="1:26">
       <c r="A471" s="1" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="B471" s="1" t="s">
-        <v>1211</v>
-      </c>
-      <c r="C471" s="1" t="s">
-        <v>1212</v>
-      </c>
-      <c r="D471" s="1" t="s">
-        <v>1213</v>
-      </c>
+        <v>1188</v>
+      </c>
+      <c r="C471" s="1"/>
+      <c r="D471" s="1"/>
       <c r="E471" s="1"/>
-      <c r="F471" s="1" t="s">
-        <v>460</v>
-      </c>
-      <c r="G471" s="1" t="s">
-        <v>147</v>
-      </c>
+      <c r="F471" s="1"/>
+      <c r="G471" s="1"/>
       <c r="H471" s="1"/>
       <c r="I471" s="1"/>
       <c r="J471" s="1"/>
@@ -19958,77 +19956,79 @@
     </row>
     <row r="472" spans="1:26">
       <c r="A472" s="1" t="s">
-        <v>139</v>
+        <v>21</v>
       </c>
       <c r="B472" s="1" t="s">
-        <v>1214</v>
-      </c>
-      <c r="C472" s="2" t="s">
-        <v>1215</v>
-      </c>
-      <c r="D472" s="2" t="s">
-        <v>1216</v>
-      </c>
-      <c r="E472" s="2"/>
-      <c r="F472" s="2"/>
-      <c r="G472" s="2"/>
-      <c r="H472" s="2"/>
-      <c r="I472" s="2"/>
-      <c r="J472" s="2"/>
-      <c r="K472" s="2"/>
-      <c r="L472" s="2"/>
-      <c r="M472" s="2"/>
+        <v>1211</v>
+      </c>
+      <c r="C472" s="1" t="s">
+        <v>1212</v>
+      </c>
+      <c r="D472" s="1" t="s">
+        <v>1213</v>
+      </c>
+      <c r="E472" s="1"/>
+      <c r="F472" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="G472" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="H472" s="1"/>
+      <c r="I472" s="1"/>
+      <c r="J472" s="1"/>
+      <c r="K472" s="1"/>
+      <c r="L472" s="1"/>
+      <c r="M472" s="1"/>
       <c r="N472" s="1"/>
       <c r="O472" s="1"/>
       <c r="P472" s="1"/>
       <c r="Q472" s="1"/>
     </row>
-    <row r="473" spans="1:26" ht="39">
+    <row r="473" spans="1:26">
       <c r="A473" s="1" t="s">
-        <v>166</v>
+        <v>139</v>
       </c>
       <c r="B473" s="1" t="s">
-        <v>1217</v>
-      </c>
-      <c r="C473" s="10" t="s">
-        <v>1218</v>
-      </c>
-      <c r="D473" s="9" t="s">
-        <v>1219</v>
-      </c>
-      <c r="E473" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F473" s="1"/>
-      <c r="G473" s="1"/>
-      <c r="H473" s="1"/>
-      <c r="I473" s="1"/>
-      <c r="J473" s="1"/>
-      <c r="K473" s="1"/>
-      <c r="L473" s="1"/>
-      <c r="M473" s="1"/>
+        <v>1214</v>
+      </c>
+      <c r="C473" s="2" t="s">
+        <v>1215</v>
+      </c>
+      <c r="D473" s="2" t="s">
+        <v>1216</v>
+      </c>
+      <c r="E473" s="2"/>
+      <c r="F473" s="2"/>
+      <c r="G473" s="2"/>
+      <c r="H473" s="2"/>
+      <c r="I473" s="2"/>
+      <c r="J473" s="2"/>
+      <c r="K473" s="2"/>
+      <c r="L473" s="2"/>
+      <c r="M473" s="2"/>
       <c r="N473" s="1"/>
       <c r="O473" s="1"/>
       <c r="P473" s="1"/>
       <c r="Q473" s="1"/>
     </row>
-    <row r="474" spans="1:26">
+    <row r="474" spans="1:26" ht="39">
       <c r="A474" s="1" t="s">
-        <v>139</v>
+        <v>166</v>
       </c>
       <c r="B474" s="1" t="s">
-        <v>1220</v>
-      </c>
-      <c r="C474" s="2" t="s">
-        <v>1221</v>
-      </c>
-      <c r="D474" s="2" t="s">
-        <v>1222</v>
-      </c>
-      <c r="E474" s="1"/>
-      <c r="F474" s="1" t="s">
-        <v>1223</v>
-      </c>
+        <v>1217</v>
+      </c>
+      <c r="C474" s="10" t="s">
+        <v>1218</v>
+      </c>
+      <c r="D474" s="9" t="s">
+        <v>1219</v>
+      </c>
+      <c r="E474" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F474" s="1"/>
       <c r="G474" s="1"/>
       <c r="H474" s="1"/>
       <c r="I474" s="1"/>
@@ -20043,15 +20043,21 @@
     </row>
     <row r="475" spans="1:26">
       <c r="A475" s="1" t="s">
-        <v>55</v>
+        <v>139</v>
       </c>
       <c r="B475" s="1" t="s">
-        <v>1211</v>
-      </c>
-      <c r="C475" s="1"/>
-      <c r="D475" s="1"/>
+        <v>1220</v>
+      </c>
+      <c r="C475" s="2" t="s">
+        <v>1221</v>
+      </c>
+      <c r="D475" s="2" t="s">
+        <v>1222</v>
+      </c>
       <c r="E475" s="1"/>
-      <c r="F475" s="1"/>
+      <c r="F475" s="1" t="s">
+        <v>1223</v>
+      </c>
       <c r="G475" s="1"/>
       <c r="H475" s="1"/>
       <c r="I475" s="1"/>
@@ -20066,24 +20072,16 @@
     </row>
     <row r="476" spans="1:26">
       <c r="A476" s="1" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="B476" s="1" t="s">
-        <v>1224</v>
-      </c>
-      <c r="C476" s="1" t="s">
-        <v>1225</v>
-      </c>
-      <c r="D476" s="1" t="s">
-        <v>1226</v>
-      </c>
+        <v>1211</v>
+      </c>
+      <c r="C476" s="1"/>
+      <c r="D476" s="1"/>
       <c r="E476" s="1"/>
-      <c r="F476" s="1" t="s">
-        <v>1227</v>
-      </c>
-      <c r="G476" s="1" t="s">
-        <v>147</v>
-      </c>
+      <c r="F476" s="1"/>
+      <c r="G476" s="1"/>
       <c r="H476" s="1"/>
       <c r="I476" s="1"/>
       <c r="J476" s="1"/>
@@ -20094,36 +20092,29 @@
       <c r="O476" s="1"/>
       <c r="P476" s="1"/>
       <c r="Q476" s="1"/>
-      <c r="R476" s="1"/>
-      <c r="S476" s="1"/>
-      <c r="T476" s="1"/>
-      <c r="U476" s="1"/>
-      <c r="V476" s="1"/>
-      <c r="W476" s="1"/>
-      <c r="X476" s="1"/>
-      <c r="Y476" s="1"/>
-      <c r="Z476" s="1"/>
     </row>
     <row r="477" spans="1:26">
       <c r="A477" s="1" t="s">
-        <v>139</v>
+        <v>21</v>
       </c>
       <c r="B477" s="1" t="s">
-        <v>1228</v>
+        <v>1224</v>
       </c>
       <c r="C477" s="1" t="s">
-        <v>1229</v>
-      </c>
-      <c r="D477" s="2" t="s">
-        <v>1230</v>
-      </c>
-      <c r="E477" s="2"/>
-      <c r="F477" s="7" t="s">
-        <v>1231</v>
-      </c>
-      <c r="G477" s="2"/>
-      <c r="H477" s="2"/>
-      <c r="I477" s="2"/>
+        <v>1225</v>
+      </c>
+      <c r="D477" s="1" t="s">
+        <v>1226</v>
+      </c>
+      <c r="E477" s="1"/>
+      <c r="F477" s="1" t="s">
+        <v>1227</v>
+      </c>
+      <c r="G477" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="H477" s="1"/>
+      <c r="I477" s="1"/>
       <c r="J477" s="1"/>
       <c r="K477" s="1"/>
       <c r="L477" s="1"/>
@@ -20147,21 +20138,21 @@
         <v>139</v>
       </c>
       <c r="B478" s="1" t="s">
-        <v>1232</v>
+        <v>1228</v>
       </c>
       <c r="C478" s="1" t="s">
-        <v>1233</v>
-      </c>
-      <c r="D478" s="1" t="s">
-        <v>1234</v>
-      </c>
-      <c r="E478" s="1"/>
+        <v>1229</v>
+      </c>
+      <c r="D478" s="2" t="s">
+        <v>1230</v>
+      </c>
+      <c r="E478" s="2"/>
       <c r="F478" s="7" t="s">
-        <v>1235</v>
-      </c>
-      <c r="G478" s="1"/>
-      <c r="H478" s="1"/>
-      <c r="I478" s="1"/>
+        <v>1231</v>
+      </c>
+      <c r="G478" s="2"/>
+      <c r="H478" s="2"/>
+      <c r="I478" s="2"/>
       <c r="J478" s="1"/>
       <c r="K478" s="1"/>
       <c r="L478" s="1"/>
@@ -20182,15 +20173,21 @@
     </row>
     <row r="479" spans="1:26">
       <c r="A479" s="1" t="s">
-        <v>55</v>
+        <v>139</v>
       </c>
       <c r="B479" s="1" t="s">
-        <v>1224</v>
-      </c>
-      <c r="C479" s="1"/>
-      <c r="D479" s="1"/>
+        <v>1232</v>
+      </c>
+      <c r="C479" s="1" t="s">
+        <v>1233</v>
+      </c>
+      <c r="D479" s="1" t="s">
+        <v>1234</v>
+      </c>
       <c r="E479" s="1"/>
-      <c r="F479" s="1"/>
+      <c r="F479" s="7" t="s">
+        <v>1235</v>
+      </c>
       <c r="G479" s="1"/>
       <c r="H479" s="1"/>
       <c r="I479" s="1"/>
@@ -20214,64 +20211,79 @@
     </row>
     <row r="480" spans="1:26">
       <c r="A480" s="1" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="B480" s="1" t="s">
-        <v>1236</v>
-      </c>
-      <c r="C480" s="1" t="s">
-        <v>1237</v>
-      </c>
-      <c r="D480" s="1" t="s">
-        <v>1238</v>
-      </c>
-      <c r="G480" s="1" t="s">
-        <v>147</v>
-      </c>
+        <v>1224</v>
+      </c>
+      <c r="C480" s="1"/>
+      <c r="D480" s="1"/>
+      <c r="E480" s="1"/>
+      <c r="F480" s="1"/>
+      <c r="G480" s="1"/>
+      <c r="H480" s="1"/>
+      <c r="I480" s="1"/>
+      <c r="J480" s="1"/>
+      <c r="K480" s="1"/>
+      <c r="L480" s="1"/>
+      <c r="M480" s="1"/>
+      <c r="N480" s="1"/>
+      <c r="O480" s="1"/>
+      <c r="P480" s="1"/>
+      <c r="Q480" s="1"/>
+      <c r="R480" s="1"/>
+      <c r="S480" s="1"/>
+      <c r="T480" s="1"/>
+      <c r="U480" s="1"/>
+      <c r="V480" s="1"/>
+      <c r="W480" s="1"/>
+      <c r="X480" s="1"/>
+      <c r="Y480" s="1"/>
+      <c r="Z480" s="1"/>
     </row>
     <row r="481" spans="1:12">
       <c r="A481" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B481" s="1" t="s">
+        <v>1236</v>
+      </c>
+      <c r="C481" s="1" t="s">
+        <v>1237</v>
+      </c>
+      <c r="D481" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="G481" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="482" spans="1:12">
+      <c r="A482" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B481" s="1" t="s">
+      <c r="B482" s="1" t="s">
         <v>1239</v>
       </c>
-      <c r="C481" s="1" t="s">
+      <c r="C482" s="1" t="s">
         <v>1240</v>
       </c>
-      <c r="D481" s="1" t="s">
+      <c r="D482" s="1" t="s">
         <v>1241</v>
       </c>
-      <c r="F481" s="1" t="s">
+      <c r="F482" s="1" t="s">
         <v>1242</v>
       </c>
     </row>
-    <row r="482" spans="1:12" ht="286">
-      <c r="A482" s="1" t="s">
+    <row r="483" spans="1:12" ht="286">
+      <c r="A483" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B482" s="1" t="s">
+      <c r="B483" s="1" t="s">
         <v>1243</v>
       </c>
-      <c r="L482" s="9" t="s">
+      <c r="L483" s="9" t="s">
         <v>1591</v>
-      </c>
-    </row>
-    <row r="483" spans="1:12">
-      <c r="A483" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="B483" s="1" t="s">
-        <v>1244</v>
-      </c>
-      <c r="C483" s="1" t="s">
-        <v>1245</v>
-      </c>
-      <c r="D483" s="1" t="s">
-        <v>1246</v>
-      </c>
-      <c r="F483" s="1" t="s">
-        <v>1247</v>
       </c>
     </row>
     <row r="484" spans="1:12">
@@ -20279,36 +20291,33 @@
         <v>139</v>
       </c>
       <c r="B484" s="1" t="s">
-        <v>1248</v>
+        <v>1244</v>
       </c>
       <c r="C484" s="1" t="s">
-        <v>1249</v>
+        <v>1245</v>
       </c>
       <c r="D484" s="1" t="s">
-        <v>1250</v>
+        <v>1246</v>
       </c>
       <c r="F484" s="1" t="s">
-        <v>1251</v>
-      </c>
-    </row>
-    <row r="485" spans="1:12" ht="14.25">
+        <v>1247</v>
+      </c>
+    </row>
+    <row r="485" spans="1:12">
       <c r="A485" s="1" t="s">
         <v>139</v>
       </c>
       <c r="B485" s="1" t="s">
-        <v>1252</v>
+        <v>1248</v>
       </c>
       <c r="C485" s="1" t="s">
-        <v>1253</v>
+        <v>1249</v>
       </c>
       <c r="D485" s="1" t="s">
-        <v>1254</v>
-      </c>
-      <c r="F485" s="15" t="s">
-        <v>1255</v>
-      </c>
-      <c r="G485" s="1" t="s">
-        <v>1256</v>
+        <v>1250</v>
+      </c>
+      <c r="F485" s="1" t="s">
+        <v>1251</v>
       </c>
     </row>
     <row r="486" spans="1:12" ht="14.25">
@@ -20316,16 +20325,16 @@
         <v>139</v>
       </c>
       <c r="B486" s="1" t="s">
-        <v>1257</v>
+        <v>1252</v>
       </c>
       <c r="C486" s="1" t="s">
-        <v>1258</v>
+        <v>1253</v>
       </c>
       <c r="D486" s="1" t="s">
-        <v>1259</v>
+        <v>1254</v>
       </c>
       <c r="F486" s="15" t="s">
-        <v>279</v>
+        <v>1255</v>
       </c>
       <c r="G486" s="1" t="s">
         <v>1256</v>
@@ -20336,16 +20345,16 @@
         <v>139</v>
       </c>
       <c r="B487" s="1" t="s">
-        <v>1260</v>
+        <v>1257</v>
       </c>
       <c r="C487" s="1" t="s">
-        <v>1261</v>
+        <v>1258</v>
       </c>
       <c r="D487" s="1" t="s">
-        <v>1262</v>
+        <v>1259</v>
       </c>
       <c r="F487" s="15" t="s">
-        <v>328</v>
+        <v>279</v>
       </c>
       <c r="G487" s="1" t="s">
         <v>1256</v>
@@ -20356,16 +20365,16 @@
         <v>139</v>
       </c>
       <c r="B488" s="1" t="s">
-        <v>1263</v>
+        <v>1260</v>
       </c>
       <c r="C488" s="1" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="D488" s="1" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
       <c r="F488" s="15" t="s">
-        <v>361</v>
+        <v>328</v>
       </c>
       <c r="G488" s="1" t="s">
         <v>1256</v>
@@ -20376,16 +20385,16 @@
         <v>139</v>
       </c>
       <c r="B489" s="1" t="s">
-        <v>1266</v>
+        <v>1263</v>
       </c>
       <c r="C489" s="1" t="s">
-        <v>1267</v>
+        <v>1264</v>
       </c>
       <c r="D489" s="1" t="s">
-        <v>1268</v>
+        <v>1265</v>
       </c>
       <c r="F489" s="15" t="s">
-        <v>391</v>
+        <v>361</v>
       </c>
       <c r="G489" s="1" t="s">
         <v>1256</v>
@@ -20396,16 +20405,16 @@
         <v>139</v>
       </c>
       <c r="B490" s="1" t="s">
-        <v>1269</v>
+        <v>1266</v>
       </c>
       <c r="C490" s="1" t="s">
-        <v>1270</v>
+        <v>1267</v>
       </c>
       <c r="D490" s="1" t="s">
-        <v>1271</v>
+        <v>1268</v>
       </c>
       <c r="F490" s="15" t="s">
-        <v>1272</v>
+        <v>391</v>
       </c>
       <c r="G490" s="1" t="s">
         <v>1256</v>
@@ -20416,16 +20425,16 @@
         <v>139</v>
       </c>
       <c r="B491" s="1" t="s">
-        <v>1273</v>
+        <v>1269</v>
       </c>
       <c r="C491" s="1" t="s">
-        <v>1274</v>
+        <v>1270</v>
       </c>
       <c r="D491" s="1" t="s">
-        <v>1275</v>
+        <v>1271</v>
       </c>
       <c r="F491" s="15" t="s">
-        <v>1276</v>
+        <v>1272</v>
       </c>
       <c r="G491" s="1" t="s">
         <v>1256</v>
@@ -20436,70 +20445,90 @@
         <v>139</v>
       </c>
       <c r="B492" s="1" t="s">
-        <v>1277</v>
+        <v>1273</v>
       </c>
       <c r="C492" s="1" t="s">
-        <v>1278</v>
+        <v>1274</v>
       </c>
       <c r="D492" s="1" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="F492" s="15" t="s">
-        <v>1280</v>
+        <v>1276</v>
       </c>
       <c r="G492" s="1" t="s">
         <v>1256</v>
       </c>
     </row>
-    <row r="493" spans="1:12">
+    <row r="493" spans="1:12" ht="14.25">
       <c r="A493" s="1" t="s">
         <v>139</v>
       </c>
       <c r="B493" s="1" t="s">
-        <v>1281</v>
+        <v>1277</v>
       </c>
       <c r="C493" s="1" t="s">
-        <v>1282</v>
+        <v>1278</v>
       </c>
       <c r="D493" s="1" t="s">
-        <v>1283</v>
-      </c>
-      <c r="F493" s="1" t="s">
-        <v>1251</v>
+        <v>1279</v>
+      </c>
+      <c r="F493" s="15" t="s">
+        <v>1280</v>
+      </c>
+      <c r="G493" s="1" t="s">
+        <v>1256</v>
       </c>
     </row>
     <row r="494" spans="1:12">
       <c r="A494" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B494" s="1" t="s">
+        <v>1281</v>
+      </c>
+      <c r="C494" s="1" t="s">
+        <v>1282</v>
+      </c>
+      <c r="D494" s="1" t="s">
+        <v>1283</v>
+      </c>
+      <c r="F494" s="1" t="s">
+        <v>1251</v>
+      </c>
+    </row>
+    <row r="495" spans="1:12">
+      <c r="A495" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B494" s="1" t="s">
+      <c r="B495" s="1" t="s">
         <v>1236</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B1:B494" xr:uid="{5FF28BC1-9D9E-4A0E-8298-F7B59A8B8CF2}"/>
+  <autoFilter ref="B1:B495" xr:uid="{5FF28BC1-9D9E-4A0E-8298-F7B59A8B8CF2}"/>
   <mergeCells count="21">
+    <mergeCell ref="F332:H332"/>
+    <mergeCell ref="K333:L333"/>
+    <mergeCell ref="K336:L336"/>
+    <mergeCell ref="K339:L339"/>
+    <mergeCell ref="F347:I347"/>
+    <mergeCell ref="F349:I349"/>
+    <mergeCell ref="K293:L293"/>
+    <mergeCell ref="F294:G294"/>
+    <mergeCell ref="K297:L297"/>
+    <mergeCell ref="K300:L300"/>
+    <mergeCell ref="K303:L303"/>
+    <mergeCell ref="K306:L306"/>
+    <mergeCell ref="K309:L309"/>
+    <mergeCell ref="K312:L312"/>
+    <mergeCell ref="K315:L315"/>
+    <mergeCell ref="K318:L318"/>
+    <mergeCell ref="K321:L321"/>
+    <mergeCell ref="K324:L324"/>
+    <mergeCell ref="K327:L327"/>
+    <mergeCell ref="K330:L330"/>
     <mergeCell ref="F331:H331"/>
-    <mergeCell ref="K332:L332"/>
-    <mergeCell ref="K335:L335"/>
-    <mergeCell ref="K338:L338"/>
-    <mergeCell ref="F346:I346"/>
-    <mergeCell ref="F348:I348"/>
-    <mergeCell ref="K292:L292"/>
-    <mergeCell ref="F293:G293"/>
-    <mergeCell ref="K296:L296"/>
-    <mergeCell ref="K299:L299"/>
-    <mergeCell ref="K302:L302"/>
-    <mergeCell ref="K305:L305"/>
-    <mergeCell ref="K308:L308"/>
-    <mergeCell ref="K311:L311"/>
-    <mergeCell ref="K314:L314"/>
-    <mergeCell ref="K317:L317"/>
-    <mergeCell ref="K320:L320"/>
-    <mergeCell ref="K323:L323"/>
-    <mergeCell ref="K326:L326"/>
-    <mergeCell ref="K329:L329"/>
-    <mergeCell ref="F330:H330"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
   <pageSetup firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -21689,10 +21718,10 @@
       <c r="C84" s="1" t="s">
         <v>1527</v>
       </c>
-      <c r="D84" s="30" t="s">
+      <c r="D84" s="32" t="s">
         <v>1528</v>
       </c>
-      <c r="E84" s="30"/>
+      <c r="E84" s="32"/>
     </row>
     <row r="85" spans="1:6">
       <c r="A85" s="1" t="s">
@@ -21704,11 +21733,11 @@
       <c r="C85" s="1" t="s">
         <v>1529</v>
       </c>
-      <c r="D85" s="30" t="s">
+      <c r="D85" s="32" t="s">
         <v>1530</v>
       </c>
-      <c r="E85" s="30"/>
-      <c r="F85" s="30"/>
+      <c r="E85" s="32"/>
+      <c r="F85" s="32"/>
     </row>
     <row r="86" spans="1:6">
       <c r="A86" s="1" t="s">
@@ -21734,10 +21763,10 @@
       <c r="C87" s="1" t="s">
         <v>1533</v>
       </c>
-      <c r="D87" s="30" t="s">
+      <c r="D87" s="32" t="s">
         <v>1534</v>
       </c>
-      <c r="E87" s="30"/>
+      <c r="E87" s="32"/>
     </row>
     <row r="88" spans="1:6">
       <c r="A88" s="1" t="s">

--- a/forms/app/infant_child.xlsx
+++ b/forms/app/infant_child.xlsx
@@ -1,16 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20400"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\D-tree\config-dtree-newrepo\config-dtree\forms\app\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F3886E4-0EF0-4C5E-A81C-01AA433891F8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15280" windowHeight="6000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="survey" sheetId="1" r:id="rId4"/>
-    <sheet state="visible" name="choices" sheetId="2" r:id="rId5"/>
-    <sheet state="visible" name="settings" sheetId="3" r:id="rId6"/>
+    <sheet name="survey" sheetId="1" r:id="rId1"/>
+    <sheet name="choices" sheetId="2" r:id="rId2"/>
+    <sheet name="settings" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">survey!$B$1:$B$611</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">survey!$B$1:$B$611</definedName>
   </definedNames>
-  <calcPr/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
@@ -5052,18 +5062,7 @@
     <t>who_engages_new</t>
   </si>
   <si>
-    <t>selected(${engage_with_child_new},"read_books") or 
-selected(${engage_with_child},"told_storied") or 
-selected(${engage_with_child},"sang") or 
-selected(${engage_with_child},"took_outside") or 
-selected(${engage_with_child},"played") or 
-selected(${engage_with_child},"named_things")</t>
-  </si>
-  <si>
     <t>who_engages_other_new</t>
-  </si>
-  <si>
-    <t>selected(${who_engages_other_new},"other")</t>
   </si>
   <si>
     <t xml:space="preserve">How many total hours did the father/partner/male household head spend playing with the child in the last 3 days? </t>
@@ -6188,9 +6187,6 @@
     <t>kusoma vitabu au kuangalia picha za vitabu</t>
   </si>
   <si>
-    <t>told_storied</t>
-  </si>
-  <si>
     <t>Told stories to the child</t>
   </si>
   <si>
@@ -6501,12 +6497,26 @@
   </si>
   <si>
     <t>data</t>
+  </si>
+  <si>
+    <t>told_stories</t>
+  </si>
+  <si>
+    <t>selected(${who_engages_new},"other")</t>
+  </si>
+  <si>
+    <t>selected(${engage_with_child_new},"read_books") or 
+selected(${engage_with_child},"told_stories") or 
+selected(${engage_with_child},"sang") or 
+selected(${engage_with_child},"took_outside") or 
+selected(${engage_with_child},"played") or 
+selected(${engage_with_child},"named_things")</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="&quot;TRUE&quot;;&quot;TRUE&quot;;&quot;FALSE&quot;"/>
     <numFmt numFmtId="165" formatCode="\$#,##0.00"/>
@@ -6514,38 +6524,38 @@
   </numFmts>
   <fonts count="7">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Roboto"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Sans"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF1D1C1D"/>
       <name val="Lato"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
@@ -6555,7 +6565,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -6571,75 +6581,77 @@
     </fill>
   </fills>
   <borders count="2">
-    <border/>
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="1" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+  <cellXfs count="21">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="165" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="165" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="166" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -6829,34 +6841,34 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:Z1000"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="28.63"/>
-    <col customWidth="1" min="2" max="2" width="38.88"/>
-    <col customWidth="1" min="3" max="3" width="81.5"/>
-    <col customWidth="1" min="4" max="4" width="207.5"/>
-    <col customWidth="1" min="5" max="5" width="36.13"/>
-    <col customWidth="1" min="6" max="6" width="86.13"/>
-    <col customWidth="1" min="7" max="8" width="14.38"/>
-    <col customWidth="1" min="9" max="9" width="86.38"/>
-    <col customWidth="1" min="10" max="10" width="53.38"/>
-    <col customWidth="1" min="11" max="11" width="50.13"/>
-    <col customWidth="1" min="12" max="13" width="14.38"/>
-    <col customWidth="1" min="14" max="14" width="50.38"/>
-    <col customWidth="1" min="15" max="17" width="14.38"/>
-    <col customWidth="1" min="18" max="18" width="17.0"/>
-    <col customWidth="1" min="19" max="26" width="14.38"/>
+    <col min="1" max="1" width="28.6328125" customWidth="1"/>
+    <col min="2" max="2" width="38.86328125" customWidth="1"/>
+    <col min="3" max="3" width="81.5" customWidth="1"/>
+    <col min="4" max="4" width="207.5" customWidth="1"/>
+    <col min="5" max="5" width="36.1328125" customWidth="1"/>
+    <col min="6" max="6" width="86.1328125" customWidth="1"/>
+    <col min="7" max="8" width="14.36328125" customWidth="1"/>
+    <col min="9" max="9" width="86.36328125" customWidth="1"/>
+    <col min="10" max="10" width="53.36328125" customWidth="1"/>
+    <col min="11" max="11" width="50.1328125" customWidth="1"/>
+    <col min="12" max="13" width="14.36328125" customWidth="1"/>
+    <col min="14" max="14" width="50.36328125" customWidth="1"/>
+    <col min="15" max="17" width="14.36328125" customWidth="1"/>
+    <col min="18" max="18" width="17" customWidth="1"/>
+    <col min="19" max="26" width="14.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="12.75" customHeight="1">
+    <row r="1" spans="1:21" ht="12.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6921,7 +6933,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" ht="12.75" customHeight="1">
+    <row r="2" spans="1:21" ht="12.75" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>21</v>
       </c>
@@ -6950,7 +6962,7 @@
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
     </row>
-    <row r="3" ht="12.75" customHeight="1">
+    <row r="3" spans="1:21" ht="12.75" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>25</v>
       </c>
@@ -6975,7 +6987,7 @@
       <c r="P3" s="1"/>
       <c r="Q3" s="1"/>
     </row>
-    <row r="4" ht="12.75" customHeight="1">
+    <row r="4" spans="1:21" ht="12.75" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>25</v>
       </c>
@@ -7000,7 +7012,7 @@
       <c r="P4" s="1"/>
       <c r="Q4" s="1"/>
     </row>
-    <row r="5" ht="12.75" customHeight="1">
+    <row r="5" spans="1:21" ht="12.75" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>25</v>
       </c>
@@ -7025,7 +7037,7 @@
       <c r="P5" s="1"/>
       <c r="Q5" s="1"/>
     </row>
-    <row r="6" ht="12.75" customHeight="1">
+    <row r="6" spans="1:21" ht="12.75" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>25</v>
       </c>
@@ -7050,7 +7062,7 @@
       <c r="P6" s="1"/>
       <c r="Q6" s="1"/>
     </row>
-    <row r="7" ht="12.75" customHeight="1">
+    <row r="7" spans="1:21" ht="12.75" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>25</v>
       </c>
@@ -7075,7 +7087,7 @@
       <c r="P7" s="1"/>
       <c r="Q7" s="1"/>
     </row>
-    <row r="8" ht="12.75" customHeight="1">
+    <row r="8" spans="1:21" ht="12.75" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>25</v>
       </c>
@@ -7100,7 +7112,7 @@
       <c r="P8" s="1"/>
       <c r="Q8" s="1"/>
     </row>
-    <row r="9" ht="12.75" customHeight="1">
+    <row r="9" spans="1:21" ht="12.75" customHeight="1">
       <c r="A9" s="1" t="s">
         <v>25</v>
       </c>
@@ -7125,7 +7137,7 @@
       <c r="P9" s="1"/>
       <c r="Q9" s="1"/>
     </row>
-    <row r="10" ht="12.75" customHeight="1">
+    <row r="10" spans="1:21" ht="12.75" customHeight="1">
       <c r="A10" s="1" t="s">
         <v>25</v>
       </c>
@@ -7150,7 +7162,7 @@
       <c r="P10" s="1"/>
       <c r="Q10" s="1"/>
     </row>
-    <row r="11" ht="12.75" customHeight="1">
+    <row r="11" spans="1:21" ht="12.75" customHeight="1">
       <c r="A11" s="1" t="s">
         <v>25</v>
       </c>
@@ -7175,7 +7187,7 @@
       <c r="P11" s="1"/>
       <c r="Q11" s="1"/>
     </row>
-    <row r="12" ht="12.75" customHeight="1">
+    <row r="12" spans="1:21" ht="12.75" customHeight="1">
       <c r="A12" s="1" t="s">
         <v>25</v>
       </c>
@@ -7200,7 +7212,7 @@
       <c r="P12" s="1"/>
       <c r="Q12" s="1"/>
     </row>
-    <row r="13" ht="12.75" customHeight="1">
+    <row r="13" spans="1:21" ht="12.75" customHeight="1">
       <c r="A13" s="1" t="s">
         <v>25</v>
       </c>
@@ -7225,7 +7237,7 @@
       <c r="P13" s="1"/>
       <c r="Q13" s="1"/>
     </row>
-    <row r="14" ht="12.75" customHeight="1">
+    <row r="14" spans="1:21" ht="12.75" customHeight="1">
       <c r="A14" s="1" t="s">
         <v>25</v>
       </c>
@@ -7250,7 +7262,7 @@
       <c r="P14" s="1"/>
       <c r="Q14" s="1"/>
     </row>
-    <row r="15" ht="12.75" customHeight="1">
+    <row r="15" spans="1:21" ht="12.75" customHeight="1">
       <c r="A15" s="1" t="s">
         <v>25</v>
       </c>
@@ -7275,7 +7287,7 @@
       <c r="P15" s="1"/>
       <c r="Q15" s="1"/>
     </row>
-    <row r="16" ht="12.75" customHeight="1">
+    <row r="16" spans="1:21" ht="12.75" customHeight="1">
       <c r="A16" s="1" t="s">
         <v>25</v>
       </c>
@@ -7300,7 +7312,7 @@
       <c r="P16" s="1"/>
       <c r="Q16" s="1"/>
     </row>
-    <row r="17" ht="12.75" customHeight="1">
+    <row r="17" spans="1:17" ht="12.75" customHeight="1">
       <c r="A17" s="1" t="s">
         <v>25</v>
       </c>
@@ -7325,7 +7337,7 @@
       <c r="P17" s="1"/>
       <c r="Q17" s="1"/>
     </row>
-    <row r="18" ht="12.75" customHeight="1">
+    <row r="18" spans="1:17" ht="12.75" customHeight="1">
       <c r="A18" s="1" t="s">
         <v>25</v>
       </c>
@@ -7350,7 +7362,7 @@
       <c r="P18" s="1"/>
       <c r="Q18" s="1"/>
     </row>
-    <row r="19" ht="12.75" customHeight="1">
+    <row r="19" spans="1:17" ht="12.75" customHeight="1">
       <c r="A19" s="1" t="s">
         <v>25</v>
       </c>
@@ -7375,7 +7387,7 @@
       <c r="P19" s="1"/>
       <c r="Q19" s="1"/>
     </row>
-    <row r="20" ht="12.75" customHeight="1">
+    <row r="20" spans="1:17" ht="12.75" customHeight="1">
       <c r="A20" s="1" t="s">
         <v>25</v>
       </c>
@@ -7400,7 +7412,7 @@
       <c r="P20" s="1"/>
       <c r="Q20" s="1"/>
     </row>
-    <row r="21" ht="12.75" customHeight="1">
+    <row r="21" spans="1:17" ht="12.75" customHeight="1">
       <c r="A21" s="1" t="s">
         <v>44</v>
       </c>
@@ -7425,7 +7437,7 @@
       <c r="P21" s="1"/>
       <c r="Q21" s="1"/>
     </row>
-    <row r="22" ht="12.75" customHeight="1">
+    <row r="22" spans="1:17" ht="12.75" customHeight="1">
       <c r="A22" s="1" t="s">
         <v>25</v>
       </c>
@@ -7450,7 +7462,7 @@
       <c r="P22" s="1"/>
       <c r="Q22" s="1"/>
     </row>
-    <row r="23" ht="12.75" customHeight="1">
+    <row r="23" spans="1:17" ht="12.75" customHeight="1">
       <c r="A23" s="1" t="s">
         <v>25</v>
       </c>
@@ -7475,7 +7487,7 @@
       <c r="P23" s="1"/>
       <c r="Q23" s="1"/>
     </row>
-    <row r="24" ht="12.75" customHeight="1">
+    <row r="24" spans="1:17" ht="12.75" customHeight="1">
       <c r="A24" s="1" t="s">
         <v>21</v>
       </c>
@@ -7500,7 +7512,7 @@
       <c r="P24" s="1"/>
       <c r="Q24" s="1"/>
     </row>
-    <row r="25" ht="12.75" customHeight="1">
+    <row r="25" spans="1:17" ht="12.75" customHeight="1">
       <c r="A25" s="1" t="s">
         <v>25</v>
       </c>
@@ -7525,7 +7537,7 @@
       <c r="P25" s="1"/>
       <c r="Q25" s="1"/>
     </row>
-    <row r="26" ht="12.75" customHeight="1">
+    <row r="26" spans="1:17" ht="12.75" customHeight="1">
       <c r="A26" s="1" t="s">
         <v>25</v>
       </c>
@@ -7550,7 +7562,7 @@
       <c r="P26" s="1"/>
       <c r="Q26" s="1"/>
     </row>
-    <row r="27" ht="12.75" customHeight="1">
+    <row r="27" spans="1:17" ht="12.75" customHeight="1">
       <c r="A27" s="1" t="s">
         <v>25</v>
       </c>
@@ -7575,7 +7587,7 @@
       <c r="P27" s="1"/>
       <c r="Q27" s="1"/>
     </row>
-    <row r="28" ht="12.75" customHeight="1">
+    <row r="28" spans="1:17" ht="12.75" customHeight="1">
       <c r="A28" s="1" t="s">
         <v>54</v>
       </c>
@@ -7598,7 +7610,7 @@
       <c r="P28" s="1"/>
       <c r="Q28" s="1"/>
     </row>
-    <row r="29" ht="12.75" customHeight="1">
+    <row r="29" spans="1:17" ht="12.75" customHeight="1">
       <c r="A29" s="1" t="s">
         <v>21</v>
       </c>
@@ -7623,7 +7635,7 @@
       <c r="P29" s="1"/>
       <c r="Q29" s="1"/>
     </row>
-    <row r="30" ht="12.75" customHeight="1">
+    <row r="30" spans="1:17" ht="12.75" customHeight="1">
       <c r="A30" s="1" t="s">
         <v>56</v>
       </c>
@@ -7650,7 +7662,7 @@
       <c r="P30" s="1"/>
       <c r="Q30" s="1"/>
     </row>
-    <row r="31" ht="12.75" customHeight="1">
+    <row r="31" spans="1:17" ht="12.75" customHeight="1">
       <c r="A31" s="1" t="s">
         <v>25</v>
       </c>
@@ -7675,7 +7687,7 @@
       <c r="P31" s="1"/>
       <c r="Q31" s="1"/>
     </row>
-    <row r="32" ht="12.75" customHeight="1">
+    <row r="32" spans="1:17" ht="12.75" customHeight="1">
       <c r="A32" s="1" t="s">
         <v>25</v>
       </c>
@@ -7700,7 +7712,7 @@
       <c r="P32" s="1"/>
       <c r="Q32" s="1"/>
     </row>
-    <row r="33" ht="12.75" customHeight="1">
+    <row r="33" spans="1:17" ht="12.75" customHeight="1">
       <c r="A33" s="1" t="s">
         <v>25</v>
       </c>
@@ -7725,7 +7737,7 @@
       <c r="P33" s="1"/>
       <c r="Q33" s="1"/>
     </row>
-    <row r="34" ht="12.75" customHeight="1">
+    <row r="34" spans="1:17" ht="12.75" customHeight="1">
       <c r="A34" s="1" t="s">
         <v>54</v>
       </c>
@@ -7748,7 +7760,7 @@
       <c r="P34" s="1"/>
       <c r="Q34" s="1"/>
     </row>
-    <row r="35" ht="12.75" customHeight="1">
+    <row r="35" spans="1:17" ht="12.75" customHeight="1">
       <c r="A35" s="1" t="s">
         <v>54</v>
       </c>
@@ -7771,7 +7783,7 @@
       <c r="P35" s="1"/>
       <c r="Q35" s="1"/>
     </row>
-    <row r="36" ht="12.75" customHeight="1">
+    <row r="36" spans="1:17" ht="12.75" customHeight="1">
       <c r="A36" s="1" t="s">
         <v>61</v>
       </c>
@@ -7796,7 +7808,7 @@
       <c r="P36" s="1"/>
       <c r="Q36" s="1"/>
     </row>
-    <row r="37" ht="12.75" customHeight="1">
+    <row r="37" spans="1:17" ht="12.75" customHeight="1">
       <c r="A37" s="1" t="s">
         <v>61</v>
       </c>
@@ -7821,7 +7833,7 @@
       <c r="P37" s="1"/>
       <c r="Q37" s="1"/>
     </row>
-    <row r="38" ht="12.75" customHeight="1">
+    <row r="38" spans="1:17" ht="12.75" customHeight="1">
       <c r="A38" s="1" t="s">
         <v>61</v>
       </c>
@@ -7846,7 +7858,7 @@
       <c r="P38" s="1"/>
       <c r="Q38" s="1"/>
     </row>
-    <row r="39" ht="12.75" customHeight="1">
+    <row r="39" spans="1:17" ht="12.75" customHeight="1">
       <c r="A39" s="1" t="s">
         <v>61</v>
       </c>
@@ -7871,7 +7883,7 @@
       <c r="P39" s="1"/>
       <c r="Q39" s="1"/>
     </row>
-    <row r="40" ht="12.75" customHeight="1">
+    <row r="40" spans="1:17" ht="12.75" customHeight="1">
       <c r="A40" s="1" t="s">
         <v>61</v>
       </c>
@@ -7896,7 +7908,7 @@
       <c r="P40" s="1"/>
       <c r="Q40" s="1"/>
     </row>
-    <row r="41" ht="12.75" customHeight="1">
+    <row r="41" spans="1:17" ht="12.75" customHeight="1">
       <c r="A41" s="1" t="s">
         <v>61</v>
       </c>
@@ -7921,7 +7933,7 @@
       <c r="P41" s="1"/>
       <c r="Q41" s="1"/>
     </row>
-    <row r="42" ht="12.75" customHeight="1">
+    <row r="42" spans="1:17" ht="12.75" customHeight="1">
       <c r="A42" s="1" t="s">
         <v>61</v>
       </c>
@@ -7946,7 +7958,7 @@
       <c r="P42" s="1"/>
       <c r="Q42" s="1"/>
     </row>
-    <row r="43" ht="12.75" customHeight="1">
+    <row r="43" spans="1:17" ht="12.75" customHeight="1">
       <c r="A43" s="1" t="s">
         <v>61</v>
       </c>
@@ -7971,7 +7983,7 @@
       <c r="P43" s="1"/>
       <c r="Q43" s="1"/>
     </row>
-    <row r="44" ht="12.75" customHeight="1">
+    <row r="44" spans="1:17" ht="12.75" customHeight="1">
       <c r="A44" s="1" t="s">
         <v>61</v>
       </c>
@@ -7996,7 +8008,7 @@
       <c r="P44" s="1"/>
       <c r="Q44" s="1"/>
     </row>
-    <row r="45" ht="12.75" customHeight="1">
+    <row r="45" spans="1:17" ht="12.75" customHeight="1">
       <c r="A45" s="1" t="s">
         <v>61</v>
       </c>
@@ -8021,7 +8033,7 @@
       <c r="P45" s="1"/>
       <c r="Q45" s="1"/>
     </row>
-    <row r="46" ht="12.75" customHeight="1">
+    <row r="46" spans="1:17" ht="12.75" customHeight="1">
       <c r="A46" s="1" t="s">
         <v>61</v>
       </c>
@@ -8046,7 +8058,7 @@
       <c r="P46" s="1"/>
       <c r="Q46" s="1"/>
     </row>
-    <row r="47" ht="12.75" customHeight="1">
+    <row r="47" spans="1:17" ht="12.75" customHeight="1">
       <c r="A47" s="1" t="s">
         <v>61</v>
       </c>
@@ -8071,7 +8083,7 @@
       <c r="P47" s="1"/>
       <c r="Q47" s="1"/>
     </row>
-    <row r="48" ht="12.75" customHeight="1">
+    <row r="48" spans="1:17" ht="12.75" customHeight="1">
       <c r="A48" s="1" t="s">
         <v>61</v>
       </c>
@@ -8096,7 +8108,7 @@
       <c r="P48" s="1"/>
       <c r="Q48" s="1"/>
     </row>
-    <row r="49" ht="12.75" customHeight="1">
+    <row r="49" spans="1:17" ht="12.75" customHeight="1">
       <c r="A49" s="1" t="s">
         <v>61</v>
       </c>
@@ -8121,7 +8133,7 @@
       <c r="P49" s="1"/>
       <c r="Q49" s="1"/>
     </row>
-    <row r="50" ht="12.75" customHeight="1">
+    <row r="50" spans="1:17" ht="12.75" customHeight="1">
       <c r="A50" s="1" t="s">
         <v>61</v>
       </c>
@@ -8146,7 +8158,7 @@
       <c r="P50" s="1"/>
       <c r="Q50" s="1"/>
     </row>
-    <row r="51" ht="12.75" customHeight="1">
+    <row r="51" spans="1:17" ht="12.75" customHeight="1">
       <c r="A51" s="1" t="s">
         <v>61</v>
       </c>
@@ -8171,7 +8183,7 @@
       <c r="P51" s="1"/>
       <c r="Q51" s="1"/>
     </row>
-    <row r="52" ht="12.75" customHeight="1">
+    <row r="52" spans="1:17" ht="12.75" customHeight="1">
       <c r="A52" s="1" t="s">
         <v>61</v>
       </c>
@@ -8196,7 +8208,7 @@
       <c r="P52" s="1"/>
       <c r="Q52" s="1"/>
     </row>
-    <row r="53" ht="12.75" customHeight="1">
+    <row r="53" spans="1:17" ht="12.75" customHeight="1">
       <c r="A53" s="1" t="s">
         <v>61</v>
       </c>
@@ -8221,7 +8233,7 @@
       <c r="P53" s="1"/>
       <c r="Q53" s="1"/>
     </row>
-    <row r="54" ht="12.75" customHeight="1">
+    <row r="54" spans="1:17" ht="12.75" customHeight="1">
       <c r="A54" s="1" t="s">
         <v>61</v>
       </c>
@@ -8246,7 +8258,7 @@
       <c r="P54" s="1"/>
       <c r="Q54" s="1"/>
     </row>
-    <row r="55" ht="12.75" customHeight="1">
+    <row r="55" spans="1:17" ht="12.75" customHeight="1">
       <c r="A55" s="1" t="s">
         <v>61</v>
       </c>
@@ -8271,7 +8283,7 @@
       <c r="P55" s="1"/>
       <c r="Q55" s="1"/>
     </row>
-    <row r="56" ht="12.75" customHeight="1">
+    <row r="56" spans="1:17" ht="12.75" customHeight="1">
       <c r="A56" s="1" t="s">
         <v>61</v>
       </c>
@@ -8296,7 +8308,7 @@
       <c r="P56" s="1"/>
       <c r="Q56" s="1"/>
     </row>
-    <row r="57" ht="12.75" customHeight="1">
+    <row r="57" spans="1:17" ht="12.75" customHeight="1">
       <c r="A57" s="1" t="s">
         <v>61</v>
       </c>
@@ -8321,7 +8333,7 @@
       <c r="P57" s="1"/>
       <c r="Q57" s="1"/>
     </row>
-    <row r="58" ht="12.75" customHeight="1">
+    <row r="58" spans="1:17" ht="12.75" customHeight="1">
       <c r="A58" s="1" t="s">
         <v>61</v>
       </c>
@@ -8346,7 +8358,7 @@
       <c r="P58" s="1"/>
       <c r="Q58" s="1"/>
     </row>
-    <row r="59" ht="12.75" customHeight="1">
+    <row r="59" spans="1:17" ht="12.75" customHeight="1">
       <c r="A59" s="1" t="s">
         <v>61</v>
       </c>
@@ -8371,7 +8383,7 @@
       <c r="P59" s="1"/>
       <c r="Q59" s="1"/>
     </row>
-    <row r="60" ht="12.75" customHeight="1">
+    <row r="60" spans="1:17" ht="12.75" customHeight="1">
       <c r="A60" s="1" t="s">
         <v>61</v>
       </c>
@@ -8396,7 +8408,7 @@
       <c r="P60" s="1"/>
       <c r="Q60" s="1"/>
     </row>
-    <row r="61" ht="12.75" customHeight="1">
+    <row r="61" spans="1:17" ht="12.75" customHeight="1">
       <c r="A61" s="1" t="s">
         <v>61</v>
       </c>
@@ -8421,7 +8433,7 @@
       <c r="P61" s="1"/>
       <c r="Q61" s="1"/>
     </row>
-    <row r="62" ht="12.75" customHeight="1">
+    <row r="62" spans="1:17" ht="12.75" customHeight="1">
       <c r="A62" s="1" t="s">
         <v>61</v>
       </c>
@@ -8446,7 +8458,7 @@
       <c r="P62" s="1"/>
       <c r="Q62" s="1"/>
     </row>
-    <row r="63" ht="12.75" customHeight="1">
+    <row r="63" spans="1:17" ht="12.75" customHeight="1">
       <c r="A63" s="1" t="s">
         <v>61</v>
       </c>
@@ -8471,7 +8483,7 @@
       <c r="P63" s="1"/>
       <c r="Q63" s="1"/>
     </row>
-    <row r="64" ht="12.75" customHeight="1">
+    <row r="64" spans="1:17" ht="12.75" customHeight="1">
       <c r="A64" s="1" t="s">
         <v>61</v>
       </c>
@@ -8496,7 +8508,7 @@
       <c r="P64" s="1"/>
       <c r="Q64" s="1"/>
     </row>
-    <row r="65" ht="12.75" customHeight="1">
+    <row r="65" spans="1:26" ht="12.75" customHeight="1">
       <c r="A65" s="1" t="s">
         <v>61</v>
       </c>
@@ -8521,7 +8533,7 @@
       <c r="P65" s="1"/>
       <c r="Q65" s="1"/>
     </row>
-    <row r="66" ht="12.75" customHeight="1">
+    <row r="66" spans="1:26" ht="12.75" customHeight="1">
       <c r="A66" s="1" t="s">
         <v>61</v>
       </c>
@@ -8538,7 +8550,7 @@
       <c r="J66" s="1"/>
       <c r="K66" s="1"/>
       <c r="L66" s="1">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="M66" s="1"/>
       <c r="N66" s="1"/>
@@ -8546,7 +8558,7 @@
       <c r="P66" s="1"/>
       <c r="Q66" s="1"/>
     </row>
-    <row r="67" ht="12.75" customHeight="1">
+    <row r="67" spans="1:26" ht="12.75" customHeight="1">
       <c r="A67" s="1" t="s">
         <v>61</v>
       </c>
@@ -8563,7 +8575,7 @@
       <c r="J67" s="1"/>
       <c r="K67" s="1"/>
       <c r="L67" s="1">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="M67" s="1"/>
       <c r="N67" s="1"/>
@@ -8571,7 +8583,7 @@
       <c r="P67" s="1"/>
       <c r="Q67" s="1"/>
     </row>
-    <row r="68" ht="12.75" customHeight="1">
+    <row r="68" spans="1:26" ht="12.75" customHeight="1">
       <c r="A68" s="4" t="s">
         <v>61</v>
       </c>
@@ -8605,7 +8617,7 @@
       <c r="Y68" s="4"/>
       <c r="Z68" s="4"/>
     </row>
-    <row r="69" ht="12.75" customHeight="1">
+    <row r="69" spans="1:26" ht="12.75" customHeight="1">
       <c r="A69" s="4" t="s">
         <v>61</v>
       </c>
@@ -8639,7 +8651,7 @@
       <c r="Y69" s="4"/>
       <c r="Z69" s="4"/>
     </row>
-    <row r="70" ht="12.75" customHeight="1">
+    <row r="70" spans="1:26" ht="12.75" customHeight="1">
       <c r="A70" s="4" t="s">
         <v>61</v>
       </c>
@@ -8673,7 +8685,7 @@
       <c r="Y70" s="4"/>
       <c r="Z70" s="4"/>
     </row>
-    <row r="71" ht="12.75" customHeight="1">
+    <row r="71" spans="1:26" ht="12.75" customHeight="1">
       <c r="A71" s="1" t="s">
         <v>61</v>
       </c>
@@ -8707,7 +8719,7 @@
       <c r="Y71" s="4"/>
       <c r="Z71" s="4"/>
     </row>
-    <row r="72" ht="12.75" customHeight="1">
+    <row r="72" spans="1:26" ht="12.75" customHeight="1">
       <c r="A72" s="1" t="s">
         <v>61</v>
       </c>
@@ -8741,7 +8753,7 @@
       <c r="Y72" s="4"/>
       <c r="Z72" s="4"/>
     </row>
-    <row r="73" ht="12.75" customHeight="1">
+    <row r="73" spans="1:26" ht="12.75" customHeight="1">
       <c r="A73" s="1" t="s">
         <v>61</v>
       </c>
@@ -8775,7 +8787,7 @@
       <c r="Y73" s="4"/>
       <c r="Z73" s="4"/>
     </row>
-    <row r="74" ht="12.75" customHeight="1">
+    <row r="74" spans="1:26" ht="12.75" customHeight="1">
       <c r="A74" s="1" t="s">
         <v>61</v>
       </c>
@@ -8809,7 +8821,7 @@
       <c r="Y74" s="4"/>
       <c r="Z74" s="4"/>
     </row>
-    <row r="75" ht="12.75" customHeight="1">
+    <row r="75" spans="1:26" ht="12.75" customHeight="1">
       <c r="A75" s="1" t="s">
         <v>136</v>
       </c>
@@ -8841,7 +8853,7 @@
       <c r="Y75" s="4"/>
       <c r="Z75" s="4"/>
     </row>
-    <row r="76" ht="12.75" customHeight="1">
+    <row r="76" spans="1:26" ht="12.75" customHeight="1">
       <c r="A76" s="1" t="s">
         <v>137</v>
       </c>
@@ -8873,7 +8885,7 @@
       <c r="Y76" s="4"/>
       <c r="Z76" s="4"/>
     </row>
-    <row r="77" ht="12.75" customHeight="1">
+    <row r="77" spans="1:26" ht="12.75" customHeight="1">
       <c r="A77" s="1" t="s">
         <v>138</v>
       </c>
@@ -8900,7 +8912,7 @@
       <c r="P77" s="1"/>
       <c r="Q77" s="1"/>
     </row>
-    <row r="78" ht="12.75" customHeight="1">
+    <row r="78" spans="1:26" ht="12.75" customHeight="1">
       <c r="A78" s="1" t="s">
         <v>142</v>
       </c>
@@ -8927,7 +8939,7 @@
       <c r="P78" s="1"/>
       <c r="Q78" s="1"/>
     </row>
-    <row r="79" ht="12.75" customHeight="1">
+    <row r="79" spans="1:26" ht="12.75" customHeight="1">
       <c r="A79" s="1" t="s">
         <v>146</v>
       </c>
@@ -8950,7 +8962,7 @@
       <c r="P79" s="1"/>
       <c r="Q79" s="1"/>
     </row>
-    <row r="80" ht="12.75" customHeight="1">
+    <row r="80" spans="1:26" ht="12.75" customHeight="1">
       <c r="A80" s="1" t="s">
         <v>21</v>
       </c>
@@ -8979,7 +8991,7 @@
       <c r="P80" s="1"/>
       <c r="Q80" s="1"/>
     </row>
-    <row r="81" ht="12.75" customHeight="1">
+    <row r="81" spans="1:17" ht="12.75" customHeight="1">
       <c r="A81" s="1" t="s">
         <v>142</v>
       </c>
@@ -9006,7 +9018,7 @@
       <c r="P81" s="1"/>
       <c r="Q81" s="1"/>
     </row>
-    <row r="82" ht="12.75" customHeight="1">
+    <row r="82" spans="1:17" ht="12.75" customHeight="1">
       <c r="A82" s="1" t="s">
         <v>142</v>
       </c>
@@ -9033,7 +9045,7 @@
       <c r="P82" s="1"/>
       <c r="Q82" s="1"/>
     </row>
-    <row r="83" ht="12.75" customHeight="1">
+    <row r="83" spans="1:17" ht="12.75" customHeight="1">
       <c r="A83" s="1" t="s">
         <v>142</v>
       </c>
@@ -9060,7 +9072,7 @@
       <c r="P83" s="1"/>
       <c r="Q83" s="1"/>
     </row>
-    <row r="84" ht="12.75" customHeight="1">
+    <row r="84" spans="1:17" ht="12.75" customHeight="1">
       <c r="A84" s="1" t="s">
         <v>142</v>
       </c>
@@ -9087,7 +9099,7 @@
       <c r="P84" s="1"/>
       <c r="Q84" s="1"/>
     </row>
-    <row r="85" ht="12.75" customHeight="1">
+    <row r="85" spans="1:17" ht="12.75" customHeight="1">
       <c r="A85" s="1" t="s">
         <v>54</v>
       </c>
@@ -9110,7 +9122,7 @@
       <c r="P85" s="1"/>
       <c r="Q85" s="1"/>
     </row>
-    <row r="86" ht="12.75" customHeight="1">
+    <row r="86" spans="1:17" ht="12.75" customHeight="1">
       <c r="A86" s="1" t="s">
         <v>21</v>
       </c>
@@ -9141,7 +9153,7 @@
       <c r="P86" s="1"/>
       <c r="Q86" s="1"/>
     </row>
-    <row r="87" ht="12.75" customHeight="1">
+    <row r="87" spans="1:17" ht="12.75" customHeight="1">
       <c r="A87" s="1" t="s">
         <v>142</v>
       </c>
@@ -9171,7 +9183,7 @@
       <c r="P87" s="1"/>
       <c r="Q87" s="1"/>
     </row>
-    <row r="88" ht="12.75" customHeight="1">
+    <row r="88" spans="1:17" ht="12.75" customHeight="1">
       <c r="A88" s="1" t="s">
         <v>170</v>
       </c>
@@ -9200,7 +9212,7 @@
       <c r="P88" s="1"/>
       <c r="Q88" s="1"/>
     </row>
-    <row r="89" ht="12.75" customHeight="1">
+    <row r="89" spans="1:17" ht="12.75" customHeight="1">
       <c r="A89" s="1" t="s">
         <v>54</v>
       </c>
@@ -9223,7 +9235,7 @@
       <c r="P89" s="1"/>
       <c r="Q89" s="1"/>
     </row>
-    <row r="90" ht="12.75" customHeight="1">
+    <row r="90" spans="1:17" ht="12.75" customHeight="1">
       <c r="A90" s="1" t="s">
         <v>142</v>
       </c>
@@ -9252,7 +9264,7 @@
       <c r="P90" s="1"/>
       <c r="Q90" s="1"/>
     </row>
-    <row r="91" ht="12.75" customHeight="1">
+    <row r="91" spans="1:17" ht="12.75" customHeight="1">
       <c r="A91" s="1" t="s">
         <v>21</v>
       </c>
@@ -9283,7 +9295,7 @@
       <c r="P91" s="1"/>
       <c r="Q91" s="1"/>
     </row>
-    <row r="92" ht="12.75" customHeight="1">
+    <row r="92" spans="1:17" ht="12.75" customHeight="1">
       <c r="A92" s="1" t="s">
         <v>183</v>
       </c>
@@ -9312,7 +9324,7 @@
       <c r="P92" s="1"/>
       <c r="Q92" s="1"/>
     </row>
-    <row r="93" ht="12.75" customHeight="1">
+    <row r="93" spans="1:17" ht="12.75" customHeight="1">
       <c r="A93" s="1" t="s">
         <v>170</v>
       </c>
@@ -9341,7 +9353,7 @@
       <c r="P93" s="1"/>
       <c r="Q93" s="1"/>
     </row>
-    <row r="94" ht="12.75" customHeight="1">
+    <row r="94" spans="1:17" ht="12.75" customHeight="1">
       <c r="A94" s="1" t="s">
         <v>170</v>
       </c>
@@ -9372,7 +9384,7 @@
       <c r="P94" s="1"/>
       <c r="Q94" s="1"/>
     </row>
-    <row r="95" ht="12.75" customHeight="1">
+    <row r="95" spans="1:17" ht="12.75" customHeight="1">
       <c r="A95" s="1" t="s">
         <v>194</v>
       </c>
@@ -9413,7 +9425,7 @@
       <c r="P95" s="1"/>
       <c r="Q95" s="1"/>
     </row>
-    <row r="96" ht="12.75" customHeight="1">
+    <row r="96" spans="1:17" ht="12.75" customHeight="1">
       <c r="A96" s="1" t="s">
         <v>204</v>
       </c>
@@ -9444,7 +9456,7 @@
       <c r="P96" s="1"/>
       <c r="Q96" s="1"/>
     </row>
-    <row r="97" ht="12.75" customHeight="1">
+    <row r="97" spans="1:17" ht="12.75" customHeight="1">
       <c r="A97" s="1" t="s">
         <v>142</v>
       </c>
@@ -9473,7 +9485,7 @@
       <c r="P97" s="1"/>
       <c r="Q97" s="1"/>
     </row>
-    <row r="98" ht="12.75" customHeight="1">
+    <row r="98" spans="1:17" ht="12.75" customHeight="1">
       <c r="A98" s="1" t="s">
         <v>61</v>
       </c>
@@ -9498,7 +9510,7 @@
       <c r="P98" s="1"/>
       <c r="Q98" s="1"/>
     </row>
-    <row r="99" ht="12.75" customHeight="1">
+    <row r="99" spans="1:17" ht="12.75" customHeight="1">
       <c r="A99" s="1" t="s">
         <v>142</v>
       </c>
@@ -9527,7 +9539,7 @@
       <c r="P99" s="1"/>
       <c r="Q99" s="1"/>
     </row>
-    <row r="100" ht="12.75" customHeight="1">
+    <row r="100" spans="1:17" ht="12.75" customHeight="1">
       <c r="A100" s="1" t="s">
         <v>170</v>
       </c>
@@ -9558,7 +9570,7 @@
       <c r="P100" s="1"/>
       <c r="Q100" s="1"/>
     </row>
-    <row r="101" ht="12.75" customHeight="1">
+    <row r="101" spans="1:17" ht="12.75" customHeight="1">
       <c r="A101" s="1" t="s">
         <v>142</v>
       </c>
@@ -9587,7 +9599,7 @@
       <c r="P101" s="1"/>
       <c r="Q101" s="1"/>
     </row>
-    <row r="102" ht="12.75" customHeight="1">
+    <row r="102" spans="1:17" ht="12.75" customHeight="1">
       <c r="A102" s="1" t="s">
         <v>61</v>
       </c>
@@ -9612,7 +9624,7 @@
       <c r="P102" s="1"/>
       <c r="Q102" s="1"/>
     </row>
-    <row r="103" ht="12.75" customHeight="1">
+    <row r="103" spans="1:17" ht="12.75" customHeight="1">
       <c r="A103" s="1" t="s">
         <v>142</v>
       </c>
@@ -9641,7 +9653,7 @@
       <c r="P103" s="1"/>
       <c r="Q103" s="1"/>
     </row>
-    <row r="104" ht="12.75" customHeight="1">
+    <row r="104" spans="1:17" ht="12.75" customHeight="1">
       <c r="A104" s="1" t="s">
         <v>54</v>
       </c>
@@ -9664,7 +9676,7 @@
       <c r="P104" s="1"/>
       <c r="Q104" s="1"/>
     </row>
-    <row r="105" ht="12.75" customHeight="1">
+    <row r="105" spans="1:17" ht="12.75" customHeight="1">
       <c r="A105" s="1" t="s">
         <v>21</v>
       </c>
@@ -9695,7 +9707,7 @@
       <c r="P105" s="1"/>
       <c r="Q105" s="1"/>
     </row>
-    <row r="106" ht="12.75" customHeight="1">
+    <row r="106" spans="1:17" ht="12.75" customHeight="1">
       <c r="A106" s="1" t="s">
         <v>142</v>
       </c>
@@ -9722,7 +9734,7 @@
       <c r="P106" s="1"/>
       <c r="Q106" s="1"/>
     </row>
-    <row r="107" ht="12.75" customHeight="1">
+    <row r="107" spans="1:17" ht="12.75" customHeight="1">
       <c r="A107" s="1" t="s">
         <v>142</v>
       </c>
@@ -9749,7 +9761,7 @@
       <c r="P107" s="1"/>
       <c r="Q107" s="1"/>
     </row>
-    <row r="108" ht="12.75" customHeight="1">
+    <row r="108" spans="1:17" ht="12.75" customHeight="1">
       <c r="A108" s="1" t="s">
         <v>142</v>
       </c>
@@ -9776,7 +9788,7 @@
       <c r="P108" s="1"/>
       <c r="Q108" s="1"/>
     </row>
-    <row r="109" ht="12.75" customHeight="1">
+    <row r="109" spans="1:17" ht="12.75" customHeight="1">
       <c r="A109" s="1" t="s">
         <v>170</v>
       </c>
@@ -9805,7 +9817,7 @@
       <c r="P109" s="1"/>
       <c r="Q109" s="1"/>
     </row>
-    <row r="110" ht="12.75" customHeight="1">
+    <row r="110" spans="1:17" ht="12.75" customHeight="1">
       <c r="A110" s="1" t="s">
         <v>170</v>
       </c>
@@ -9834,7 +9846,7 @@
       <c r="P110" s="1"/>
       <c r="Q110" s="1"/>
     </row>
-    <row r="111" ht="12.75" customHeight="1">
+    <row r="111" spans="1:17" ht="12.75" customHeight="1">
       <c r="A111" s="1" t="s">
         <v>170</v>
       </c>
@@ -9863,7 +9875,7 @@
       <c r="P111" s="1"/>
       <c r="Q111" s="1"/>
     </row>
-    <row r="112" ht="12.75" customHeight="1">
+    <row r="112" spans="1:17" ht="12.75" customHeight="1">
       <c r="A112" s="1" t="s">
         <v>170</v>
       </c>
@@ -9892,7 +9904,7 @@
       <c r="P112" s="1"/>
       <c r="Q112" s="1"/>
     </row>
-    <row r="113" ht="12.75" customHeight="1">
+    <row r="113" spans="1:17" ht="12.75" customHeight="1">
       <c r="A113" s="1" t="s">
         <v>170</v>
       </c>
@@ -9921,7 +9933,7 @@
       <c r="P113" s="1"/>
       <c r="Q113" s="1"/>
     </row>
-    <row r="114" ht="12.75" customHeight="1">
+    <row r="114" spans="1:17" ht="12.75" customHeight="1">
       <c r="A114" s="1" t="s">
         <v>170</v>
       </c>
@@ -9950,7 +9962,7 @@
       <c r="P114" s="1"/>
       <c r="Q114" s="1"/>
     </row>
-    <row r="115" ht="12.75" customHeight="1">
+    <row r="115" spans="1:17" ht="12.75" customHeight="1">
       <c r="A115" s="1" t="s">
         <v>170</v>
       </c>
@@ -9979,7 +9991,7 @@
       <c r="P115" s="1"/>
       <c r="Q115" s="1"/>
     </row>
-    <row r="116" ht="12.75" customHeight="1">
+    <row r="116" spans="1:17" ht="12.75" customHeight="1">
       <c r="A116" s="1" t="s">
         <v>170</v>
       </c>
@@ -10008,7 +10020,7 @@
       <c r="P116" s="1"/>
       <c r="Q116" s="1"/>
     </row>
-    <row r="117" ht="12.75" customHeight="1">
+    <row r="117" spans="1:17" ht="12.75" customHeight="1">
       <c r="A117" s="1" t="s">
         <v>170</v>
       </c>
@@ -10037,7 +10049,7 @@
       <c r="P117" s="1"/>
       <c r="Q117" s="1"/>
     </row>
-    <row r="118" ht="12.75" customHeight="1">
+    <row r="118" spans="1:17" ht="12.75" customHeight="1">
       <c r="A118" s="1" t="s">
         <v>170</v>
       </c>
@@ -10066,7 +10078,7 @@
       <c r="P118" s="1"/>
       <c r="Q118" s="1"/>
     </row>
-    <row r="119" ht="12.75" customHeight="1">
+    <row r="119" spans="1:17" ht="12.75" customHeight="1">
       <c r="A119" s="1" t="s">
         <v>170</v>
       </c>
@@ -10095,7 +10107,7 @@
       <c r="P119" s="1"/>
       <c r="Q119" s="1"/>
     </row>
-    <row r="120" ht="12.75" customHeight="1">
+    <row r="120" spans="1:17" ht="12.75" customHeight="1">
       <c r="A120" s="1" t="s">
         <v>61</v>
       </c>
@@ -10120,7 +10132,7 @@
       <c r="P120" s="1"/>
       <c r="Q120" s="1"/>
     </row>
-    <row r="121" ht="12.75" customHeight="1">
+    <row r="121" spans="1:17" ht="12.75" customHeight="1">
       <c r="A121" s="1" t="s">
         <v>142</v>
       </c>
@@ -10149,7 +10161,7 @@
       <c r="P121" s="1"/>
       <c r="Q121" s="1"/>
     </row>
-    <row r="122" ht="12.75" customHeight="1">
+    <row r="122" spans="1:17" ht="12.75" customHeight="1">
       <c r="A122" s="1" t="s">
         <v>54</v>
       </c>
@@ -10172,7 +10184,7 @@
       <c r="P122" s="1"/>
       <c r="Q122" s="1"/>
     </row>
-    <row r="123" ht="12.75" customHeight="1">
+    <row r="123" spans="1:17" ht="12.75" customHeight="1">
       <c r="A123" s="1" t="s">
         <v>21</v>
       </c>
@@ -10203,7 +10215,7 @@
       <c r="P123" s="1"/>
       <c r="Q123" s="1"/>
     </row>
-    <row r="124" ht="12.75" customHeight="1">
+    <row r="124" spans="1:17" ht="12.75" customHeight="1">
       <c r="A124" s="1" t="s">
         <v>170</v>
       </c>
@@ -10232,7 +10244,7 @@
       <c r="P124" s="1"/>
       <c r="Q124" s="1"/>
     </row>
-    <row r="125" ht="12.75" customHeight="1">
+    <row r="125" spans="1:17" ht="12.75" customHeight="1">
       <c r="A125" s="1" t="s">
         <v>170</v>
       </c>
@@ -10261,7 +10273,7 @@
       <c r="P125" s="1"/>
       <c r="Q125" s="1"/>
     </row>
-    <row r="126" ht="12.75" customHeight="1">
+    <row r="126" spans="1:17" ht="12.75" customHeight="1">
       <c r="A126" s="1" t="s">
         <v>170</v>
       </c>
@@ -10290,7 +10302,7 @@
       <c r="P126" s="1"/>
       <c r="Q126" s="1"/>
     </row>
-    <row r="127" ht="12.75" customHeight="1">
+    <row r="127" spans="1:17" ht="12.75" customHeight="1">
       <c r="A127" s="1" t="s">
         <v>170</v>
       </c>
@@ -10319,7 +10331,7 @@
       <c r="P127" s="1"/>
       <c r="Q127" s="1"/>
     </row>
-    <row r="128" ht="12.75" customHeight="1">
+    <row r="128" spans="1:17" ht="12.75" customHeight="1">
       <c r="A128" s="1" t="s">
         <v>170</v>
       </c>
@@ -10348,7 +10360,7 @@
       <c r="P128" s="1"/>
       <c r="Q128" s="1"/>
     </row>
-    <row r="129" ht="12.75" customHeight="1">
+    <row r="129" spans="1:17" ht="12.75" customHeight="1">
       <c r="A129" s="1" t="s">
         <v>170</v>
       </c>
@@ -10377,7 +10389,7 @@
       <c r="P129" s="1"/>
       <c r="Q129" s="1"/>
     </row>
-    <row r="130" ht="12.75" customHeight="1">
+    <row r="130" spans="1:17" ht="12.75" customHeight="1">
       <c r="A130" s="1" t="s">
         <v>170</v>
       </c>
@@ -10406,7 +10418,7 @@
       <c r="P130" s="1"/>
       <c r="Q130" s="1"/>
     </row>
-    <row r="131" ht="12.75" customHeight="1">
+    <row r="131" spans="1:17" ht="12.75" customHeight="1">
       <c r="A131" s="1" t="s">
         <v>170</v>
       </c>
@@ -10435,7 +10447,7 @@
       <c r="P131" s="1"/>
       <c r="Q131" s="1"/>
     </row>
-    <row r="132" ht="12.75" customHeight="1">
+    <row r="132" spans="1:17" ht="12.75" customHeight="1">
       <c r="A132" s="1" t="s">
         <v>170</v>
       </c>
@@ -10464,7 +10476,7 @@
       <c r="P132" s="1"/>
       <c r="Q132" s="1"/>
     </row>
-    <row r="133" ht="12.75" customHeight="1">
+    <row r="133" spans="1:17" ht="12.75" customHeight="1">
       <c r="A133" s="1" t="s">
         <v>170</v>
       </c>
@@ -10493,7 +10505,7 @@
       <c r="P133" s="1"/>
       <c r="Q133" s="1"/>
     </row>
-    <row r="134" ht="12.75" customHeight="1">
+    <row r="134" spans="1:17" ht="12.75" customHeight="1">
       <c r="A134" s="1" t="s">
         <v>170</v>
       </c>
@@ -10522,7 +10534,7 @@
       <c r="P134" s="1"/>
       <c r="Q134" s="1"/>
     </row>
-    <row r="135" ht="12.75" customHeight="1">
+    <row r="135" spans="1:17" ht="12.75" customHeight="1">
       <c r="A135" s="1" t="s">
         <v>170</v>
       </c>
@@ -10551,7 +10563,7 @@
       <c r="P135" s="1"/>
       <c r="Q135" s="1"/>
     </row>
-    <row r="136" ht="12.75" customHeight="1">
+    <row r="136" spans="1:17" ht="12.75" customHeight="1">
       <c r="A136" s="1" t="s">
         <v>170</v>
       </c>
@@ -10580,7 +10592,7 @@
       <c r="P136" s="1"/>
       <c r="Q136" s="1"/>
     </row>
-    <row r="137" ht="12.75" customHeight="1">
+    <row r="137" spans="1:17" ht="12.75" customHeight="1">
       <c r="A137" s="1" t="s">
         <v>61</v>
       </c>
@@ -10605,7 +10617,7 @@
       <c r="P137" s="1"/>
       <c r="Q137" s="1"/>
     </row>
-    <row r="138" ht="12.75" customHeight="1">
+    <row r="138" spans="1:17" ht="12.75" customHeight="1">
       <c r="A138" s="1" t="s">
         <v>142</v>
       </c>
@@ -10634,7 +10646,7 @@
       <c r="P138" s="1"/>
       <c r="Q138" s="1"/>
     </row>
-    <row r="139" ht="12.75" customHeight="1">
+    <row r="139" spans="1:17" ht="12.75" customHeight="1">
       <c r="A139" s="1" t="s">
         <v>142</v>
       </c>
@@ -10663,7 +10675,7 @@
       <c r="P139" s="1"/>
       <c r="Q139" s="1"/>
     </row>
-    <row r="140" ht="12.75" customHeight="1">
+    <row r="140" spans="1:17" ht="12.75" customHeight="1">
       <c r="A140" s="1" t="s">
         <v>54</v>
       </c>
@@ -10686,7 +10698,7 @@
       <c r="P140" s="1"/>
       <c r="Q140" s="1"/>
     </row>
-    <row r="141" ht="12.75" customHeight="1">
+    <row r="141" spans="1:17" ht="12.75" customHeight="1">
       <c r="A141" s="1" t="s">
         <v>21</v>
       </c>
@@ -10717,7 +10729,7 @@
       <c r="P141" s="1"/>
       <c r="Q141" s="1"/>
     </row>
-    <row r="142" ht="12.75" customHeight="1">
+    <row r="142" spans="1:17" ht="12.75" customHeight="1">
       <c r="A142" s="1" t="s">
         <v>142</v>
       </c>
@@ -10744,7 +10756,7 @@
       <c r="P142" s="1"/>
       <c r="Q142" s="1"/>
     </row>
-    <row r="143" ht="12.75" customHeight="1">
+    <row r="143" spans="1:17" ht="12.75" customHeight="1">
       <c r="A143" s="1" t="s">
         <v>142</v>
       </c>
@@ -10771,7 +10783,7 @@
       <c r="P143" s="1"/>
       <c r="Q143" s="1"/>
     </row>
-    <row r="144" ht="12.75" customHeight="1">
+    <row r="144" spans="1:17" ht="12.75" customHeight="1">
       <c r="A144" s="1" t="s">
         <v>170</v>
       </c>
@@ -10800,7 +10812,7 @@
       <c r="P144" s="1"/>
       <c r="Q144" s="1"/>
     </row>
-    <row r="145" ht="12.75" customHeight="1">
+    <row r="145" spans="1:26" ht="12.75" customHeight="1">
       <c r="A145" s="1" t="s">
         <v>170</v>
       </c>
@@ -10829,7 +10841,7 @@
       <c r="P145" s="1"/>
       <c r="Q145" s="1"/>
     </row>
-    <row r="146" ht="12.75" customHeight="1">
+    <row r="146" spans="1:26" ht="12.75" customHeight="1">
       <c r="A146" s="1" t="s">
         <v>170</v>
       </c>
@@ -10858,7 +10870,7 @@
       <c r="P146" s="1"/>
       <c r="Q146" s="1"/>
     </row>
-    <row r="147" ht="12.75" customHeight="1">
+    <row r="147" spans="1:26" ht="12.75" customHeight="1">
       <c r="A147" s="1" t="s">
         <v>170</v>
       </c>
@@ -10887,7 +10899,7 @@
       <c r="P147" s="1"/>
       <c r="Q147" s="1"/>
     </row>
-    <row r="148" ht="12.75" customHeight="1">
+    <row r="148" spans="1:26" ht="12.75" customHeight="1">
       <c r="A148" s="1" t="s">
         <v>170</v>
       </c>
@@ -10916,7 +10928,7 @@
       <c r="P148" s="1"/>
       <c r="Q148" s="1"/>
     </row>
-    <row r="149" ht="12.75" customHeight="1">
+    <row r="149" spans="1:26" ht="12.75" customHeight="1">
       <c r="A149" s="1" t="s">
         <v>170</v>
       </c>
@@ -10945,7 +10957,7 @@
       <c r="P149" s="1"/>
       <c r="Q149" s="1"/>
     </row>
-    <row r="150" ht="12.75" customHeight="1">
+    <row r="150" spans="1:26" ht="12.75" customHeight="1">
       <c r="A150" s="1" t="s">
         <v>61</v>
       </c>
@@ -10970,7 +10982,7 @@
       <c r="P150" s="1"/>
       <c r="Q150" s="1"/>
     </row>
-    <row r="151" ht="12.75" customHeight="1">
+    <row r="151" spans="1:26" ht="12.75" customHeight="1">
       <c r="A151" s="1" t="s">
         <v>142</v>
       </c>
@@ -10999,7 +11011,7 @@
       <c r="P151" s="1"/>
       <c r="Q151" s="1"/>
     </row>
-    <row r="152" ht="12.75" customHeight="1">
+    <row r="152" spans="1:26" ht="12.75" customHeight="1">
       <c r="A152" s="1" t="s">
         <v>54</v>
       </c>
@@ -11022,7 +11034,7 @@
       <c r="P152" s="1"/>
       <c r="Q152" s="1"/>
     </row>
-    <row r="153" ht="12.75" customHeight="1">
+    <row r="153" spans="1:26" ht="12.75" customHeight="1">
       <c r="A153" s="1" t="s">
         <v>21</v>
       </c>
@@ -11053,7 +11065,7 @@
       <c r="P153" s="1"/>
       <c r="Q153" s="1"/>
     </row>
-    <row r="154" ht="12.75" customHeight="1">
+    <row r="154" spans="1:26" ht="12.75" customHeight="1">
       <c r="A154" s="1" t="s">
         <v>170</v>
       </c>
@@ -11084,7 +11096,7 @@
       <c r="P154" s="1"/>
       <c r="Q154" s="1"/>
     </row>
-    <row r="155" ht="12.75" customHeight="1">
+    <row r="155" spans="1:26" ht="12.75" customHeight="1">
       <c r="A155" s="1" t="s">
         <v>170</v>
       </c>
@@ -11115,7 +11127,7 @@
       <c r="P155" s="1"/>
       <c r="Q155" s="1"/>
     </row>
-    <row r="156" ht="12.75" customHeight="1">
+    <row r="156" spans="1:26" ht="12.75" customHeight="1">
       <c r="A156" s="1" t="s">
         <v>170</v>
       </c>
@@ -11146,7 +11158,7 @@
       <c r="P156" s="1"/>
       <c r="Q156" s="1"/>
     </row>
-    <row r="157" ht="12.75" customHeight="1">
+    <row r="157" spans="1:26" ht="12.75" customHeight="1">
       <c r="A157" s="1" t="s">
         <v>170</v>
       </c>
@@ -11175,7 +11187,7 @@
       <c r="P157" s="1"/>
       <c r="Q157" s="1"/>
     </row>
-    <row r="158" ht="12.75" customHeight="1">
+    <row r="158" spans="1:26" ht="12.75" customHeight="1">
       <c r="A158" s="1" t="s">
         <v>170</v>
       </c>
@@ -11213,7 +11225,7 @@
       <c r="Y158" s="1"/>
       <c r="Z158" s="1"/>
     </row>
-    <row r="159" ht="12.75" customHeight="1">
+    <row r="159" spans="1:26" ht="12.75" customHeight="1">
       <c r="A159" s="1" t="s">
         <v>170</v>
       </c>
@@ -11242,7 +11254,7 @@
       <c r="P159" s="1"/>
       <c r="Q159" s="1"/>
     </row>
-    <row r="160" ht="12.75" customHeight="1">
+    <row r="160" spans="1:26" ht="12.75" customHeight="1">
       <c r="A160" s="1" t="s">
         <v>170</v>
       </c>
@@ -11271,7 +11283,7 @@
       <c r="P160" s="1"/>
       <c r="Q160" s="1"/>
     </row>
-    <row r="161" ht="12.75" customHeight="1">
+    <row r="161" spans="1:17" ht="12.75" customHeight="1">
       <c r="A161" s="1" t="s">
         <v>61</v>
       </c>
@@ -11296,7 +11308,7 @@
       <c r="P161" s="1"/>
       <c r="Q161" s="1"/>
     </row>
-    <row r="162" ht="12.75" customHeight="1">
+    <row r="162" spans="1:17" ht="12.75" customHeight="1">
       <c r="A162" s="1" t="s">
         <v>142</v>
       </c>
@@ -11325,7 +11337,7 @@
       <c r="P162" s="1"/>
       <c r="Q162" s="1"/>
     </row>
-    <row r="163" ht="12.75" customHeight="1">
+    <row r="163" spans="1:17" ht="12.75" customHeight="1">
       <c r="A163" s="1" t="s">
         <v>142</v>
       </c>
@@ -11354,7 +11366,7 @@
       <c r="P163" s="1"/>
       <c r="Q163" s="1"/>
     </row>
-    <row r="164" ht="12.75" customHeight="1">
+    <row r="164" spans="1:17" ht="12.75" customHeight="1">
       <c r="A164" s="1" t="s">
         <v>54</v>
       </c>
@@ -11377,7 +11389,7 @@
       <c r="P164" s="1"/>
       <c r="Q164" s="1"/>
     </row>
-    <row r="165" ht="12.75" customHeight="1">
+    <row r="165" spans="1:17" ht="12.75" customHeight="1">
       <c r="A165" s="1" t="s">
         <v>21</v>
       </c>
@@ -11408,7 +11420,7 @@
       <c r="P165" s="1"/>
       <c r="Q165" s="1"/>
     </row>
-    <row r="166" ht="12.75" customHeight="1">
+    <row r="166" spans="1:17" ht="12.75" customHeight="1">
       <c r="A166" s="1" t="s">
         <v>142</v>
       </c>
@@ -11437,7 +11449,7 @@
       <c r="P166" s="1"/>
       <c r="Q166" s="1"/>
     </row>
-    <row r="167" ht="12.75" customHeight="1">
+    <row r="167" spans="1:17" ht="12.75" customHeight="1">
       <c r="A167" s="1" t="s">
         <v>410</v>
       </c>
@@ -11468,7 +11480,7 @@
       <c r="P167" s="1"/>
       <c r="Q167" s="1"/>
     </row>
-    <row r="168" ht="12.75" customHeight="1">
+    <row r="168" spans="1:17" ht="12.75" customHeight="1">
       <c r="A168" s="1" t="s">
         <v>142</v>
       </c>
@@ -11497,7 +11509,7 @@
       <c r="P168" s="1"/>
       <c r="Q168" s="1"/>
     </row>
-    <row r="169" ht="12.75" customHeight="1">
+    <row r="169" spans="1:17" ht="12.75" customHeight="1">
       <c r="A169" s="1" t="s">
         <v>418</v>
       </c>
@@ -11528,7 +11540,7 @@
       <c r="P169" s="1"/>
       <c r="Q169" s="1"/>
     </row>
-    <row r="170" ht="12.75" customHeight="1">
+    <row r="170" spans="1:17" ht="12.75" customHeight="1">
       <c r="A170" s="1" t="s">
         <v>142</v>
       </c>
@@ -11557,7 +11569,7 @@
       <c r="P170" s="1"/>
       <c r="Q170" s="1"/>
     </row>
-    <row r="171" ht="12.75" customHeight="1">
+    <row r="171" spans="1:17" ht="12.75" customHeight="1">
       <c r="A171" s="1" t="s">
         <v>142</v>
       </c>
@@ -11586,7 +11598,7 @@
       <c r="P171" s="1"/>
       <c r="Q171" s="1"/>
     </row>
-    <row r="172" ht="12.75" customHeight="1">
+    <row r="172" spans="1:17" ht="12.75" customHeight="1">
       <c r="A172" s="1" t="s">
         <v>142</v>
       </c>
@@ -11615,7 +11627,7 @@
       <c r="P172" s="1"/>
       <c r="Q172" s="1"/>
     </row>
-    <row r="173" ht="12.75" customHeight="1">
+    <row r="173" spans="1:17" ht="12.75" customHeight="1">
       <c r="A173" s="1" t="s">
         <v>61</v>
       </c>
@@ -11640,7 +11652,7 @@
       <c r="P173" s="1"/>
       <c r="Q173" s="1"/>
     </row>
-    <row r="174" ht="12.75" customHeight="1">
+    <row r="174" spans="1:17" ht="12.75" customHeight="1">
       <c r="A174" s="1" t="s">
         <v>142</v>
       </c>
@@ -11669,7 +11681,7 @@
       <c r="P174" s="1"/>
       <c r="Q174" s="1"/>
     </row>
-    <row r="175" ht="12.75" customHeight="1">
+    <row r="175" spans="1:17" ht="12.75" customHeight="1">
       <c r="A175" s="1" t="s">
         <v>441</v>
       </c>
@@ -11700,7 +11712,7 @@
       <c r="P175" s="1"/>
       <c r="Q175" s="1"/>
     </row>
-    <row r="176" ht="12.75" customHeight="1">
+    <row r="176" spans="1:17" ht="12.75" customHeight="1">
       <c r="A176" s="1" t="s">
         <v>142</v>
       </c>
@@ -11729,7 +11741,7 @@
       <c r="P176" s="1"/>
       <c r="Q176" s="1"/>
     </row>
-    <row r="177" ht="12.75" customHeight="1">
+    <row r="177" spans="1:26" ht="12.75" customHeight="1">
       <c r="A177" s="1" t="s">
         <v>61</v>
       </c>
@@ -11754,7 +11766,7 @@
       <c r="P177" s="1"/>
       <c r="Q177" s="1"/>
     </row>
-    <row r="178" ht="12.75" customHeight="1">
+    <row r="178" spans="1:26" ht="12.75" customHeight="1">
       <c r="A178" s="1" t="s">
         <v>451</v>
       </c>
@@ -11785,7 +11797,7 @@
       <c r="P178" s="1"/>
       <c r="Q178" s="1"/>
     </row>
-    <row r="179" ht="12.75" customHeight="1">
+    <row r="179" spans="1:26" ht="12.75" customHeight="1">
       <c r="A179" s="1" t="s">
         <v>61</v>
       </c>
@@ -11810,7 +11822,7 @@
       <c r="P179" s="1"/>
       <c r="Q179" s="1"/>
     </row>
-    <row r="180" ht="12.75" customHeight="1">
+    <row r="180" spans="1:26" ht="12.75" customHeight="1">
       <c r="A180" s="1" t="s">
         <v>61</v>
       </c>
@@ -11835,7 +11847,7 @@
       <c r="P180" s="1"/>
       <c r="Q180" s="1"/>
     </row>
-    <row r="181" ht="12.75" customHeight="1">
+    <row r="181" spans="1:26" ht="12.75" customHeight="1">
       <c r="A181" s="1" t="s">
         <v>460</v>
       </c>
@@ -11866,7 +11878,7 @@
       <c r="P181" s="1"/>
       <c r="Q181" s="1"/>
     </row>
-    <row r="182" ht="12.75" customHeight="1">
+    <row r="182" spans="1:26" ht="12.75" customHeight="1">
       <c r="A182" s="1" t="s">
         <v>54</v>
       </c>
@@ -11889,7 +11901,7 @@
       <c r="P182" s="1"/>
       <c r="Q182" s="1"/>
     </row>
-    <row r="183" ht="12.75" customHeight="1">
+    <row r="183" spans="1:26" ht="12.75" customHeight="1">
       <c r="A183" s="1" t="s">
         <v>61</v>
       </c>
@@ -11914,7 +11926,7 @@
       <c r="P183" s="1"/>
       <c r="Q183" s="1"/>
     </row>
-    <row r="184" ht="12.75" customHeight="1">
+    <row r="184" spans="1:26" ht="12.75" customHeight="1">
       <c r="A184" s="1" t="s">
         <v>21</v>
       </c>
@@ -11950,7 +11962,7 @@
       <c r="Y184" s="4"/>
       <c r="Z184" s="4"/>
     </row>
-    <row r="185" ht="36.0" customHeight="1">
+    <row r="185" spans="1:26" ht="36" customHeight="1">
       <c r="A185" s="1" t="s">
         <v>21</v>
       </c>
@@ -11976,7 +11988,7 @@
       <c r="P185" s="1"/>
       <c r="Q185" s="1"/>
     </row>
-    <row r="186" ht="36.0" customHeight="1">
+    <row r="186" spans="1:26" ht="36" customHeight="1">
       <c r="A186" s="1" t="s">
         <v>142</v>
       </c>
@@ -12003,7 +12015,7 @@
       <c r="P186" s="1"/>
       <c r="Q186" s="1"/>
     </row>
-    <row r="187" ht="36.0" customHeight="1">
+    <row r="187" spans="1:26" ht="36" customHeight="1">
       <c r="A187" s="1" t="s">
         <v>146</v>
       </c>
@@ -12026,7 +12038,7 @@
       <c r="P187" s="1"/>
       <c r="Q187" s="1"/>
     </row>
-    <row r="188" ht="36.0" customHeight="1">
+    <row r="188" spans="1:26" ht="36" customHeight="1">
       <c r="A188" s="1" t="s">
         <v>138</v>
       </c>
@@ -12053,7 +12065,7 @@
       <c r="P188" s="1"/>
       <c r="Q188" s="1"/>
     </row>
-    <row r="189" ht="36.0" customHeight="1">
+    <row r="189" spans="1:26" ht="36" customHeight="1">
       <c r="A189" s="1" t="s">
         <v>142</v>
       </c>
@@ -12078,7 +12090,7 @@
       <c r="P189" s="1"/>
       <c r="Q189" s="1"/>
     </row>
-    <row r="190" ht="36.0" customHeight="1">
+    <row r="190" spans="1:26" ht="36" customHeight="1">
       <c r="A190" s="1" t="s">
         <v>142</v>
       </c>
@@ -12103,7 +12115,7 @@
       <c r="P190" s="1"/>
       <c r="Q190" s="1"/>
     </row>
-    <row r="191" ht="36.0" customHeight="1">
+    <row r="191" spans="1:26" ht="36" customHeight="1">
       <c r="A191" s="1" t="s">
         <v>54</v>
       </c>
@@ -12126,7 +12138,7 @@
       <c r="P191" s="1"/>
       <c r="Q191" s="1"/>
     </row>
-    <row r="192" ht="36.0" customHeight="1">
+    <row r="192" spans="1:26" ht="36" customHeight="1">
       <c r="A192" s="1" t="s">
         <v>138</v>
       </c>
@@ -12153,7 +12165,7 @@
       <c r="P192" s="1"/>
       <c r="Q192" s="1"/>
     </row>
-    <row r="193" ht="36.0" customHeight="1">
+    <row r="193" spans="1:19" ht="36" customHeight="1">
       <c r="A193" s="1" t="s">
         <v>142</v>
       </c>
@@ -12180,7 +12192,7 @@
       <c r="P193" s="1"/>
       <c r="Q193" s="1"/>
     </row>
-    <row r="194" ht="36.0" customHeight="1">
+    <row r="194" spans="1:19" ht="36" customHeight="1">
       <c r="A194" s="1" t="s">
         <v>146</v>
       </c>
@@ -12203,7 +12215,7 @@
       <c r="P194" s="1"/>
       <c r="Q194" s="1"/>
     </row>
-    <row r="195" ht="36.0" customHeight="1">
+    <row r="195" spans="1:19" ht="36" customHeight="1">
       <c r="A195" s="1" t="s">
         <v>21</v>
       </c>
@@ -12230,7 +12242,7 @@
       <c r="P195" s="1"/>
       <c r="Q195" s="1"/>
     </row>
-    <row r="196" ht="36.0" customHeight="1">
+    <row r="196" spans="1:19" ht="36" customHeight="1">
       <c r="A196" s="1" t="s">
         <v>142</v>
       </c>
@@ -12255,7 +12267,7 @@
       <c r="P196" s="1"/>
       <c r="Q196" s="1"/>
     </row>
-    <row r="197" ht="36.0" customHeight="1">
+    <row r="197" spans="1:19" ht="36" customHeight="1">
       <c r="A197" s="1" t="s">
         <v>486</v>
       </c>
@@ -12282,7 +12294,7 @@
       <c r="P197" s="1"/>
       <c r="Q197" s="1"/>
     </row>
-    <row r="198" ht="36.0" customHeight="1">
+    <row r="198" spans="1:19" ht="36" customHeight="1">
       <c r="A198" s="1" t="s">
         <v>54</v>
       </c>
@@ -12305,7 +12317,7 @@
       <c r="P198" s="1"/>
       <c r="Q198" s="1"/>
     </row>
-    <row r="199" ht="36.0" customHeight="1">
+    <row r="199" spans="1:19" ht="36" customHeight="1">
       <c r="A199" s="1" t="s">
         <v>21</v>
       </c>
@@ -12334,7 +12346,7 @@
       <c r="P199" s="1"/>
       <c r="Q199" s="1"/>
     </row>
-    <row r="200" ht="36.0" customHeight="1">
+    <row r="200" spans="1:19" ht="36" customHeight="1">
       <c r="A200" s="1" t="s">
         <v>142</v>
       </c>
@@ -12359,7 +12371,7 @@
       <c r="P200" s="1"/>
       <c r="Q200" s="1"/>
     </row>
-    <row r="201" ht="36.0" customHeight="1">
+    <row r="201" spans="1:19" ht="36" customHeight="1">
       <c r="A201" s="1" t="s">
         <v>170</v>
       </c>
@@ -12386,7 +12398,7 @@
       <c r="P201" s="1"/>
       <c r="Q201" s="1"/>
     </row>
-    <row r="202" ht="36.0" customHeight="1">
+    <row r="202" spans="1:19" ht="36" customHeight="1">
       <c r="A202" s="1" t="s">
         <v>142</v>
       </c>
@@ -12411,7 +12423,7 @@
       <c r="P202" s="1"/>
       <c r="Q202" s="1"/>
     </row>
-    <row r="203" ht="36.0" customHeight="1">
+    <row r="203" spans="1:19" ht="36" customHeight="1">
       <c r="A203" s="1" t="s">
         <v>142</v>
       </c>
@@ -12436,7 +12448,7 @@
       <c r="P203" s="1"/>
       <c r="Q203" s="1"/>
     </row>
-    <row r="204" ht="36.0" customHeight="1">
+    <row r="204" spans="1:19" ht="36" customHeight="1">
       <c r="A204" s="1" t="s">
         <v>142</v>
       </c>
@@ -12461,7 +12473,7 @@
       <c r="P204" s="1"/>
       <c r="Q204" s="1"/>
     </row>
-    <row r="205" ht="36.0" customHeight="1">
+    <row r="205" spans="1:19" ht="36" customHeight="1">
       <c r="A205" s="1" t="s">
         <v>142</v>
       </c>
@@ -12490,7 +12502,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="206" ht="36.0" customHeight="1">
+    <row r="206" spans="1:19" ht="36" customHeight="1">
       <c r="A206" s="1" t="s">
         <v>54</v>
       </c>
@@ -12513,7 +12525,7 @@
       <c r="P206" s="1"/>
       <c r="Q206" s="1"/>
     </row>
-    <row r="207" ht="36.0" customHeight="1">
+    <row r="207" spans="1:19" ht="36" customHeight="1">
       <c r="A207" s="1" t="s">
         <v>21</v>
       </c>
@@ -12542,7 +12554,7 @@
       <c r="P207" s="1"/>
       <c r="Q207" s="1"/>
     </row>
-    <row r="208" ht="36.0" customHeight="1">
+    <row r="208" spans="1:19" ht="36" customHeight="1">
       <c r="A208" s="1" t="s">
         <v>142</v>
       </c>
@@ -12567,7 +12579,7 @@
       <c r="P208" s="1"/>
       <c r="Q208" s="1"/>
     </row>
-    <row r="209" ht="36.0" customHeight="1">
+    <row r="209" spans="1:21" ht="36" customHeight="1">
       <c r="A209" s="1" t="s">
         <v>142</v>
       </c>
@@ -12598,7 +12610,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="210" ht="36.0" customHeight="1">
+    <row r="210" spans="1:21" ht="36" customHeight="1">
       <c r="A210" s="1" t="s">
         <v>54</v>
       </c>
@@ -12621,7 +12633,7 @@
       <c r="P210" s="1"/>
       <c r="Q210" s="1"/>
     </row>
-    <row r="211" ht="36.0" customHeight="1">
+    <row r="211" spans="1:21" ht="36" customHeight="1">
       <c r="A211" s="1" t="s">
         <v>21</v>
       </c>
@@ -12650,7 +12662,7 @@
       <c r="P211" s="1"/>
       <c r="Q211" s="1"/>
     </row>
-    <row r="212" ht="36.0" customHeight="1">
+    <row r="212" spans="1:21" ht="36" customHeight="1">
       <c r="A212" s="1" t="s">
         <v>142</v>
       </c>
@@ -12675,7 +12687,7 @@
       <c r="P212" s="1"/>
       <c r="Q212" s="1"/>
     </row>
-    <row r="213" ht="36.0" customHeight="1">
+    <row r="213" spans="1:21" ht="36" customHeight="1">
       <c r="A213" s="1" t="s">
         <v>54</v>
       </c>
@@ -12698,7 +12710,7 @@
       <c r="P213" s="1"/>
       <c r="Q213" s="1"/>
     </row>
-    <row r="214" ht="36.0" customHeight="1">
+    <row r="214" spans="1:21" ht="36" customHeight="1">
       <c r="A214" s="1" t="s">
         <v>54</v>
       </c>
@@ -12719,7 +12731,7 @@
       <c r="P214" s="1"/>
       <c r="Q214" s="1"/>
     </row>
-    <row r="215" ht="12.75" customHeight="1">
+    <row r="215" spans="1:21" ht="12.75" customHeight="1">
       <c r="A215" s="1" t="s">
         <v>21</v>
       </c>
@@ -12736,7 +12748,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="216" ht="12.75" customHeight="1">
+    <row r="216" spans="1:21" ht="12.75" customHeight="1">
       <c r="A216" s="1" t="s">
         <v>142</v>
       </c>
@@ -12753,7 +12765,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="217" ht="12.75" customHeight="1">
+    <row r="217" spans="1:21" ht="12.75" customHeight="1">
       <c r="A217" s="1" t="s">
         <v>142</v>
       </c>
@@ -12782,7 +12794,7 @@
       <c r="P217" s="1"/>
       <c r="Q217" s="1"/>
     </row>
-    <row r="218" ht="12.75" customHeight="1">
+    <row r="218" spans="1:21" ht="12.75" customHeight="1">
       <c r="A218" s="1" t="s">
         <v>170</v>
       </c>
@@ -12813,7 +12825,7 @@
       <c r="P218" s="1"/>
       <c r="Q218" s="1"/>
     </row>
-    <row r="219" ht="12.75" customHeight="1">
+    <row r="219" spans="1:21" ht="12.75" customHeight="1">
       <c r="A219" s="1" t="s">
         <v>529</v>
       </c>
@@ -12844,7 +12856,7 @@
       <c r="P219" s="1"/>
       <c r="Q219" s="1"/>
     </row>
-    <row r="220" ht="12.75" customHeight="1">
+    <row r="220" spans="1:21" ht="12.75" customHeight="1">
       <c r="A220" s="1" t="s">
         <v>170</v>
       </c>
@@ -12875,7 +12887,7 @@
       <c r="P220" s="1"/>
       <c r="Q220" s="1"/>
     </row>
-    <row r="221" ht="12.75" customHeight="1">
+    <row r="221" spans="1:21" ht="12.75" customHeight="1">
       <c r="A221" s="1" t="s">
         <v>142</v>
       </c>
@@ -12904,7 +12916,7 @@
       <c r="P221" s="1"/>
       <c r="Q221" s="1"/>
     </row>
-    <row r="222" ht="12.75" customHeight="1">
+    <row r="222" spans="1:21" ht="12.75" customHeight="1">
       <c r="A222" s="1" t="s">
         <v>142</v>
       </c>
@@ -12933,7 +12945,7 @@
       <c r="P222" s="1"/>
       <c r="Q222" s="1"/>
     </row>
-    <row r="223" ht="12.75" customHeight="1">
+    <row r="223" spans="1:21" ht="12.75" customHeight="1">
       <c r="A223" s="1" t="s">
         <v>142</v>
       </c>
@@ -12962,7 +12974,7 @@
       <c r="P223" s="1"/>
       <c r="Q223" s="1"/>
     </row>
-    <row r="224" ht="12.75" customHeight="1">
+    <row r="224" spans="1:21" ht="12.75" customHeight="1">
       <c r="A224" s="1" t="s">
         <v>170</v>
       </c>
@@ -12993,7 +13005,7 @@
       <c r="P224" s="1"/>
       <c r="Q224" s="1"/>
     </row>
-    <row r="225" ht="12.75" customHeight="1">
+    <row r="225" spans="1:19" ht="12.75" customHeight="1">
       <c r="A225" s="1" t="s">
         <v>142</v>
       </c>
@@ -13010,7 +13022,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="226" ht="12.75" customHeight="1">
+    <row r="226" spans="1:19" ht="12.75" customHeight="1">
       <c r="A226" s="1" t="s">
         <v>61</v>
       </c>
@@ -13024,7 +13036,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="227" ht="12.75" customHeight="1">
+    <row r="227" spans="1:19" ht="12.75" customHeight="1">
       <c r="A227" s="1" t="s">
         <v>170</v>
       </c>
@@ -13055,7 +13067,7 @@
       <c r="P227" s="1"/>
       <c r="Q227" s="1"/>
     </row>
-    <row r="228" ht="12.75" customHeight="1">
+    <row r="228" spans="1:19" ht="12.75" customHeight="1">
       <c r="A228" s="1" t="s">
         <v>562</v>
       </c>
@@ -13081,7 +13093,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="229" ht="12.75" customHeight="1">
+    <row r="229" spans="1:19" ht="12.75" customHeight="1">
       <c r="A229" s="1" t="s">
         <v>142</v>
       </c>
@@ -13098,7 +13110,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="230" ht="12.75" customHeight="1">
+    <row r="230" spans="1:19" ht="12.75" customHeight="1">
       <c r="A230" s="1" t="s">
         <v>142</v>
       </c>
@@ -13115,7 +13127,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="231" ht="12.75" customHeight="1">
+    <row r="231" spans="1:19" ht="12.75" customHeight="1">
       <c r="A231" s="1" t="s">
         <v>577</v>
       </c>
@@ -13146,7 +13158,7 @@
       <c r="P231" s="1"/>
       <c r="Q231" s="1"/>
     </row>
-    <row r="232" ht="12.75" customHeight="1">
+    <row r="232" spans="1:19" ht="12.75" customHeight="1">
       <c r="A232" s="1" t="s">
         <v>142</v>
       </c>
@@ -13163,7 +13175,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="233" ht="12.75" customHeight="1">
+    <row r="233" spans="1:19" ht="12.75" customHeight="1">
       <c r="A233" s="1" t="s">
         <v>142</v>
       </c>
@@ -13192,7 +13204,7 @@
       <c r="P233" s="1"/>
       <c r="Q233" s="1"/>
     </row>
-    <row r="234" ht="12.75" customHeight="1">
+    <row r="234" spans="1:19" ht="12.75" customHeight="1">
       <c r="A234" s="1" t="s">
         <v>54</v>
       </c>
@@ -13200,7 +13212,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="235" ht="12.75" customHeight="1">
+    <row r="235" spans="1:19" ht="12.75" customHeight="1">
       <c r="A235" s="1" t="s">
         <v>21</v>
       </c>
@@ -13231,7 +13243,7 @@
       <c r="P235" s="1"/>
       <c r="Q235" s="1"/>
     </row>
-    <row r="236" ht="12.75" customHeight="1">
+    <row r="236" spans="1:19" ht="12.75" customHeight="1">
       <c r="A236" s="1" t="s">
         <v>142</v>
       </c>
@@ -13258,7 +13270,7 @@
       <c r="P236" s="1"/>
       <c r="Q236" s="1"/>
     </row>
-    <row r="237" ht="12.75" customHeight="1">
+    <row r="237" spans="1:19" ht="12.75" customHeight="1">
       <c r="A237" s="1" t="s">
         <v>170</v>
       </c>
@@ -13287,7 +13299,7 @@
       <c r="P237" s="1"/>
       <c r="Q237" s="1"/>
     </row>
-    <row r="238" ht="12.75" customHeight="1">
+    <row r="238" spans="1:19" ht="12.75" customHeight="1">
       <c r="A238" s="1" t="s">
         <v>142</v>
       </c>
@@ -13316,7 +13328,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="239" ht="12.75" customHeight="1">
+    <row r="239" spans="1:19" ht="12.75" customHeight="1">
       <c r="A239" s="1" t="s">
         <v>142</v>
       </c>
@@ -13345,7 +13357,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="240" ht="12.75" customHeight="1">
+    <row r="240" spans="1:19" ht="12.75" customHeight="1">
       <c r="A240" s="1" t="s">
         <v>142</v>
       </c>
@@ -13374,7 +13386,7 @@
       <c r="P240" s="1"/>
       <c r="Q240" s="1"/>
     </row>
-    <row r="241" ht="12.75" customHeight="1">
+    <row r="241" spans="1:17" ht="12.75" customHeight="1">
       <c r="A241" s="1" t="s">
         <v>142</v>
       </c>
@@ -13403,7 +13415,7 @@
       <c r="P241" s="1"/>
       <c r="Q241" s="1"/>
     </row>
-    <row r="242" ht="12.75" customHeight="1">
+    <row r="242" spans="1:17" ht="12.75" customHeight="1">
       <c r="A242" s="1" t="s">
         <v>142</v>
       </c>
@@ -13432,7 +13444,7 @@
       <c r="P242" s="1"/>
       <c r="Q242" s="1"/>
     </row>
-    <row r="243" ht="12.75" customHeight="1">
+    <row r="243" spans="1:17" ht="12.75" customHeight="1">
       <c r="A243" s="1" t="s">
         <v>170</v>
       </c>
@@ -13461,7 +13473,7 @@
       <c r="P243" s="1"/>
       <c r="Q243" s="1"/>
     </row>
-    <row r="244" ht="12.75" customHeight="1">
+    <row r="244" spans="1:17" ht="12.75" customHeight="1">
       <c r="A244" s="1" t="s">
         <v>142</v>
       </c>
@@ -13490,7 +13502,7 @@
       <c r="P244" s="1"/>
       <c r="Q244" s="1"/>
     </row>
-    <row r="245" ht="12.75" customHeight="1">
+    <row r="245" spans="1:17" ht="12.75" customHeight="1">
       <c r="A245" s="1" t="s">
         <v>142</v>
       </c>
@@ -13519,7 +13531,7 @@
       <c r="P245" s="1"/>
       <c r="Q245" s="1"/>
     </row>
-    <row r="246" ht="12.75" customHeight="1">
+    <row r="246" spans="1:17" ht="12.75" customHeight="1">
       <c r="A246" s="1" t="s">
         <v>54</v>
       </c>
@@ -13542,7 +13554,7 @@
       <c r="P246" s="1"/>
       <c r="Q246" s="1"/>
     </row>
-    <row r="247" ht="12.75" customHeight="1">
+    <row r="247" spans="1:17" ht="12.75" customHeight="1">
       <c r="A247" s="1" t="s">
         <v>21</v>
       </c>
@@ -13573,7 +13585,7 @@
       <c r="P247" s="1"/>
       <c r="Q247" s="1"/>
     </row>
-    <row r="248" ht="12.75" customHeight="1">
+    <row r="248" spans="1:17" ht="12.75" customHeight="1">
       <c r="A248" s="1" t="s">
         <v>142</v>
       </c>
@@ -13600,7 +13612,7 @@
       <c r="P248" s="1"/>
       <c r="Q248" s="1"/>
     </row>
-    <row r="249" ht="12.75" customHeight="1">
+    <row r="249" spans="1:17" ht="12.75" customHeight="1">
       <c r="A249" s="1" t="s">
         <v>54</v>
       </c>
@@ -13623,7 +13635,7 @@
       <c r="P249" s="1"/>
       <c r="Q249" s="1"/>
     </row>
-    <row r="250" ht="12.75" customHeight="1">
+    <row r="250" spans="1:17" ht="12.75" customHeight="1">
       <c r="A250" s="1" t="s">
         <v>21</v>
       </c>
@@ -13654,7 +13666,7 @@
       <c r="P250" s="1"/>
       <c r="Q250" s="1"/>
     </row>
-    <row r="251" ht="12.75" customHeight="1">
+    <row r="251" spans="1:17" ht="12.75" customHeight="1">
       <c r="A251" s="1" t="s">
         <v>142</v>
       </c>
@@ -13681,7 +13693,7 @@
       <c r="P251" s="1"/>
       <c r="Q251" s="1"/>
     </row>
-    <row r="252" ht="12.75" customHeight="1">
+    <row r="252" spans="1:17" ht="12.75" customHeight="1">
       <c r="A252" s="1" t="s">
         <v>142</v>
       </c>
@@ -13710,7 +13722,7 @@
       <c r="P252" s="1"/>
       <c r="Q252" s="1"/>
     </row>
-    <row r="253" ht="12.75" customHeight="1">
+    <row r="253" spans="1:17" ht="12.75" customHeight="1">
       <c r="A253" s="1" t="s">
         <v>142</v>
       </c>
@@ -13739,7 +13751,7 @@
       <c r="P253" s="1"/>
       <c r="Q253" s="1"/>
     </row>
-    <row r="254" ht="12.75" customHeight="1">
+    <row r="254" spans="1:17" ht="12.75" customHeight="1">
       <c r="A254" s="1" t="s">
         <v>54</v>
       </c>
@@ -13762,7 +13774,7 @@
       <c r="P254" s="1"/>
       <c r="Q254" s="1"/>
     </row>
-    <row r="255" ht="12.75" customHeight="1">
+    <row r="255" spans="1:17" ht="12.75" customHeight="1">
       <c r="A255" s="1" t="s">
         <v>21</v>
       </c>
@@ -13793,7 +13805,7 @@
       <c r="P255" s="1"/>
       <c r="Q255" s="1"/>
     </row>
-    <row r="256" ht="12.75" customHeight="1">
+    <row r="256" spans="1:17" ht="12.75" customHeight="1">
       <c r="A256" s="1" t="s">
         <v>142</v>
       </c>
@@ -13820,7 +13832,7 @@
       <c r="P256" s="1"/>
       <c r="Q256" s="1"/>
     </row>
-    <row r="257" ht="12.75" customHeight="1">
+    <row r="257" spans="1:19" ht="12.75" customHeight="1">
       <c r="A257" s="1" t="s">
         <v>142</v>
       </c>
@@ -13847,7 +13859,7 @@
       <c r="P257" s="1"/>
       <c r="Q257" s="1"/>
     </row>
-    <row r="258" ht="12.75" customHeight="1">
+    <row r="258" spans="1:19" ht="12.75" customHeight="1">
       <c r="A258" s="1" t="s">
         <v>142</v>
       </c>
@@ -13874,7 +13886,7 @@
       <c r="P258" s="1"/>
       <c r="Q258" s="1"/>
     </row>
-    <row r="259" ht="12.75" customHeight="1">
+    <row r="259" spans="1:19" ht="12.75" customHeight="1">
       <c r="A259" s="1" t="s">
         <v>142</v>
       </c>
@@ -13903,7 +13915,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="260" ht="12.75" customHeight="1">
+    <row r="260" spans="1:19" ht="12.75" customHeight="1">
       <c r="A260" s="1" t="s">
         <v>142</v>
       </c>
@@ -13932,7 +13944,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="261" ht="12.75" customHeight="1">
+    <row r="261" spans="1:19" ht="12.75" customHeight="1">
       <c r="A261" s="1" t="s">
         <v>54</v>
       </c>
@@ -13955,7 +13967,7 @@
       <c r="P261" s="1"/>
       <c r="Q261" s="1"/>
     </row>
-    <row r="262" ht="12.75" customHeight="1">
+    <row r="262" spans="1:19" ht="12.75" customHeight="1">
       <c r="A262" s="1" t="s">
         <v>21</v>
       </c>
@@ -13986,7 +13998,7 @@
       <c r="P262" s="1"/>
       <c r="Q262" s="1"/>
     </row>
-    <row r="263" ht="12.75" customHeight="1">
+    <row r="263" spans="1:19" ht="12.75" customHeight="1">
       <c r="A263" s="1" t="s">
         <v>142</v>
       </c>
@@ -14013,7 +14025,7 @@
       <c r="P263" s="1"/>
       <c r="Q263" s="1"/>
     </row>
-    <row r="264" ht="12.75" customHeight="1">
+    <row r="264" spans="1:19" ht="12.75" customHeight="1">
       <c r="A264" s="1" t="s">
         <v>54</v>
       </c>
@@ -14036,7 +14048,7 @@
       <c r="P264" s="1"/>
       <c r="Q264" s="1"/>
     </row>
-    <row r="265" ht="12.75" customHeight="1">
+    <row r="265" spans="1:19" ht="12.75" customHeight="1">
       <c r="A265" s="1" t="s">
         <v>21</v>
       </c>
@@ -14067,7 +14079,7 @@
       <c r="P265" s="1"/>
       <c r="Q265" s="1"/>
     </row>
-    <row r="266" ht="12.75" customHeight="1">
+    <row r="266" spans="1:19" ht="12.75" customHeight="1">
       <c r="A266" s="1" t="s">
         <v>142</v>
       </c>
@@ -14094,7 +14106,7 @@
       <c r="P266" s="1"/>
       <c r="Q266" s="1"/>
     </row>
-    <row r="267" ht="12.75" customHeight="1">
+    <row r="267" spans="1:19" ht="12.75" customHeight="1">
       <c r="A267" s="1" t="s">
         <v>54</v>
       </c>
@@ -14117,7 +14129,7 @@
       <c r="P267" s="1"/>
       <c r="Q267" s="1"/>
     </row>
-    <row r="268" ht="12.75" customHeight="1">
+    <row r="268" spans="1:19" ht="12.75" customHeight="1">
       <c r="A268" s="1" t="s">
         <v>21</v>
       </c>
@@ -14148,7 +14160,7 @@
       <c r="P268" s="1"/>
       <c r="Q268" s="1"/>
     </row>
-    <row r="269" ht="12.75" customHeight="1">
+    <row r="269" spans="1:19" ht="12.75" customHeight="1">
       <c r="A269" s="1" t="s">
         <v>142</v>
       </c>
@@ -14175,7 +14187,7 @@
       <c r="P269" s="1"/>
       <c r="Q269" s="1"/>
     </row>
-    <row r="270" ht="12.75" customHeight="1">
+    <row r="270" spans="1:19" ht="12.75" customHeight="1">
       <c r="A270" s="1" t="s">
         <v>142</v>
       </c>
@@ -14204,7 +14216,7 @@
       <c r="P270" s="1"/>
       <c r="Q270" s="1"/>
     </row>
-    <row r="271" ht="12.75" customHeight="1">
+    <row r="271" spans="1:19" ht="12.75" customHeight="1">
       <c r="A271" s="1" t="s">
         <v>142</v>
       </c>
@@ -14233,7 +14245,7 @@
       <c r="P271" s="1"/>
       <c r="Q271" s="1"/>
     </row>
-    <row r="272" ht="12.75" customHeight="1">
+    <row r="272" spans="1:19" ht="12.75" customHeight="1">
       <c r="A272" s="1" t="s">
         <v>54</v>
       </c>
@@ -14256,7 +14268,7 @@
       <c r="P272" s="1"/>
       <c r="Q272" s="1"/>
     </row>
-    <row r="273" ht="12.75" customHeight="1">
+    <row r="273" spans="1:26" ht="12.75" customHeight="1">
       <c r="A273" s="1" t="s">
         <v>21</v>
       </c>
@@ -14287,7 +14299,7 @@
       <c r="P273" s="1"/>
       <c r="Q273" s="1"/>
     </row>
-    <row r="274" ht="12.75" customHeight="1">
+    <row r="274" spans="1:26" ht="12.75" customHeight="1">
       <c r="A274" s="1" t="s">
         <v>142</v>
       </c>
@@ -14316,7 +14328,7 @@
       <c r="P274" s="1"/>
       <c r="Q274" s="1"/>
     </row>
-    <row r="275" ht="12.75" customHeight="1">
+    <row r="275" spans="1:26" ht="12.75" customHeight="1">
       <c r="A275" s="1" t="s">
         <v>142</v>
       </c>
@@ -14345,7 +14357,7 @@
       <c r="P275" s="1"/>
       <c r="Q275" s="1"/>
     </row>
-    <row r="276" ht="12.75" customHeight="1">
+    <row r="276" spans="1:26" ht="12.75" customHeight="1">
       <c r="A276" s="1" t="s">
         <v>142</v>
       </c>
@@ -14374,7 +14386,7 @@
       <c r="P276" s="1"/>
       <c r="Q276" s="1"/>
     </row>
-    <row r="277" ht="12.75" customHeight="1">
+    <row r="277" spans="1:26" ht="12.75" customHeight="1">
       <c r="A277" s="1" t="s">
         <v>142</v>
       </c>
@@ -14403,7 +14415,7 @@
       <c r="P277" s="1"/>
       <c r="Q277" s="1"/>
     </row>
-    <row r="278" ht="12.75" customHeight="1">
+    <row r="278" spans="1:26" ht="12.75" customHeight="1">
       <c r="A278" s="1" t="s">
         <v>142</v>
       </c>
@@ -14432,7 +14444,7 @@
       <c r="P278" s="1"/>
       <c r="Q278" s="1"/>
     </row>
-    <row r="279" ht="12.75" customHeight="1">
+    <row r="279" spans="1:26" ht="12.75" customHeight="1">
       <c r="A279" s="1" t="s">
         <v>142</v>
       </c>
@@ -14461,7 +14473,7 @@
       <c r="P279" s="1"/>
       <c r="Q279" s="1"/>
     </row>
-    <row r="280" ht="12.75" customHeight="1">
+    <row r="280" spans="1:26" ht="12.75" customHeight="1">
       <c r="A280" s="1" t="s">
         <v>142</v>
       </c>
@@ -14492,7 +14504,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="281" ht="12.75" customHeight="1">
+    <row r="281" spans="1:26" ht="12.75" customHeight="1">
       <c r="A281" s="1" t="s">
         <v>61</v>
       </c>
@@ -14509,7 +14521,7 @@
       <c r="J281" s="1"/>
       <c r="K281" s="1"/>
       <c r="L281" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="M281" s="1"/>
       <c r="N281" s="1"/>
@@ -14517,7 +14529,7 @@
       <c r="P281" s="1"/>
       <c r="Q281" s="1"/>
     </row>
-    <row r="282" ht="12.75" customHeight="1">
+    <row r="282" spans="1:26" ht="12.75" customHeight="1">
       <c r="A282" s="1" t="s">
         <v>54</v>
       </c>
@@ -14540,7 +14552,7 @@
       <c r="P282" s="1"/>
       <c r="Q282" s="1"/>
     </row>
-    <row r="283" ht="12.75" customHeight="1">
+    <row r="283" spans="1:26" ht="12.75" customHeight="1">
       <c r="A283" s="1" t="s">
         <v>21</v>
       </c>
@@ -14580,7 +14592,7 @@
       <c r="Y283" s="1"/>
       <c r="Z283" s="1"/>
     </row>
-    <row r="284" ht="12.75" customHeight="1">
+    <row r="284" spans="1:26" ht="12.75" customHeight="1">
       <c r="A284" s="1" t="s">
         <v>142</v>
       </c>
@@ -14618,7 +14630,7 @@
       <c r="Y284" s="1"/>
       <c r="Z284" s="1"/>
     </row>
-    <row r="285" ht="12.75" customHeight="1">
+    <row r="285" spans="1:26" ht="12.75" customHeight="1">
       <c r="A285" s="1" t="s">
         <v>142</v>
       </c>
@@ -14656,7 +14668,7 @@
       <c r="Y285" s="1"/>
       <c r="Z285" s="1"/>
     </row>
-    <row r="286" ht="12.75" customHeight="1">
+    <row r="286" spans="1:26" ht="12.75" customHeight="1">
       <c r="A286" s="1" t="s">
         <v>142</v>
       </c>
@@ -14692,7 +14704,7 @@
       <c r="Y286" s="1"/>
       <c r="Z286" s="1"/>
     </row>
-    <row r="287" ht="12.75" customHeight="1">
+    <row r="287" spans="1:26" ht="12.75" customHeight="1">
       <c r="A287" s="1" t="s">
         <v>170</v>
       </c>
@@ -14732,7 +14744,7 @@
       <c r="Y287" s="1"/>
       <c r="Z287" s="1"/>
     </row>
-    <row r="288" ht="12.75" customHeight="1">
+    <row r="288" spans="1:26" ht="12.75" customHeight="1">
       <c r="A288" s="1" t="s">
         <v>142</v>
       </c>
@@ -14770,7 +14782,7 @@
       <c r="Y288" s="1"/>
       <c r="Z288" s="1"/>
     </row>
-    <row r="289" ht="12.75" customHeight="1">
+    <row r="289" spans="1:26" ht="12.75" customHeight="1">
       <c r="A289" s="1" t="s">
         <v>21</v>
       </c>
@@ -14806,7 +14818,7 @@
       <c r="Y289" s="1"/>
       <c r="Z289" s="1"/>
     </row>
-    <row r="290" ht="12.75" customHeight="1">
+    <row r="290" spans="1:26" ht="12.75" customHeight="1">
       <c r="A290" s="1" t="s">
         <v>142</v>
       </c>
@@ -14842,7 +14854,7 @@
       <c r="Y290" s="1"/>
       <c r="Z290" s="1"/>
     </row>
-    <row r="291" ht="12.75" customHeight="1">
+    <row r="291" spans="1:26" ht="12.75" customHeight="1">
       <c r="A291" s="1" t="s">
         <v>142</v>
       </c>
@@ -14880,7 +14892,7 @@
       <c r="Y291" s="1"/>
       <c r="Z291" s="1"/>
     </row>
-    <row r="292" ht="12.75" customHeight="1">
+    <row r="292" spans="1:26" ht="12.75" customHeight="1">
       <c r="A292" s="1" t="s">
         <v>170</v>
       </c>
@@ -14918,7 +14930,7 @@
       <c r="Y292" s="1"/>
       <c r="Z292" s="1"/>
     </row>
-    <row r="293" ht="12.75" customHeight="1">
+    <row r="293" spans="1:26" ht="12.75" customHeight="1">
       <c r="A293" s="1" t="s">
         <v>753</v>
       </c>
@@ -14945,9 +14957,10 @@
       <c r="J293" s="1" t="s">
         <v>759</v>
       </c>
-      <c r="K293" s="1" t="s">
+      <c r="K293" s="19" t="s">
         <v>760</v>
       </c>
+      <c r="L293" s="20"/>
       <c r="M293" s="1"/>
       <c r="N293" s="1"/>
       <c r="O293" s="1"/>
@@ -14963,7 +14976,7 @@
       <c r="Y293" s="1"/>
       <c r="Z293" s="1"/>
     </row>
-    <row r="294" ht="12.75" customHeight="1">
+    <row r="294" spans="1:26" ht="12.75" customHeight="1">
       <c r="A294" s="1" t="s">
         <v>142</v>
       </c>
@@ -14977,9 +14990,10 @@
         <v>763</v>
       </c>
       <c r="E294" s="1"/>
-      <c r="F294" s="1" t="s">
+      <c r="F294" s="19" t="s">
         <v>764</v>
       </c>
+      <c r="G294" s="20"/>
       <c r="H294" s="1"/>
       <c r="I294" s="1"/>
       <c r="J294" s="1"/>
@@ -15000,7 +15014,7 @@
       <c r="Y294" s="1"/>
       <c r="Z294" s="1"/>
     </row>
-    <row r="295" ht="12.75" customHeight="1">
+    <row r="295" spans="1:26" ht="12.75" customHeight="1">
       <c r="A295" s="1" t="s">
         <v>142</v>
       </c>
@@ -15038,7 +15052,7 @@
       <c r="Y295" s="1"/>
       <c r="Z295" s="1"/>
     </row>
-    <row r="296" ht="12.75" customHeight="1">
+    <row r="296" spans="1:26" ht="12.75" customHeight="1">
       <c r="A296" s="1" t="s">
         <v>170</v>
       </c>
@@ -15078,7 +15092,7 @@
       <c r="Y296" s="1"/>
       <c r="Z296" s="1"/>
     </row>
-    <row r="297" ht="12.75" customHeight="1">
+    <row r="297" spans="1:26" ht="12.75" customHeight="1">
       <c r="A297" s="1" t="s">
         <v>753</v>
       </c>
@@ -15103,9 +15117,10 @@
       <c r="J297" s="1" t="s">
         <v>759</v>
       </c>
-      <c r="K297" s="1" t="s">
+      <c r="K297" s="19" t="s">
         <v>760</v>
       </c>
+      <c r="L297" s="20"/>
       <c r="M297" s="1"/>
       <c r="N297" s="1"/>
       <c r="O297" s="1"/>
@@ -15121,7 +15136,7 @@
       <c r="Y297" s="1"/>
       <c r="Z297" s="1"/>
     </row>
-    <row r="298" ht="12.75" customHeight="1">
+    <row r="298" spans="1:26" ht="12.75" customHeight="1">
       <c r="A298" s="1" t="s">
         <v>142</v>
       </c>
@@ -15159,7 +15174,7 @@
       <c r="Y298" s="1"/>
       <c r="Z298" s="1"/>
     </row>
-    <row r="299" ht="12.75" customHeight="1">
+    <row r="299" spans="1:26" ht="12.75" customHeight="1">
       <c r="A299" s="1" t="s">
         <v>170</v>
       </c>
@@ -15199,7 +15214,7 @@
       <c r="Y299" s="1"/>
       <c r="Z299" s="1"/>
     </row>
-    <row r="300" ht="12.75" customHeight="1">
+    <row r="300" spans="1:26" ht="12.75" customHeight="1">
       <c r="A300" s="1" t="s">
         <v>753</v>
       </c>
@@ -15224,9 +15239,10 @@
       <c r="J300" s="1" t="s">
         <v>759</v>
       </c>
-      <c r="K300" s="1" t="s">
+      <c r="K300" s="19" t="s">
         <v>760</v>
       </c>
+      <c r="L300" s="20"/>
       <c r="M300" s="1"/>
       <c r="N300" s="1"/>
       <c r="O300" s="1"/>
@@ -15242,7 +15258,7 @@
       <c r="Y300" s="1"/>
       <c r="Z300" s="1"/>
     </row>
-    <row r="301" ht="12.75" customHeight="1">
+    <row r="301" spans="1:26" ht="12.75" customHeight="1">
       <c r="A301" s="1" t="s">
         <v>142</v>
       </c>
@@ -15280,7 +15296,7 @@
       <c r="Y301" s="1"/>
       <c r="Z301" s="1"/>
     </row>
-    <row r="302" ht="12.75" customHeight="1">
+    <row r="302" spans="1:26" ht="12.75" customHeight="1">
       <c r="A302" s="1" t="s">
         <v>170</v>
       </c>
@@ -15320,7 +15336,7 @@
       <c r="Y302" s="1"/>
       <c r="Z302" s="1"/>
     </row>
-    <row r="303" ht="12.75" customHeight="1">
+    <row r="303" spans="1:26" ht="12.75" customHeight="1">
       <c r="A303" s="1" t="s">
         <v>753</v>
       </c>
@@ -15345,9 +15361,10 @@
       <c r="J303" s="1" t="s">
         <v>759</v>
       </c>
-      <c r="K303" s="1" t="s">
+      <c r="K303" s="19" t="s">
         <v>760</v>
       </c>
+      <c r="L303" s="20"/>
       <c r="M303" s="1"/>
       <c r="N303" s="1"/>
       <c r="O303" s="1"/>
@@ -15363,7 +15380,7 @@
       <c r="Y303" s="1"/>
       <c r="Z303" s="1"/>
     </row>
-    <row r="304" ht="12.75" customHeight="1">
+    <row r="304" spans="1:26" ht="12.75" customHeight="1">
       <c r="A304" s="1" t="s">
         <v>142</v>
       </c>
@@ -15401,7 +15418,7 @@
       <c r="Y304" s="1"/>
       <c r="Z304" s="1"/>
     </row>
-    <row r="305" ht="12.75" customHeight="1">
+    <row r="305" spans="1:26" ht="12.75" customHeight="1">
       <c r="A305" s="1" t="s">
         <v>170</v>
       </c>
@@ -15441,7 +15458,7 @@
       <c r="Y305" s="1"/>
       <c r="Z305" s="1"/>
     </row>
-    <row r="306" ht="12.75" customHeight="1">
+    <row r="306" spans="1:26" ht="12.75" customHeight="1">
       <c r="A306" s="1" t="s">
         <v>753</v>
       </c>
@@ -15466,9 +15483,10 @@
       <c r="J306" s="1" t="s">
         <v>759</v>
       </c>
-      <c r="K306" s="1" t="s">
+      <c r="K306" s="19" t="s">
         <v>760</v>
       </c>
+      <c r="L306" s="20"/>
       <c r="M306" s="1"/>
       <c r="N306" s="1"/>
       <c r="O306" s="1"/>
@@ -15484,7 +15502,7 @@
       <c r="Y306" s="1"/>
       <c r="Z306" s="1"/>
     </row>
-    <row r="307" ht="12.75" customHeight="1">
+    <row r="307" spans="1:26" ht="12.75" customHeight="1">
       <c r="A307" s="1" t="s">
         <v>142</v>
       </c>
@@ -15522,7 +15540,7 @@
       <c r="Y307" s="1"/>
       <c r="Z307" s="1"/>
     </row>
-    <row r="308" ht="12.75" customHeight="1">
+    <row r="308" spans="1:26" ht="12.75" customHeight="1">
       <c r="A308" s="1" t="s">
         <v>170</v>
       </c>
@@ -15562,7 +15580,7 @@
       <c r="Y308" s="1"/>
       <c r="Z308" s="1"/>
     </row>
-    <row r="309" ht="12.75" customHeight="1">
+    <row r="309" spans="1:26" ht="12.75" customHeight="1">
       <c r="A309" s="1" t="s">
         <v>753</v>
       </c>
@@ -15587,9 +15605,10 @@
       <c r="J309" s="1" t="s">
         <v>759</v>
       </c>
-      <c r="K309" s="1" t="s">
+      <c r="K309" s="19" t="s">
         <v>760</v>
       </c>
+      <c r="L309" s="20"/>
       <c r="M309" s="1"/>
       <c r="N309" s="1"/>
       <c r="O309" s="1"/>
@@ -15605,7 +15624,7 @@
       <c r="Y309" s="1"/>
       <c r="Z309" s="1"/>
     </row>
-    <row r="310" ht="12.75" customHeight="1">
+    <row r="310" spans="1:26" ht="12.75" customHeight="1">
       <c r="A310" s="1" t="s">
         <v>142</v>
       </c>
@@ -15643,7 +15662,7 @@
       <c r="Y310" s="1"/>
       <c r="Z310" s="1"/>
     </row>
-    <row r="311" ht="12.75" customHeight="1">
+    <row r="311" spans="1:26" ht="12.75" customHeight="1">
       <c r="A311" s="1" t="s">
         <v>170</v>
       </c>
@@ -15683,7 +15702,7 @@
       <c r="Y311" s="1"/>
       <c r="Z311" s="1"/>
     </row>
-    <row r="312" ht="12.75" customHeight="1">
+    <row r="312" spans="1:26" ht="12.75" customHeight="1">
       <c r="A312" s="1" t="s">
         <v>753</v>
       </c>
@@ -15708,9 +15727,10 @@
       <c r="J312" s="1" t="s">
         <v>759</v>
       </c>
-      <c r="K312" s="1" t="s">
+      <c r="K312" s="19" t="s">
         <v>760</v>
       </c>
+      <c r="L312" s="20"/>
       <c r="M312" s="1"/>
       <c r="N312" s="1"/>
       <c r="O312" s="1"/>
@@ -15726,7 +15746,7 @@
       <c r="Y312" s="1"/>
       <c r="Z312" s="1"/>
     </row>
-    <row r="313" ht="12.75" customHeight="1">
+    <row r="313" spans="1:26" ht="12.75" customHeight="1">
       <c r="A313" s="1" t="s">
         <v>142</v>
       </c>
@@ -15764,7 +15784,7 @@
       <c r="Y313" s="1"/>
       <c r="Z313" s="1"/>
     </row>
-    <row r="314" ht="12.75" customHeight="1">
+    <row r="314" spans="1:26" ht="12.75" customHeight="1">
       <c r="A314" s="1" t="s">
         <v>170</v>
       </c>
@@ -15804,7 +15824,7 @@
       <c r="Y314" s="1"/>
       <c r="Z314" s="1"/>
     </row>
-    <row r="315" ht="12.75" customHeight="1">
+    <row r="315" spans="1:26" ht="12.75" customHeight="1">
       <c r="A315" s="1" t="s">
         <v>753</v>
       </c>
@@ -15829,9 +15849,10 @@
       <c r="J315" s="1" t="s">
         <v>759</v>
       </c>
-      <c r="K315" s="1" t="s">
+      <c r="K315" s="19" t="s">
         <v>760</v>
       </c>
+      <c r="L315" s="20"/>
       <c r="M315" s="1"/>
       <c r="N315" s="1"/>
       <c r="O315" s="1"/>
@@ -15847,7 +15868,7 @@
       <c r="Y315" s="1"/>
       <c r="Z315" s="1"/>
     </row>
-    <row r="316" ht="12.75" customHeight="1">
+    <row r="316" spans="1:26" ht="12.75" customHeight="1">
       <c r="A316" s="1" t="s">
         <v>142</v>
       </c>
@@ -15885,7 +15906,7 @@
       <c r="Y316" s="1"/>
       <c r="Z316" s="1"/>
     </row>
-    <row r="317" ht="12.75" customHeight="1">
+    <row r="317" spans="1:26" ht="12.75" customHeight="1">
       <c r="A317" s="1" t="s">
         <v>170</v>
       </c>
@@ -15925,7 +15946,7 @@
       <c r="Y317" s="1"/>
       <c r="Z317" s="1"/>
     </row>
-    <row r="318" ht="12.75" customHeight="1">
+    <row r="318" spans="1:26" ht="12.75" customHeight="1">
       <c r="A318" s="1" t="s">
         <v>753</v>
       </c>
@@ -15950,9 +15971,10 @@
       <c r="J318" s="1" t="s">
         <v>759</v>
       </c>
-      <c r="K318" s="1" t="s">
+      <c r="K318" s="19" t="s">
         <v>760</v>
       </c>
+      <c r="L318" s="20"/>
       <c r="M318" s="1"/>
       <c r="N318" s="1"/>
       <c r="O318" s="1"/>
@@ -15968,7 +15990,7 @@
       <c r="Y318" s="1"/>
       <c r="Z318" s="1"/>
     </row>
-    <row r="319" ht="12.75" customHeight="1">
+    <row r="319" spans="1:26" ht="12.75" customHeight="1">
       <c r="A319" s="1" t="s">
         <v>142</v>
       </c>
@@ -16006,7 +16028,7 @@
       <c r="Y319" s="1"/>
       <c r="Z319" s="1"/>
     </row>
-    <row r="320" ht="12.75" customHeight="1">
+    <row r="320" spans="1:26" ht="12.75" customHeight="1">
       <c r="A320" s="1" t="s">
         <v>170</v>
       </c>
@@ -16046,7 +16068,7 @@
       <c r="Y320" s="1"/>
       <c r="Z320" s="1"/>
     </row>
-    <row r="321" ht="12.75" customHeight="1">
+    <row r="321" spans="1:26" ht="12.75" customHeight="1">
       <c r="A321" s="1" t="s">
         <v>753</v>
       </c>
@@ -16071,9 +16093,10 @@
       <c r="J321" s="1" t="s">
         <v>759</v>
       </c>
-      <c r="K321" s="1" t="s">
+      <c r="K321" s="19" t="s">
         <v>760</v>
       </c>
+      <c r="L321" s="20"/>
       <c r="M321" s="1"/>
       <c r="N321" s="1"/>
       <c r="O321" s="1"/>
@@ -16089,7 +16112,7 @@
       <c r="Y321" s="1"/>
       <c r="Z321" s="1"/>
     </row>
-    <row r="322" ht="12.75" customHeight="1">
+    <row r="322" spans="1:26" ht="12.75" customHeight="1">
       <c r="A322" s="1" t="s">
         <v>142</v>
       </c>
@@ -16127,7 +16150,7 @@
       <c r="Y322" s="1"/>
       <c r="Z322" s="1"/>
     </row>
-    <row r="323" ht="12.75" customHeight="1">
+    <row r="323" spans="1:26" ht="12.75" customHeight="1">
       <c r="A323" s="1" t="s">
         <v>170</v>
       </c>
@@ -16167,7 +16190,7 @@
       <c r="Y323" s="1"/>
       <c r="Z323" s="1"/>
     </row>
-    <row r="324" ht="12.75" customHeight="1">
+    <row r="324" spans="1:26" ht="12.75" customHeight="1">
       <c r="A324" s="1" t="s">
         <v>753</v>
       </c>
@@ -16192,9 +16215,10 @@
       <c r="J324" s="1" t="s">
         <v>759</v>
       </c>
-      <c r="K324" s="1" t="s">
+      <c r="K324" s="19" t="s">
         <v>760</v>
       </c>
+      <c r="L324" s="20"/>
       <c r="M324" s="1"/>
       <c r="N324" s="1"/>
       <c r="O324" s="1"/>
@@ -16210,7 +16234,7 @@
       <c r="Y324" s="1"/>
       <c r="Z324" s="1"/>
     </row>
-    <row r="325" ht="12.75" customHeight="1">
+    <row r="325" spans="1:26" ht="12.75" customHeight="1">
       <c r="A325" s="1" t="s">
         <v>142</v>
       </c>
@@ -16248,7 +16272,7 @@
       <c r="Y325" s="1"/>
       <c r="Z325" s="1"/>
     </row>
-    <row r="326" ht="12.75" customHeight="1">
+    <row r="326" spans="1:26" ht="12.75" customHeight="1">
       <c r="A326" s="1" t="s">
         <v>170</v>
       </c>
@@ -16288,7 +16312,7 @@
       <c r="Y326" s="1"/>
       <c r="Z326" s="1"/>
     </row>
-    <row r="327" ht="12.75" customHeight="1">
+    <row r="327" spans="1:26" ht="12.75" customHeight="1">
       <c r="A327" s="1" t="s">
         <v>753</v>
       </c>
@@ -16313,9 +16337,10 @@
       <c r="J327" s="1" t="s">
         <v>759</v>
       </c>
-      <c r="K327" s="1" t="s">
+      <c r="K327" s="19" t="s">
         <v>760</v>
       </c>
+      <c r="L327" s="20"/>
       <c r="M327" s="1"/>
       <c r="N327" s="1"/>
       <c r="O327" s="1"/>
@@ -16331,7 +16356,7 @@
       <c r="Y327" s="1"/>
       <c r="Z327" s="1"/>
     </row>
-    <row r="328" ht="12.75" customHeight="1">
+    <row r="328" spans="1:26" ht="12.75" customHeight="1">
       <c r="A328" s="1" t="s">
         <v>142</v>
       </c>
@@ -16369,7 +16394,7 @@
       <c r="Y328" s="1"/>
       <c r="Z328" s="1"/>
     </row>
-    <row r="329" ht="12.75" customHeight="1">
+    <row r="329" spans="1:26" ht="12.75" customHeight="1">
       <c r="A329" s="1" t="s">
         <v>170</v>
       </c>
@@ -16409,7 +16434,7 @@
       <c r="Y329" s="1"/>
       <c r="Z329" s="1"/>
     </row>
-    <row r="330" ht="12.75" customHeight="1">
+    <row r="330" spans="1:26" ht="12.75" customHeight="1">
       <c r="A330" s="1" t="s">
         <v>753</v>
       </c>
@@ -16434,9 +16459,10 @@
       <c r="J330" s="1" t="s">
         <v>759</v>
       </c>
-      <c r="K330" s="1" t="s">
+      <c r="K330" s="19" t="s">
         <v>760</v>
       </c>
+      <c r="L330" s="20"/>
       <c r="M330" s="1"/>
       <c r="N330" s="1"/>
       <c r="O330" s="1"/>
@@ -16452,7 +16478,7 @@
       <c r="Y330" s="1"/>
       <c r="Z330" s="1"/>
     </row>
-    <row r="331" ht="12.75" customHeight="1">
+    <row r="331" spans="1:26" ht="12.75" customHeight="1">
       <c r="A331" s="1" t="s">
         <v>142</v>
       </c>
@@ -16466,9 +16492,11 @@
         <v>748</v>
       </c>
       <c r="E331" s="1"/>
-      <c r="F331" s="1" t="s">
+      <c r="F331" s="19" t="s">
         <v>874</v>
       </c>
+      <c r="G331" s="20"/>
+      <c r="H331" s="20"/>
       <c r="I331" s="1"/>
       <c r="J331" s="1"/>
       <c r="K331" s="1"/>
@@ -16488,7 +16516,7 @@
       <c r="Y331" s="1"/>
       <c r="Z331" s="1"/>
     </row>
-    <row r="332" ht="12.75" customHeight="1">
+    <row r="332" spans="1:26" ht="12.75" customHeight="1">
       <c r="A332" s="1" t="s">
         <v>170</v>
       </c>
@@ -16504,9 +16532,11 @@
       <c r="E332" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="F332" s="1" t="s">
+      <c r="F332" s="19" t="s">
         <v>874</v>
       </c>
+      <c r="G332" s="20"/>
+      <c r="H332" s="20"/>
       <c r="I332" s="1"/>
       <c r="J332" s="1"/>
       <c r="K332" s="1"/>
@@ -16526,7 +16556,7 @@
       <c r="Y332" s="1"/>
       <c r="Z332" s="1"/>
     </row>
-    <row r="333" ht="12.75" customHeight="1">
+    <row r="333" spans="1:26" ht="12.75" customHeight="1">
       <c r="A333" s="1" t="s">
         <v>753</v>
       </c>
@@ -16551,9 +16581,10 @@
       <c r="J333" s="1" t="s">
         <v>759</v>
       </c>
-      <c r="K333" s="1" t="s">
+      <c r="K333" s="19" t="s">
         <v>760</v>
       </c>
+      <c r="L333" s="20"/>
       <c r="M333" s="1"/>
       <c r="N333" s="1"/>
       <c r="O333" s="1"/>
@@ -16569,7 +16600,7 @@
       <c r="Y333" s="1"/>
       <c r="Z333" s="1"/>
     </row>
-    <row r="334" ht="12.75" customHeight="1">
+    <row r="334" spans="1:26" ht="12.75" customHeight="1">
       <c r="A334" s="1" t="s">
         <v>142</v>
       </c>
@@ -16607,7 +16638,7 @@
       <c r="Y334" s="1"/>
       <c r="Z334" s="1"/>
     </row>
-    <row r="335" ht="12.75" customHeight="1">
+    <row r="335" spans="1:26" ht="12.75" customHeight="1">
       <c r="A335" s="1" t="s">
         <v>170</v>
       </c>
@@ -16647,7 +16678,7 @@
       <c r="Y335" s="1"/>
       <c r="Z335" s="1"/>
     </row>
-    <row r="336" ht="12.75" customHeight="1">
+    <row r="336" spans="1:26" ht="12.75" customHeight="1">
       <c r="A336" s="1" t="s">
         <v>753</v>
       </c>
@@ -16672,9 +16703,10 @@
       <c r="J336" s="1" t="s">
         <v>759</v>
       </c>
-      <c r="K336" s="1" t="s">
+      <c r="K336" s="19" t="s">
         <v>760</v>
       </c>
+      <c r="L336" s="20"/>
       <c r="M336" s="1"/>
       <c r="N336" s="1"/>
       <c r="O336" s="1"/>
@@ -16690,7 +16722,7 @@
       <c r="Y336" s="1"/>
       <c r="Z336" s="1"/>
     </row>
-    <row r="337" ht="12.75" customHeight="1">
+    <row r="337" spans="1:26" ht="12.75" customHeight="1">
       <c r="A337" s="13" t="s">
         <v>142</v>
       </c>
@@ -16728,7 +16760,7 @@
       <c r="Y337" s="1"/>
       <c r="Z337" s="1"/>
     </row>
-    <row r="338" ht="12.75" customHeight="1">
+    <row r="338" spans="1:26" ht="12.75" customHeight="1">
       <c r="A338" s="13" t="s">
         <v>170</v>
       </c>
@@ -16768,7 +16800,7 @@
       <c r="Y338" s="1"/>
       <c r="Z338" s="1"/>
     </row>
-    <row r="339" ht="12.75" customHeight="1">
+    <row r="339" spans="1:26" ht="12.75" customHeight="1">
       <c r="A339" s="13" t="s">
         <v>753</v>
       </c>
@@ -16793,9 +16825,10 @@
       <c r="J339" s="1" t="s">
         <v>759</v>
       </c>
-      <c r="K339" s="1" t="s">
+      <c r="K339" s="19" t="s">
         <v>760</v>
       </c>
+      <c r="L339" s="20"/>
       <c r="M339" s="1"/>
       <c r="N339" s="1"/>
       <c r="O339" s="1"/>
@@ -16811,7 +16844,7 @@
       <c r="Y339" s="1"/>
       <c r="Z339" s="1"/>
     </row>
-    <row r="340" ht="12.75" customHeight="1">
+    <row r="340" spans="1:26" ht="12.75" customHeight="1">
       <c r="A340" s="13" t="s">
         <v>54</v>
       </c>
@@ -16843,7 +16876,7 @@
       <c r="Y340" s="1"/>
       <c r="Z340" s="1"/>
     </row>
-    <row r="341" ht="12.75" customHeight="1">
+    <row r="341" spans="1:26" ht="12.75" customHeight="1">
       <c r="A341" s="13" t="s">
         <v>142</v>
       </c>
@@ -16881,7 +16914,7 @@
       <c r="Y341" s="1"/>
       <c r="Z341" s="1"/>
     </row>
-    <row r="342" ht="12.75" customHeight="1">
+    <row r="342" spans="1:26" ht="12.75" customHeight="1">
       <c r="A342" s="13" t="s">
         <v>170</v>
       </c>
@@ -16921,7 +16954,7 @@
       <c r="Y342" s="1"/>
       <c r="Z342" s="1"/>
     </row>
-    <row r="343" ht="12.75" customHeight="1">
+    <row r="343" spans="1:26" ht="12.75" customHeight="1">
       <c r="A343" s="13" t="s">
         <v>142</v>
       </c>
@@ -16959,7 +16992,7 @@
       <c r="Y343" s="1"/>
       <c r="Z343" s="1"/>
     </row>
-    <row r="344" ht="12.75" customHeight="1">
+    <row r="344" spans="1:26" ht="12.75" customHeight="1">
       <c r="A344" s="13" t="s">
         <v>909</v>
       </c>
@@ -16999,7 +17032,7 @@
       <c r="Y344" s="1"/>
       <c r="Z344" s="1"/>
     </row>
-    <row r="345" ht="12.75" customHeight="1">
+    <row r="345" spans="1:26" ht="12.75" customHeight="1">
       <c r="A345" s="13" t="s">
         <v>142</v>
       </c>
@@ -17037,7 +17070,7 @@
       <c r="Y345" s="1"/>
       <c r="Z345" s="1"/>
     </row>
-    <row r="346" ht="12.75" customHeight="1">
+    <row r="346" spans="1:26" ht="12.75" customHeight="1">
       <c r="A346" s="13" t="s">
         <v>142</v>
       </c>
@@ -17075,7 +17108,7 @@
       <c r="Y346" s="1"/>
       <c r="Z346" s="1"/>
     </row>
-    <row r="347" ht="12.75" customHeight="1">
+    <row r="347" spans="1:26" ht="12.75" customHeight="1">
       <c r="A347" s="13" t="s">
         <v>142</v>
       </c>
@@ -17089,9 +17122,12 @@
         <v>924</v>
       </c>
       <c r="E347" s="1"/>
-      <c r="F347" s="1" t="s">
+      <c r="F347" s="19" t="s">
         <v>925</v>
       </c>
+      <c r="G347" s="20"/>
+      <c r="H347" s="20"/>
+      <c r="I347" s="20"/>
       <c r="J347" s="1"/>
       <c r="K347" s="1"/>
       <c r="L347" s="1"/>
@@ -17110,7 +17146,7 @@
       <c r="Y347" s="1"/>
       <c r="Z347" s="1"/>
     </row>
-    <row r="348" ht="12.75" customHeight="1">
+    <row r="348" spans="1:26" ht="12.75" customHeight="1">
       <c r="A348" s="13" t="s">
         <v>142</v>
       </c>
@@ -17148,7 +17184,7 @@
       <c r="Y348" s="1"/>
       <c r="Z348" s="1"/>
     </row>
-    <row r="349" ht="12.75" customHeight="1">
+    <row r="349" spans="1:26" ht="12.75" customHeight="1">
       <c r="A349" s="13" t="s">
         <v>142</v>
       </c>
@@ -17162,9 +17198,12 @@
         <v>932</v>
       </c>
       <c r="E349" s="1"/>
-      <c r="F349" s="1" t="s">
+      <c r="F349" s="19" t="s">
         <v>933</v>
       </c>
+      <c r="G349" s="20"/>
+      <c r="H349" s="20"/>
+      <c r="I349" s="20"/>
       <c r="J349" s="1"/>
       <c r="K349" s="1"/>
       <c r="L349" s="1"/>
@@ -17183,7 +17222,7 @@
       <c r="Y349" s="1"/>
       <c r="Z349" s="1"/>
     </row>
-    <row r="350" ht="12.75" customHeight="1">
+    <row r="350" spans="1:26" ht="12.75" customHeight="1">
       <c r="A350" s="13" t="s">
         <v>142</v>
       </c>
@@ -17221,7 +17260,7 @@
       <c r="Y350" s="1"/>
       <c r="Z350" s="1"/>
     </row>
-    <row r="351" ht="12.75" customHeight="1">
+    <row r="351" spans="1:26" ht="12.75" customHeight="1">
       <c r="A351" s="13" t="s">
         <v>142</v>
       </c>
@@ -17259,7 +17298,7 @@
       <c r="Y351" s="1"/>
       <c r="Z351" s="1"/>
     </row>
-    <row r="352" ht="12.75" customHeight="1">
+    <row r="352" spans="1:26" ht="12.75" customHeight="1">
       <c r="A352" s="13" t="s">
         <v>142</v>
       </c>
@@ -17297,7 +17336,7 @@
       <c r="Y352" s="1"/>
       <c r="Z352" s="1"/>
     </row>
-    <row r="353" ht="12.75" customHeight="1">
+    <row r="353" spans="1:26" ht="12.75" customHeight="1">
       <c r="A353" s="13" t="s">
         <v>54</v>
       </c>
@@ -17329,7 +17368,7 @@
       <c r="Y353" s="1"/>
       <c r="Z353" s="1"/>
     </row>
-    <row r="354" ht="12.75" customHeight="1">
+    <row r="354" spans="1:26" ht="12.75" customHeight="1">
       <c r="A354" s="15" t="s">
         <v>21</v>
       </c>
@@ -17369,7 +17408,7 @@
       <c r="Y354" s="1"/>
       <c r="Z354" s="1"/>
     </row>
-    <row r="355" ht="12.75" customHeight="1">
+    <row r="355" spans="1:26" ht="12.75" customHeight="1">
       <c r="A355" s="15" t="s">
         <v>949</v>
       </c>
@@ -17407,7 +17446,7 @@
       <c r="Y355" s="1"/>
       <c r="Z355" s="1"/>
     </row>
-    <row r="356" ht="12.75" customHeight="1">
+    <row r="356" spans="1:26" ht="12.75" customHeight="1">
       <c r="A356" s="15" t="s">
         <v>142</v>
       </c>
@@ -17445,7 +17484,7 @@
       <c r="Y356" s="1"/>
       <c r="Z356" s="1"/>
     </row>
-    <row r="357" ht="12.75" customHeight="1">
+    <row r="357" spans="1:26" ht="12.75" customHeight="1">
       <c r="A357" s="15" t="s">
         <v>142</v>
       </c>
@@ -17481,7 +17520,7 @@
       <c r="Y357" s="1"/>
       <c r="Z357" s="1"/>
     </row>
-    <row r="358" ht="12.75" customHeight="1">
+    <row r="358" spans="1:26" ht="12.75" customHeight="1">
       <c r="A358" s="15" t="s">
         <v>142</v>
       </c>
@@ -17517,7 +17556,7 @@
       <c r="Y358" s="1"/>
       <c r="Z358" s="1"/>
     </row>
-    <row r="359" ht="12.75" customHeight="1">
+    <row r="359" spans="1:26" ht="12.75" customHeight="1">
       <c r="A359" s="15" t="s">
         <v>142</v>
       </c>
@@ -17553,7 +17592,7 @@
       <c r="Y359" s="1"/>
       <c r="Z359" s="1"/>
     </row>
-    <row r="360" ht="12.75" customHeight="1">
+    <row r="360" spans="1:26" ht="12.75" customHeight="1">
       <c r="A360" s="15" t="s">
         <v>61</v>
       </c>
@@ -17587,7 +17626,7 @@
       <c r="Y360" s="1"/>
       <c r="Z360" s="1"/>
     </row>
-    <row r="361" ht="12.75" customHeight="1">
+    <row r="361" spans="1:26" ht="12.75" customHeight="1">
       <c r="A361" s="15" t="s">
         <v>142</v>
       </c>
@@ -17623,7 +17662,7 @@
       <c r="Y361" s="1"/>
       <c r="Z361" s="1"/>
     </row>
-    <row r="362" ht="12.75" customHeight="1">
+    <row r="362" spans="1:26" ht="12.75" customHeight="1">
       <c r="A362" s="15" t="s">
         <v>971</v>
       </c>
@@ -17661,7 +17700,7 @@
       <c r="Y362" s="1"/>
       <c r="Z362" s="1"/>
     </row>
-    <row r="363" ht="12.75" customHeight="1">
+    <row r="363" spans="1:26" ht="12.75" customHeight="1">
       <c r="A363" s="15" t="s">
         <v>21</v>
       </c>
@@ -17699,7 +17738,7 @@
       <c r="Y363" s="1"/>
       <c r="Z363" s="1"/>
     </row>
-    <row r="364" ht="12.75" customHeight="1">
+    <row r="364" spans="1:26" ht="12.75" customHeight="1">
       <c r="A364" s="15" t="s">
         <v>977</v>
       </c>
@@ -17743,7 +17782,7 @@
       <c r="Y364" s="1"/>
       <c r="Z364" s="1"/>
     </row>
-    <row r="365" ht="12.75" customHeight="1">
+    <row r="365" spans="1:26" ht="12.75" customHeight="1">
       <c r="A365" s="15" t="s">
         <v>142</v>
       </c>
@@ -17781,7 +17820,7 @@
       <c r="Y365" s="1"/>
       <c r="Z365" s="1"/>
     </row>
-    <row r="366" ht="12.75" customHeight="1">
+    <row r="366" spans="1:26" ht="12.75" customHeight="1">
       <c r="A366" s="15" t="s">
         <v>142</v>
       </c>
@@ -17819,7 +17858,7 @@
       <c r="Y366" s="1"/>
       <c r="Z366" s="1"/>
     </row>
-    <row r="367" ht="12.75" customHeight="1">
+    <row r="367" spans="1:26" ht="12.75" customHeight="1">
       <c r="A367" s="15" t="s">
         <v>142</v>
       </c>
@@ -17855,7 +17894,7 @@
       <c r="Y367" s="1"/>
       <c r="Z367" s="1"/>
     </row>
-    <row r="368" ht="12.75" customHeight="1">
+    <row r="368" spans="1:26" ht="12.75" customHeight="1">
       <c r="A368" s="15" t="s">
         <v>995</v>
       </c>
@@ -17897,7 +17936,7 @@
       <c r="Y368" s="1"/>
       <c r="Z368" s="1"/>
     </row>
-    <row r="369" ht="12.75" customHeight="1">
+    <row r="369" spans="1:26" ht="12.75" customHeight="1">
       <c r="A369" s="15" t="s">
         <v>142</v>
       </c>
@@ -17935,7 +17974,7 @@
       <c r="Y369" s="1"/>
       <c r="Z369" s="1"/>
     </row>
-    <row r="370" ht="12.75" customHeight="1">
+    <row r="370" spans="1:26" ht="12.75" customHeight="1">
       <c r="A370" s="15" t="s">
         <v>142</v>
       </c>
@@ -17973,7 +18012,7 @@
       <c r="Y370" s="1"/>
       <c r="Z370" s="1"/>
     </row>
-    <row r="371" ht="12.75" customHeight="1">
+    <row r="371" spans="1:26" ht="12.75" customHeight="1">
       <c r="A371" s="15" t="s">
         <v>142</v>
       </c>
@@ -18009,7 +18048,7 @@
       <c r="Y371" s="1"/>
       <c r="Z371" s="1"/>
     </row>
-    <row r="372" ht="12.75" customHeight="1">
+    <row r="372" spans="1:26" ht="12.75" customHeight="1">
       <c r="A372" s="15" t="s">
         <v>54</v>
       </c>
@@ -18041,7 +18080,7 @@
       <c r="Y372" s="1"/>
       <c r="Z372" s="1"/>
     </row>
-    <row r="373" ht="12.75" customHeight="1">
+    <row r="373" spans="1:26" ht="12.75" customHeight="1">
       <c r="A373" s="15" t="s">
         <v>21</v>
       </c>
@@ -18079,7 +18118,7 @@
       <c r="Y373" s="1"/>
       <c r="Z373" s="1"/>
     </row>
-    <row r="374" ht="12.75" customHeight="1">
+    <row r="374" spans="1:26" ht="12.75" customHeight="1">
       <c r="A374" s="15" t="s">
         <v>170</v>
       </c>
@@ -18117,7 +18156,7 @@
       <c r="Y374" s="1"/>
       <c r="Z374" s="1"/>
     </row>
-    <row r="375" ht="12.75" customHeight="1">
+    <row r="375" spans="1:26" ht="12.75" customHeight="1">
       <c r="A375" s="15" t="s">
         <v>142</v>
       </c>
@@ -18155,7 +18194,7 @@
       <c r="Y375" s="1"/>
       <c r="Z375" s="1"/>
     </row>
-    <row r="376" ht="12.75" customHeight="1">
+    <row r="376" spans="1:26" ht="12.75" customHeight="1">
       <c r="A376" s="15" t="s">
         <v>142</v>
       </c>
@@ -18193,7 +18232,7 @@
       <c r="Y376" s="1"/>
       <c r="Z376" s="1"/>
     </row>
-    <row r="377" ht="12.75" customHeight="1">
+    <row r="377" spans="1:26" ht="12.75" customHeight="1">
       <c r="A377" s="15" t="s">
         <v>142</v>
       </c>
@@ -18229,7 +18268,7 @@
       <c r="Y377" s="1"/>
       <c r="Z377" s="1"/>
     </row>
-    <row r="378" ht="12.75" customHeight="1">
+    <row r="378" spans="1:26" ht="12.75" customHeight="1">
       <c r="A378" s="15" t="s">
         <v>142</v>
       </c>
@@ -18267,7 +18306,7 @@
       <c r="Y378" s="1"/>
       <c r="Z378" s="1"/>
     </row>
-    <row r="379" ht="12.75" customHeight="1">
+    <row r="379" spans="1:26" ht="12.75" customHeight="1">
       <c r="A379" s="15" t="s">
         <v>142</v>
       </c>
@@ -18305,7 +18344,7 @@
       <c r="Y379" s="1"/>
       <c r="Z379" s="1"/>
     </row>
-    <row r="380" ht="12.75" customHeight="1">
+    <row r="380" spans="1:26" ht="12.75" customHeight="1">
       <c r="A380" s="15" t="s">
         <v>142</v>
       </c>
@@ -18343,7 +18382,7 @@
       <c r="Y380" s="1"/>
       <c r="Z380" s="1"/>
     </row>
-    <row r="381" ht="12.75" customHeight="1">
+    <row r="381" spans="1:26" ht="12.75" customHeight="1">
       <c r="A381" s="15" t="s">
         <v>142</v>
       </c>
@@ -18381,7 +18420,7 @@
       <c r="Y381" s="1"/>
       <c r="Z381" s="1"/>
     </row>
-    <row r="382" ht="12.75" customHeight="1">
+    <row r="382" spans="1:26" ht="12.75" customHeight="1">
       <c r="A382" s="15" t="s">
         <v>995</v>
       </c>
@@ -18423,7 +18462,7 @@
       <c r="Y382" s="1"/>
       <c r="Z382" s="1"/>
     </row>
-    <row r="383" ht="12.75" customHeight="1">
+    <row r="383" spans="1:26" ht="12.75" customHeight="1">
       <c r="A383" s="15" t="s">
         <v>142</v>
       </c>
@@ -18461,7 +18500,7 @@
       <c r="Y383" s="1"/>
       <c r="Z383" s="1"/>
     </row>
-    <row r="384" ht="12.75" customHeight="1">
+    <row r="384" spans="1:26" ht="12.75" customHeight="1">
       <c r="A384" s="15" t="s">
         <v>142</v>
       </c>
@@ -18499,7 +18538,7 @@
       <c r="Y384" s="1"/>
       <c r="Z384" s="1"/>
     </row>
-    <row r="385" ht="12.75" customHeight="1">
+    <row r="385" spans="1:26" ht="12.75" customHeight="1">
       <c r="A385" s="15" t="s">
         <v>142</v>
       </c>
@@ -18535,7 +18574,7 @@
       <c r="Y385" s="1"/>
       <c r="Z385" s="1"/>
     </row>
-    <row r="386" ht="12.75" customHeight="1">
+    <row r="386" spans="1:26" ht="12.75" customHeight="1">
       <c r="A386" s="15" t="s">
         <v>142</v>
       </c>
@@ -18573,7 +18612,7 @@
       <c r="Y386" s="1"/>
       <c r="Z386" s="1"/>
     </row>
-    <row r="387" ht="12.75" customHeight="1">
+    <row r="387" spans="1:26" ht="12.75" customHeight="1">
       <c r="A387" s="15" t="s">
         <v>142</v>
       </c>
@@ -18611,7 +18650,7 @@
       <c r="Y387" s="1"/>
       <c r="Z387" s="1"/>
     </row>
-    <row r="388" ht="12.75" customHeight="1">
+    <row r="388" spans="1:26" ht="12.75" customHeight="1">
       <c r="A388" s="15" t="s">
         <v>142</v>
       </c>
@@ -18649,7 +18688,7 @@
       <c r="Y388" s="1"/>
       <c r="Z388" s="1"/>
     </row>
-    <row r="389" ht="12.75" customHeight="1">
+    <row r="389" spans="1:26" ht="12.75" customHeight="1">
       <c r="A389" s="15" t="s">
         <v>142</v>
       </c>
@@ -18687,7 +18726,7 @@
       <c r="Y389" s="1"/>
       <c r="Z389" s="1"/>
     </row>
-    <row r="390" ht="12.75" customHeight="1">
+    <row r="390" spans="1:26" ht="12.75" customHeight="1">
       <c r="A390" s="15" t="s">
         <v>54</v>
       </c>
@@ -18719,7 +18758,7 @@
       <c r="Y390" s="1"/>
       <c r="Z390" s="1"/>
     </row>
-    <row r="391" ht="12.75" customHeight="1">
+    <row r="391" spans="1:26" ht="12.75" customHeight="1">
       <c r="A391" s="15" t="s">
         <v>54</v>
       </c>
@@ -18751,7 +18790,7 @@
       <c r="Y391" s="1"/>
       <c r="Z391" s="1"/>
     </row>
-    <row r="392" ht="12.75" customHeight="1">
+    <row r="392" spans="1:26" ht="12.75" customHeight="1">
       <c r="A392" s="15" t="s">
         <v>21</v>
       </c>
@@ -18791,7 +18830,7 @@
       <c r="Y392" s="1"/>
       <c r="Z392" s="1"/>
     </row>
-    <row r="393" ht="12.75" customHeight="1">
+    <row r="393" spans="1:26" ht="12.75" customHeight="1">
       <c r="A393" s="15" t="s">
         <v>142</v>
       </c>
@@ -18827,7 +18866,7 @@
       <c r="Y393" s="1"/>
       <c r="Z393" s="1"/>
     </row>
-    <row r="394" ht="12.75" customHeight="1">
+    <row r="394" spans="1:26" ht="12.75" customHeight="1">
       <c r="A394" s="15" t="s">
         <v>1067</v>
       </c>
@@ -18865,7 +18904,7 @@
       <c r="Y394" s="1"/>
       <c r="Z394" s="1"/>
     </row>
-    <row r="395" ht="12.75" customHeight="1">
+    <row r="395" spans="1:26" ht="12.75" customHeight="1">
       <c r="A395" s="15" t="s">
         <v>142</v>
       </c>
@@ -18903,7 +18942,7 @@
       <c r="Y395" s="1"/>
       <c r="Z395" s="1"/>
     </row>
-    <row r="396" ht="12.75" customHeight="1">
+    <row r="396" spans="1:26" ht="12.75" customHeight="1">
       <c r="A396" s="15" t="s">
         <v>142</v>
       </c>
@@ -18941,7 +18980,7 @@
       <c r="Y396" s="1"/>
       <c r="Z396" s="1"/>
     </row>
-    <row r="397" ht="12.75" customHeight="1">
+    <row r="397" spans="1:26" ht="12.75" customHeight="1">
       <c r="A397" s="15" t="s">
         <v>170</v>
       </c>
@@ -18979,7 +19018,7 @@
       <c r="Y397" s="1"/>
       <c r="Z397" s="1"/>
     </row>
-    <row r="398" ht="12.75" customHeight="1">
+    <row r="398" spans="1:26" ht="12.75" customHeight="1">
       <c r="A398" s="15" t="s">
         <v>1082</v>
       </c>
@@ -19019,7 +19058,7 @@
       <c r="Y398" s="1"/>
       <c r="Z398" s="1"/>
     </row>
-    <row r="399" ht="12.75" customHeight="1">
+    <row r="399" spans="1:26" ht="12.75" customHeight="1">
       <c r="A399" s="15" t="s">
         <v>142</v>
       </c>
@@ -19057,7 +19096,7 @@
       <c r="Y399" s="1"/>
       <c r="Z399" s="1"/>
     </row>
-    <row r="400" ht="12.75" customHeight="1">
+    <row r="400" spans="1:26" ht="12.75" customHeight="1">
       <c r="A400" s="15" t="s">
         <v>142</v>
       </c>
@@ -19095,7 +19134,7 @@
       <c r="Y400" s="1"/>
       <c r="Z400" s="1"/>
     </row>
-    <row r="401" ht="12.75" customHeight="1">
+    <row r="401" spans="1:26" ht="12.75" customHeight="1">
       <c r="A401" s="15" t="s">
         <v>170</v>
       </c>
@@ -19135,7 +19174,7 @@
       <c r="Y401" s="1"/>
       <c r="Z401" s="1"/>
     </row>
-    <row r="402" ht="12.75" customHeight="1">
+    <row r="402" spans="1:26" ht="12.75" customHeight="1">
       <c r="A402" s="15" t="s">
         <v>142</v>
       </c>
@@ -19173,7 +19212,7 @@
       <c r="Y402" s="1"/>
       <c r="Z402" s="1"/>
     </row>
-    <row r="403" ht="12.75" customHeight="1">
+    <row r="403" spans="1:26" ht="12.75" customHeight="1">
       <c r="A403" s="15" t="s">
         <v>1102</v>
       </c>
@@ -19213,7 +19252,7 @@
       <c r="Y403" s="1"/>
       <c r="Z403" s="1"/>
     </row>
-    <row r="404" ht="12.75" customHeight="1">
+    <row r="404" spans="1:26" ht="12.75" customHeight="1">
       <c r="A404" s="15" t="s">
         <v>142</v>
       </c>
@@ -19251,7 +19290,7 @@
       <c r="Y404" s="1"/>
       <c r="Z404" s="1"/>
     </row>
-    <row r="405" ht="12.75" customHeight="1">
+    <row r="405" spans="1:26" ht="12.75" customHeight="1">
       <c r="A405" s="15" t="s">
         <v>142</v>
       </c>
@@ -19289,7 +19328,7 @@
       <c r="Y405" s="1"/>
       <c r="Z405" s="1"/>
     </row>
-    <row r="406" ht="12.75" customHeight="1">
+    <row r="406" spans="1:26" ht="12.75" customHeight="1">
       <c r="A406" s="15" t="s">
         <v>54</v>
       </c>
@@ -19321,7 +19360,7 @@
       <c r="Y406" s="1"/>
       <c r="Z406" s="1"/>
     </row>
-    <row r="407" ht="12.75" customHeight="1">
+    <row r="407" spans="1:26" ht="12.75" customHeight="1">
       <c r="A407" s="15" t="s">
         <v>21</v>
       </c>
@@ -19361,7 +19400,7 @@
       <c r="Y407" s="1"/>
       <c r="Z407" s="1"/>
     </row>
-    <row r="408" ht="12.75" customHeight="1">
+    <row r="408" spans="1:26" ht="12.75" customHeight="1">
       <c r="A408" s="15" t="s">
         <v>142</v>
       </c>
@@ -19399,7 +19438,7 @@
       <c r="Y408" s="1"/>
       <c r="Z408" s="1"/>
     </row>
-    <row r="409" ht="12.75" customHeight="1">
+    <row r="409" spans="1:26" ht="12.75" customHeight="1">
       <c r="A409" s="15" t="s">
         <v>170</v>
       </c>
@@ -19439,7 +19478,7 @@
       <c r="Y409" s="1"/>
       <c r="Z409" s="1"/>
     </row>
-    <row r="410" ht="12.75" customHeight="1">
+    <row r="410" spans="1:26" ht="12.75" customHeight="1">
       <c r="A410" s="15" t="s">
         <v>142</v>
       </c>
@@ -19477,7 +19516,7 @@
       <c r="Y410" s="1"/>
       <c r="Z410" s="1"/>
     </row>
-    <row r="411" ht="12.75" customHeight="1">
+    <row r="411" spans="1:26" ht="12.75" customHeight="1">
       <c r="A411" s="15" t="s">
         <v>170</v>
       </c>
@@ -19517,7 +19556,7 @@
       <c r="Y411" s="1"/>
       <c r="Z411" s="1"/>
     </row>
-    <row r="412" ht="12.75" customHeight="1">
+    <row r="412" spans="1:26" ht="12.75" customHeight="1">
       <c r="A412" s="15" t="s">
         <v>142</v>
       </c>
@@ -19555,7 +19594,7 @@
       <c r="Y412" s="1"/>
       <c r="Z412" s="1"/>
     </row>
-    <row r="413" ht="12.75" customHeight="1">
+    <row r="413" spans="1:26" ht="12.75" customHeight="1">
       <c r="A413" s="15" t="s">
         <v>1137</v>
       </c>
@@ -19601,7 +19640,7 @@
       <c r="Y413" s="1"/>
       <c r="Z413" s="1"/>
     </row>
-    <row r="414" ht="12.75" customHeight="1">
+    <row r="414" spans="1:26" ht="12.75" customHeight="1">
       <c r="A414" s="15" t="s">
         <v>1143</v>
       </c>
@@ -19641,7 +19680,7 @@
       <c r="Y414" s="1"/>
       <c r="Z414" s="1"/>
     </row>
-    <row r="415" ht="12.75" customHeight="1">
+    <row r="415" spans="1:26" ht="12.75" customHeight="1">
       <c r="A415" s="15" t="s">
         <v>1148</v>
       </c>
@@ -19679,7 +19718,7 @@
       <c r="Y415" s="1"/>
       <c r="Z415" s="1"/>
     </row>
-    <row r="416" ht="12.75" customHeight="1">
+    <row r="416" spans="1:26" ht="12.75" customHeight="1">
       <c r="A416" s="15" t="s">
         <v>1153</v>
       </c>
@@ -19721,7 +19760,7 @@
       <c r="Y416" s="1"/>
       <c r="Z416" s="1"/>
     </row>
-    <row r="417" ht="12.75" customHeight="1">
+    <row r="417" spans="1:26" ht="12.75" customHeight="1">
       <c r="A417" s="15" t="s">
         <v>170</v>
       </c>
@@ -19761,7 +19800,7 @@
       <c r="Y417" s="1"/>
       <c r="Z417" s="1"/>
     </row>
-    <row r="418" ht="12.75" customHeight="1">
+    <row r="418" spans="1:26" ht="12.75" customHeight="1">
       <c r="A418" s="15" t="s">
         <v>142</v>
       </c>
@@ -19799,7 +19838,7 @@
       <c r="Y418" s="1"/>
       <c r="Z418" s="1"/>
     </row>
-    <row r="419" ht="12.75" customHeight="1">
+    <row r="419" spans="1:26" ht="12.75" customHeight="1">
       <c r="A419" s="15" t="s">
         <v>170</v>
       </c>
@@ -19839,7 +19878,7 @@
       <c r="Y419" s="1"/>
       <c r="Z419" s="1"/>
     </row>
-    <row r="420" ht="12.75" customHeight="1">
+    <row r="420" spans="1:26" ht="12.75" customHeight="1">
       <c r="A420" s="15" t="s">
         <v>170</v>
       </c>
@@ -19879,7 +19918,7 @@
       <c r="Y420" s="1"/>
       <c r="Z420" s="1"/>
     </row>
-    <row r="421" ht="12.75" customHeight="1">
+    <row r="421" spans="1:26" ht="12.75" customHeight="1">
       <c r="A421" s="15" t="s">
         <v>170</v>
       </c>
@@ -19919,7 +19958,7 @@
       <c r="Y421" s="1"/>
       <c r="Z421" s="1"/>
     </row>
-    <row r="422" ht="12.75" customHeight="1">
+    <row r="422" spans="1:26" ht="12.75" customHeight="1">
       <c r="A422" s="15" t="s">
         <v>1153</v>
       </c>
@@ -19961,7 +20000,7 @@
       <c r="Y422" s="1"/>
       <c r="Z422" s="1"/>
     </row>
-    <row r="423" ht="12.75" customHeight="1">
+    <row r="423" spans="1:26" ht="12.75" customHeight="1">
       <c r="A423" s="15" t="s">
         <v>170</v>
       </c>
@@ -20001,7 +20040,7 @@
       <c r="Y423" s="1"/>
       <c r="Z423" s="1"/>
     </row>
-    <row r="424" ht="12.75" customHeight="1">
+    <row r="424" spans="1:26" ht="12.75" customHeight="1">
       <c r="A424" s="15" t="s">
         <v>142</v>
       </c>
@@ -20039,7 +20078,7 @@
       <c r="Y424" s="1"/>
       <c r="Z424" s="1"/>
     </row>
-    <row r="425" ht="12.75" customHeight="1">
+    <row r="425" spans="1:26" ht="12.75" customHeight="1">
       <c r="A425" s="15" t="s">
         <v>142</v>
       </c>
@@ -20077,7 +20116,7 @@
       <c r="Y425" s="1"/>
       <c r="Z425" s="1"/>
     </row>
-    <row r="426" ht="12.75" customHeight="1">
+    <row r="426" spans="1:26" ht="12.75" customHeight="1">
       <c r="A426" s="15" t="s">
         <v>1153</v>
       </c>
@@ -20119,7 +20158,7 @@
       <c r="Y426" s="1"/>
       <c r="Z426" s="1"/>
     </row>
-    <row r="427" ht="12.75" customHeight="1">
+    <row r="427" spans="1:26" ht="12.75" customHeight="1">
       <c r="A427" s="15" t="s">
         <v>1153</v>
       </c>
@@ -20161,7 +20200,7 @@
       <c r="Y427" s="1"/>
       <c r="Z427" s="1"/>
     </row>
-    <row r="428" ht="12.75" customHeight="1">
+    <row r="428" spans="1:26" ht="12.75" customHeight="1">
       <c r="A428" s="15" t="s">
         <v>142</v>
       </c>
@@ -20199,7 +20238,7 @@
       <c r="Y428" s="1"/>
       <c r="Z428" s="1"/>
     </row>
-    <row r="429" ht="12.75" customHeight="1">
+    <row r="429" spans="1:26" ht="12.75" customHeight="1">
       <c r="A429" s="15" t="s">
         <v>142</v>
       </c>
@@ -20237,7 +20276,7 @@
       <c r="Y429" s="1"/>
       <c r="Z429" s="1"/>
     </row>
-    <row r="430" ht="12.75" customHeight="1">
+    <row r="430" spans="1:26" ht="12.75" customHeight="1">
       <c r="A430" s="15" t="s">
         <v>142</v>
       </c>
@@ -20275,7 +20314,7 @@
       <c r="Y430" s="1"/>
       <c r="Z430" s="1"/>
     </row>
-    <row r="431" ht="12.75" customHeight="1">
+    <row r="431" spans="1:26" ht="12.75" customHeight="1">
       <c r="A431" s="15" t="s">
         <v>142</v>
       </c>
@@ -20313,7 +20352,7 @@
       <c r="Y431" s="1"/>
       <c r="Z431" s="1"/>
     </row>
-    <row r="432" ht="12.75" customHeight="1">
+    <row r="432" spans="1:26" ht="12.75" customHeight="1">
       <c r="A432" s="15" t="s">
         <v>170</v>
       </c>
@@ -20353,7 +20392,7 @@
       <c r="Y432" s="1"/>
       <c r="Z432" s="1"/>
     </row>
-    <row r="433" ht="12.75" customHeight="1">
+    <row r="433" spans="1:26" ht="12.75" customHeight="1">
       <c r="A433" s="15" t="s">
         <v>142</v>
       </c>
@@ -20391,7 +20430,7 @@
       <c r="Y433" s="1"/>
       <c r="Z433" s="1"/>
     </row>
-    <row r="434" ht="12.75" customHeight="1">
+    <row r="434" spans="1:26" ht="12.75" customHeight="1">
       <c r="A434" s="15" t="s">
         <v>142</v>
       </c>
@@ -20429,7 +20468,7 @@
       <c r="Y434" s="1"/>
       <c r="Z434" s="1"/>
     </row>
-    <row r="435" ht="12.75" customHeight="1">
+    <row r="435" spans="1:26" ht="12.75" customHeight="1">
       <c r="A435" s="15" t="s">
         <v>142</v>
       </c>
@@ -20467,7 +20506,7 @@
       <c r="Y435" s="1"/>
       <c r="Z435" s="1"/>
     </row>
-    <row r="436" ht="12.75" customHeight="1">
+    <row r="436" spans="1:26" ht="12.75" customHeight="1">
       <c r="A436" s="15" t="s">
         <v>170</v>
       </c>
@@ -20507,7 +20546,7 @@
       <c r="Y436" s="1"/>
       <c r="Z436" s="1"/>
     </row>
-    <row r="437" ht="12.75" customHeight="1">
+    <row r="437" spans="1:26" ht="12.75" customHeight="1">
       <c r="A437" s="15" t="s">
         <v>142</v>
       </c>
@@ -20545,7 +20584,7 @@
       <c r="Y437" s="1"/>
       <c r="Z437" s="1"/>
     </row>
-    <row r="438" ht="12.75" customHeight="1">
+    <row r="438" spans="1:26" ht="12.75" customHeight="1">
       <c r="A438" s="15" t="s">
         <v>54</v>
       </c>
@@ -20577,7 +20616,7 @@
       <c r="Y438" s="1"/>
       <c r="Z438" s="1"/>
     </row>
-    <row r="439" ht="12.75" customHeight="1">
+    <row r="439" spans="1:26" ht="12.75" customHeight="1">
       <c r="A439" s="15" t="s">
         <v>21</v>
       </c>
@@ -20617,7 +20656,7 @@
       <c r="Y439" s="1"/>
       <c r="Z439" s="1"/>
     </row>
-    <row r="440" ht="12.75" customHeight="1">
+    <row r="440" spans="1:26" ht="12.75" customHeight="1">
       <c r="A440" s="15" t="s">
         <v>170</v>
       </c>
@@ -20655,7 +20694,7 @@
       <c r="Y440" s="1"/>
       <c r="Z440" s="1"/>
     </row>
-    <row r="441" ht="12.75" customHeight="1">
+    <row r="441" spans="1:26" ht="12.75" customHeight="1">
       <c r="A441" s="15" t="s">
         <v>142</v>
       </c>
@@ -20693,7 +20732,7 @@
       <c r="Y441" s="1"/>
       <c r="Z441" s="1"/>
     </row>
-    <row r="442" ht="12.75" customHeight="1">
+    <row r="442" spans="1:26" ht="12.75" customHeight="1">
       <c r="A442" s="15" t="s">
         <v>142</v>
       </c>
@@ -20731,7 +20770,7 @@
       <c r="Y442" s="1"/>
       <c r="Z442" s="1"/>
     </row>
-    <row r="443" ht="12.75" customHeight="1">
+    <row r="443" spans="1:26" ht="12.75" customHeight="1">
       <c r="A443" s="15" t="s">
         <v>170</v>
       </c>
@@ -20771,7 +20810,7 @@
       <c r="Y443" s="1"/>
       <c r="Z443" s="1"/>
     </row>
-    <row r="444" ht="12.75" customHeight="1">
+    <row r="444" spans="1:26" ht="12.75" customHeight="1">
       <c r="A444" s="15" t="s">
         <v>170</v>
       </c>
@@ -20811,7 +20850,7 @@
       <c r="Y444" s="1"/>
       <c r="Z444" s="1"/>
     </row>
-    <row r="445" ht="12.75" customHeight="1">
+    <row r="445" spans="1:26" ht="12.75" customHeight="1">
       <c r="A445" s="15" t="s">
         <v>170</v>
       </c>
@@ -20851,7 +20890,7 @@
       <c r="Y445" s="1"/>
       <c r="Z445" s="1"/>
     </row>
-    <row r="446" ht="12.75" customHeight="1">
+    <row r="446" spans="1:26" ht="12.75" customHeight="1">
       <c r="A446" s="15" t="s">
         <v>170</v>
       </c>
@@ -20891,7 +20930,7 @@
       <c r="Y446" s="1"/>
       <c r="Z446" s="1"/>
     </row>
-    <row r="447" ht="12.75" customHeight="1">
+    <row r="447" spans="1:26" ht="12.75" customHeight="1">
       <c r="A447" s="15" t="s">
         <v>170</v>
       </c>
@@ -20931,7 +20970,7 @@
       <c r="Y447" s="1"/>
       <c r="Z447" s="1"/>
     </row>
-    <row r="448" ht="12.75" customHeight="1">
+    <row r="448" spans="1:26" ht="12.75" customHeight="1">
       <c r="A448" s="15" t="s">
         <v>170</v>
       </c>
@@ -20971,7 +21010,7 @@
       <c r="Y448" s="1"/>
       <c r="Z448" s="1"/>
     </row>
-    <row r="449" ht="12.75" customHeight="1">
+    <row r="449" spans="1:26" ht="12.75" customHeight="1">
       <c r="A449" s="15" t="s">
         <v>170</v>
       </c>
@@ -21011,7 +21050,7 @@
       <c r="Y449" s="1"/>
       <c r="Z449" s="1"/>
     </row>
-    <row r="450" ht="12.75" customHeight="1">
+    <row r="450" spans="1:26" ht="12.75" customHeight="1">
       <c r="A450" s="15" t="s">
         <v>170</v>
       </c>
@@ -21051,7 +21090,7 @@
       <c r="Y450" s="1"/>
       <c r="Z450" s="1"/>
     </row>
-    <row r="451" ht="12.75" customHeight="1">
+    <row r="451" spans="1:26" ht="12.75" customHeight="1">
       <c r="A451" s="15" t="s">
         <v>170</v>
       </c>
@@ -21091,7 +21130,7 @@
       <c r="Y451" s="1"/>
       <c r="Z451" s="1"/>
     </row>
-    <row r="452" ht="12.75" customHeight="1">
+    <row r="452" spans="1:26" ht="12.75" customHeight="1">
       <c r="A452" s="15" t="s">
         <v>170</v>
       </c>
@@ -21131,7 +21170,7 @@
       <c r="Y452" s="1"/>
       <c r="Z452" s="1"/>
     </row>
-    <row r="453" ht="12.75" customHeight="1">
+    <row r="453" spans="1:26" ht="12.75" customHeight="1">
       <c r="A453" s="15" t="s">
         <v>170</v>
       </c>
@@ -21171,7 +21210,7 @@
       <c r="Y453" s="1"/>
       <c r="Z453" s="1"/>
     </row>
-    <row r="454" ht="12.75" customHeight="1">
+    <row r="454" spans="1:26" ht="12.75" customHeight="1">
       <c r="A454" s="15" t="s">
         <v>61</v>
       </c>
@@ -21205,7 +21244,7 @@
       <c r="Y454" s="1"/>
       <c r="Z454" s="1"/>
     </row>
-    <row r="455" ht="12.75" customHeight="1">
+    <row r="455" spans="1:26" ht="12.75" customHeight="1">
       <c r="A455" s="15" t="s">
         <v>142</v>
       </c>
@@ -21243,7 +21282,7 @@
       <c r="Y455" s="1"/>
       <c r="Z455" s="1"/>
     </row>
-    <row r="456" ht="12.75" customHeight="1">
+    <row r="456" spans="1:26" ht="12.75" customHeight="1">
       <c r="A456" s="15" t="s">
         <v>54</v>
       </c>
@@ -21275,7 +21314,7 @@
       <c r="Y456" s="1"/>
       <c r="Z456" s="1"/>
     </row>
-    <row r="457" ht="12.75" customHeight="1">
+    <row r="457" spans="1:26" ht="12.75" customHeight="1">
       <c r="A457" s="13"/>
       <c r="B457" s="1"/>
       <c r="C457" s="1"/>
@@ -21303,7 +21342,7 @@
       <c r="Y457" s="1"/>
       <c r="Z457" s="1"/>
     </row>
-    <row r="458" ht="12.75" customHeight="1">
+    <row r="458" spans="1:26" ht="12.75" customHeight="1">
       <c r="A458" s="15" t="s">
         <v>21</v>
       </c>
@@ -21343,7 +21382,7 @@
       <c r="Y458" s="1"/>
       <c r="Z458" s="1"/>
     </row>
-    <row r="459" ht="12.75" customHeight="1">
+    <row r="459" spans="1:26" ht="12.75" customHeight="1">
       <c r="A459" s="15" t="s">
         <v>949</v>
       </c>
@@ -21381,7 +21420,7 @@
       <c r="Y459" s="1"/>
       <c r="Z459" s="1"/>
     </row>
-    <row r="460" ht="12.75" customHeight="1">
+    <row r="460" spans="1:26" ht="12.75" customHeight="1">
       <c r="A460" s="15" t="s">
         <v>142</v>
       </c>
@@ -21419,7 +21458,7 @@
       <c r="Y460" s="1"/>
       <c r="Z460" s="1"/>
     </row>
-    <row r="461" ht="12.75" customHeight="1">
+    <row r="461" spans="1:26" ht="12.75" customHeight="1">
       <c r="A461" s="15" t="s">
         <v>142</v>
       </c>
@@ -21455,7 +21494,7 @@
       <c r="Y461" s="1"/>
       <c r="Z461" s="1"/>
     </row>
-    <row r="462" ht="12.75" customHeight="1">
+    <row r="462" spans="1:26" ht="12.75" customHeight="1">
       <c r="A462" s="15" t="s">
         <v>142</v>
       </c>
@@ -21491,7 +21530,7 @@
       <c r="Y462" s="1"/>
       <c r="Z462" s="1"/>
     </row>
-    <row r="463" ht="12.75" customHeight="1">
+    <row r="463" spans="1:26" ht="12.75" customHeight="1">
       <c r="A463" s="15" t="s">
         <v>142</v>
       </c>
@@ -21527,7 +21566,7 @@
       <c r="Y463" s="1"/>
       <c r="Z463" s="1"/>
     </row>
-    <row r="464" ht="12.75" customHeight="1">
+    <row r="464" spans="1:26" ht="12.75" customHeight="1">
       <c r="A464" s="15" t="s">
         <v>142</v>
       </c>
@@ -21563,7 +21602,7 @@
       <c r="Y464" s="1"/>
       <c r="Z464" s="1"/>
     </row>
-    <row r="465" ht="12.75" customHeight="1">
+    <row r="465" spans="1:26" ht="12.75" customHeight="1">
       <c r="A465" s="15" t="s">
         <v>170</v>
       </c>
@@ -21601,7 +21640,7 @@
       <c r="Y465" s="1"/>
       <c r="Z465" s="1"/>
     </row>
-    <row r="466" ht="12.75" customHeight="1">
+    <row r="466" spans="1:26" ht="12.75" customHeight="1">
       <c r="A466" s="15" t="s">
         <v>170</v>
       </c>
@@ -21639,7 +21678,7 @@
       <c r="Y466" s="1"/>
       <c r="Z466" s="1"/>
     </row>
-    <row r="467" ht="12.75" customHeight="1">
+    <row r="467" spans="1:26" ht="12.75" customHeight="1">
       <c r="A467" s="15" t="s">
         <v>142</v>
       </c>
@@ -21677,7 +21716,7 @@
       <c r="Y467" s="1"/>
       <c r="Z467" s="1"/>
     </row>
-    <row r="468" ht="12.75" customHeight="1">
+    <row r="468" spans="1:26" ht="12.75" customHeight="1">
       <c r="A468" s="15" t="s">
         <v>170</v>
       </c>
@@ -21717,7 +21756,7 @@
       <c r="Y468" s="1"/>
       <c r="Z468" s="1"/>
     </row>
-    <row r="469" ht="12.75" customHeight="1">
+    <row r="469" spans="1:26" ht="12.75" customHeight="1">
       <c r="A469" s="15" t="s">
         <v>170</v>
       </c>
@@ -21757,7 +21796,7 @@
       <c r="Y469" s="1"/>
       <c r="Z469" s="1"/>
     </row>
-    <row r="470" ht="12.75" customHeight="1">
+    <row r="470" spans="1:26" ht="12.75" customHeight="1">
       <c r="A470" s="15" t="s">
         <v>170</v>
       </c>
@@ -21797,7 +21836,7 @@
       <c r="Y470" s="1"/>
       <c r="Z470" s="1"/>
     </row>
-    <row r="471" ht="12.75" customHeight="1">
+    <row r="471" spans="1:26" ht="12.75" customHeight="1">
       <c r="A471" s="15" t="s">
         <v>170</v>
       </c>
@@ -21837,7 +21876,7 @@
       <c r="Y471" s="1"/>
       <c r="Z471" s="1"/>
     </row>
-    <row r="472" ht="12.75" customHeight="1">
+    <row r="472" spans="1:26" ht="12.75" customHeight="1">
       <c r="A472" s="15" t="s">
         <v>170</v>
       </c>
@@ -21877,7 +21916,7 @@
       <c r="Y472" s="1"/>
       <c r="Z472" s="1"/>
     </row>
-    <row r="473" ht="12.75" customHeight="1">
+    <row r="473" spans="1:26" ht="12.75" customHeight="1">
       <c r="A473" s="15" t="s">
         <v>170</v>
       </c>
@@ -21917,7 +21956,7 @@
       <c r="Y473" s="1"/>
       <c r="Z473" s="1"/>
     </row>
-    <row r="474" ht="12.75" customHeight="1">
+    <row r="474" spans="1:26" ht="12.75" customHeight="1">
       <c r="A474" s="15" t="s">
         <v>170</v>
       </c>
@@ -21957,7 +21996,7 @@
       <c r="Y474" s="1"/>
       <c r="Z474" s="1"/>
     </row>
-    <row r="475" ht="12.75" customHeight="1">
+    <row r="475" spans="1:26" ht="12.75" customHeight="1">
       <c r="A475" s="15" t="s">
         <v>170</v>
       </c>
@@ -21997,7 +22036,7 @@
       <c r="Y475" s="1"/>
       <c r="Z475" s="1"/>
     </row>
-    <row r="476" ht="12.75" customHeight="1">
+    <row r="476" spans="1:26" ht="12.75" customHeight="1">
       <c r="A476" s="15" t="s">
         <v>170</v>
       </c>
@@ -22037,7 +22076,7 @@
       <c r="Y476" s="1"/>
       <c r="Z476" s="1"/>
     </row>
-    <row r="477" ht="12.75" customHeight="1">
+    <row r="477" spans="1:26" ht="12.75" customHeight="1">
       <c r="A477" s="15" t="s">
         <v>170</v>
       </c>
@@ -22077,7 +22116,7 @@
       <c r="Y477" s="1"/>
       <c r="Z477" s="1"/>
     </row>
-    <row r="478" ht="12.75" customHeight="1">
+    <row r="478" spans="1:26" ht="12.75" customHeight="1">
       <c r="A478" s="15" t="s">
         <v>170</v>
       </c>
@@ -22117,7 +22156,7 @@
       <c r="Y478" s="1"/>
       <c r="Z478" s="1"/>
     </row>
-    <row r="479" ht="12.75" customHeight="1">
+    <row r="479" spans="1:26" ht="12.75" customHeight="1">
       <c r="A479" s="15" t="s">
         <v>61</v>
       </c>
@@ -22151,7 +22190,7 @@
       <c r="Y479" s="1"/>
       <c r="Z479" s="1"/>
     </row>
-    <row r="480" ht="12.75" customHeight="1">
+    <row r="480" spans="1:26" ht="12.75" customHeight="1">
       <c r="A480" s="15" t="s">
         <v>142</v>
       </c>
@@ -22189,7 +22228,7 @@
       <c r="Y480" s="1"/>
       <c r="Z480" s="1"/>
     </row>
-    <row r="481" ht="12.75" customHeight="1">
+    <row r="481" spans="1:26" ht="12.75" customHeight="1">
       <c r="A481" s="15" t="s">
         <v>142</v>
       </c>
@@ -22227,7 +22266,7 @@
       <c r="Y481" s="1"/>
       <c r="Z481" s="1"/>
     </row>
-    <row r="482" ht="12.75" customHeight="1">
+    <row r="482" spans="1:26" ht="12.75" customHeight="1">
       <c r="A482" s="15" t="s">
         <v>61</v>
       </c>
@@ -22261,7 +22300,7 @@
       <c r="Y482" s="1"/>
       <c r="Z482" s="1"/>
     </row>
-    <row r="483" ht="12.75" customHeight="1">
+    <row r="483" spans="1:26" ht="12.75" customHeight="1">
       <c r="A483" s="15" t="s">
         <v>142</v>
       </c>
@@ -22297,7 +22336,7 @@
       <c r="Y483" s="1"/>
       <c r="Z483" s="1"/>
     </row>
-    <row r="484" ht="12.75" customHeight="1">
+    <row r="484" spans="1:26" ht="12.75" customHeight="1">
       <c r="A484" s="15" t="s">
         <v>971</v>
       </c>
@@ -22335,7 +22374,7 @@
       <c r="Y484" s="1"/>
       <c r="Z484" s="1"/>
     </row>
-    <row r="485" ht="12.75" customHeight="1">
+    <row r="485" spans="1:26" ht="12.75" customHeight="1">
       <c r="A485" s="15" t="s">
         <v>142</v>
       </c>
@@ -22371,7 +22410,7 @@
       <c r="Y485" s="1"/>
       <c r="Z485" s="1"/>
     </row>
-    <row r="486" ht="12.75" customHeight="1">
+    <row r="486" spans="1:26" ht="12.75" customHeight="1">
       <c r="A486" s="15" t="s">
         <v>54</v>
       </c>
@@ -22403,7 +22442,7 @@
       <c r="Y486" s="1"/>
       <c r="Z486" s="1"/>
     </row>
-    <row r="487" ht="12.75" customHeight="1">
+    <row r="487" spans="1:26" ht="12.75" customHeight="1">
       <c r="A487" s="15" t="s">
         <v>138</v>
       </c>
@@ -22443,7 +22482,7 @@
       <c r="Y487" s="1"/>
       <c r="Z487" s="1"/>
     </row>
-    <row r="488" ht="12.75" customHeight="1">
+    <row r="488" spans="1:26" ht="12.75" customHeight="1">
       <c r="A488" s="15" t="s">
         <v>170</v>
       </c>
@@ -22481,7 +22520,7 @@
       <c r="Y488" s="1"/>
       <c r="Z488" s="1"/>
     </row>
-    <row r="489" ht="12.75" customHeight="1">
+    <row r="489" spans="1:26" ht="12.75" customHeight="1">
       <c r="A489" s="15" t="s">
         <v>170</v>
       </c>
@@ -22519,7 +22558,7 @@
       <c r="Y489" s="1"/>
       <c r="Z489" s="1"/>
     </row>
-    <row r="490" ht="12.75" customHeight="1">
+    <row r="490" spans="1:26" ht="12.75" customHeight="1">
       <c r="A490" s="15" t="s">
         <v>142</v>
       </c>
@@ -22557,7 +22596,7 @@
       <c r="Y490" s="1"/>
       <c r="Z490" s="1"/>
     </row>
-    <row r="491" ht="12.75" customHeight="1">
+    <row r="491" spans="1:26" ht="12.75" customHeight="1">
       <c r="A491" s="15" t="s">
         <v>142</v>
       </c>
@@ -22595,7 +22634,7 @@
       <c r="Y491" s="1"/>
       <c r="Z491" s="1"/>
     </row>
-    <row r="492" ht="12.75" customHeight="1">
+    <row r="492" spans="1:26" ht="12.75" customHeight="1">
       <c r="A492" s="15" t="s">
         <v>142</v>
       </c>
@@ -22633,7 +22672,7 @@
       <c r="Y492" s="1"/>
       <c r="Z492" s="1"/>
     </row>
-    <row r="493" ht="12.75" customHeight="1">
+    <row r="493" spans="1:26" ht="12.75" customHeight="1">
       <c r="A493" s="15" t="s">
         <v>142</v>
       </c>
@@ -22669,7 +22708,7 @@
       <c r="Y493" s="1"/>
       <c r="Z493" s="1"/>
     </row>
-    <row r="494" ht="12.75" customHeight="1">
+    <row r="494" spans="1:26" ht="12.75" customHeight="1">
       <c r="A494" s="15" t="s">
         <v>170</v>
       </c>
@@ -22707,7 +22746,7 @@
       <c r="Y494" s="1"/>
       <c r="Z494" s="1"/>
     </row>
-    <row r="495" ht="12.75" customHeight="1">
+    <row r="495" spans="1:26" ht="12.75" customHeight="1">
       <c r="A495" s="15" t="s">
         <v>170</v>
       </c>
@@ -22745,7 +22784,7 @@
       <c r="Y495" s="1"/>
       <c r="Z495" s="1"/>
     </row>
-    <row r="496" ht="12.75" customHeight="1">
+    <row r="496" spans="1:26" ht="12.75" customHeight="1">
       <c r="A496" s="15" t="s">
         <v>142</v>
       </c>
@@ -22783,7 +22822,7 @@
       <c r="Y496" s="1"/>
       <c r="Z496" s="1"/>
     </row>
-    <row r="497" ht="12.75" customHeight="1">
+    <row r="497" spans="1:26" ht="12.75" customHeight="1">
       <c r="A497" s="15" t="s">
         <v>170</v>
       </c>
@@ -22821,7 +22860,7 @@
       <c r="Y497" s="1"/>
       <c r="Z497" s="1"/>
     </row>
-    <row r="498" ht="12.75" customHeight="1">
+    <row r="498" spans="1:26" ht="12.75" customHeight="1">
       <c r="A498" s="15" t="s">
         <v>142</v>
       </c>
@@ -22859,7 +22898,7 @@
       <c r="Y498" s="1"/>
       <c r="Z498" s="1"/>
     </row>
-    <row r="499" ht="12.75" customHeight="1">
+    <row r="499" spans="1:26" ht="12.75" customHeight="1">
       <c r="A499" s="15" t="s">
         <v>142</v>
       </c>
@@ -22897,7 +22936,7 @@
       <c r="Y499" s="1"/>
       <c r="Z499" s="1"/>
     </row>
-    <row r="500" ht="12.75" customHeight="1">
+    <row r="500" spans="1:26" ht="12.75" customHeight="1">
       <c r="A500" s="15" t="s">
         <v>146</v>
       </c>
@@ -22929,7 +22968,7 @@
       <c r="Y500" s="1"/>
       <c r="Z500" s="1"/>
     </row>
-    <row r="501" ht="12.75" customHeight="1">
+    <row r="501" spans="1:26" ht="12.75" customHeight="1">
       <c r="A501" s="15" t="s">
         <v>138</v>
       </c>
@@ -22969,7 +23008,7 @@
       <c r="Y501" s="1"/>
       <c r="Z501" s="1"/>
     </row>
-    <row r="502" ht="12.75" customHeight="1">
+    <row r="502" spans="1:26" ht="12.75" customHeight="1">
       <c r="A502" s="15" t="s">
         <v>142</v>
       </c>
@@ -23005,7 +23044,7 @@
       <c r="Y502" s="1"/>
       <c r="Z502" s="1"/>
     </row>
-    <row r="503" ht="12.75" customHeight="1">
+    <row r="503" spans="1:26" ht="12.75" customHeight="1">
       <c r="A503" s="15" t="s">
         <v>170</v>
       </c>
@@ -23043,7 +23082,7 @@
       <c r="Y503" s="1"/>
       <c r="Z503" s="1"/>
     </row>
-    <row r="504" ht="12.75" customHeight="1">
+    <row r="504" spans="1:26" ht="12.75" customHeight="1">
       <c r="A504" s="15" t="s">
         <v>142</v>
       </c>
@@ -23081,7 +23120,7 @@
       <c r="Y504" s="1"/>
       <c r="Z504" s="1"/>
     </row>
-    <row r="505" ht="12.75" customHeight="1">
+    <row r="505" spans="1:26" ht="12.75" customHeight="1">
       <c r="A505" s="15" t="s">
         <v>142</v>
       </c>
@@ -23119,7 +23158,7 @@
       <c r="Y505" s="1"/>
       <c r="Z505" s="1"/>
     </row>
-    <row r="506" ht="12.75" customHeight="1">
+    <row r="506" spans="1:26" ht="12.75" customHeight="1">
       <c r="A506" s="15" t="s">
         <v>170</v>
       </c>
@@ -23157,7 +23196,7 @@
       <c r="Y506" s="1"/>
       <c r="Z506" s="1"/>
     </row>
-    <row r="507" ht="12.75" customHeight="1">
+    <row r="507" spans="1:26" ht="12.75" customHeight="1">
       <c r="A507" s="15" t="s">
         <v>142</v>
       </c>
@@ -23195,7 +23234,7 @@
       <c r="Y507" s="1"/>
       <c r="Z507" s="1"/>
     </row>
-    <row r="508" ht="12.75" customHeight="1">
+    <row r="508" spans="1:26" ht="12.75" customHeight="1">
       <c r="A508" s="15" t="s">
         <v>142</v>
       </c>
@@ -23233,7 +23272,7 @@
       <c r="Y508" s="1"/>
       <c r="Z508" s="1"/>
     </row>
-    <row r="509" ht="12.75" customHeight="1">
+    <row r="509" spans="1:26" ht="12.75" customHeight="1">
       <c r="A509" s="15" t="s">
         <v>170</v>
       </c>
@@ -23271,7 +23310,7 @@
       <c r="Y509" s="1"/>
       <c r="Z509" s="1"/>
     </row>
-    <row r="510" ht="12.75" customHeight="1">
+    <row r="510" spans="1:26" ht="12.75" customHeight="1">
       <c r="A510" s="15" t="s">
         <v>142</v>
       </c>
@@ -23309,7 +23348,7 @@
       <c r="Y510" s="1"/>
       <c r="Z510" s="1"/>
     </row>
-    <row r="511" ht="12.75" customHeight="1">
+    <row r="511" spans="1:26" ht="12.75" customHeight="1">
       <c r="A511" s="15" t="s">
         <v>1102</v>
       </c>
@@ -23349,7 +23388,7 @@
       <c r="Y511" s="1"/>
       <c r="Z511" s="1"/>
     </row>
-    <row r="512" ht="12.75" customHeight="1">
+    <row r="512" spans="1:26" ht="12.75" customHeight="1">
       <c r="A512" s="15" t="s">
         <v>142</v>
       </c>
@@ -23387,7 +23426,7 @@
       <c r="Y512" s="1"/>
       <c r="Z512" s="1"/>
     </row>
-    <row r="513" ht="12.75" customHeight="1">
+    <row r="513" spans="1:26" ht="12.75" customHeight="1">
       <c r="A513" s="15" t="s">
         <v>142</v>
       </c>
@@ -23425,7 +23464,7 @@
       <c r="Y513" s="1"/>
       <c r="Z513" s="1"/>
     </row>
-    <row r="514" ht="12.75" customHeight="1">
+    <row r="514" spans="1:26" ht="12.75" customHeight="1">
       <c r="A514" s="15" t="s">
         <v>146</v>
       </c>
@@ -23457,7 +23496,7 @@
       <c r="Y514" s="1"/>
       <c r="Z514" s="1"/>
     </row>
-    <row r="515" ht="12.75" customHeight="1">
+    <row r="515" spans="1:26" ht="12.75" customHeight="1">
       <c r="A515" s="15" t="s">
         <v>138</v>
       </c>
@@ -23497,7 +23536,7 @@
       <c r="Y515" s="1"/>
       <c r="Z515" s="1"/>
     </row>
-    <row r="516" ht="12.75" customHeight="1">
+    <row r="516" spans="1:26" ht="12.75" customHeight="1">
       <c r="A516" s="15" t="s">
         <v>142</v>
       </c>
@@ -23533,7 +23572,7 @@
       <c r="Y516" s="1"/>
       <c r="Z516" s="1"/>
     </row>
-    <row r="517" ht="36.0" customHeight="1">
+    <row r="517" spans="1:26" ht="36" customHeight="1">
       <c r="A517" s="15" t="s">
         <v>142</v>
       </c>
@@ -23569,7 +23608,7 @@
       <c r="Y517" s="1"/>
       <c r="Z517" s="1"/>
     </row>
-    <row r="518" ht="12.75" customHeight="1">
+    <row r="518" spans="1:26" ht="12.75" customHeight="1">
       <c r="A518" s="15" t="s">
         <v>142</v>
       </c>
@@ -23607,7 +23646,7 @@
       <c r="Y518" s="1"/>
       <c r="Z518" s="1"/>
     </row>
-    <row r="519" ht="12.75" customHeight="1">
+    <row r="519" spans="1:26" ht="12.75" customHeight="1">
       <c r="A519" s="15" t="s">
         <v>142</v>
       </c>
@@ -23645,7 +23684,7 @@
       <c r="Y519" s="1"/>
       <c r="Z519" s="1"/>
     </row>
-    <row r="520" ht="12.75" customHeight="1">
+    <row r="520" spans="1:26" ht="12.75" customHeight="1">
       <c r="A520" s="15" t="s">
         <v>142</v>
       </c>
@@ -23683,7 +23722,7 @@
       <c r="Y520" s="1"/>
       <c r="Z520" s="1"/>
     </row>
-    <row r="521" ht="12.75" customHeight="1">
+    <row r="521" spans="1:26" ht="12.75" customHeight="1">
       <c r="A521" s="15" t="s">
         <v>142</v>
       </c>
@@ -23721,7 +23760,7 @@
       <c r="Y521" s="1"/>
       <c r="Z521" s="1"/>
     </row>
-    <row r="522" ht="12.75" customHeight="1">
+    <row r="522" spans="1:26" ht="12.75" customHeight="1">
       <c r="A522" s="15" t="s">
         <v>142</v>
       </c>
@@ -23759,7 +23798,7 @@
       <c r="Y522" s="1"/>
       <c r="Z522" s="1"/>
     </row>
-    <row r="523" ht="12.75" customHeight="1">
+    <row r="523" spans="1:26" ht="12.75" customHeight="1">
       <c r="A523" s="15" t="s">
         <v>142</v>
       </c>
@@ -23795,7 +23834,7 @@
       <c r="Y523" s="1"/>
       <c r="Z523" s="1"/>
     </row>
-    <row r="524" ht="12.75" customHeight="1">
+    <row r="524" spans="1:26" ht="12.75" customHeight="1">
       <c r="A524" s="15" t="s">
         <v>142</v>
       </c>
@@ -23833,7 +23872,7 @@
       <c r="Y524" s="1"/>
       <c r="Z524" s="1"/>
     </row>
-    <row r="525" ht="12.75" customHeight="1">
+    <row r="525" spans="1:26" ht="12.75" customHeight="1">
       <c r="A525" s="15" t="s">
         <v>142</v>
       </c>
@@ -23871,7 +23910,7 @@
       <c r="Y525" s="1"/>
       <c r="Z525" s="1"/>
     </row>
-    <row r="526" ht="12.75" customHeight="1">
+    <row r="526" spans="1:26" ht="12.75" customHeight="1">
       <c r="A526" s="15" t="s">
         <v>142</v>
       </c>
@@ -23909,7 +23948,7 @@
       <c r="Y526" s="1"/>
       <c r="Z526" s="1"/>
     </row>
-    <row r="527" ht="12.75" customHeight="1">
+    <row r="527" spans="1:26" ht="12.75" customHeight="1">
       <c r="A527" s="15" t="s">
         <v>142</v>
       </c>
@@ -23947,7 +23986,7 @@
       <c r="Y527" s="1"/>
       <c r="Z527" s="1"/>
     </row>
-    <row r="528" ht="12.75" customHeight="1">
+    <row r="528" spans="1:26" ht="12.75" customHeight="1">
       <c r="A528" s="15" t="s">
         <v>142</v>
       </c>
@@ -23985,7 +24024,7 @@
       <c r="Y528" s="1"/>
       <c r="Z528" s="1"/>
     </row>
-    <row r="529" ht="12.75" customHeight="1">
+    <row r="529" spans="1:26" ht="12.75" customHeight="1">
       <c r="A529" s="15" t="s">
         <v>142</v>
       </c>
@@ -24021,7 +24060,7 @@
       <c r="Y529" s="1"/>
       <c r="Z529" s="1"/>
     </row>
-    <row r="530" ht="12.75" customHeight="1">
+    <row r="530" spans="1:26" ht="12.75" customHeight="1">
       <c r="A530" s="15" t="s">
         <v>146</v>
       </c>
@@ -24053,7 +24092,7 @@
       <c r="Y530" s="1"/>
       <c r="Z530" s="1"/>
     </row>
-    <row r="531" ht="12.75" customHeight="1">
+    <row r="531" spans="1:26" ht="12.75" customHeight="1">
       <c r="A531" s="15" t="s">
         <v>21</v>
       </c>
@@ -24093,7 +24132,7 @@
       <c r="Y531" s="1"/>
       <c r="Z531" s="1"/>
     </row>
-    <row r="532" ht="12.75" customHeight="1">
+    <row r="532" spans="1:26" ht="12.75" customHeight="1">
       <c r="A532" s="15" t="s">
         <v>142</v>
       </c>
@@ -24131,7 +24170,7 @@
       <c r="Y532" s="1"/>
       <c r="Z532" s="1"/>
     </row>
-    <row r="533" ht="12.75" customHeight="1">
+    <row r="533" spans="1:26" ht="12.75" customHeight="1">
       <c r="A533" s="15" t="s">
         <v>1137</v>
       </c>
@@ -24177,7 +24216,7 @@
       <c r="Y533" s="1"/>
       <c r="Z533" s="1"/>
     </row>
-    <row r="534" ht="12.75" customHeight="1">
+    <row r="534" spans="1:26" ht="12.75" customHeight="1">
       <c r="A534" s="15" t="s">
         <v>142</v>
       </c>
@@ -24215,7 +24254,7 @@
       <c r="Y534" s="1"/>
       <c r="Z534" s="1"/>
     </row>
-    <row r="535" ht="12.75" customHeight="1">
+    <row r="535" spans="1:26" ht="12.75" customHeight="1">
       <c r="A535" s="15" t="s">
         <v>1153</v>
       </c>
@@ -24259,7 +24298,7 @@
       <c r="Y535" s="1"/>
       <c r="Z535" s="1"/>
     </row>
-    <row r="536" ht="12.75" customHeight="1">
+    <row r="536" spans="1:26" ht="12.75" customHeight="1">
       <c r="A536" s="15" t="s">
         <v>1153</v>
       </c>
@@ -24303,7 +24342,7 @@
       <c r="Y536" s="1"/>
       <c r="Z536" s="1"/>
     </row>
-    <row r="537" ht="12.75" customHeight="1">
+    <row r="537" spans="1:26" ht="12.75" customHeight="1">
       <c r="A537" s="15" t="s">
         <v>1153</v>
       </c>
@@ -24347,7 +24386,7 @@
       <c r="Y537" s="1"/>
       <c r="Z537" s="1"/>
     </row>
-    <row r="538" ht="12.75" customHeight="1">
+    <row r="538" spans="1:26" ht="12.75" customHeight="1">
       <c r="A538" s="15" t="s">
         <v>1153</v>
       </c>
@@ -24391,7 +24430,7 @@
       <c r="Y538" s="1"/>
       <c r="Z538" s="1"/>
     </row>
-    <row r="539" ht="12.75" customHeight="1">
+    <row r="539" spans="1:26" ht="12.75" customHeight="1">
       <c r="A539" s="15" t="s">
         <v>1481</v>
       </c>
@@ -24435,7 +24474,7 @@
       <c r="Y539" s="1"/>
       <c r="Z539" s="1"/>
     </row>
-    <row r="540" ht="12.75" customHeight="1">
+    <row r="540" spans="1:26" ht="12.75" customHeight="1">
       <c r="A540" s="15" t="s">
         <v>1153</v>
       </c>
@@ -24479,7 +24518,7 @@
       <c r="Y540" s="1"/>
       <c r="Z540" s="1"/>
     </row>
-    <row r="541" ht="12.75" customHeight="1">
+    <row r="541" spans="1:26" ht="12.75" customHeight="1">
       <c r="A541" s="15" t="s">
         <v>1143</v>
       </c>
@@ -24496,7 +24535,7 @@
         <v>174</v>
       </c>
       <c r="F541" s="16" t="s">
-        <v>1491</v>
+        <v>1961</v>
       </c>
       <c r="G541" s="15"/>
       <c r="H541" s="15"/>
@@ -24519,12 +24558,12 @@
       <c r="Y541" s="1"/>
       <c r="Z541" s="1"/>
     </row>
-    <row r="542" ht="12.75" customHeight="1">
+    <row r="542" spans="1:26" ht="12.75" customHeight="1">
       <c r="A542" s="15" t="s">
         <v>1148</v>
       </c>
       <c r="B542" s="15" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="C542" s="15" t="s">
         <v>1150</v>
@@ -24534,7 +24573,7 @@
       </c>
       <c r="E542" s="15"/>
       <c r="F542" s="15" t="s">
-        <v>1493</v>
+        <v>1960</v>
       </c>
       <c r="G542" s="15"/>
       <c r="H542" s="15"/>
@@ -24557,7 +24596,7 @@
       <c r="Y542" s="1"/>
       <c r="Z542" s="1"/>
     </row>
-    <row r="543" ht="12.75" customHeight="1">
+    <row r="543" spans="1:26" ht="12.75" customHeight="1">
       <c r="A543" s="15" t="s">
         <v>1153</v>
       </c>
@@ -24565,7 +24604,7 @@
         <v>1154</v>
       </c>
       <c r="C543" s="15" t="s">
-        <v>1494</v>
+        <v>1492</v>
       </c>
       <c r="D543" s="15" t="s">
         <v>1156</v>
@@ -24599,18 +24638,18 @@
       <c r="Y543" s="1"/>
       <c r="Z543" s="1"/>
     </row>
-    <row r="544" ht="12.75" customHeight="1">
+    <row r="544" spans="1:26" ht="12.75" customHeight="1">
       <c r="A544" s="15" t="s">
         <v>142</v>
       </c>
       <c r="B544" s="15" t="s">
+        <v>1493</v>
+      </c>
+      <c r="C544" s="15" t="s">
+        <v>1494</v>
+      </c>
+      <c r="D544" s="15" t="s">
         <v>1495</v>
-      </c>
-      <c r="C544" s="15" t="s">
-        <v>1496</v>
-      </c>
-      <c r="D544" s="15" t="s">
-        <v>1497</v>
       </c>
       <c r="E544" s="15"/>
       <c r="F544" s="16"/>
@@ -24635,18 +24674,18 @@
       <c r="Y544" s="1"/>
       <c r="Z544" s="1"/>
     </row>
-    <row r="545" ht="12.75" customHeight="1">
+    <row r="545" spans="1:26" ht="12.75" customHeight="1">
       <c r="A545" s="15" t="s">
         <v>170</v>
       </c>
       <c r="B545" s="15" t="s">
+        <v>1496</v>
+      </c>
+      <c r="C545" s="15" t="s">
+        <v>1497</v>
+      </c>
+      <c r="D545" s="15" t="s">
         <v>1498</v>
-      </c>
-      <c r="C545" s="15" t="s">
-        <v>1499</v>
-      </c>
-      <c r="D545" s="15" t="s">
-        <v>1500</v>
       </c>
       <c r="E545" s="15" t="s">
         <v>174</v>
@@ -24673,22 +24712,22 @@
       <c r="Y545" s="1"/>
       <c r="Z545" s="1"/>
     </row>
-    <row r="546" ht="12.75" customHeight="1">
+    <row r="546" spans="1:26" ht="12.75" customHeight="1">
       <c r="A546" s="15" t="s">
         <v>142</v>
       </c>
       <c r="B546" s="15" t="s">
+        <v>1499</v>
+      </c>
+      <c r="C546" s="16" t="s">
+        <v>1500</v>
+      </c>
+      <c r="D546" s="16" t="s">
         <v>1501</v>
-      </c>
-      <c r="C546" s="16" t="s">
-        <v>1502</v>
-      </c>
-      <c r="D546" s="16" t="s">
-        <v>1503</v>
       </c>
       <c r="E546" s="15"/>
       <c r="F546" s="16" t="s">
-        <v>1504</v>
+        <v>1502</v>
       </c>
       <c r="G546" s="15"/>
       <c r="H546" s="15"/>
@@ -24711,18 +24750,18 @@
       <c r="Y546" s="1"/>
       <c r="Z546" s="1"/>
     </row>
-    <row r="547" ht="12.75" customHeight="1">
+    <row r="547" spans="1:26" ht="12.75" customHeight="1">
       <c r="A547" s="15" t="s">
         <v>142</v>
       </c>
       <c r="B547" s="15" t="s">
+        <v>1503</v>
+      </c>
+      <c r="C547" s="16" t="s">
+        <v>1504</v>
+      </c>
+      <c r="D547" s="16" t="s">
         <v>1505</v>
-      </c>
-      <c r="C547" s="16" t="s">
-        <v>1506</v>
-      </c>
-      <c r="D547" s="16" t="s">
-        <v>1507</v>
       </c>
       <c r="E547" s="15"/>
       <c r="F547" s="16"/>
@@ -24747,18 +24786,18 @@
       <c r="Y547" s="1"/>
       <c r="Z547" s="1"/>
     </row>
-    <row r="548" ht="12.75" customHeight="1">
+    <row r="548" spans="1:26" ht="12.75" customHeight="1">
       <c r="A548" s="15" t="s">
         <v>170</v>
       </c>
       <c r="B548" s="15" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C548" s="16" t="s">
+        <v>1507</v>
+      </c>
+      <c r="D548" s="16" t="s">
         <v>1508</v>
-      </c>
-      <c r="C548" s="16" t="s">
-        <v>1509</v>
-      </c>
-      <c r="D548" s="16" t="s">
-        <v>1510</v>
       </c>
       <c r="E548" s="15" t="s">
         <v>174</v>
@@ -24785,22 +24824,22 @@
       <c r="Y548" s="1"/>
       <c r="Z548" s="1"/>
     </row>
-    <row r="549" ht="12.75" customHeight="1">
+    <row r="549" spans="1:26" ht="12.75" customHeight="1">
       <c r="A549" s="15" t="s">
         <v>142</v>
       </c>
       <c r="B549" s="15" t="s">
+        <v>1509</v>
+      </c>
+      <c r="C549" s="16" t="s">
+        <v>1510</v>
+      </c>
+      <c r="D549" s="16" t="s">
         <v>1511</v>
-      </c>
-      <c r="C549" s="16" t="s">
-        <v>1512</v>
-      </c>
-      <c r="D549" s="16" t="s">
-        <v>1513</v>
       </c>
       <c r="E549" s="15"/>
       <c r="F549" s="16" t="s">
-        <v>1514</v>
+        <v>1512</v>
       </c>
       <c r="G549" s="15"/>
       <c r="H549" s="15"/>
@@ -24823,15 +24862,15 @@
       <c r="Y549" s="1"/>
       <c r="Z549" s="1"/>
     </row>
-    <row r="550" ht="12.75" customHeight="1">
+    <row r="550" spans="1:26" ht="12.75" customHeight="1">
       <c r="A550" s="15" t="s">
         <v>170</v>
       </c>
       <c r="B550" s="15" t="s">
-        <v>1515</v>
+        <v>1513</v>
       </c>
       <c r="C550" s="15" t="s">
-        <v>1516</v>
+        <v>1514</v>
       </c>
       <c r="D550" s="15" t="s">
         <v>1167</v>
@@ -24863,32 +24902,32 @@
       <c r="Y550" s="1"/>
       <c r="Z550" s="1"/>
     </row>
-    <row r="551" ht="12.75" customHeight="1">
+    <row r="551" spans="1:26" ht="12.75" customHeight="1">
       <c r="A551" s="15" t="s">
         <v>1153</v>
       </c>
       <c r="B551" s="15" t="s">
+        <v>1515</v>
+      </c>
+      <c r="C551" s="15" t="s">
+        <v>1516</v>
+      </c>
+      <c r="D551" s="15" t="s">
         <v>1517</v>
-      </c>
-      <c r="C551" s="15" t="s">
-        <v>1518</v>
-      </c>
-      <c r="D551" s="15" t="s">
-        <v>1519</v>
       </c>
       <c r="E551" s="15" t="s">
         <v>174</v>
       </c>
       <c r="F551" s="15" t="s">
-        <v>1520</v>
+        <v>1518</v>
       </c>
       <c r="G551" s="15"/>
       <c r="H551" s="15"/>
       <c r="I551" s="15" t="s">
-        <v>1521</v>
+        <v>1519</v>
       </c>
       <c r="J551" s="15" t="s">
-        <v>1522</v>
+        <v>1520</v>
       </c>
       <c r="K551" s="15"/>
       <c r="L551" s="15"/>
@@ -24907,7 +24946,7 @@
       <c r="Y551" s="1"/>
       <c r="Z551" s="1"/>
     </row>
-    <row r="552" ht="12.75" customHeight="1">
+    <row r="552" spans="1:26" ht="12.75" customHeight="1">
       <c r="A552" s="15" t="s">
         <v>170</v>
       </c>
@@ -24947,7 +24986,7 @@
       <c r="Y552" s="1"/>
       <c r="Z552" s="1"/>
     </row>
-    <row r="553" ht="12.75" customHeight="1">
+    <row r="553" spans="1:26" ht="12.75" customHeight="1">
       <c r="A553" s="15" t="s">
         <v>1153</v>
       </c>
@@ -24989,12 +25028,12 @@
       <c r="Y553" s="1"/>
       <c r="Z553" s="1"/>
     </row>
-    <row r="554" ht="12.75" customHeight="1">
+    <row r="554" spans="1:26" ht="12.75" customHeight="1">
       <c r="A554" s="15" t="s">
         <v>170</v>
       </c>
       <c r="B554" s="15" t="s">
-        <v>1523</v>
+        <v>1521</v>
       </c>
       <c r="C554" s="15" t="s">
         <v>1159</v>
@@ -25029,7 +25068,7 @@
       <c r="Y554" s="1"/>
       <c r="Z554" s="1"/>
     </row>
-    <row r="555" ht="12.75" customHeight="1">
+    <row r="555" spans="1:26" ht="12.75" customHeight="1">
       <c r="A555" s="15" t="s">
         <v>142</v>
       </c>
@@ -25037,14 +25076,14 @@
         <v>1161</v>
       </c>
       <c r="C555" s="16" t="s">
-        <v>1524</v>
+        <v>1522</v>
       </c>
       <c r="D555" s="16" t="s">
         <v>1163</v>
       </c>
       <c r="E555" s="15"/>
       <c r="F555" s="15" t="s">
-        <v>1525</v>
+        <v>1523</v>
       </c>
       <c r="G555" s="15"/>
       <c r="H555" s="15"/>
@@ -25067,18 +25106,18 @@
       <c r="Y555" s="1"/>
       <c r="Z555" s="1"/>
     </row>
-    <row r="556" ht="12.75" customHeight="1">
+    <row r="556" spans="1:26" ht="12.75" customHeight="1">
       <c r="A556" s="15" t="s">
         <v>142</v>
       </c>
       <c r="B556" s="15" t="s">
+        <v>1524</v>
+      </c>
+      <c r="C556" s="16" t="s">
+        <v>1525</v>
+      </c>
+      <c r="D556" s="16" t="s">
         <v>1526</v>
-      </c>
-      <c r="C556" s="16" t="s">
-        <v>1527</v>
-      </c>
-      <c r="D556" s="16" t="s">
-        <v>1528</v>
       </c>
       <c r="E556" s="15"/>
       <c r="F556" s="15"/>
@@ -25103,18 +25142,18 @@
       <c r="Y556" s="1"/>
       <c r="Z556" s="1"/>
     </row>
-    <row r="557" ht="12.75" customHeight="1">
+    <row r="557" spans="1:26" ht="12.75" customHeight="1">
       <c r="A557" s="15" t="s">
         <v>142</v>
       </c>
       <c r="B557" s="15" t="s">
+        <v>1527</v>
+      </c>
+      <c r="C557" s="16" t="s">
+        <v>1528</v>
+      </c>
+      <c r="D557" s="16" t="s">
         <v>1529</v>
-      </c>
-      <c r="C557" s="16" t="s">
-        <v>1530</v>
-      </c>
-      <c r="D557" s="16" t="s">
-        <v>1531</v>
       </c>
       <c r="E557" s="15"/>
       <c r="F557" s="15"/>
@@ -25139,18 +25178,18 @@
       <c r="Y557" s="1"/>
       <c r="Z557" s="1"/>
     </row>
-    <row r="558" ht="12.75" customHeight="1">
+    <row r="558" spans="1:26" ht="12.75" customHeight="1">
       <c r="A558" s="15" t="s">
         <v>170</v>
       </c>
       <c r="B558" s="15" t="s">
-        <v>1532</v>
+        <v>1530</v>
       </c>
       <c r="C558" s="15" t="s">
         <v>1179</v>
       </c>
       <c r="D558" s="15" t="s">
-        <v>1533</v>
+        <v>1531</v>
       </c>
       <c r="E558" s="15" t="s">
         <v>174</v>
@@ -25179,18 +25218,18 @@
       <c r="Y558" s="1"/>
       <c r="Z558" s="1"/>
     </row>
-    <row r="559" ht="12.75" customHeight="1">
+    <row r="559" spans="1:26" ht="12.75" customHeight="1">
       <c r="A559" s="15" t="s">
         <v>170</v>
       </c>
       <c r="B559" s="15" t="s">
+        <v>1532</v>
+      </c>
+      <c r="C559" s="15" t="s">
+        <v>1533</v>
+      </c>
+      <c r="D559" s="15" t="s">
         <v>1534</v>
-      </c>
-      <c r="C559" s="15" t="s">
-        <v>1535</v>
-      </c>
-      <c r="D559" s="15" t="s">
-        <v>1536</v>
       </c>
       <c r="E559" s="15" t="s">
         <v>174</v>
@@ -25219,7 +25258,7 @@
       <c r="Y559" s="1"/>
       <c r="Z559" s="1"/>
     </row>
-    <row r="560" ht="12.75" customHeight="1">
+    <row r="560" spans="1:26" ht="12.75" customHeight="1">
       <c r="A560" s="15" t="s">
         <v>142</v>
       </c>
@@ -25227,14 +25266,14 @@
         <v>1181</v>
       </c>
       <c r="C560" s="16" t="s">
-        <v>1537</v>
+        <v>1535</v>
       </c>
       <c r="D560" s="16" t="s">
-        <v>1538</v>
+        <v>1536</v>
       </c>
       <c r="E560" s="15"/>
       <c r="F560" s="15" t="s">
-        <v>1539</v>
+        <v>1537</v>
       </c>
       <c r="G560" s="15"/>
       <c r="H560" s="15"/>
@@ -25257,18 +25296,18 @@
       <c r="Y560" s="1"/>
       <c r="Z560" s="1"/>
     </row>
-    <row r="561" ht="12.75" customHeight="1">
+    <row r="561" spans="1:26" ht="12.75" customHeight="1">
       <c r="A561" s="15" t="s">
         <v>142</v>
       </c>
       <c r="B561" s="15" t="s">
+        <v>1538</v>
+      </c>
+      <c r="C561" s="16" t="s">
+        <v>1539</v>
+      </c>
+      <c r="D561" s="16" t="s">
         <v>1540</v>
-      </c>
-      <c r="C561" s="16" t="s">
-        <v>1541</v>
-      </c>
-      <c r="D561" s="16" t="s">
-        <v>1542</v>
       </c>
       <c r="E561" s="15"/>
       <c r="F561" s="16" t="s">
@@ -25295,15 +25334,15 @@
       <c r="Y561" s="1"/>
       <c r="Z561" s="1"/>
     </row>
-    <row r="562" ht="12.75" customHeight="1">
+    <row r="562" spans="1:26" ht="12.75" customHeight="1">
       <c r="A562" s="15" t="s">
         <v>142</v>
       </c>
       <c r="B562" s="15" t="s">
-        <v>1543</v>
+        <v>1541</v>
       </c>
       <c r="C562" s="5" t="s">
-        <v>1544</v>
+        <v>1542</v>
       </c>
       <c r="D562" s="15" t="s">
         <v>747</v>
@@ -25333,12 +25372,12 @@
       <c r="Y562" s="15"/>
       <c r="Z562" s="15"/>
     </row>
-    <row r="563" ht="12.75" customHeight="1">
+    <row r="563" spans="1:26" ht="12.75" customHeight="1">
       <c r="A563" s="15" t="s">
         <v>170</v>
       </c>
       <c r="B563" s="15" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
       <c r="C563" s="15" t="s">
         <v>1207</v>
@@ -25373,7 +25412,7 @@
       <c r="Y563" s="1"/>
       <c r="Z563" s="1"/>
     </row>
-    <row r="564" ht="12.75" customHeight="1">
+    <row r="564" spans="1:26" ht="12.75" customHeight="1">
       <c r="A564" s="15" t="s">
         <v>142</v>
       </c>
@@ -25381,14 +25420,14 @@
         <v>1209</v>
       </c>
       <c r="C564" s="16" t="s">
-        <v>1546</v>
+        <v>1544</v>
       </c>
       <c r="D564" s="16" t="s">
         <v>1211</v>
       </c>
       <c r="E564" s="15"/>
       <c r="F564" s="15" t="s">
-        <v>1547</v>
+        <v>1545</v>
       </c>
       <c r="G564" s="15"/>
       <c r="H564" s="15"/>
@@ -25411,22 +25450,22 @@
       <c r="Y564" s="1"/>
       <c r="Z564" s="1"/>
     </row>
-    <row r="565" ht="12.75" customHeight="1">
+    <row r="565" spans="1:26" ht="12.75" customHeight="1">
       <c r="A565" s="15" t="s">
         <v>142</v>
       </c>
       <c r="B565" s="15" t="s">
-        <v>1548</v>
+        <v>1546</v>
       </c>
       <c r="C565" s="15" t="s">
         <v>1214</v>
       </c>
       <c r="D565" s="15" t="s">
-        <v>1549</v>
+        <v>1547</v>
       </c>
       <c r="E565" s="15"/>
       <c r="F565" s="15" t="s">
-        <v>1547</v>
+        <v>1545</v>
       </c>
       <c r="G565" s="15"/>
       <c r="H565" s="15"/>
@@ -25449,12 +25488,12 @@
       <c r="Y565" s="1"/>
       <c r="Z565" s="1"/>
     </row>
-    <row r="566" ht="12.75" customHeight="1">
+    <row r="566" spans="1:26" ht="12.75" customHeight="1">
       <c r="A566" s="15" t="s">
         <v>61</v>
       </c>
       <c r="B566" s="15" t="s">
-        <v>1550</v>
+        <v>1548</v>
       </c>
       <c r="C566" s="15"/>
       <c r="D566" s="15"/>
@@ -25466,7 +25505,7 @@
       <c r="J566" s="15"/>
       <c r="K566" s="15"/>
       <c r="L566" s="15" t="s">
-        <v>1551</v>
+        <v>1549</v>
       </c>
       <c r="M566" s="15"/>
       <c r="N566" s="15"/>
@@ -25483,18 +25522,18 @@
       <c r="Y566" s="1"/>
       <c r="Z566" s="1"/>
     </row>
-    <row r="567" ht="12.75" customHeight="1">
+    <row r="567" spans="1:26" ht="12.75" customHeight="1">
       <c r="A567" s="15" t="s">
         <v>142</v>
       </c>
       <c r="B567" s="15" t="s">
+        <v>1550</v>
+      </c>
+      <c r="C567" s="15" t="s">
+        <v>1551</v>
+      </c>
+      <c r="D567" s="15" t="s">
         <v>1552</v>
-      </c>
-      <c r="C567" s="15" t="s">
-        <v>1553</v>
-      </c>
-      <c r="D567" s="15" t="s">
-        <v>1554</v>
       </c>
       <c r="E567" s="15"/>
       <c r="F567" s="16" t="s">
@@ -25521,15 +25560,15 @@
       <c r="Y567" s="1"/>
       <c r="Z567" s="1"/>
     </row>
-    <row r="568" ht="12.75" customHeight="1">
+    <row r="568" spans="1:26" ht="12.75" customHeight="1">
       <c r="A568" s="15" t="s">
         <v>142</v>
       </c>
       <c r="B568" s="15" t="s">
-        <v>1555</v>
+        <v>1553</v>
       </c>
       <c r="C568" s="5" t="s">
-        <v>1544</v>
+        <v>1542</v>
       </c>
       <c r="D568" s="15" t="s">
         <v>747</v>
@@ -25559,18 +25598,18 @@
       <c r="Y568" s="15"/>
       <c r="Z568" s="15"/>
     </row>
-    <row r="569" ht="12.75" customHeight="1">
+    <row r="569" spans="1:26" ht="12.75" customHeight="1">
       <c r="A569" s="15" t="s">
         <v>170</v>
       </c>
       <c r="B569" s="15" t="s">
+        <v>1554</v>
+      </c>
+      <c r="C569" s="16" t="s">
+        <v>1555</v>
+      </c>
+      <c r="D569" s="16" t="s">
         <v>1556</v>
-      </c>
-      <c r="C569" s="16" t="s">
-        <v>1557</v>
-      </c>
-      <c r="D569" s="16" t="s">
-        <v>1558</v>
       </c>
       <c r="E569" s="15" t="s">
         <v>174</v>
@@ -25597,22 +25636,22 @@
       <c r="Y569" s="1"/>
       <c r="Z569" s="1"/>
     </row>
-    <row r="570" ht="12.75" customHeight="1">
+    <row r="570" spans="1:26" ht="12.75" customHeight="1">
       <c r="A570" s="15" t="s">
         <v>142</v>
       </c>
       <c r="B570" s="15" t="s">
+        <v>1557</v>
+      </c>
+      <c r="C570" s="15" t="s">
+        <v>1558</v>
+      </c>
+      <c r="D570" s="15" t="s">
         <v>1559</v>
-      </c>
-      <c r="C570" s="15" t="s">
-        <v>1560</v>
-      </c>
-      <c r="D570" s="15" t="s">
-        <v>1561</v>
       </c>
       <c r="E570" s="15"/>
       <c r="F570" s="15" t="s">
-        <v>1562</v>
+        <v>1560</v>
       </c>
       <c r="G570" s="15"/>
       <c r="H570" s="15"/>
@@ -25635,12 +25674,12 @@
       <c r="Y570" s="1"/>
       <c r="Z570" s="1"/>
     </row>
-    <row r="571" ht="12.75" customHeight="1">
+    <row r="571" spans="1:26" ht="12.75" customHeight="1">
       <c r="A571" s="15" t="s">
         <v>61</v>
       </c>
       <c r="B571" s="15" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="C571" s="15"/>
       <c r="D571" s="15"/>
@@ -25652,7 +25691,7 @@
       <c r="J571" s="15"/>
       <c r="K571" s="15"/>
       <c r="L571" s="15" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="M571" s="15"/>
       <c r="N571" s="15"/>
@@ -25669,7 +25708,7 @@
       <c r="Y571" s="1"/>
       <c r="Z571" s="1"/>
     </row>
-    <row r="572" ht="12.75" customHeight="1">
+    <row r="572" spans="1:26" ht="12.75" customHeight="1">
       <c r="A572" s="15" t="s">
         <v>146</v>
       </c>
@@ -25701,18 +25740,18 @@
       <c r="Y572" s="1"/>
       <c r="Z572" s="1"/>
     </row>
-    <row r="573" ht="12.75" customHeight="1">
+    <row r="573" spans="1:26" ht="12.75" customHeight="1">
       <c r="A573" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B573" s="1" t="s">
+        <v>1563</v>
+      </c>
+      <c r="C573" s="1" t="s">
+        <v>1564</v>
+      </c>
+      <c r="D573" s="1" t="s">
         <v>1565</v>
-      </c>
-      <c r="C573" s="1" t="s">
-        <v>1566</v>
-      </c>
-      <c r="D573" s="1" t="s">
-        <v>1567</v>
       </c>
       <c r="E573" s="1"/>
       <c r="F573" s="5" t="s">
@@ -25732,12 +25771,12 @@
       <c r="P573" s="1"/>
       <c r="Q573" s="1"/>
     </row>
-    <row r="574" ht="12.75" customHeight="1">
+    <row r="574" spans="1:26" ht="12.75" customHeight="1">
       <c r="A574" s="1" t="s">
         <v>142</v>
       </c>
       <c r="B574" s="1" t="s">
-        <v>1568</v>
+        <v>1566</v>
       </c>
       <c r="C574" s="1" t="s">
         <v>748</v>
@@ -25759,18 +25798,18 @@
       <c r="P574" s="1"/>
       <c r="Q574" s="1"/>
     </row>
-    <row r="575" ht="12.75" customHeight="1">
+    <row r="575" spans="1:26" ht="12.75" customHeight="1">
       <c r="A575" s="1" t="s">
         <v>170</v>
       </c>
       <c r="B575" s="1" t="s">
+        <v>1567</v>
+      </c>
+      <c r="C575" s="1" t="s">
+        <v>1568</v>
+      </c>
+      <c r="D575" s="1" t="s">
         <v>1569</v>
-      </c>
-      <c r="C575" s="1" t="s">
-        <v>1570</v>
-      </c>
-      <c r="D575" s="1" t="s">
-        <v>1571</v>
       </c>
       <c r="E575" s="1" t="s">
         <v>174</v>
@@ -25788,12 +25827,12 @@
       <c r="P575" s="1"/>
       <c r="Q575" s="1"/>
     </row>
-    <row r="576" ht="12.75" customHeight="1">
+    <row r="576" spans="1:26" ht="12.75" customHeight="1">
       <c r="A576" s="1" t="s">
         <v>142</v>
       </c>
       <c r="B576" s="1" t="s">
-        <v>1572</v>
+        <v>1570</v>
       </c>
       <c r="C576" s="1" t="s">
         <v>748</v>
@@ -25803,7 +25842,7 @@
       </c>
       <c r="E576" s="1"/>
       <c r="F576" s="3" t="s">
-        <v>1573</v>
+        <v>1571</v>
       </c>
       <c r="G576" s="1"/>
       <c r="H576" s="1"/>
@@ -25817,24 +25856,24 @@
       <c r="P576" s="1"/>
       <c r="Q576" s="1"/>
     </row>
-    <row r="577" ht="12.75" customHeight="1">
+    <row r="577" spans="1:17" ht="12.75" customHeight="1">
       <c r="A577" s="1" t="s">
         <v>170</v>
       </c>
       <c r="B577" s="1" t="s">
+        <v>1572</v>
+      </c>
+      <c r="C577" s="1" t="s">
+        <v>1573</v>
+      </c>
+      <c r="D577" s="1" t="s">
         <v>1574</v>
-      </c>
-      <c r="C577" s="1" t="s">
-        <v>1575</v>
-      </c>
-      <c r="D577" s="1" t="s">
-        <v>1576</v>
       </c>
       <c r="E577" s="1" t="s">
         <v>174</v>
       </c>
       <c r="F577" s="3" t="s">
-        <v>1573</v>
+        <v>1571</v>
       </c>
       <c r="G577" s="1"/>
       <c r="H577" s="1"/>
@@ -25848,22 +25887,22 @@
       <c r="P577" s="1"/>
       <c r="Q577" s="1"/>
     </row>
-    <row r="578" ht="12.75" customHeight="1">
+    <row r="578" spans="1:17" ht="12.75" customHeight="1">
       <c r="A578" s="1" t="s">
         <v>142</v>
       </c>
       <c r="B578" s="1" t="s">
-        <v>1577</v>
+        <v>1575</v>
       </c>
       <c r="C578" s="1" t="s">
-        <v>1578</v>
+        <v>1576</v>
       </c>
       <c r="D578" s="1" t="s">
-        <v>1578</v>
+        <v>1576</v>
       </c>
       <c r="E578" s="1"/>
       <c r="F578" s="1" t="s">
-        <v>1579</v>
+        <v>1577</v>
       </c>
       <c r="G578" s="1"/>
       <c r="H578" s="1"/>
@@ -25877,24 +25916,24 @@
       <c r="P578" s="1"/>
       <c r="Q578" s="1"/>
     </row>
-    <row r="579" ht="12.75" customHeight="1">
+    <row r="579" spans="1:17" ht="12.75" customHeight="1">
       <c r="A579" s="1" t="s">
+        <v>1578</v>
+      </c>
+      <c r="B579" s="1" t="s">
+        <v>1579</v>
+      </c>
+      <c r="C579" s="1" t="s">
         <v>1580</v>
       </c>
-      <c r="B579" s="1" t="s">
+      <c r="D579" s="1" t="s">
         <v>1581</v>
-      </c>
-      <c r="C579" s="1" t="s">
-        <v>1582</v>
-      </c>
-      <c r="D579" s="1" t="s">
-        <v>1583</v>
       </c>
       <c r="E579" s="1" t="s">
         <v>174</v>
       </c>
       <c r="F579" s="1" t="s">
-        <v>1579</v>
+        <v>1577</v>
       </c>
       <c r="G579" s="1"/>
       <c r="H579" s="1"/>
@@ -25908,12 +25947,12 @@
       <c r="P579" s="1"/>
       <c r="Q579" s="1"/>
     </row>
-    <row r="580" ht="12.75" customHeight="1">
+    <row r="580" spans="1:17" ht="12.75" customHeight="1">
       <c r="A580" s="1" t="s">
         <v>54</v>
       </c>
       <c r="B580" s="1" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="C580" s="1"/>
       <c r="D580" s="1"/>
@@ -25931,22 +25970,22 @@
       <c r="P580" s="1"/>
       <c r="Q580" s="1"/>
     </row>
-    <row r="581" ht="12.75" customHeight="1">
+    <row r="581" spans="1:17" ht="12.75" customHeight="1">
       <c r="A581" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B581" s="1" t="s">
+        <v>1582</v>
+      </c>
+      <c r="C581" s="1" t="s">
+        <v>1583</v>
+      </c>
+      <c r="D581" s="1" t="s">
         <v>1584</v>
-      </c>
-      <c r="C581" s="1" t="s">
-        <v>1585</v>
-      </c>
-      <c r="D581" s="1" t="s">
-        <v>1586</v>
       </c>
       <c r="E581" s="1"/>
       <c r="F581" s="1" t="s">
-        <v>1587</v>
+        <v>1585</v>
       </c>
       <c r="G581" s="1" t="s">
         <v>150</v>
@@ -25962,18 +26001,18 @@
       <c r="P581" s="1"/>
       <c r="Q581" s="1"/>
     </row>
-    <row r="582" ht="12.75" customHeight="1">
+    <row r="582" spans="1:17" ht="12.75" customHeight="1">
       <c r="A582" s="1" t="s">
         <v>142</v>
       </c>
       <c r="B582" s="1" t="s">
+        <v>1586</v>
+      </c>
+      <c r="C582" s="7" t="s">
+        <v>1587</v>
+      </c>
+      <c r="D582" s="7" t="s">
         <v>1588</v>
-      </c>
-      <c r="C582" s="7" t="s">
-        <v>1589</v>
-      </c>
-      <c r="D582" s="7" t="s">
-        <v>1590</v>
       </c>
       <c r="E582" s="1"/>
       <c r="F582" s="1"/>
@@ -25989,24 +26028,24 @@
       <c r="P582" s="1"/>
       <c r="Q582" s="1"/>
     </row>
-    <row r="583" ht="12.75" customHeight="1">
+    <row r="583" spans="1:17" ht="12.75" customHeight="1">
       <c r="A583" s="1" t="s">
         <v>170</v>
       </c>
       <c r="B583" s="1" t="s">
+        <v>1589</v>
+      </c>
+      <c r="C583" s="1" t="s">
+        <v>1590</v>
+      </c>
+      <c r="D583" s="1" t="s">
         <v>1591</v>
-      </c>
-      <c r="C583" s="1" t="s">
-        <v>1592</v>
-      </c>
-      <c r="D583" s="1" t="s">
-        <v>1593</v>
       </c>
       <c r="E583" s="1" t="s">
         <v>174</v>
       </c>
       <c r="F583" s="1" t="s">
-        <v>1594</v>
+        <v>1592</v>
       </c>
       <c r="G583" s="1"/>
       <c r="H583" s="1"/>
@@ -26020,24 +26059,24 @@
       <c r="P583" s="1"/>
       <c r="Q583" s="1"/>
     </row>
-    <row r="584" ht="12.75" customHeight="1">
+    <row r="584" spans="1:17" ht="12.75" customHeight="1">
       <c r="A584" s="1" t="s">
+        <v>1593</v>
+      </c>
+      <c r="B584" s="1" t="s">
+        <v>1594</v>
+      </c>
+      <c r="C584" s="1" t="s">
         <v>1595</v>
       </c>
-      <c r="B584" s="1" t="s">
+      <c r="D584" s="1" t="s">
         <v>1596</v>
-      </c>
-      <c r="C584" s="1" t="s">
-        <v>1597</v>
-      </c>
-      <c r="D584" s="1" t="s">
-        <v>1598</v>
       </c>
       <c r="E584" s="1" t="s">
         <v>174</v>
       </c>
       <c r="F584" s="1" t="s">
-        <v>1599</v>
+        <v>1597</v>
       </c>
       <c r="G584" s="1"/>
       <c r="H584" s="1"/>
@@ -26051,22 +26090,22 @@
       <c r="P584" s="1"/>
       <c r="Q584" s="1"/>
     </row>
-    <row r="585" ht="12.75" customHeight="1">
+    <row r="585" spans="1:17" ht="12.75" customHeight="1">
       <c r="A585" s="1" t="s">
         <v>142</v>
       </c>
       <c r="B585" s="1" t="s">
+        <v>1598</v>
+      </c>
+      <c r="C585" s="1" t="s">
+        <v>1599</v>
+      </c>
+      <c r="D585" s="1" t="s">
         <v>1600</v>
-      </c>
-      <c r="C585" s="1" t="s">
-        <v>1601</v>
-      </c>
-      <c r="D585" s="1" t="s">
-        <v>1602</v>
       </c>
       <c r="E585" s="1"/>
       <c r="F585" s="1" t="s">
-        <v>1603</v>
+        <v>1601</v>
       </c>
       <c r="G585" s="1"/>
       <c r="H585" s="1"/>
@@ -26080,18 +26119,18 @@
       <c r="P585" s="1"/>
       <c r="Q585" s="1"/>
     </row>
-    <row r="586" ht="12.75" customHeight="1">
+    <row r="586" spans="1:17" ht="12.75" customHeight="1">
       <c r="A586" s="1" t="s">
         <v>142</v>
       </c>
       <c r="B586" s="1" t="s">
+        <v>1602</v>
+      </c>
+      <c r="C586" s="7" t="s">
+        <v>1603</v>
+      </c>
+      <c r="D586" s="7" t="s">
         <v>1604</v>
-      </c>
-      <c r="C586" s="7" t="s">
-        <v>1605</v>
-      </c>
-      <c r="D586" s="7" t="s">
-        <v>1606</v>
       </c>
       <c r="E586" s="1"/>
       <c r="F586" s="1"/>
@@ -26107,12 +26146,12 @@
       <c r="P586" s="1"/>
       <c r="Q586" s="1"/>
     </row>
-    <row r="587" ht="12.75" customHeight="1">
+    <row r="587" spans="1:17" ht="12.75" customHeight="1">
       <c r="A587" s="1" t="s">
         <v>54</v>
       </c>
       <c r="B587" s="1" t="s">
-        <v>1584</v>
+        <v>1582</v>
       </c>
       <c r="C587" s="1"/>
       <c r="D587" s="1"/>
@@ -26130,18 +26169,18 @@
       <c r="P587" s="1"/>
       <c r="Q587" s="1"/>
     </row>
-    <row r="588" ht="12.75" customHeight="1">
+    <row r="588" spans="1:17" ht="12.75" customHeight="1">
       <c r="A588" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B588" s="1" t="s">
+        <v>1605</v>
+      </c>
+      <c r="C588" s="1" t="s">
+        <v>1606</v>
+      </c>
+      <c r="D588" s="1" t="s">
         <v>1607</v>
-      </c>
-      <c r="C588" s="1" t="s">
-        <v>1608</v>
-      </c>
-      <c r="D588" s="1" t="s">
-        <v>1609</v>
       </c>
       <c r="E588" s="1"/>
       <c r="F588" s="1" t="s">
@@ -26161,18 +26200,18 @@
       <c r="P588" s="1"/>
       <c r="Q588" s="1"/>
     </row>
-    <row r="589" ht="12.75" customHeight="1">
+    <row r="589" spans="1:17" ht="12.75" customHeight="1">
       <c r="A589" s="1" t="s">
         <v>142</v>
       </c>
       <c r="B589" s="1" t="s">
+        <v>1608</v>
+      </c>
+      <c r="C589" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="D589" s="1" t="s">
         <v>1610</v>
-      </c>
-      <c r="C589" s="1" t="s">
-        <v>1611</v>
-      </c>
-      <c r="D589" s="1" t="s">
-        <v>1612</v>
       </c>
       <c r="E589" s="1"/>
       <c r="F589" s="1"/>
@@ -26188,18 +26227,18 @@
       <c r="P589" s="1"/>
       <c r="Q589" s="1"/>
     </row>
-    <row r="590" ht="12.75" customHeight="1">
+    <row r="590" spans="1:17" ht="12.75" customHeight="1">
       <c r="A590" s="1" t="s">
         <v>170</v>
       </c>
       <c r="B590" s="1" t="s">
+        <v>1611</v>
+      </c>
+      <c r="C590" s="7" t="s">
+        <v>1612</v>
+      </c>
+      <c r="D590" s="7" t="s">
         <v>1613</v>
-      </c>
-      <c r="C590" s="7" t="s">
-        <v>1614</v>
-      </c>
-      <c r="D590" s="7" t="s">
-        <v>1615</v>
       </c>
       <c r="E590" s="1" t="s">
         <v>174</v>
@@ -26217,22 +26256,22 @@
       <c r="P590" s="1"/>
       <c r="Q590" s="1"/>
     </row>
-    <row r="591" ht="12.75" customHeight="1">
+    <row r="591" spans="1:17" ht="12.75" customHeight="1">
       <c r="A591" s="1" t="s">
         <v>142</v>
       </c>
       <c r="B591" s="1" t="s">
+        <v>1614</v>
+      </c>
+      <c r="C591" s="1" t="s">
+        <v>1615</v>
+      </c>
+      <c r="D591" s="1" t="s">
         <v>1616</v>
-      </c>
-      <c r="C591" s="1" t="s">
-        <v>1617</v>
-      </c>
-      <c r="D591" s="1" t="s">
-        <v>1618</v>
       </c>
       <c r="E591" s="1"/>
       <c r="F591" s="1" t="s">
-        <v>1619</v>
+        <v>1617</v>
       </c>
       <c r="G591" s="1"/>
       <c r="H591" s="1"/>
@@ -26246,12 +26285,12 @@
       <c r="P591" s="1"/>
       <c r="Q591" s="1"/>
     </row>
-    <row r="592" ht="12.75" customHeight="1">
+    <row r="592" spans="1:17" ht="12.75" customHeight="1">
       <c r="A592" s="1" t="s">
         <v>54</v>
       </c>
       <c r="B592" s="1" t="s">
-        <v>1607</v>
+        <v>1605</v>
       </c>
       <c r="C592" s="1"/>
       <c r="D592" s="1"/>
@@ -26269,22 +26308,22 @@
       <c r="P592" s="1"/>
       <c r="Q592" s="1"/>
     </row>
-    <row r="593" ht="12.75" customHeight="1">
+    <row r="593" spans="1:26" ht="12.75" customHeight="1">
       <c r="A593" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B593" s="1" t="s">
+        <v>1618</v>
+      </c>
+      <c r="C593" s="1" t="s">
+        <v>1619</v>
+      </c>
+      <c r="D593" s="1" t="s">
         <v>1620</v>
-      </c>
-      <c r="C593" s="1" t="s">
-        <v>1621</v>
-      </c>
-      <c r="D593" s="1" t="s">
-        <v>1622</v>
       </c>
       <c r="E593" s="1"/>
       <c r="F593" s="1" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="G593" s="1" t="s">
         <v>150</v>
@@ -26309,22 +26348,22 @@
       <c r="Y593" s="1"/>
       <c r="Z593" s="1"/>
     </row>
-    <row r="594" ht="12.75" customHeight="1">
+    <row r="594" spans="1:26" ht="12.75" customHeight="1">
       <c r="A594" s="1" t="s">
         <v>142</v>
       </c>
       <c r="B594" s="1" t="s">
+        <v>1622</v>
+      </c>
+      <c r="C594" s="1" t="s">
+        <v>1623</v>
+      </c>
+      <c r="D594" s="1" t="s">
         <v>1624</v>
-      </c>
-      <c r="C594" s="1" t="s">
-        <v>1625</v>
-      </c>
-      <c r="D594" s="1" t="s">
-        <v>1626</v>
       </c>
       <c r="E594" s="1"/>
       <c r="F594" s="5" t="s">
-        <v>1627</v>
+        <v>1625</v>
       </c>
       <c r="G594" s="1"/>
       <c r="H594" s="1"/>
@@ -26347,22 +26386,22 @@
       <c r="Y594" s="1"/>
       <c r="Z594" s="1"/>
     </row>
-    <row r="595" ht="12.75" customHeight="1">
+    <row r="595" spans="1:26" ht="12.75" customHeight="1">
       <c r="A595" s="1" t="s">
         <v>142</v>
       </c>
       <c r="B595" s="1" t="s">
+        <v>1626</v>
+      </c>
+      <c r="C595" s="1" t="s">
+        <v>1627</v>
+      </c>
+      <c r="D595" s="1" t="s">
         <v>1628</v>
-      </c>
-      <c r="C595" s="1" t="s">
-        <v>1629</v>
-      </c>
-      <c r="D595" s="1" t="s">
-        <v>1630</v>
       </c>
       <c r="E595" s="1"/>
       <c r="F595" s="5" t="s">
-        <v>1631</v>
+        <v>1629</v>
       </c>
       <c r="G595" s="1"/>
       <c r="H595" s="1"/>
@@ -26385,12 +26424,12 @@
       <c r="Y595" s="1"/>
       <c r="Z595" s="1"/>
     </row>
-    <row r="596" ht="12.75" customHeight="1">
+    <row r="596" spans="1:26" ht="12.75" customHeight="1">
       <c r="A596" s="1" t="s">
         <v>54</v>
       </c>
       <c r="B596" s="1" t="s">
-        <v>1620</v>
+        <v>1618</v>
       </c>
       <c r="C596" s="1"/>
       <c r="D596" s="1"/>
@@ -26417,283 +26456,283 @@
       <c r="Y596" s="1"/>
       <c r="Z596" s="1"/>
     </row>
-    <row r="597" ht="12.75" customHeight="1">
+    <row r="597" spans="1:26" ht="12.75" customHeight="1">
       <c r="A597" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B597" s="1" t="s">
+        <v>1630</v>
+      </c>
+      <c r="C597" s="1" t="s">
+        <v>1631</v>
+      </c>
+      <c r="D597" s="1" t="s">
         <v>1632</v>
-      </c>
-      <c r="C597" s="1" t="s">
-        <v>1633</v>
-      </c>
-      <c r="D597" s="1" t="s">
-        <v>1634</v>
       </c>
       <c r="G597" s="1" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="598" ht="12.75" customHeight="1">
+    <row r="598" spans="1:26" ht="12.75" customHeight="1">
       <c r="A598" s="1" t="s">
         <v>142</v>
       </c>
       <c r="B598" s="1" t="s">
+        <v>1633</v>
+      </c>
+      <c r="C598" s="1" t="s">
+        <v>1634</v>
+      </c>
+      <c r="D598" s="1" t="s">
         <v>1635</v>
       </c>
-      <c r="C598" s="1" t="s">
+      <c r="F598" s="1" t="s">
         <v>1636</v>
       </c>
-      <c r="D598" s="1" t="s">
-        <v>1637</v>
-      </c>
-      <c r="F598" s="1" t="s">
-        <v>1638</v>
-      </c>
-    </row>
-    <row r="599" ht="12.75" customHeight="1">
+    </row>
+    <row r="599" spans="1:26" ht="12.75" customHeight="1">
       <c r="A599" s="1" t="s">
         <v>61</v>
       </c>
       <c r="B599" s="1" t="s">
-        <v>1639</v>
+        <v>1637</v>
       </c>
       <c r="L599" s="7" t="s">
-        <v>1640</v>
-      </c>
-    </row>
-    <row r="600" ht="12.75" customHeight="1">
+        <v>1638</v>
+      </c>
+    </row>
+    <row r="600" spans="1:26" ht="12.75" customHeight="1">
       <c r="A600" s="1" t="s">
         <v>142</v>
       </c>
       <c r="B600" s="1" t="s">
+        <v>1639</v>
+      </c>
+      <c r="C600" s="1" t="s">
+        <v>1640</v>
+      </c>
+      <c r="D600" s="1" t="s">
         <v>1641</v>
       </c>
-      <c r="C600" s="1" t="s">
+      <c r="F600" s="1" t="s">
         <v>1642</v>
       </c>
-      <c r="D600" s="1" t="s">
-        <v>1643</v>
-      </c>
-      <c r="F600" s="1" t="s">
-        <v>1644</v>
-      </c>
-    </row>
-    <row r="601" ht="12.75" customHeight="1">
+    </row>
+    <row r="601" spans="1:26" ht="12.75" customHeight="1">
       <c r="A601" s="1" t="s">
         <v>142</v>
       </c>
       <c r="B601" s="1" t="s">
+        <v>1643</v>
+      </c>
+      <c r="C601" s="1" t="s">
+        <v>1644</v>
+      </c>
+      <c r="D601" s="1" t="s">
         <v>1645</v>
       </c>
-      <c r="C601" s="1" t="s">
+      <c r="F601" s="1" t="s">
         <v>1646</v>
       </c>
-      <c r="D601" s="1" t="s">
-        <v>1647</v>
-      </c>
-      <c r="F601" s="1" t="s">
-        <v>1648</v>
-      </c>
-    </row>
-    <row r="602" ht="12.75" customHeight="1">
+    </row>
+    <row r="602" spans="1:26" ht="12.75" customHeight="1">
       <c r="A602" s="1" t="s">
         <v>142</v>
       </c>
       <c r="B602" s="1" t="s">
+        <v>1647</v>
+      </c>
+      <c r="C602" s="1" t="s">
+        <v>1648</v>
+      </c>
+      <c r="D602" s="1" t="s">
         <v>1649</v>
       </c>
-      <c r="C602" s="1" t="s">
+      <c r="F602" s="11" t="s">
         <v>1650</v>
       </c>
-      <c r="D602" s="1" t="s">
+      <c r="G602" s="1" t="s">
         <v>1651</v>
       </c>
-      <c r="F602" s="11" t="s">
-        <v>1652</v>
-      </c>
-      <c r="G602" s="1" t="s">
-        <v>1653</v>
-      </c>
-    </row>
-    <row r="603" ht="12.75" customHeight="1">
+    </row>
+    <row r="603" spans="1:26" ht="12.75" customHeight="1">
       <c r="A603" s="1" t="s">
         <v>142</v>
       </c>
       <c r="B603" s="1" t="s">
+        <v>1652</v>
+      </c>
+      <c r="C603" s="1" t="s">
+        <v>1653</v>
+      </c>
+      <c r="D603" s="1" t="s">
         <v>1654</v>
-      </c>
-      <c r="C603" s="1" t="s">
-        <v>1655</v>
-      </c>
-      <c r="D603" s="1" t="s">
-        <v>1656</v>
       </c>
       <c r="F603" s="11" t="s">
         <v>284</v>
       </c>
       <c r="G603" s="1" t="s">
-        <v>1653</v>
-      </c>
-    </row>
-    <row r="604" ht="12.75" customHeight="1">
+        <v>1651</v>
+      </c>
+    </row>
+    <row r="604" spans="1:26" ht="12.75" customHeight="1">
       <c r="A604" s="1" t="s">
         <v>142</v>
       </c>
       <c r="B604" s="1" t="s">
+        <v>1655</v>
+      </c>
+      <c r="C604" s="1" t="s">
+        <v>1656</v>
+      </c>
+      <c r="D604" s="1" t="s">
         <v>1657</v>
-      </c>
-      <c r="C604" s="1" t="s">
-        <v>1658</v>
-      </c>
-      <c r="D604" s="1" t="s">
-        <v>1659</v>
       </c>
       <c r="F604" s="11" t="s">
         <v>333</v>
       </c>
       <c r="G604" s="1" t="s">
-        <v>1653</v>
-      </c>
-    </row>
-    <row r="605" ht="12.75" customHeight="1">
+        <v>1651</v>
+      </c>
+    </row>
+    <row r="605" spans="1:26" ht="12.75" customHeight="1">
       <c r="A605" s="1" t="s">
         <v>142</v>
       </c>
       <c r="B605" s="1" t="s">
+        <v>1658</v>
+      </c>
+      <c r="C605" s="1" t="s">
+        <v>1659</v>
+      </c>
+      <c r="D605" s="1" t="s">
         <v>1660</v>
-      </c>
-      <c r="C605" s="1" t="s">
-        <v>1661</v>
-      </c>
-      <c r="D605" s="1" t="s">
-        <v>1662</v>
       </c>
       <c r="F605" s="11" t="s">
         <v>367</v>
       </c>
       <c r="G605" s="1" t="s">
-        <v>1653</v>
-      </c>
-    </row>
-    <row r="606" ht="12.75" customHeight="1">
+        <v>1651</v>
+      </c>
+    </row>
+    <row r="606" spans="1:26" ht="12.75" customHeight="1">
       <c r="A606" s="1" t="s">
         <v>142</v>
       </c>
       <c r="B606" s="1" t="s">
+        <v>1661</v>
+      </c>
+      <c r="C606" s="1" t="s">
+        <v>1662</v>
+      </c>
+      <c r="D606" s="1" t="s">
         <v>1663</v>
-      </c>
-      <c r="C606" s="1" t="s">
-        <v>1664</v>
-      </c>
-      <c r="D606" s="1" t="s">
-        <v>1665</v>
       </c>
       <c r="F606" s="11" t="s">
         <v>397</v>
       </c>
       <c r="G606" s="1" t="s">
-        <v>1653</v>
-      </c>
-    </row>
-    <row r="607" ht="12.75" customHeight="1">
+        <v>1651</v>
+      </c>
+    </row>
+    <row r="607" spans="1:26" ht="12.75" customHeight="1">
       <c r="A607" s="1" t="s">
         <v>142</v>
       </c>
       <c r="B607" s="15" t="s">
+        <v>1664</v>
+      </c>
+      <c r="C607" s="1" t="s">
+        <v>1665</v>
+      </c>
+      <c r="D607" s="1" t="s">
         <v>1666</v>
       </c>
-      <c r="C607" s="1" t="s">
+      <c r="F607" s="11" t="s">
         <v>1667</v>
       </c>
-      <c r="D607" s="1" t="s">
-        <v>1668</v>
-      </c>
-      <c r="F607" s="11" t="s">
-        <v>1669</v>
-      </c>
       <c r="G607" s="1" t="s">
-        <v>1653</v>
-      </c>
-    </row>
-    <row r="608" ht="12.75" customHeight="1">
+        <v>1651</v>
+      </c>
+    </row>
+    <row r="608" spans="1:26" ht="12.75" customHeight="1">
       <c r="A608" s="1" t="s">
         <v>142</v>
       </c>
       <c r="B608" s="15" t="s">
+        <v>1668</v>
+      </c>
+      <c r="C608" s="1" t="s">
+        <v>1669</v>
+      </c>
+      <c r="D608" s="1" t="s">
         <v>1670</v>
       </c>
-      <c r="C608" s="1" t="s">
+      <c r="F608" s="11" t="s">
         <v>1671</v>
       </c>
-      <c r="D608" s="1" t="s">
-        <v>1672</v>
-      </c>
-      <c r="F608" s="11" t="s">
-        <v>1673</v>
-      </c>
       <c r="G608" s="1" t="s">
-        <v>1653</v>
-      </c>
-    </row>
-    <row r="609" ht="12.75" customHeight="1">
+        <v>1651</v>
+      </c>
+    </row>
+    <row r="609" spans="1:7" ht="12.75" customHeight="1">
       <c r="A609" s="1" t="s">
         <v>142</v>
       </c>
       <c r="B609" s="1" t="s">
+        <v>1672</v>
+      </c>
+      <c r="C609" s="1" t="s">
+        <v>1673</v>
+      </c>
+      <c r="D609" s="1" t="s">
         <v>1674</v>
       </c>
-      <c r="C609" s="1" t="s">
+      <c r="F609" s="11" t="s">
         <v>1675</v>
       </c>
-      <c r="D609" s="1" t="s">
-        <v>1676</v>
-      </c>
-      <c r="F609" s="11" t="s">
-        <v>1677</v>
-      </c>
       <c r="G609" s="1" t="s">
-        <v>1653</v>
-      </c>
-    </row>
-    <row r="610" ht="12.75" customHeight="1">
+        <v>1651</v>
+      </c>
+    </row>
+    <row r="610" spans="1:7" ht="12.75" customHeight="1">
       <c r="A610" s="1" t="s">
         <v>142</v>
       </c>
       <c r="B610" s="1" t="s">
+        <v>1676</v>
+      </c>
+      <c r="C610" s="1" t="s">
+        <v>1677</v>
+      </c>
+      <c r="D610" s="1" t="s">
         <v>1678</v>
       </c>
-      <c r="C610" s="1" t="s">
-        <v>1679</v>
-      </c>
-      <c r="D610" s="1" t="s">
-        <v>1680</v>
-      </c>
       <c r="F610" s="1" t="s">
-        <v>1648</v>
-      </c>
-    </row>
-    <row r="611" ht="12.75" customHeight="1">
+        <v>1646</v>
+      </c>
+    </row>
+    <row r="611" spans="1:7" ht="12.75" customHeight="1">
       <c r="A611" s="1" t="s">
         <v>54</v>
       </c>
       <c r="B611" s="1" t="s">
-        <v>1632</v>
-      </c>
-    </row>
-    <row r="612" ht="12.75" customHeight="1"/>
-    <row r="613" ht="12.75" customHeight="1"/>
-    <row r="614" ht="12.75" customHeight="1"/>
-    <row r="615" ht="12.75" customHeight="1"/>
-    <row r="616" ht="12.75" customHeight="1"/>
-    <row r="617" ht="12.75" customHeight="1"/>
-    <row r="618" ht="12.75" customHeight="1"/>
-    <row r="619" ht="12.75" customHeight="1"/>
-    <row r="620" ht="12.75" customHeight="1"/>
-    <row r="621" ht="12.75" customHeight="1"/>
-    <row r="622" ht="12.75" customHeight="1"/>
-    <row r="623" ht="12.75" customHeight="1"/>
-    <row r="624" ht="12.75" customHeight="1"/>
+        <v>1630</v>
+      </c>
+    </row>
+    <row r="612" spans="1:7" ht="12.75" customHeight="1"/>
+    <row r="613" spans="1:7" ht="12.75" customHeight="1"/>
+    <row r="614" spans="1:7" ht="12.75" customHeight="1"/>
+    <row r="615" spans="1:7" ht="12.75" customHeight="1"/>
+    <row r="616" spans="1:7" ht="12.75" customHeight="1"/>
+    <row r="617" spans="1:7" ht="12.75" customHeight="1"/>
+    <row r="618" spans="1:7" ht="12.75" customHeight="1"/>
+    <row r="619" spans="1:7" ht="12.75" customHeight="1"/>
+    <row r="620" spans="1:7" ht="12.75" customHeight="1"/>
+    <row r="621" spans="1:7" ht="12.75" customHeight="1"/>
+    <row r="622" spans="1:7" ht="12.75" customHeight="1"/>
+    <row r="623" spans="1:7" ht="12.75" customHeight="1"/>
+    <row r="624" spans="1:7" ht="12.75" customHeight="1"/>
     <row r="625" ht="12.75" customHeight="1"/>
     <row r="626" ht="12.75" customHeight="1"/>
     <row r="627" ht="12.75" customHeight="1"/>
@@ -27071,18 +27110,8 @@
     <row r="999" ht="12.75" customHeight="1"/>
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
-  <autoFilter ref="$B$1:$B$611"/>
+  <autoFilter ref="B1:B611" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="21">
-    <mergeCell ref="K293:L293"/>
-    <mergeCell ref="F294:G294"/>
-    <mergeCell ref="K297:L297"/>
-    <mergeCell ref="K300:L300"/>
-    <mergeCell ref="K303:L303"/>
-    <mergeCell ref="K306:L306"/>
-    <mergeCell ref="K309:L309"/>
-    <mergeCell ref="F331:H331"/>
-    <mergeCell ref="F332:H332"/>
-    <mergeCell ref="F347:I347"/>
     <mergeCell ref="F349:I349"/>
     <mergeCell ref="K333:L333"/>
     <mergeCell ref="K336:L336"/>
@@ -27094,30 +27123,36 @@
     <mergeCell ref="K324:L324"/>
     <mergeCell ref="K327:L327"/>
     <mergeCell ref="K330:L330"/>
+    <mergeCell ref="K306:L306"/>
+    <mergeCell ref="K309:L309"/>
+    <mergeCell ref="F331:H331"/>
+    <mergeCell ref="F332:H332"/>
+    <mergeCell ref="F347:I347"/>
+    <mergeCell ref="K293:L293"/>
+    <mergeCell ref="F294:G294"/>
+    <mergeCell ref="K297:L297"/>
+    <mergeCell ref="K300:L300"/>
+    <mergeCell ref="K303:L303"/>
   </mergeCells>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="portrait"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:F1000"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="24.38"/>
-    <col customWidth="1" min="2" max="2" width="36.5"/>
-    <col customWidth="1" min="3" max="3" width="76.88"/>
-    <col customWidth="1" min="4" max="6" width="14.38"/>
+    <col min="1" max="1" width="24.36328125" customWidth="1"/>
+    <col min="2" max="2" width="36.5" customWidth="1"/>
+    <col min="3" max="3" width="76.86328125" customWidth="1"/>
+    <col min="4" max="6" width="14.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
+    <row r="1" spans="1:4" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>1681</v>
+        <v>1679</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -27129,1334 +27164,1338 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1">
+    <row r="2" spans="1:4" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>1682</v>
+        <v>1680</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>174</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>1681</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>1682</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A3" s="1" t="s">
+        <v>1680</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>1683</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>1684</v>
       </c>
-    </row>
-    <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="1" t="s">
-        <v>1682</v>
-      </c>
-      <c r="B3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>1685</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>1686</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>1687</v>
-      </c>
-    </row>
-    <row r="4" ht="15.75" customHeight="1">
+    </row>
+    <row r="4" spans="1:4" ht="15.75" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>184</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>1686</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>1687</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>1688</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>1689</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>1690</v>
-      </c>
-    </row>
-    <row r="5" ht="15.75" customHeight="1">
+    </row>
+    <row r="5" spans="1:4" ht="15.75" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>184</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>1689</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>1690</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>1691</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>1692</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>1693</v>
-      </c>
-    </row>
-    <row r="6" ht="15.75" customHeight="1">
+    </row>
+    <row r="6" spans="1:4" ht="15.75" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>184</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>1692</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>1693</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>1694</v>
       </c>
-      <c r="C6" s="1" t="s">
+    </row>
+    <row r="7" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A7" s="1" t="s">
         <v>1695</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="B7" s="1" t="s">
         <v>1696</v>
       </c>
-    </row>
-    <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="1" t="s">
+      <c r="C7" s="1" t="s">
         <v>1697</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="D7" s="1" t="s">
         <v>1698</v>
       </c>
-      <c r="C7" s="1" t="s">
+    </row>
+    <row r="8" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A8" s="1" t="s">
+        <v>1695</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>1699</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="C8" s="1" t="s">
         <v>1700</v>
       </c>
-    </row>
-    <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="1" t="s">
-        <v>1697</v>
-      </c>
-      <c r="B8" s="1" t="s">
+      <c r="D8" s="1" t="s">
         <v>1701</v>
       </c>
-      <c r="C8" s="1" t="s">
+    </row>
+    <row r="9" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A9" s="1" t="s">
+        <v>1695</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>1702</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="C9" s="1" t="s">
         <v>1703</v>
       </c>
-    </row>
-    <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="1" t="s">
-        <v>1697</v>
-      </c>
-      <c r="B9" s="1" t="s">
+      <c r="D9" s="1" t="s">
         <v>1704</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>1705</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>1706</v>
-      </c>
-    </row>
-    <row r="10" ht="15.75" customHeight="1">
+    </row>
+    <row r="10" spans="1:4" ht="15.75" customHeight="1">
       <c r="A10" s="1" t="s">
         <v>950</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>1705</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>1706</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>1707</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>1708</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>1709</v>
-      </c>
-    </row>
-    <row r="11" ht="15.75" customHeight="1">
+    </row>
+    <row r="11" spans="1:4" ht="15.75" customHeight="1">
       <c r="A11" s="1" t="s">
         <v>950</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>1708</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>1709</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>1710</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>1711</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>1712</v>
-      </c>
-    </row>
-    <row r="12" ht="15.75" customHeight="1">
+    </row>
+    <row r="12" spans="1:4" ht="15.75" customHeight="1">
       <c r="A12" s="1" t="s">
         <v>972</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>1711</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>1712</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>1713</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>1714</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>1715</v>
-      </c>
-    </row>
-    <row r="13" ht="15.75" customHeight="1">
+    </row>
+    <row r="13" spans="1:4" ht="15.75" customHeight="1">
       <c r="A13" s="1" t="s">
         <v>972</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>1714</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>1715</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>1716</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>1717</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>1718</v>
-      </c>
-    </row>
-    <row r="14" ht="15.75" customHeight="1">
+    </row>
+    <row r="14" spans="1:4" ht="15.75" customHeight="1">
       <c r="A14" s="1" t="s">
         <v>972</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>1717</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>1718</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>1719</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>1720</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>1721</v>
-      </c>
-    </row>
-    <row r="15" ht="15.75" customHeight="1">
+    </row>
+    <row r="15" spans="1:4" ht="15.75" customHeight="1">
       <c r="A15" s="1" t="s">
         <v>972</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>1720</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>1721</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>1722</v>
       </c>
-      <c r="C15" s="1" t="s">
-        <v>1723</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>1724</v>
-      </c>
-    </row>
-    <row r="16" ht="15.75" customHeight="1">
+    </row>
+    <row r="16" spans="1:4" ht="15.75" customHeight="1">
       <c r="A16" s="1" t="s">
         <v>972</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>1723</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>1724</v>
+      </c>
+      <c r="D16" s="1" t="s">
         <v>1725</v>
       </c>
-      <c r="C16" s="1" t="s">
-        <v>1726</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>1727</v>
-      </c>
-    </row>
-    <row r="17" ht="15.75" customHeight="1">
+    </row>
+    <row r="17" spans="1:4" ht="15.75" customHeight="1">
       <c r="A17" s="1" t="s">
         <v>411</v>
       </c>
       <c r="B17" s="1" t="s">
+        <v>1726</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>1727</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>1728</v>
       </c>
-      <c r="C17" s="5" t="s">
-        <v>1729</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>1730</v>
-      </c>
-    </row>
-    <row r="18" ht="15.75" customHeight="1">
+    </row>
+    <row r="18" spans="1:4" ht="15.75" customHeight="1">
       <c r="A18" s="1" t="s">
         <v>411</v>
       </c>
       <c r="B18" s="1" t="s">
+        <v>1729</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>1730</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>1731</v>
       </c>
-      <c r="C18" s="5" t="s">
-        <v>1732</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>1733</v>
-      </c>
-    </row>
-    <row r="19" ht="12.75" customHeight="1">
+    </row>
+    <row r="19" spans="1:4" ht="12.75" customHeight="1">
       <c r="A19" s="1" t="s">
         <v>411</v>
       </c>
       <c r="B19" s="1" t="s">
+        <v>1732</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>1733</v>
+      </c>
+      <c r="D19" s="1" t="s">
         <v>1734</v>
       </c>
-      <c r="C19" s="5" t="s">
-        <v>1735</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>1736</v>
-      </c>
-    </row>
-    <row r="20" ht="12.75" customHeight="1">
+    </row>
+    <row r="20" spans="1:4" ht="12.75" customHeight="1">
       <c r="A20" s="1" t="s">
         <v>411</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>1735</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>1736</v>
+      </c>
+      <c r="D20" s="1" t="s">
         <v>1737</v>
       </c>
-      <c r="C20" s="5" t="s">
-        <v>1738</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>1739</v>
-      </c>
-    </row>
-    <row r="21" ht="12.75" customHeight="1">
+    </row>
+    <row r="21" spans="1:4" ht="12.75" customHeight="1">
       <c r="A21" s="1" t="s">
         <v>411</v>
       </c>
       <c r="B21" s="1" t="s">
+        <v>1738</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>1739</v>
+      </c>
+      <c r="D21" s="1" t="s">
         <v>1740</v>
       </c>
-      <c r="C21" s="1" t="s">
+    </row>
+    <row r="22" spans="1:4" ht="12.75" customHeight="1">
+      <c r="A22" s="1" t="s">
         <v>1741</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="B22" s="1" t="s">
         <v>1742</v>
       </c>
-    </row>
-    <row r="22" ht="12.75" customHeight="1">
-      <c r="A22" s="1" t="s">
+      <c r="C22" s="1" t="s">
         <v>1743</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="D22" s="1" t="s">
         <v>1744</v>
       </c>
-      <c r="C22" s="1" t="s">
+    </row>
+    <row r="23" spans="1:4" ht="12.75" customHeight="1">
+      <c r="A23" s="1" t="s">
+        <v>1741</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>1745</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="C23" s="1" t="s">
         <v>1746</v>
       </c>
-    </row>
-    <row r="23" ht="12.75" customHeight="1">
-      <c r="A23" s="1" t="s">
-        <v>1743</v>
-      </c>
-      <c r="B23" s="1" t="s">
+      <c r="D23" s="1" t="s">
         <v>1747</v>
       </c>
-      <c r="C23" s="1" t="s">
+    </row>
+    <row r="24" spans="1:4" ht="12.75" customHeight="1">
+      <c r="A24" s="1" t="s">
+        <v>1741</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>1748</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="C24" s="1" t="s">
         <v>1749</v>
       </c>
-    </row>
-    <row r="24" ht="12.75" customHeight="1">
-      <c r="A24" s="1" t="s">
-        <v>1743</v>
-      </c>
-      <c r="B24" s="1" t="s">
+      <c r="D24" s="1" t="s">
         <v>1750</v>
       </c>
-      <c r="C24" s="1" t="s">
-        <v>1751</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>1752</v>
-      </c>
-    </row>
-    <row r="25" ht="12.75" customHeight="1">
+    </row>
+    <row r="25" spans="1:4" ht="12.75" customHeight="1">
       <c r="A25" s="1" t="s">
         <v>442</v>
       </c>
       <c r="B25" s="1" t="s">
+        <v>1751</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>1752</v>
+      </c>
+      <c r="D25" s="1" t="s">
         <v>1753</v>
       </c>
-      <c r="C25" s="5" t="s">
-        <v>1754</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>1755</v>
-      </c>
-    </row>
-    <row r="26" ht="12.75" customHeight="1">
+    </row>
+    <row r="26" spans="1:4" ht="12.75" customHeight="1">
       <c r="A26" s="1" t="s">
         <v>442</v>
       </c>
       <c r="B26" s="1" t="s">
+        <v>1754</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>1755</v>
+      </c>
+      <c r="D26" s="1" t="s">
         <v>1756</v>
       </c>
-      <c r="C26" s="5" t="s">
-        <v>1757</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>1758</v>
-      </c>
-    </row>
-    <row r="27" ht="12.75" customHeight="1">
+    </row>
+    <row r="27" spans="1:4" ht="12.75" customHeight="1">
       <c r="A27" s="1" t="s">
         <v>978</v>
       </c>
       <c r="B27" s="1" t="s">
+        <v>1757</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>1758</v>
+      </c>
+      <c r="D27" s="1" t="s">
         <v>1759</v>
       </c>
-      <c r="C27" s="1" t="s">
-        <v>1760</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>1761</v>
-      </c>
-    </row>
-    <row r="28" ht="12.75" customHeight="1">
+    </row>
+    <row r="28" spans="1:4" ht="12.75" customHeight="1">
       <c r="A28" s="1" t="s">
         <v>978</v>
       </c>
       <c r="B28" s="1" t="s">
+        <v>1760</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>1761</v>
+      </c>
+      <c r="D28" s="1" t="s">
         <v>1762</v>
       </c>
-      <c r="C28" s="1" t="s">
-        <v>1763</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>1764</v>
-      </c>
-    </row>
-    <row r="29" ht="12.75" customHeight="1">
+    </row>
+    <row r="29" spans="1:4" ht="12.75" customHeight="1">
       <c r="A29" s="1" t="s">
         <v>978</v>
       </c>
       <c r="B29" s="1" t="s">
+        <v>1763</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>1764</v>
+      </c>
+      <c r="D29" s="1" t="s">
         <v>1765</v>
       </c>
-      <c r="C29" s="1" t="s">
-        <v>1766</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>1767</v>
-      </c>
-    </row>
-    <row r="30" ht="12.75" customHeight="1">
+    </row>
+    <row r="30" spans="1:4" ht="12.75" customHeight="1">
       <c r="A30" s="1" t="s">
         <v>996</v>
       </c>
       <c r="B30" s="1" t="s">
+        <v>1766</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>1767</v>
+      </c>
+      <c r="D30" s="1" t="s">
         <v>1768</v>
       </c>
-      <c r="C30" s="1" t="s">
-        <v>1769</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>1770</v>
-      </c>
-    </row>
-    <row r="31" ht="12.75" customHeight="1">
+    </row>
+    <row r="31" spans="1:4" ht="12.75" customHeight="1">
       <c r="A31" s="1" t="s">
         <v>996</v>
       </c>
       <c r="B31" s="1" t="s">
+        <v>1769</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>1770</v>
+      </c>
+      <c r="D31" s="1" t="s">
         <v>1771</v>
       </c>
-      <c r="C31" s="1" t="s">
-        <v>1772</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>1773</v>
-      </c>
-    </row>
-    <row r="32" ht="12.75" customHeight="1">
+    </row>
+    <row r="32" spans="1:4" ht="12.75" customHeight="1">
       <c r="A32" s="1" t="s">
         <v>996</v>
       </c>
       <c r="B32" s="1" t="s">
+        <v>1772</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>1773</v>
+      </c>
+      <c r="D32" s="1" t="s">
         <v>1774</v>
       </c>
-      <c r="C32" s="1" t="s">
-        <v>1775</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>1776</v>
-      </c>
-    </row>
-    <row r="33" ht="12.75" customHeight="1">
+    </row>
+    <row r="33" spans="1:4" ht="12.75" customHeight="1">
       <c r="A33" s="1" t="s">
         <v>530</v>
       </c>
       <c r="B33" s="1" t="s">
+        <v>1775</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>1776</v>
+      </c>
+      <c r="D33" s="1" t="s">
         <v>1777</v>
       </c>
-      <c r="C33" s="5" t="s">
-        <v>1778</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>1779</v>
-      </c>
-    </row>
-    <row r="34" ht="12.75" customHeight="1">
+    </row>
+    <row r="34" spans="1:4" ht="12.75" customHeight="1">
       <c r="A34" s="1" t="s">
         <v>530</v>
       </c>
       <c r="B34" s="1" t="s">
+        <v>1778</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>1779</v>
+      </c>
+      <c r="D34" s="1" t="s">
         <v>1780</v>
       </c>
-      <c r="C34" s="5" t="s">
-        <v>1781</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>1782</v>
-      </c>
-    </row>
-    <row r="35" ht="12.75" customHeight="1">
+    </row>
+    <row r="35" spans="1:4" ht="12.75" customHeight="1">
       <c r="A35" s="1" t="s">
         <v>530</v>
       </c>
       <c r="B35" s="1" t="s">
+        <v>1781</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>1782</v>
+      </c>
+      <c r="D35" s="1" t="s">
         <v>1783</v>
       </c>
-      <c r="C35" s="5" t="s">
-        <v>1784</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>1785</v>
-      </c>
-    </row>
-    <row r="36" ht="12.75" customHeight="1">
+    </row>
+    <row r="36" spans="1:4" ht="12.75" customHeight="1">
       <c r="A36" s="1" t="s">
         <v>530</v>
       </c>
       <c r="B36" s="1" t="s">
+        <v>1784</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>1785</v>
+      </c>
+      <c r="D36" s="1" t="s">
         <v>1786</v>
       </c>
-      <c r="C36" s="5" t="s">
+    </row>
+    <row r="37" spans="1:4" ht="12.75" customHeight="1">
+      <c r="A37" s="1" t="s">
         <v>1787</v>
       </c>
-      <c r="D36" s="1" t="s">
+      <c r="B37" s="1" t="s">
         <v>1788</v>
       </c>
-    </row>
-    <row r="37" ht="12.75" customHeight="1">
-      <c r="A37" s="1" t="s">
+      <c r="C37" s="5" t="s">
         <v>1789</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="D37" s="1" t="s">
         <v>1790</v>
       </c>
-      <c r="C37" s="5" t="s">
+    </row>
+    <row r="38" spans="1:4" ht="12.75" customHeight="1">
+      <c r="A38" s="1" t="s">
+        <v>1787</v>
+      </c>
+      <c r="B38" s="1" t="s">
         <v>1791</v>
       </c>
-      <c r="D37" s="1" t="s">
+      <c r="C38" s="5" t="s">
         <v>1792</v>
       </c>
-    </row>
-    <row r="38" ht="12.75" customHeight="1">
-      <c r="A38" s="1" t="s">
-        <v>1789</v>
-      </c>
-      <c r="B38" s="1" t="s">
+      <c r="D38" s="1" t="s">
         <v>1793</v>
       </c>
-      <c r="C38" s="5" t="s">
+    </row>
+    <row r="39" spans="1:4" ht="12.75" customHeight="1">
+      <c r="A39" s="1" t="s">
+        <v>1787</v>
+      </c>
+      <c r="B39" s="1" t="s">
         <v>1794</v>
       </c>
-      <c r="D38" s="1" t="s">
+      <c r="C39" s="5" t="s">
         <v>1795</v>
       </c>
-    </row>
-    <row r="39" ht="12.75" customHeight="1">
-      <c r="A39" s="1" t="s">
-        <v>1789</v>
-      </c>
-      <c r="B39" s="1" t="s">
+      <c r="D39" s="1" t="s">
         <v>1796</v>
       </c>
-      <c r="C39" s="5" t="s">
+    </row>
+    <row r="40" spans="1:4" ht="12.75" customHeight="1">
+      <c r="A40" s="1" t="s">
+        <v>1787</v>
+      </c>
+      <c r="B40" s="1" t="s">
         <v>1797</v>
       </c>
-      <c r="D39" s="1" t="s">
+      <c r="C40" s="5" t="s">
         <v>1798</v>
       </c>
-    </row>
-    <row r="40" ht="12.75" customHeight="1">
-      <c r="A40" s="1" t="s">
-        <v>1789</v>
-      </c>
-      <c r="B40" s="1" t="s">
+      <c r="D40" s="1" t="s">
         <v>1799</v>
       </c>
-      <c r="C40" s="5" t="s">
+    </row>
+    <row r="41" spans="1:4" ht="12.75" customHeight="1">
+      <c r="A41" s="1" t="s">
+        <v>1787</v>
+      </c>
+      <c r="B41" s="1" t="s">
         <v>1800</v>
       </c>
-      <c r="D40" s="1" t="s">
+      <c r="C41" s="5" t="s">
         <v>1801</v>
       </c>
-    </row>
-    <row r="41" ht="12.75" customHeight="1">
-      <c r="A41" s="1" t="s">
-        <v>1789</v>
-      </c>
-      <c r="B41" s="1" t="s">
+      <c r="D41" s="1" t="s">
         <v>1802</v>
       </c>
-      <c r="C41" s="5" t="s">
+    </row>
+    <row r="42" spans="1:4" ht="12.75" customHeight="1">
+      <c r="A42" s="1" t="s">
+        <v>1787</v>
+      </c>
+      <c r="B42" s="1" t="s">
         <v>1803</v>
       </c>
-      <c r="D41" s="1" t="s">
+      <c r="C42" s="5" t="s">
         <v>1804</v>
       </c>
-    </row>
-    <row r="42" ht="12.75" customHeight="1">
-      <c r="A42" s="1" t="s">
-        <v>1789</v>
-      </c>
-      <c r="B42" s="1" t="s">
+      <c r="D42" s="1" t="s">
         <v>1805</v>
       </c>
-      <c r="C42" s="5" t="s">
+    </row>
+    <row r="43" spans="1:4" ht="12.75" customHeight="1">
+      <c r="A43" s="1" t="s">
+        <v>1787</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>1708</v>
+      </c>
+      <c r="C43" s="5" t="s">
         <v>1806</v>
       </c>
-      <c r="D42" s="1" t="s">
+      <c r="D43" s="1" t="s">
         <v>1807</v>
       </c>
     </row>
-    <row r="43" ht="12.75" customHeight="1">
-      <c r="A43" s="1" t="s">
-        <v>1789</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>1710</v>
-      </c>
-      <c r="C43" s="5" t="s">
+    <row r="44" spans="1:4" ht="12.75" customHeight="1">
+      <c r="A44" s="1" t="s">
+        <v>1787</v>
+      </c>
+      <c r="B44" s="1" t="s">
         <v>1808</v>
       </c>
-      <c r="D43" s="1" t="s">
+      <c r="C44" s="5" t="s">
         <v>1809</v>
       </c>
-    </row>
-    <row r="44" ht="12.75" customHeight="1">
-      <c r="A44" s="1" t="s">
-        <v>1789</v>
-      </c>
-      <c r="B44" s="1" t="s">
+      <c r="D44" s="1" t="s">
         <v>1810</v>
       </c>
-      <c r="C44" s="5" t="s">
+    </row>
+    <row r="45" spans="1:4" ht="12.75" customHeight="1">
+      <c r="A45" s="1" t="s">
         <v>1811</v>
       </c>
-      <c r="D44" s="1" t="s">
+      <c r="B45" s="1" t="s">
+        <v>1766</v>
+      </c>
+      <c r="C45" s="1" t="s">
         <v>1812</v>
       </c>
-    </row>
-    <row r="45" ht="12.75" customHeight="1">
-      <c r="A45" s="1" t="s">
+      <c r="D45" s="1" t="s">
         <v>1813</v>
       </c>
-      <c r="B45" s="1" t="s">
-        <v>1768</v>
-      </c>
-      <c r="C45" s="1" t="s">
+    </row>
+    <row r="46" spans="1:4" ht="12.75" customHeight="1">
+      <c r="A46" s="1" t="s">
+        <v>1811</v>
+      </c>
+      <c r="B46" s="1" t="s">
         <v>1814</v>
       </c>
-      <c r="D45" s="1" t="s">
+      <c r="C46" s="1" t="s">
         <v>1815</v>
       </c>
-    </row>
-    <row r="46" ht="12.75" customHeight="1">
-      <c r="A46" s="1" t="s">
-        <v>1813</v>
-      </c>
-      <c r="B46" s="1" t="s">
+      <c r="D46" s="1" t="s">
         <v>1816</v>
       </c>
-      <c r="C46" s="1" t="s">
+    </row>
+    <row r="47" spans="1:4" ht="12.75" customHeight="1">
+      <c r="A47" s="1" t="s">
+        <v>1811</v>
+      </c>
+      <c r="B47" s="1" t="s">
         <v>1817</v>
       </c>
-      <c r="D46" s="1" t="s">
+      <c r="C47" s="1" t="s">
         <v>1818</v>
       </c>
-    </row>
-    <row r="47" ht="12.75" customHeight="1">
-      <c r="A47" s="1" t="s">
-        <v>1813</v>
-      </c>
-      <c r="B47" s="1" t="s">
+      <c r="D47" s="1" t="s">
         <v>1819</v>
       </c>
-      <c r="C47" s="1" t="s">
+    </row>
+    <row r="48" spans="1:4" ht="12.75" customHeight="1">
+      <c r="A48" s="1" t="s">
+        <v>1811</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>1772</v>
+      </c>
+      <c r="C48" s="1" t="s">
         <v>1820</v>
       </c>
-      <c r="D47" s="1" t="s">
+      <c r="D48" s="1" t="s">
         <v>1821</v>
       </c>
     </row>
-    <row r="48" ht="12.75" customHeight="1">
-      <c r="A48" s="1" t="s">
-        <v>1813</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>1774</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>1822</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>1823</v>
-      </c>
-    </row>
-    <row r="49" ht="12.75" customHeight="1">
+    <row r="49" spans="1:4" ht="12.75" customHeight="1">
       <c r="A49" s="1" t="s">
         <v>1068</v>
       </c>
       <c r="B49" s="1" t="s">
+        <v>1822</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>1823</v>
+      </c>
+      <c r="D49" s="1" t="s">
         <v>1824</v>
       </c>
-      <c r="C49" s="1" t="s">
-        <v>1825</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>1826</v>
-      </c>
-    </row>
-    <row r="50" ht="12.75" customHeight="1">
+    </row>
+    <row r="50" spans="1:4" ht="12.75" customHeight="1">
       <c r="A50" s="1" t="s">
         <v>1068</v>
       </c>
       <c r="B50" s="1" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>1826</v>
+      </c>
+      <c r="D50" s="1" t="s">
         <v>1827</v>
       </c>
-      <c r="C50" s="1" t="s">
-        <v>1828</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>1829</v>
-      </c>
-    </row>
-    <row r="51" ht="12.75" customHeight="1">
+    </row>
+    <row r="51" spans="1:4" ht="12.75" customHeight="1">
       <c r="A51" s="1" t="s">
         <v>1083</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>1768</v>
+        <v>1766</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>1830</v>
+        <v>1828</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>1831</v>
-      </c>
-    </row>
-    <row r="52" ht="12.75" customHeight="1">
+        <v>1829</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="12.75" customHeight="1">
       <c r="A52" s="1" t="s">
         <v>1083</v>
       </c>
       <c r="B52" s="1" t="s">
+        <v>1830</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>1831</v>
+      </c>
+      <c r="D52" s="1" t="s">
         <v>1832</v>
       </c>
-      <c r="C52" s="1" t="s">
-        <v>1833</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>1834</v>
-      </c>
-    </row>
-    <row r="53" ht="12.75" customHeight="1">
+    </row>
+    <row r="53" spans="1:4" ht="12.75" customHeight="1">
       <c r="A53" s="1" t="s">
         <v>1103</v>
       </c>
       <c r="B53" s="1" t="s">
+        <v>1833</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>1834</v>
+      </c>
+      <c r="D53" s="1" t="s">
         <v>1835</v>
       </c>
-      <c r="C53" s="1" t="s">
-        <v>1836</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>1837</v>
-      </c>
-    </row>
-    <row r="54" ht="12.75" customHeight="1">
+    </row>
+    <row r="54" spans="1:4" ht="12.75" customHeight="1">
       <c r="A54" s="1" t="s">
         <v>1103</v>
       </c>
       <c r="B54" s="1" t="s">
+        <v>1836</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>1837</v>
+      </c>
+      <c r="D54" s="1" t="s">
         <v>1838</v>
       </c>
-      <c r="C54" s="1" t="s">
+    </row>
+    <row r="55" spans="1:4" ht="12.75" customHeight="1">
+      <c r="A55" s="1" t="s">
         <v>1839</v>
       </c>
-      <c r="D54" s="1" t="s">
+      <c r="B55" s="1" t="s">
         <v>1840</v>
       </c>
-    </row>
-    <row r="55" ht="12.75" customHeight="1">
-      <c r="A55" s="1" t="s">
+      <c r="C55" s="5" t="s">
         <v>1841</v>
       </c>
-      <c r="B55" s="1" t="s">
+      <c r="D55" s="1" t="s">
         <v>1842</v>
       </c>
-      <c r="C55" s="5" t="s">
+    </row>
+    <row r="56" spans="1:4" ht="12.75" customHeight="1">
+      <c r="A56" s="1" t="s">
+        <v>1839</v>
+      </c>
+      <c r="B56" s="1" t="s">
         <v>1843</v>
       </c>
-      <c r="D55" s="1" t="s">
+      <c r="C56" s="5" t="s">
         <v>1844</v>
       </c>
-    </row>
-    <row r="56" ht="12.75" customHeight="1">
-      <c r="A56" s="1" t="s">
-        <v>1841</v>
-      </c>
-      <c r="B56" s="1" t="s">
+      <c r="D56" s="1" t="s">
         <v>1845</v>
       </c>
-      <c r="C56" s="5" t="s">
+    </row>
+    <row r="57" spans="1:4" ht="12.75" customHeight="1">
+      <c r="A57" s="1" t="s">
+        <v>1839</v>
+      </c>
+      <c r="B57" s="1" t="s">
         <v>1846</v>
       </c>
-      <c r="D56" s="1" t="s">
+      <c r="C57" s="5" t="s">
         <v>1847</v>
       </c>
-    </row>
-    <row r="57" ht="12.75" customHeight="1">
-      <c r="A57" s="1" t="s">
-        <v>1841</v>
-      </c>
-      <c r="B57" s="1" t="s">
+      <c r="D57" s="1" t="s">
         <v>1848</v>
       </c>
-      <c r="C57" s="5" t="s">
+    </row>
+    <row r="58" spans="1:4" ht="12.75" customHeight="1">
+      <c r="A58" s="1" t="s">
+        <v>1839</v>
+      </c>
+      <c r="B58" s="1" t="s">
         <v>1849</v>
       </c>
-      <c r="D57" s="1" t="s">
+      <c r="C58" s="5" t="s">
         <v>1850</v>
       </c>
-    </row>
-    <row r="58" ht="12.75" customHeight="1">
-      <c r="A58" s="1" t="s">
-        <v>1841</v>
-      </c>
-      <c r="B58" s="1" t="s">
+      <c r="D58" s="1" t="s">
         <v>1851</v>
       </c>
-      <c r="C58" s="5" t="s">
-        <v>1852</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>1853</v>
-      </c>
-    </row>
-    <row r="59" ht="12.75" customHeight="1">
+    </row>
+    <row r="59" spans="1:4" ht="12.75" customHeight="1">
       <c r="A59" s="1" t="s">
         <v>1138</v>
       </c>
       <c r="B59" s="1" t="s">
+        <v>1852</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>1853</v>
+      </c>
+      <c r="D59" s="1" t="s">
         <v>1854</v>
       </c>
-      <c r="C59" s="1" t="s">
-        <v>1855</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>1856</v>
-      </c>
-    </row>
-    <row r="60" ht="12.75" customHeight="1">
+    </row>
+    <row r="60" spans="1:4" ht="12.75" customHeight="1">
       <c r="A60" s="1" t="s">
         <v>1138</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>1857</v>
+        <v>1959</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>1858</v>
+        <v>1855</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>1859</v>
-      </c>
-    </row>
-    <row r="61" ht="12.75" customHeight="1">
+        <v>1856</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" ht="12.75" customHeight="1">
       <c r="A61" s="1" t="s">
         <v>1138</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>1860</v>
+        <v>1857</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>1861</v>
+        <v>1858</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>1862</v>
-      </c>
-    </row>
-    <row r="62" ht="12.75" customHeight="1">
+        <v>1859</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" ht="12.75" customHeight="1">
       <c r="A62" s="1" t="s">
         <v>1138</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>1863</v>
+        <v>1860</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>1478</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>1864</v>
-      </c>
-    </row>
-    <row r="63" ht="12.75" customHeight="1">
+        <v>1861</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" ht="12.75" customHeight="1">
       <c r="A63" s="1" t="s">
         <v>1138</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>1865</v>
+        <v>1862</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>1866</v>
+        <v>1863</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>1867</v>
-      </c>
-    </row>
-    <row r="64" ht="12.75" customHeight="1">
+        <v>1864</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" ht="12.75" customHeight="1">
       <c r="A64" s="1" t="s">
         <v>1138</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>1868</v>
+        <v>1865</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>1869</v>
+        <v>1866</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>1870</v>
-      </c>
-    </row>
-    <row r="65" ht="12.75" customHeight="1">
+        <v>1867</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" ht="12.75" customHeight="1">
       <c r="A65" s="1" t="s">
         <v>1138</v>
       </c>
       <c r="B65" s="1" t="s">
+        <v>1808</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>1809</v>
+      </c>
+      <c r="D65" s="1" t="s">
         <v>1810</v>
       </c>
-      <c r="C65" s="1" t="s">
-        <v>1811</v>
-      </c>
-      <c r="D65" s="1" t="s">
-        <v>1812</v>
-      </c>
-    </row>
-    <row r="66" ht="12.75" customHeight="1">
+    </row>
+    <row r="66" spans="1:4" ht="12.75" customHeight="1">
       <c r="A66" s="1" t="s">
         <v>1144</v>
       </c>
       <c r="B66" s="1" t="s">
+        <v>1705</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>1706</v>
+      </c>
+      <c r="D66" s="1" t="s">
         <v>1707</v>
       </c>
-      <c r="C66" s="1" t="s">
-        <v>1708</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>1709</v>
-      </c>
-    </row>
-    <row r="67" ht="12.75" customHeight="1">
+    </row>
+    <row r="67" spans="1:4" ht="12.75" customHeight="1">
       <c r="A67" s="1" t="s">
         <v>1144</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>1871</v>
+        <v>1868</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>1872</v>
+        <v>1869</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>1873</v>
-      </c>
-    </row>
-    <row r="68" ht="12.75" customHeight="1">
+        <v>1870</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" ht="12.75" customHeight="1">
       <c r="A68" s="1" t="s">
         <v>1144</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>1874</v>
+        <v>1871</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>1875</v>
+        <v>1872</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>1876</v>
-      </c>
-    </row>
-    <row r="69" ht="12.75" customHeight="1">
+        <v>1873</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" ht="12.75" customHeight="1">
       <c r="A69" s="1" t="s">
         <v>1144</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>1877</v>
+        <v>1874</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>1878</v>
+        <v>1875</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>1879</v>
-      </c>
-    </row>
-    <row r="70" ht="12.75" customHeight="1">
+        <v>1876</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" ht="12.75" customHeight="1">
       <c r="A70" s="1" t="s">
         <v>1144</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>1710</v>
+        <v>1708</v>
       </c>
       <c r="C70" s="1" t="s">
+        <v>1877</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>1878</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" ht="12.75" customHeight="1">
+      <c r="A71" s="5" t="s">
+        <v>1879</v>
+      </c>
+      <c r="B71" s="1" t="s">
         <v>1880</v>
       </c>
-      <c r="D70" s="1" t="s">
+      <c r="C71" s="5" t="s">
         <v>1881</v>
       </c>
-    </row>
-    <row r="71" ht="12.75" customHeight="1">
-      <c r="A71" s="5" t="s">
+      <c r="D71" s="1" t="s">
         <v>1882</v>
       </c>
-      <c r="B71" s="1" t="s">
+    </row>
+    <row r="72" spans="1:4" ht="12.75" customHeight="1">
+      <c r="A72" s="5" t="s">
+        <v>1879</v>
+      </c>
+      <c r="B72" s="1" t="s">
         <v>1883</v>
       </c>
-      <c r="C71" s="5" t="s">
+      <c r="C72" s="5" t="s">
         <v>1884</v>
       </c>
-      <c r="D71" s="1" t="s">
+      <c r="D72" s="1" t="s">
         <v>1885</v>
       </c>
     </row>
-    <row r="72" ht="12.75" customHeight="1">
-      <c r="A72" s="5" t="s">
-        <v>1882</v>
-      </c>
-      <c r="B72" s="1" t="s">
+    <row r="73" spans="1:4" ht="12.75" customHeight="1">
+      <c r="A73" s="5" t="s">
+        <v>1879</v>
+      </c>
+      <c r="B73" s="1" t="s">
         <v>1886</v>
       </c>
-      <c r="C72" s="5" t="s">
+      <c r="C73" s="5" t="s">
         <v>1887</v>
       </c>
-      <c r="D72" s="1" t="s">
+      <c r="D73" s="1" t="s">
         <v>1888</v>
       </c>
     </row>
-    <row r="73" ht="12.75" customHeight="1">
-      <c r="A73" s="5" t="s">
-        <v>1882</v>
-      </c>
-      <c r="B73" s="1" t="s">
+    <row r="74" spans="1:4" ht="12.75" customHeight="1">
+      <c r="A74" s="5" t="s">
+        <v>1879</v>
+      </c>
+      <c r="B74" s="1" t="s">
         <v>1889</v>
       </c>
-      <c r="C73" s="5" t="s">
+      <c r="C74" s="5" t="s">
         <v>1890</v>
       </c>
-      <c r="D73" s="1" t="s">
+      <c r="D74" s="1" t="s">
         <v>1891</v>
       </c>
     </row>
-    <row r="74" ht="12.75" customHeight="1">
-      <c r="A74" s="5" t="s">
-        <v>1882</v>
-      </c>
-      <c r="B74" s="1" t="s">
+    <row r="75" spans="1:4" ht="12.75" customHeight="1">
+      <c r="A75" s="5" t="s">
+        <v>1879</v>
+      </c>
+      <c r="B75" s="1" t="s">
         <v>1892</v>
       </c>
-      <c r="C74" s="5" t="s">
+      <c r="C75" s="5" t="s">
         <v>1893</v>
       </c>
-      <c r="D74" s="1" t="s">
+      <c r="D75" s="1" t="s">
         <v>1894</v>
       </c>
     </row>
-    <row r="75" ht="12.75" customHeight="1">
-      <c r="A75" s="5" t="s">
-        <v>1882</v>
-      </c>
-      <c r="B75" s="1" t="s">
+    <row r="76" spans="1:4" ht="12.75" customHeight="1">
+      <c r="A76" s="1" t="s">
+        <v>1579</v>
+      </c>
+      <c r="B76" s="1" t="s">
         <v>1895</v>
       </c>
-      <c r="C75" s="5" t="s">
+      <c r="C76" s="1" t="s">
         <v>1896</v>
       </c>
-      <c r="D75" s="1" t="s">
+      <c r="D76" s="1" t="s">
         <v>1897</v>
       </c>
     </row>
-    <row r="76" ht="12.75" customHeight="1">
-      <c r="A76" s="1" t="s">
-        <v>1581</v>
-      </c>
-      <c r="B76" s="1" t="s">
+    <row r="77" spans="1:4" ht="12.75" customHeight="1">
+      <c r="A77" s="1" t="s">
+        <v>1579</v>
+      </c>
+      <c r="B77" s="1" t="s">
         <v>1898</v>
       </c>
-      <c r="C76" s="1" t="s">
+      <c r="C77" s="1" t="s">
         <v>1899</v>
       </c>
-      <c r="D76" s="1" t="s">
+      <c r="D77" s="1" t="s">
         <v>1900</v>
       </c>
     </row>
-    <row r="77" ht="12.75" customHeight="1">
-      <c r="A77" s="1" t="s">
-        <v>1581</v>
-      </c>
-      <c r="B77" s="1" t="s">
+    <row r="78" spans="1:4" ht="12.75" customHeight="1">
+      <c r="A78" s="1" t="s">
+        <v>1579</v>
+      </c>
+      <c r="B78" s="1" t="s">
         <v>1901</v>
       </c>
-      <c r="C77" s="1" t="s">
+      <c r="C78" s="1" t="s">
         <v>1902</v>
       </c>
-      <c r="D77" s="1" t="s">
+      <c r="D78" s="1" t="s">
         <v>1903</v>
       </c>
     </row>
-    <row r="78" ht="12.75" customHeight="1">
-      <c r="A78" s="1" t="s">
-        <v>1581</v>
-      </c>
-      <c r="B78" s="1" t="s">
+    <row r="79" spans="1:4" ht="12.75" customHeight="1">
+      <c r="A79" s="1" t="s">
+        <v>1579</v>
+      </c>
+      <c r="B79" s="1" t="s">
         <v>1904</v>
       </c>
-      <c r="C78" s="1" t="s">
+      <c r="C79" s="1" t="s">
         <v>1905</v>
       </c>
-      <c r="D78" s="1" t="s">
+      <c r="D79" s="1" t="s">
         <v>1906</v>
       </c>
     </row>
-    <row r="79" ht="12.75" customHeight="1">
-      <c r="A79" s="1" t="s">
-        <v>1581</v>
-      </c>
-      <c r="B79" s="1" t="s">
+    <row r="80" spans="1:4" ht="12.75" customHeight="1">
+      <c r="A80" s="1" t="s">
+        <v>1594</v>
+      </c>
+      <c r="B80" s="1" t="s">
         <v>1907</v>
       </c>
-      <c r="C79" s="1" t="s">
+      <c r="C80" s="1" t="s">
         <v>1908</v>
       </c>
-      <c r="D79" s="1" t="s">
+      <c r="D80" s="1" t="s">
         <v>1909</v>
       </c>
     </row>
-    <row r="80" ht="12.75" customHeight="1">
-      <c r="A80" s="1" t="s">
-        <v>1596</v>
-      </c>
-      <c r="B80" s="1" t="s">
+    <row r="81" spans="1:6" ht="12.75" customHeight="1">
+      <c r="A81" s="1" t="s">
+        <v>1594</v>
+      </c>
+      <c r="B81" s="1" t="s">
         <v>1910</v>
       </c>
-      <c r="C80" s="1" t="s">
+      <c r="C81" s="1" t="s">
         <v>1911</v>
       </c>
-      <c r="D80" s="1" t="s">
+      <c r="D81" s="1" t="s">
         <v>1912</v>
       </c>
     </row>
-    <row r="81" ht="12.75" customHeight="1">
-      <c r="A81" s="1" t="s">
-        <v>1596</v>
-      </c>
-      <c r="B81" s="1" t="s">
+    <row r="82" spans="1:6" ht="12.75" customHeight="1">
+      <c r="A82" s="1" t="s">
+        <v>1594</v>
+      </c>
+      <c r="B82" s="1" t="s">
         <v>1913</v>
       </c>
-      <c r="C81" s="1" t="s">
+      <c r="C82" s="1" t="s">
         <v>1914</v>
       </c>
-      <c r="D81" s="1" t="s">
+      <c r="D82" s="1" t="s">
         <v>1915</v>
       </c>
     </row>
-    <row r="82" ht="12.75" customHeight="1">
-      <c r="A82" s="1" t="s">
-        <v>1596</v>
-      </c>
-      <c r="B82" s="1" t="s">
+    <row r="83" spans="1:6" ht="12.75" customHeight="1">
+      <c r="A83" s="1" t="s">
+        <v>1594</v>
+      </c>
+      <c r="B83" s="1" t="s">
         <v>1916</v>
       </c>
-      <c r="C82" s="1" t="s">
+      <c r="C83" s="1" t="s">
+        <v>1877</v>
+      </c>
+      <c r="D83" s="1" t="s">
         <v>1917</v>
       </c>
-      <c r="D82" s="1" t="s">
+    </row>
+    <row r="84" spans="1:6" ht="12.75" customHeight="1">
+      <c r="A84" s="1" t="s">
         <v>1918</v>
       </c>
-    </row>
-    <row r="83" ht="12.75" customHeight="1">
-      <c r="A83" s="1" t="s">
-        <v>1596</v>
-      </c>
-      <c r="B83" s="1" t="s">
+      <c r="B84" s="1">
+        <v>1</v>
+      </c>
+      <c r="C84" s="1" t="s">
         <v>1919</v>
       </c>
-      <c r="C83" s="1" t="s">
-        <v>1880</v>
-      </c>
-      <c r="D83" s="1" t="s">
+      <c r="D84" s="19" t="s">
         <v>1920</v>
       </c>
-    </row>
-    <row r="84" ht="12.75" customHeight="1">
-      <c r="A84" s="1" t="s">
+      <c r="E84" s="20"/>
+    </row>
+    <row r="85" spans="1:6" ht="12.75" customHeight="1">
+      <c r="A85" s="1" t="s">
+        <v>1918</v>
+      </c>
+      <c r="B85" s="1">
+        <v>2</v>
+      </c>
+      <c r="C85" s="1" t="s">
         <v>1921</v>
       </c>
-      <c r="B84" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="C84" s="1" t="s">
+      <c r="D85" s="19" t="s">
         <v>1922</v>
       </c>
-      <c r="D84" s="1" t="s">
+      <c r="E85" s="20"/>
+      <c r="F85" s="20"/>
+    </row>
+    <row r="86" spans="1:6" ht="12.75" customHeight="1">
+      <c r="A86" s="1" t="s">
+        <v>1918</v>
+      </c>
+      <c r="B86" s="1">
+        <v>3</v>
+      </c>
+      <c r="C86" s="1" t="s">
         <v>1923</v>
       </c>
-    </row>
-    <row r="85" ht="12.75" customHeight="1">
-      <c r="A85" s="1" t="s">
-        <v>1921</v>
-      </c>
-      <c r="B85" s="1">
-        <v>2.0</v>
-      </c>
-      <c r="C85" s="1" t="s">
+      <c r="D86" s="1" t="s">
         <v>1924</v>
       </c>
-      <c r="D85" s="1" t="s">
+    </row>
+    <row r="87" spans="1:6" ht="12.75" customHeight="1">
+      <c r="A87" s="1" t="s">
+        <v>1918</v>
+      </c>
+      <c r="B87" s="1">
+        <v>4</v>
+      </c>
+      <c r="C87" s="1" t="s">
         <v>1925</v>
       </c>
-    </row>
-    <row r="86" ht="12.75" customHeight="1">
-      <c r="A86" s="1" t="s">
-        <v>1921</v>
-      </c>
-      <c r="B86" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="C86" s="1" t="s">
+      <c r="D87" s="19" t="s">
         <v>1926</v>
       </c>
-      <c r="D86" s="1" t="s">
+      <c r="E87" s="20"/>
+    </row>
+    <row r="88" spans="1:6" ht="12.75" customHeight="1">
+      <c r="A88" s="1" t="s">
+        <v>1918</v>
+      </c>
+      <c r="B88" s="1">
+        <v>5</v>
+      </c>
+      <c r="C88" s="1" t="s">
         <v>1927</v>
       </c>
-    </row>
-    <row r="87" ht="12.75" customHeight="1">
-      <c r="A87" s="1" t="s">
-        <v>1921</v>
-      </c>
-      <c r="B87" s="1">
-        <v>4.0</v>
-      </c>
-      <c r="C87" s="1" t="s">
+      <c r="D88" s="1" t="s">
         <v>1928</v>
       </c>
-      <c r="D87" s="1" t="s">
+    </row>
+    <row r="89" spans="1:6" ht="12.75" customHeight="1">
+      <c r="A89" s="1" t="s">
+        <v>1918</v>
+      </c>
+      <c r="B89" s="1">
+        <v>6</v>
+      </c>
+      <c r="C89" s="1" t="s">
         <v>1929</v>
       </c>
-    </row>
-    <row r="88" ht="12.75" customHeight="1">
-      <c r="A88" s="1" t="s">
-        <v>1921</v>
-      </c>
-      <c r="B88" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="C88" s="1" t="s">
+      <c r="D89" s="1" t="s">
         <v>1930</v>
       </c>
-      <c r="D88" s="1" t="s">
+    </row>
+    <row r="90" spans="1:6" ht="12.75" customHeight="1">
+      <c r="A90" s="1" t="s">
+        <v>1918</v>
+      </c>
+      <c r="B90" s="1">
+        <v>7</v>
+      </c>
+      <c r="C90" s="1" t="s">
         <v>1931</v>
       </c>
-    </row>
-    <row r="89" ht="12.75" customHeight="1">
-      <c r="A89" s="1" t="s">
-        <v>1921</v>
-      </c>
-      <c r="B89" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="C89" s="1" t="s">
+      <c r="D90" s="1" t="s">
         <v>1932</v>
       </c>
-      <c r="D89" s="1" t="s">
+    </row>
+    <row r="91" spans="1:6" ht="12.75" customHeight="1">
+      <c r="A91" s="1" t="s">
         <v>1933</v>
       </c>
-    </row>
-    <row r="90" ht="12.75" customHeight="1">
-      <c r="A90" s="1" t="s">
-        <v>1921</v>
-      </c>
-      <c r="B90" s="1">
-        <v>7.0</v>
-      </c>
-      <c r="C90" s="1" t="s">
+      <c r="B91" s="1">
+        <v>1</v>
+      </c>
+      <c r="C91" s="1" t="s">
         <v>1934</v>
       </c>
-      <c r="D90" s="1" t="s">
+      <c r="D91" s="1" t="s">
         <v>1935</v>
       </c>
     </row>
-    <row r="91" ht="12.75" customHeight="1">
-      <c r="A91" s="1" t="s">
+    <row r="92" spans="1:6" ht="12.75" customHeight="1">
+      <c r="A92" s="1" t="s">
+        <v>1933</v>
+      </c>
+      <c r="B92" s="1">
+        <v>0</v>
+      </c>
+      <c r="C92" s="1" t="s">
         <v>1936</v>
       </c>
-      <c r="B91" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="C91" s="1" t="s">
+      <c r="D92" s="1" t="s">
+        <v>1936</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" ht="12.75" customHeight="1">
+      <c r="A93" s="1" t="s">
+        <v>1933</v>
+      </c>
+      <c r="B93" s="1">
+        <v>99</v>
+      </c>
+      <c r="C93" s="1" t="s">
         <v>1937</v>
       </c>
-      <c r="D91" s="1" t="s">
+      <c r="D93" s="1" t="s">
         <v>1938</v>
       </c>
     </row>
-    <row r="92" ht="12.75" customHeight="1">
-      <c r="A92" s="1" t="s">
-        <v>1936</v>
-      </c>
-      <c r="B92" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="C92" s="1" t="s">
+    <row r="94" spans="1:6" ht="12.75" customHeight="1">
+      <c r="A94" s="1" t="s">
         <v>1939</v>
       </c>
-      <c r="D92" s="1" t="s">
+      <c r="B94" s="1" t="s">
+        <v>1940</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>1941</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>1942</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" ht="12.75" customHeight="1">
+      <c r="A95" s="1" t="s">
         <v>1939</v>
       </c>
-    </row>
-    <row r="93" ht="12.75" customHeight="1">
-      <c r="A93" s="1" t="s">
-        <v>1936</v>
-      </c>
-      <c r="B93" s="1">
-        <v>99.0</v>
-      </c>
-      <c r="C93" s="1" t="s">
-        <v>1940</v>
-      </c>
-      <c r="D93" s="1" t="s">
-        <v>1941</v>
-      </c>
-    </row>
-    <row r="94" ht="12.75" customHeight="1">
-      <c r="A94" s="1" t="s">
-        <v>1942</v>
-      </c>
-      <c r="B94" s="1" t="s">
+      <c r="B95" s="1" t="s">
         <v>1943</v>
       </c>
-      <c r="C94" s="1" t="s">
+      <c r="C95" s="1" t="s">
         <v>1944</v>
       </c>
-      <c r="D94" s="1" t="s">
+      <c r="D95" s="1" t="s">
         <v>1945</v>
       </c>
     </row>
-    <row r="95" ht="12.75" customHeight="1">
-      <c r="A95" s="1" t="s">
-        <v>1942</v>
-      </c>
-      <c r="B95" s="1" t="s">
+    <row r="96" spans="1:6" ht="12.75" customHeight="1">
+      <c r="A96" s="1" t="s">
+        <v>1939</v>
+      </c>
+      <c r="B96" s="1" t="s">
         <v>1946</v>
       </c>
-      <c r="C95" s="1" t="s">
+      <c r="C96" s="1" t="s">
         <v>1947</v>
       </c>
-      <c r="D95" s="1" t="s">
+      <c r="D96" s="1" t="s">
         <v>1948</v>
-      </c>
-    </row>
-    <row r="96" ht="12.75" customHeight="1">
-      <c r="A96" s="1" t="s">
-        <v>1942</v>
-      </c>
-      <c r="B96" s="1" t="s">
-        <v>1949</v>
-      </c>
-      <c r="C96" s="1" t="s">
-        <v>1950</v>
-      </c>
-      <c r="D96" s="1" t="s">
-        <v>1951</v>
       </c>
     </row>
     <row r="97" ht="12.75" customHeight="1"/>
@@ -29369,79 +29408,75 @@
     <mergeCell ref="D85:F85"/>
     <mergeCell ref="D87:E87"/>
   </mergeCells>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="portrait"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:F1000"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="26.38"/>
-    <col customWidth="1" min="2" max="2" width="10.5"/>
-    <col customWidth="1" min="3" max="3" width="9.38"/>
-    <col customWidth="1" min="4" max="4" width="6.13"/>
-    <col customWidth="1" min="5" max="5" width="11.0"/>
-    <col customWidth="1" min="6" max="6" width="13.63"/>
+    <col min="1" max="1" width="26.36328125" customWidth="1"/>
+    <col min="2" max="2" width="10.5" customWidth="1"/>
+    <col min="3" max="3" width="9.36328125" customWidth="1"/>
+    <col min="4" max="4" width="6.1328125" customWidth="1"/>
+    <col min="5" max="5" width="11" customWidth="1"/>
+    <col min="6" max="6" width="13.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
+    <row r="1" spans="1:6" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
+        <v>1949</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1950</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1951</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>1952</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>1953</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>1954</v>
       </c>
-      <c r="D1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A2" s="1" t="s">
         <v>1955</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>1956</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="C2" s="18">
+        <v>43580</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>1957</v>
       </c>
-    </row>
-    <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>1958</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>1959</v>
-      </c>
-      <c r="C2" s="18">
-        <v>43580.0</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>1960</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>1961</v>
-      </c>
-    </row>
-    <row r="3" ht="12.75" customHeight="1"/>
-    <row r="4" ht="12.75" customHeight="1"/>
-    <row r="5" ht="12.75" customHeight="1"/>
-    <row r="6" ht="12.75" customHeight="1"/>
-    <row r="7" ht="12.75" customHeight="1"/>
-    <row r="8" ht="12.75" customHeight="1"/>
-    <row r="9" ht="12.75" customHeight="1"/>
-    <row r="10" ht="12.75" customHeight="1"/>
-    <row r="11" ht="12.75" customHeight="1"/>
-    <row r="12" ht="12.75" customHeight="1"/>
-    <row r="13" ht="12.75" customHeight="1"/>
-    <row r="14" ht="12.75" customHeight="1"/>
-    <row r="15" ht="12.75" customHeight="1"/>
-    <row r="16" ht="12.75" customHeight="1"/>
+    </row>
+    <row r="3" spans="1:6" ht="12.75" customHeight="1"/>
+    <row r="4" spans="1:6" ht="12.75" customHeight="1"/>
+    <row r="5" spans="1:6" ht="12.75" customHeight="1"/>
+    <row r="6" spans="1:6" ht="12.75" customHeight="1"/>
+    <row r="7" spans="1:6" ht="12.75" customHeight="1"/>
+    <row r="8" spans="1:6" ht="12.75" customHeight="1"/>
+    <row r="9" spans="1:6" ht="12.75" customHeight="1"/>
+    <row r="10" spans="1:6" ht="12.75" customHeight="1"/>
+    <row r="11" spans="1:6" ht="12.75" customHeight="1"/>
+    <row r="12" spans="1:6" ht="12.75" customHeight="1"/>
+    <row r="13" spans="1:6" ht="12.75" customHeight="1"/>
+    <row r="14" spans="1:6" ht="12.75" customHeight="1"/>
+    <row r="15" spans="1:6" ht="12.75" customHeight="1"/>
+    <row r="16" spans="1:6" ht="12.75" customHeight="1"/>
     <row r="17" ht="12.75" customHeight="1"/>
     <row r="18" ht="12.75" customHeight="1"/>
     <row r="19" ht="12.75" customHeight="1"/>
@@ -30427,9 +30462,7 @@
     <row r="999" ht="12.75" customHeight="1"/>
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="portrait"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>